--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit_turisticne_regije_app_v4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976BB245-1900-1E49-B335-CCBCFD866476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94DDDA7-DAEF-3947-BF50-F00B1B973273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38700" yWindow="5240" windowWidth="33320" windowHeight="21620" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
+    <workbookView xWindow="21480" yWindow="14380" windowWidth="49940" windowHeight="34980" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Skupna Tabela" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="317">
   <si>
     <t>Občine</t>
   </si>
@@ -725,9 +725,6 @@
     <t>Povprečna starost prebivalcev</t>
   </si>
   <si>
-    <t>Število prebivalcev H2/2024)</t>
-  </si>
-  <si>
     <t>Površina območja (km2)</t>
   </si>
   <si>
@@ -743,25 +740,13 @@
     <t>Ocenjena povp. Letna zased. sob (nedeljivih enot)</t>
   </si>
   <si>
-    <t>Pritisk turizma na družbeni prostor</t>
-  </si>
-  <si>
     <t>Gostota turizma</t>
-  </si>
-  <si>
-    <t>Intenzivnost turizma</t>
   </si>
   <si>
     <t>Delovno aktivni v  turizmu (OECD/WTO)</t>
   </si>
   <si>
-    <t>Število zaposl. in samozaposl. V aktivnih podjetjih v Gostinstvu (I)</t>
-  </si>
-  <si>
     <t>Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p.</t>
   </si>
   <si>
     <t>Vsi delovni aktivni na območju</t>
@@ -821,9 +806,6 @@
     <t>Donosnost kapitala v reg. podjetjih in s.p. v Gostinstvu (I)</t>
   </si>
   <si>
-    <t>Dobičkovnost prihodkov v podjetjih in s.p. v Gostinstvu (I)21</t>
-  </si>
-  <si>
     <t>Število reg. podjetij in s.p. v nastanitveni dejav. (I 55)</t>
   </si>
   <si>
@@ -843,9 +825,6 @@
   </si>
   <si>
     <t>Delež stroškov dela v prihodkih v reg. podj. v nast.gost.dej. (I 55)</t>
-  </si>
-  <si>
-    <t>Delež stroškov dela v dod vredn. v reg. podj. v nast.gost.dej. (I)</t>
   </si>
   <si>
     <t>EBITDA v reg.podjetjih in s.p. v nastanitveni dejav. (I 55)</t>
@@ -870,15 +849,6 @@
   </si>
   <si>
     <t>Dobičkovnost prihodkov v nastanitveni dejav. (I 55)</t>
-  </si>
-  <si>
-    <t>Cel.prihodki v nastan. dejav. na prenočitev</t>
-  </si>
-  <si>
-    <t>Ocenjeni.prihodki iz nast. dejav. na prenočitev</t>
-  </si>
-  <si>
-    <t>Ocenj.prihodki iz nastan. dej. na razpoložljivo sobo (enoto)</t>
   </si>
   <si>
     <t>Ocenjeni prihodki iz nast.dej. na prodano sobo (ned.enoto)</t>
@@ -911,13 +881,7 @@
     <t>Povprečna neto plača izplačana na zaposl. osebo v Gostinstvu (I)</t>
   </si>
   <si>
-    <t xml:space="preserve"> Indeks neto plača v Gostinstvu (I) /pvp. plača v vseh dejavnostih</t>
-  </si>
-  <si>
     <t>Število izdanih gradbenih dovoljenj/1000 prebivalcev</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Število počitniških stanovanj</t>
   </si>
   <si>
     <t>Delež naseljenih stanovanj od vseh razp.</t>
@@ -941,16 +905,10 @@
     <t>Prihodi turistov SKUPAJ</t>
   </si>
   <si>
-    <t>Prihodi turistov Domaći</t>
-  </si>
-  <si>
     <t>Prihodi turistov Tuji</t>
   </si>
   <si>
     <t>PDB turistov	SKUPAJ</t>
-  </si>
-  <si>
-    <t>PDB turistov	Domaći</t>
   </si>
   <si>
     <t>PDB turistov	Tuji</t>
@@ -981,6 +939,54 @@
   </si>
   <si>
     <t>Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet</t>
+  </si>
+  <si>
+    <t>Število prebivalcev (H2/2024)</t>
+  </si>
+  <si>
+    <t>Prihodi turistov Domači</t>
+  </si>
+  <si>
+    <t>PDB turistov	Domači</t>
+  </si>
+  <si>
+    <t>Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)</t>
+  </si>
+  <si>
+    <t>Dobičkovnost prihodkov v podjetjih in s.p. v Gostinstvu (I)</t>
+  </si>
+  <si>
+    <t>Delež stroškov dela v dod vredn. v reg. podj. v nast.gost.dej. (I 55)</t>
+  </si>
+  <si>
+    <t>Pritisk turizma na družbeni prostor (število stalnih ležišč / 100 prebivalcev)</t>
+  </si>
+  <si>
+    <t>Intenzivnost turizma (število nočitev na dan / 100 prebivalcev)</t>
+  </si>
+  <si>
+    <t>Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p.</t>
+  </si>
+  <si>
+    <t>Celotni prihodki v nastan. dejav. na prenočitev</t>
+  </si>
+  <si>
+    <t>Ocenjeni prihodki iz nastan. dej. na razpoložljivo sobo (enoto)</t>
+  </si>
+  <si>
+    <t>Ocenjeni prihodki iz nast. dejav. na prenočitev</t>
+  </si>
+  <si>
+    <t>Indeks neto plača v Gostinstvu (I) /pvp. plača v vseh dejavnostih</t>
+  </si>
+  <si>
+    <t>Število počitniških stanovanj</t>
+  </si>
+  <si>
+    <t>Delež naseljenih stanovanj</t>
+  </si>
+  <si>
+    <t>Število vseh stanovanj</t>
   </si>
 </sst>
 </file>
@@ -1041,13 +1047,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B15064BA-5E36-434F-9555-4D01A0E03380}" name="Table1" displayName="Table1" ref="A1:CL214" totalsRowShown="0">
-  <autoFilter ref="A1:CL214" xr:uid="{B15064BA-5E36-434F-9555-4D01A0E03380}"/>
-  <tableColumns count="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B15064BA-5E36-434F-9555-4D01A0E03380}" name="Table1" displayName="Table1" ref="A1:CN214" totalsRowShown="0">
+  <autoFilter ref="A1:CN214" xr:uid="{B15064BA-5E36-434F-9555-4D01A0E03380}"/>
+  <tableColumns count="92">
     <tableColumn id="1" xr3:uid="{C7C32248-C834-9C44-AFE7-AB13CDAAE424}" name="Občine"/>
     <tableColumn id="2" xr3:uid="{C4443C77-0C1D-3441-8686-6D6A33F6AF30}" name="Turistična regija"/>
     <tableColumn id="3" xr3:uid="{9C93C5AB-E721-1A4A-90F2-B3397080611D}" name="Površina območja (km2)"/>
-    <tableColumn id="4" xr3:uid="{6A516117-D02C-9042-BED8-A834718FD32E}" name="Število prebivalcev H2/2024)"/>
+    <tableColumn id="4" xr3:uid="{6A516117-D02C-9042-BED8-A834718FD32E}" name="Število prebivalcev (H2/2024)"/>
     <tableColumn id="5" xr3:uid="{91CEC2B5-9950-E340-9265-15A390DF7689}" name="Povprečna starost prebivalcev"/>
     <tableColumn id="6" xr3:uid="{FB5CAD11-15F3-A24F-9CAF-8E64EAD3A48D}" name="Naravni prirast /1000 prebival."/>
     <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ" dataDxfId="0"/>
@@ -1055,10 +1061,10 @@
     <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov_x0009_Tuji"/>
     <tableColumn id="10" xr3:uid="{AE7EC853-0402-A44C-9F12-18D82AF38827}" name="Delež tujih prenočitev"/>
     <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ"/>
-    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domaći"/>
+    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači"/>
     <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji"/>
     <tableColumn id="14" xr3:uid="{494C63A2-19AC-0544-861F-B7FA12714240}" name="PDB turistov_x0009_SKUPAJ"/>
-    <tableColumn id="15" xr3:uid="{A743FB1C-E3E3-8340-BA42-61AD9082C50D}" name="PDB turistov_x0009_Domaći"/>
+    <tableColumn id="15" xr3:uid="{A743FB1C-E3E3-8340-BA42-61AD9082C50D}" name="PDB turistov_x0009_Domači"/>
     <tableColumn id="16" xr3:uid="{D6397E34-AE62-1B40-8641-B68E90F526C0}" name="PDB turistov_x0009_Tuji"/>
     <tableColumn id="17" xr3:uid="{FF46E309-259F-F74C-B4E3-7DF480EC498E}" name="Nastanitvene kapacitete - Nedeljive enote"/>
     <tableColumn id="18" xr3:uid="{DFA7A743-7B9B-AC4B-B555-AB008106AD20}" name="Nastanitvene kapacitete - vsa ležišča"/>
@@ -1072,13 +1078,13 @@
     <tableColumn id="26" xr3:uid="{6B98A6DD-4A64-EE45-AE54-458C05388214}" name="Delež stalnih ležišč v Hotelih ipd."/>
     <tableColumn id="27" xr3:uid="{CC3F87E6-B3CD-E841-BCED-E5C77DFA385B}" name="Povprečna letna zasedenost staln. ležišč"/>
     <tableColumn id="28" xr3:uid="{36E12EEC-F431-7640-B38F-3F28A52A27A2}" name="Ocenjena povp. Letna zased. sob (nedeljivih enot)"/>
-    <tableColumn id="29" xr3:uid="{E32E1653-4218-8144-AE1B-7DA0234BDD6B}" name="Pritisk turizma na družbeni prostor"/>
+    <tableColumn id="29" xr3:uid="{E32E1653-4218-8144-AE1B-7DA0234BDD6B}" name="Pritisk turizma na družbeni prostor (število stalnih ležišč / 100 prebivalcev)"/>
     <tableColumn id="30" xr3:uid="{6235832E-2F71-6247-9BC2-BB497EF940F1}" name="Gostota turizma"/>
-    <tableColumn id="31" xr3:uid="{6059D037-013F-3443-92BE-556256221BB9}" name="Intenzivnost turizma"/>
+    <tableColumn id="31" xr3:uid="{6059D037-013F-3443-92BE-556256221BB9}" name="Intenzivnost turizma (število nočitev na dan / 100 prebivalcev)"/>
     <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)"/>
-    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. V aktivnih podjetjih v Gostinstvu (I)"/>
+    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)"/>
     <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p."/>
-    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name=" Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p."/>
+    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p."/>
     <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju"/>
     <tableColumn id="37" xr3:uid="{52A7F38A-5C90-964D-B065-B17C7BA263D5}" name="Delež delovno aktivnih v turizmu (OECD/WTO)"/>
     <tableColumn id="38" xr3:uid="{C0F240E5-648C-7342-B26C-C8B4E0C3F6B4}" name="Število vseh vrst podjetij na območju"/>
@@ -1098,7 +1104,7 @@
     <tableColumn id="52" xr3:uid="{52578512-2D9B-3042-ABA7-4979793AD721}" name="Kapital v reg. Podjetjih in s.p. v Gostinstvu (I)"/>
     <tableColumn id="53" xr3:uid="{0B4E2348-7F98-4A4E-853F-4ACB891509F5}" name="Donosnost sredstev v reg. podjetjih in s.p. v Gostinstvu (I)"/>
     <tableColumn id="54" xr3:uid="{AF0EB5FE-DC22-5A48-BE37-FDD50761F05E}" name="Donosnost kapitala v reg. podjetjih in s.p. v Gostinstvu (I)"/>
-    <tableColumn id="55" xr3:uid="{128A26A4-FAEE-BC4A-B6EE-1A08B8D44E9B}" name="Dobičkovnost prihodkov v podjetjih in s.p. v Gostinstvu (I)21"/>
+    <tableColumn id="55" xr3:uid="{128A26A4-FAEE-BC4A-B6EE-1A08B8D44E9B}" name="Dobičkovnost prihodkov v podjetjih in s.p. v Gostinstvu (I)"/>
     <tableColumn id="56" xr3:uid="{F3FBED48-E964-884C-83EF-540A4CB997DE}" name="Število reg. podjetij in s.p. v nastanitveni dejav. (I 55)"/>
     <tableColumn id="57" xr3:uid="{7E9C06A6-EE05-5A4B-BFC4-1470DA5C6480}" name="Prihodki reg.podjetij in s.p. v nastanitveni dejav. (I 55)"/>
     <tableColumn id="58" xr3:uid="{594A7048-030B-7641-B062-ED36E3B0A3D9}" name="Dodana vrednost reg.podjetij v nastanitveni dejav. (I 55)"/>
@@ -1106,7 +1112,7 @@
     <tableColumn id="60" xr3:uid="{DB8C5AB7-2761-3A43-9547-30F272D35A19}" name="Ocenjeni stroški dela v reg. podj. v nastan.gost. (I 55) dejavnosti"/>
     <tableColumn id="61" xr3:uid="{C40A32FF-D555-5543-9E84-A6DEFFEAA3D9}" name="Stroški dela na zaposl. na leto v reg. podj. v nast.gost. (I 55) dejavnosti"/>
     <tableColumn id="62" xr3:uid="{D0F52755-EE67-9D44-8FB1-80277D4514B0}" name="Delež stroškov dela v prihodkih v reg. podj. v nast.gost.dej. (I 55)"/>
-    <tableColumn id="63" xr3:uid="{901DFC53-DFEE-1A4A-8CD7-EE7638EC34CF}" name="Delež stroškov dela v dod vredn. v reg. podj. v nast.gost.dej. (I)"/>
+    <tableColumn id="63" xr3:uid="{901DFC53-DFEE-1A4A-8CD7-EE7638EC34CF}" name="Delež stroškov dela v dod vredn. v reg. podj. v nast.gost.dej. (I 55)"/>
     <tableColumn id="64" xr3:uid="{8B14609D-EBDD-BD49-B52D-3A5DF542F21A}" name="EBITDA v reg.podjetjih in s.p. v nastanitveni dejav. (I 55)"/>
     <tableColumn id="65" xr3:uid="{F940FDC4-628D-364F-BF83-D4D71F989F3F}" name="EBITDA marža v reg.podjetjih v nastanitveni dejav. (I 55)"/>
     <tableColumn id="66" xr3:uid="{BBFA76B5-9A49-2E42-988A-3ED0E2C22836}" name="Čisti dobiček/izguba v reg. podj. v nastanitveni dejav. (I 55)"/>
@@ -1115,9 +1121,9 @@
     <tableColumn id="69" xr3:uid="{6E81CF29-3AC5-C946-B039-485FA0709B48}" name="Donosnost sredstev v nastanitveni dejav. (I 55)"/>
     <tableColumn id="70" xr3:uid="{8EC89FA0-B734-AB47-8230-A8F5756399A3}" name="Donosnost kapitala v nastanitveni dejav. (I 55)"/>
     <tableColumn id="71" xr3:uid="{BECD681F-4DC8-514B-AC4E-61683DFC409E}" name="Dobičkovnost prihodkov v nastanitveni dejav. (I 55)"/>
-    <tableColumn id="72" xr3:uid="{42865412-C344-4447-BA19-C224FF882D0F}" name="Cel.prihodki v nastan. dejav. na prenočitev"/>
-    <tableColumn id="73" xr3:uid="{C0A55036-7621-FF4E-B008-BD37F9C1DCB0}" name="Ocenjeni.prihodki iz nast. dejav. na prenočitev"/>
-    <tableColumn id="74" xr3:uid="{E97D5474-CD02-7942-9804-B61A028DC811}" name="Ocenj.prihodki iz nastan. dej. na razpoložljivo sobo (enoto)"/>
+    <tableColumn id="72" xr3:uid="{42865412-C344-4447-BA19-C224FF882D0F}" name="Celotni prihodki v nastan. dejav. na prenočitev"/>
+    <tableColumn id="73" xr3:uid="{C0A55036-7621-FF4E-B008-BD37F9C1DCB0}" name="Ocenjeni prihodki iz nast. dejav. na prenočitev"/>
+    <tableColumn id="74" xr3:uid="{E97D5474-CD02-7942-9804-B61A028DC811}" name="Ocenjeni prihodki iz nastan. dej. na razpoložljivo sobo (enoto)"/>
     <tableColumn id="75" xr3:uid="{2E828850-84D9-2047-A9B6-FCFA99B11C13}" name="Ocenjeni prihodki iz nast.dej. na prodano sobo (ned.enoto)"/>
     <tableColumn id="76" xr3:uid="{00135647-AE9B-654D-B4EF-EE54DDE5B2F9}" name="Poraba el.energije (MWh) Dejavnost Gostinstvo (I)"/>
     <tableColumn id="77" xr3:uid="{EB369050-8294-2D49-B9A4-DCA87CEA6142}" name="Poraba el.energ. v kWh na realiz. 1000 EUR prihodka v Gostinstvu (I)"/>
@@ -1128,12 +1134,14 @@
     <tableColumn id="82" xr3:uid="{12B8BC13-DF99-C743-95EC-792C5DC3DBFE}" name="Neto prejeti dohodek iz premoženja, kapitala, idr.povp. na preb."/>
     <tableColumn id="83" xr3:uid="{61271605-FB16-634F-A8C8-C46971209CAE}" name="Povprečna mesečna neto  plača/zaposl. osebo (EUR)"/>
     <tableColumn id="84" xr3:uid="{B839E3AE-E1FB-E546-BD00-FFE1920EB8E0}" name="Povprečna neto plača izplačana na zaposl. osebo v Gostinstvu (I)"/>
-    <tableColumn id="85" xr3:uid="{3DEB35FE-64B9-0843-A98D-1CA12FC3FA2D}" name=" Indeks neto plača v Gostinstvu (I) /pvp. plača v vseh dejavnostih"/>
+    <tableColumn id="85" xr3:uid="{3DEB35FE-64B9-0843-A98D-1CA12FC3FA2D}" name="Indeks neto plača v Gostinstvu (I) /pvp. plača v vseh dejavnostih"/>
     <tableColumn id="86" xr3:uid="{C9E1D9B1-1C78-B646-8ABF-40838C839C1A}" name="Število izdanih gradbenih dovoljenj/1000 prebivalcev"/>
-    <tableColumn id="87" xr3:uid="{4D5B6348-89BA-3242-A0DA-760B9847698D}" name=" Število počitniških stanovanj"/>
+    <tableColumn id="87" xr3:uid="{4D5B6348-89BA-3242-A0DA-760B9847698D}" name="Število počitniških stanovanj"/>
     <tableColumn id="88" xr3:uid="{76D8799C-B5BC-1944-B3D8-EFC1B6DE222D}" name="Delež naseljenih stanovanj od vseh razp."/>
     <tableColumn id="89" xr3:uid="{4A8C349E-38AA-514D-BDE6-DEB9AD9CC3E3}" name="Komunalni odpadki, zbrani  z javnim odvozom (kg/prebivalca)"/>
     <tableColumn id="90" xr3:uid="{1078F758-38E2-CE4E-AA92-AFDF93546914}" name="Štev.dijakov in študentov višjih strok. in visokošolsk.progr./1000 preb."/>
+    <tableColumn id="93" xr3:uid="{94D6BDF5-8A68-FD4A-8B32-B6C002FD5FD7}" name="Število vseh stanovanj"/>
+    <tableColumn id="91" xr3:uid="{C03597A0-F33A-DD4C-91CA-1B1BDC8046EA}" name="Delež naseljenih stanovanj"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1456,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B947C3-A9C5-6843-B1A9-C8C5050E73E5}">
-  <dimension ref="A1:CL214"/>
+  <dimension ref="A1:CN214"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
@@ -1492,8 +1500,9 @@
     <col min="38" max="38" width="15" customWidth="1"/>
     <col min="39" max="39" width="23.6640625" customWidth="1"/>
     <col min="40" max="40" width="15.83203125" customWidth="1"/>
-    <col min="41" max="42" width="17.83203125" customWidth="1"/>
-    <col min="43" max="43" width="24.33203125" customWidth="1"/>
+    <col min="41" max="41" width="17.83203125" customWidth="1"/>
+    <col min="42" max="42" width="33.1640625" customWidth="1"/>
+    <col min="43" max="43" width="63.5" customWidth="1"/>
     <col min="44" max="44" width="23.6640625" customWidth="1"/>
     <col min="45" max="45" width="32.6640625" customWidth="1"/>
     <col min="46" max="46" width="24.83203125" customWidth="1"/>
@@ -1529,10 +1538,10 @@
     <col min="87" max="87" width="11.83203125" customWidth="1"/>
     <col min="88" max="88" width="22.33203125" customWidth="1"/>
     <col min="89" max="89" width="30.6640625" customWidth="1"/>
-    <col min="90" max="90" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="63" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1540,271 +1549,277 @@
         <v>214</v>
       </c>
       <c r="C1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D1" t="s">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="E1" t="s">
         <v>228</v>
       </c>
       <c r="F1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="H1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="I1" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="J1" t="s">
         <v>227</v>
       </c>
       <c r="K1" t="s">
+        <v>288</v>
+      </c>
+      <c r="L1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M1" t="s">
+        <v>289</v>
+      </c>
+      <c r="N1" t="s">
+        <v>290</v>
+      </c>
+      <c r="O1" t="s">
+        <v>303</v>
+      </c>
+      <c r="P1" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>292</v>
+      </c>
+      <c r="R1" t="s">
+        <v>293</v>
+      </c>
+      <c r="S1" t="s">
+        <v>294</v>
+      </c>
+      <c r="T1" t="s">
+        <v>295</v>
+      </c>
+      <c r="U1" t="s">
+        <v>296</v>
+      </c>
+      <c r="V1" t="s">
+        <v>297</v>
+      </c>
+      <c r="W1" t="s">
+        <v>298</v>
+      </c>
+      <c r="X1" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y1" t="s">
         <v>300</v>
       </c>
-      <c r="L1" t="s">
-        <v>301</v>
-      </c>
-      <c r="M1" t="s">
-        <v>302</v>
-      </c>
-      <c r="N1" t="s">
-        <v>303</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="Z1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>307</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>308</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AG1" t="s">
         <v>304</v>
       </c>
-      <c r="P1" t="s">
+      <c r="AH1" t="s">
+        <v>236</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>309</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>238</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>243</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>245</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>249</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>253</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>254</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>255</v>
+      </c>
+      <c r="BC1" t="s">
         <v>305</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="BD1" t="s">
+        <v>256</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>257</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>258</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>259</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>260</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>261</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>262</v>
+      </c>
+      <c r="BK1" t="s">
         <v>306</v>
       </c>
-      <c r="R1" t="s">
-        <v>307</v>
-      </c>
-      <c r="S1" t="s">
-        <v>308</v>
-      </c>
-      <c r="T1" t="s">
-        <v>309</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="BL1" t="s">
+        <v>263</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>264</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>265</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>266</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>267</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>268</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>269</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>270</v>
+      </c>
+      <c r="BT1" t="s">
         <v>310</v>
       </c>
-      <c r="V1" t="s">
+      <c r="BU1" t="s">
+        <v>312</v>
+      </c>
+      <c r="BV1" t="s">
         <v>311</v>
       </c>
-      <c r="W1" t="s">
-        <v>312</v>
-      </c>
-      <c r="X1" t="s">
+      <c r="BW1" t="s">
+        <v>271</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>272</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>273</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>274</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>275</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>276</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>277</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>278</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>279</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>280</v>
+      </c>
+      <c r="CG1" t="s">
         <v>313</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="CH1" t="s">
+        <v>281</v>
+      </c>
+      <c r="CI1" t="s">
         <v>314</v>
       </c>
-      <c r="Z1" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>233</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>234</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>235</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>236</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>237</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>238</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>240</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>242</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>243</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>244</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>245</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>246</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>247</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>248</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>249</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>252</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>253</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>254</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>255</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>256</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>257</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>258</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>259</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>260</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>261</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>262</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>263</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>264</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>265</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>266</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>267</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>268</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>269</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>270</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>271</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>272</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>273</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>274</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>275</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>276</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>277</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>278</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>279</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>280</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>281</v>
-      </c>
-      <c r="BX1" t="s">
+      <c r="CJ1" t="s">
         <v>282</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CK1" t="s">
         <v>283</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CL1" t="s">
         <v>284</v>
       </c>
-      <c r="CA1" t="s">
-        <v>285</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>286</v>
-      </c>
-      <c r="CC1" t="s">
-        <v>287</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>288</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>289</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>290</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>291</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>292</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>293</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>294</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>295</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>296</v>
+      <c r="CM1" t="s">
+        <v>316</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>315</v>
       </c>
     </row>
-    <row r="2" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2072,8 +2087,14 @@
       <c r="CL2">
         <v>78.3</v>
       </c>
+      <c r="CM2">
+        <v>7322</v>
+      </c>
+      <c r="CN2">
+        <v>0.81876536465446603</v>
+      </c>
     </row>
-    <row r="3" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2344,8 +2365,14 @@
       <c r="CL3">
         <v>81.099999999999994</v>
       </c>
+      <c r="CM3">
+        <v>1891</v>
+      </c>
+      <c r="CN3">
+        <v>0.68746694870438918</v>
+      </c>
     </row>
-    <row r="4" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2616,8 +2643,14 @@
       <c r="CL4">
         <v>67.7</v>
       </c>
+      <c r="CM4">
+        <v>1464</v>
+      </c>
+      <c r="CN4">
+        <v>0.80259562841530052</v>
+      </c>
     </row>
-    <row r="5" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2888,8 +2921,14 @@
       <c r="CL5">
         <v>61.3</v>
       </c>
+      <c r="CM5">
+        <v>2866</v>
+      </c>
+      <c r="CN5">
+        <v>0.85729239357990228</v>
+      </c>
     </row>
-    <row r="6" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3160,8 +3199,14 @@
       <c r="CL6">
         <v>68.8</v>
       </c>
+      <c r="CM6">
+        <v>1041</v>
+      </c>
+      <c r="CN6">
+        <v>0.78770413064361189</v>
+      </c>
     </row>
-    <row r="7" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -3432,8 +3477,14 @@
       <c r="CL7">
         <v>78.099999999999994</v>
       </c>
+      <c r="CM7">
+        <v>620</v>
+      </c>
+      <c r="CN7">
+        <v>0.7129032258064516</v>
+      </c>
     </row>
-    <row r="8" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3704,8 +3755,14 @@
       <c r="CL8">
         <v>72.7</v>
       </c>
+      <c r="CM8">
+        <v>3799</v>
+      </c>
+      <c r="CN8">
+        <v>0.7341405633061332</v>
+      </c>
     </row>
-    <row r="9" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3976,8 +4033,14 @@
       <c r="CL9">
         <v>65.400000000000006</v>
       </c>
+      <c r="CM9">
+        <v>805</v>
+      </c>
+      <c r="CN9">
+        <v>0.67577639751552798</v>
+      </c>
     </row>
-    <row r="10" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4248,8 +4311,14 @@
       <c r="CL10">
         <v>66.7</v>
       </c>
+      <c r="CM10">
+        <v>3387</v>
+      </c>
+      <c r="CN10">
+        <v>0.55683495718925302</v>
+      </c>
     </row>
-    <row r="11" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4520,8 +4589,14 @@
       <c r="CL11">
         <v>65.8</v>
       </c>
+      <c r="CM11">
+        <v>1572</v>
+      </c>
+      <c r="CN11">
+        <v>0.87786259541984735</v>
+      </c>
     </row>
-    <row r="12" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4792,8 +4867,14 @@
       <c r="CL12">
         <v>72.2</v>
       </c>
+      <c r="CM12">
+        <v>2666</v>
+      </c>
+      <c r="CN12">
+        <v>0.49699924981245314</v>
+      </c>
     </row>
-    <row r="13" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -5064,8 +5145,14 @@
       <c r="CL13">
         <v>57</v>
       </c>
+      <c r="CM13">
+        <v>2167</v>
+      </c>
+      <c r="CN13">
+        <v>0.82418089524688509</v>
+      </c>
     </row>
-    <row r="14" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -5336,8 +5423,14 @@
       <c r="CL14">
         <v>80.400000000000006</v>
       </c>
+      <c r="CM14">
+        <v>2339</v>
+      </c>
+      <c r="CN14">
+        <v>0.74476271911073111</v>
+      </c>
     </row>
-    <row r="15" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -5608,8 +5701,14 @@
       <c r="CL15">
         <v>71.099999999999994</v>
       </c>
+      <c r="CM15">
+        <v>4316</v>
+      </c>
+      <c r="CN15">
+        <v>0.84708063021316038</v>
+      </c>
     </row>
-    <row r="16" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -5880,8 +5979,14 @@
       <c r="CL16">
         <v>92.7</v>
       </c>
+      <c r="CM16">
+        <v>10515</v>
+      </c>
+      <c r="CN16">
+        <v>0.76966238706609602</v>
+      </c>
     </row>
-    <row r="17" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -6152,8 +6257,14 @@
       <c r="CL17">
         <v>65.400000000000006</v>
       </c>
+      <c r="CM17">
+        <v>786</v>
+      </c>
+      <c r="CN17">
+        <v>0.71755725190839692</v>
+      </c>
     </row>
-    <row r="18" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -6424,8 +6535,14 @@
       <c r="CL18">
         <v>54.1</v>
       </c>
+      <c r="CM18">
+        <v>21321</v>
+      </c>
+      <c r="CN18">
+        <v>0.84967872051029503</v>
+      </c>
     </row>
-    <row r="19" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -6696,8 +6813,14 @@
       <c r="CL19">
         <v>69.900000000000006</v>
       </c>
+      <c r="CM19">
+        <v>2721</v>
+      </c>
+      <c r="CN19">
+        <v>0.78868063212054396</v>
+      </c>
     </row>
-    <row r="20" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -6968,8 +7091,14 @@
       <c r="CL20">
         <v>86.7</v>
       </c>
+      <c r="CM20">
+        <v>4541</v>
+      </c>
+      <c r="CN20">
+        <v>0.82426778242677823</v>
+      </c>
     </row>
-    <row r="21" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -7240,8 +7369,14 @@
       <c r="CL21">
         <v>77.900000000000006</v>
       </c>
+      <c r="CM21">
+        <v>1997</v>
+      </c>
+      <c r="CN21">
+        <v>0.74211316975463193</v>
+      </c>
     </row>
-    <row r="22" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -7512,8 +7647,14 @@
       <c r="CL22">
         <v>78.900000000000006</v>
       </c>
+      <c r="CM22">
+        <v>866</v>
+      </c>
+      <c r="CN22">
+        <v>0.74018475750577373</v>
+      </c>
     </row>
-    <row r="23" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -7784,8 +7925,14 @@
       <c r="CL23">
         <v>54.2</v>
       </c>
+      <c r="CM23">
+        <v>1527</v>
+      </c>
+      <c r="CN23">
+        <v>0.53176162409954153</v>
+      </c>
     </row>
-    <row r="24" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -8056,8 +8203,14 @@
       <c r="CL24">
         <v>61.9</v>
       </c>
+      <c r="CM24">
+        <v>1483</v>
+      </c>
+      <c r="CN24">
+        <v>0.78624409979770737</v>
+      </c>
     </row>
-    <row r="25" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -8328,8 +8481,14 @@
       <c r="CL25">
         <v>70.3</v>
       </c>
+      <c r="CM25">
+        <v>1420</v>
+      </c>
+      <c r="CN25">
+        <v>0.78169014084507038</v>
+      </c>
     </row>
-    <row r="26" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -8600,8 +8759,14 @@
       <c r="CL26">
         <v>65.5</v>
       </c>
+      <c r="CM26">
+        <v>5950</v>
+      </c>
+      <c r="CN26">
+        <v>0.75344537815126056</v>
+      </c>
     </row>
-    <row r="27" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -8872,8 +9037,14 @@
       <c r="CL27">
         <v>66</v>
       </c>
+      <c r="CM27">
+        <v>1076</v>
+      </c>
+      <c r="CN27">
+        <v>0.79182156133828996</v>
+      </c>
     </row>
-    <row r="28" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -9144,8 +9315,14 @@
       <c r="CL28">
         <v>70.400000000000006</v>
       </c>
+      <c r="CM28">
+        <v>1942</v>
+      </c>
+      <c r="CN28">
+        <v>0.7646755921730175</v>
+      </c>
     </row>
-    <row r="29" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -9416,8 +9593,14 @@
       <c r="CL29">
         <v>56.8</v>
       </c>
+      <c r="CM29">
+        <v>402</v>
+      </c>
+      <c r="CN29">
+        <v>0.70646766169154229</v>
+      </c>
     </row>
-    <row r="30" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -9688,8 +9871,14 @@
       <c r="CL30">
         <v>86.6</v>
       </c>
+      <c r="CM30">
+        <v>1449</v>
+      </c>
+      <c r="CN30">
+        <v>0.77639751552795033</v>
+      </c>
     </row>
-    <row r="31" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -9960,8 +10149,14 @@
       <c r="CL31">
         <v>78.400000000000006</v>
       </c>
+      <c r="CM31">
+        <v>890</v>
+      </c>
+      <c r="CN31">
+        <v>0.77078651685393262</v>
+      </c>
     </row>
-    <row r="32" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -10232,8 +10427,14 @@
       <c r="CL32">
         <v>63.1</v>
       </c>
+      <c r="CM32">
+        <v>2714</v>
+      </c>
+      <c r="CN32">
+        <v>0.79624170965364771</v>
+      </c>
     </row>
-    <row r="33" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -10504,8 +10705,14 @@
       <c r="CL33">
         <v>95.4</v>
       </c>
+      <c r="CM33">
+        <v>585</v>
+      </c>
+      <c r="CN33">
+        <v>0.74358974358974361</v>
+      </c>
     </row>
-    <row r="34" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -10776,8 +10983,14 @@
       <c r="CL34">
         <v>65.2</v>
       </c>
+      <c r="CM34">
+        <v>2186</v>
+      </c>
+      <c r="CN34">
+        <v>0.86276303751143646</v>
+      </c>
     </row>
-    <row r="35" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -11048,8 +11261,14 @@
       <c r="CL35">
         <v>89.4</v>
       </c>
+      <c r="CM35">
+        <v>1468</v>
+      </c>
+      <c r="CN35">
+        <v>0.75544959128065392</v>
+      </c>
     </row>
-    <row r="36" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -11320,8 +11539,14 @@
       <c r="CL36">
         <v>83.4</v>
       </c>
+      <c r="CM36">
+        <v>12824</v>
+      </c>
+      <c r="CN36">
+        <v>0.8792108546475359</v>
+      </c>
     </row>
-    <row r="37" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -11592,8 +11817,14 @@
       <c r="CL37">
         <v>83</v>
       </c>
+      <c r="CM37">
+        <v>1063</v>
+      </c>
+      <c r="CN37">
+        <v>0.78833490122295391</v>
+      </c>
     </row>
-    <row r="38" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -11864,8 +12095,14 @@
       <c r="CL38">
         <v>64.099999999999994</v>
       </c>
+      <c r="CM38">
+        <v>3116</v>
+      </c>
+      <c r="CN38">
+        <v>0.85654685494223359</v>
+      </c>
     </row>
-    <row r="39" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -12136,8 +12373,14 @@
       <c r="CL39">
         <v>71.400000000000006</v>
       </c>
+      <c r="CM39">
+        <v>2605</v>
+      </c>
+      <c r="CN39">
+        <v>0.83685220729366605</v>
+      </c>
     </row>
-    <row r="40" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -12408,8 +12651,14 @@
       <c r="CL40">
         <v>68.7</v>
       </c>
+      <c r="CM40">
+        <v>2599</v>
+      </c>
+      <c r="CN40">
+        <v>0.75836860330896494</v>
+      </c>
     </row>
-    <row r="41" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -12680,8 +12929,14 @@
       <c r="CL41">
         <v>96.6</v>
       </c>
+      <c r="CM41">
+        <v>1435</v>
+      </c>
+      <c r="CN41">
+        <v>0.83344947735191632</v>
+      </c>
     </row>
-    <row r="42" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -12952,8 +13207,14 @@
       <c r="CL42">
         <v>72.5</v>
       </c>
+      <c r="CM42">
+        <v>1151</v>
+      </c>
+      <c r="CN42">
+        <v>0.77584708948740222</v>
+      </c>
     </row>
-    <row r="43" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -13224,8 +13485,14 @@
       <c r="CL43">
         <v>74.099999999999994</v>
       </c>
+      <c r="CM43">
+        <v>3745</v>
+      </c>
+      <c r="CN43">
+        <v>0.7965287049399199</v>
+      </c>
     </row>
-    <row r="44" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -13496,8 +13763,14 @@
       <c r="CL44">
         <v>60.9</v>
       </c>
+      <c r="CM44">
+        <v>953</v>
+      </c>
+      <c r="CN44">
+        <v>0.77334732423924446</v>
+      </c>
     </row>
-    <row r="45" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -13768,8 +14041,14 @@
       <c r="CL45">
         <v>69.7</v>
       </c>
+      <c r="CM45">
+        <v>1104</v>
+      </c>
+      <c r="CN45">
+        <v>0.65489130434782605</v>
+      </c>
     </row>
-    <row r="46" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -14040,8 +14319,14 @@
       <c r="CL46">
         <v>44.4</v>
       </c>
+      <c r="CM46">
+        <v>897</v>
+      </c>
+      <c r="CN46">
+        <v>0.75027870680044595</v>
+      </c>
     </row>
-    <row r="47" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -14312,8 +14597,14 @@
       <c r="CL47">
         <v>51.9</v>
       </c>
+      <c r="CM47">
+        <v>6916</v>
+      </c>
+      <c r="CN47">
+        <v>0.86871023713128981</v>
+      </c>
     </row>
-    <row r="48" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -14584,8 +14875,14 @@
       <c r="CL48">
         <v>88</v>
       </c>
+      <c r="CM48">
+        <v>1374</v>
+      </c>
+      <c r="CN48">
+        <v>0.86171761280931591</v>
+      </c>
     </row>
-    <row r="49" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -14856,8 +15153,14 @@
       <c r="CL49">
         <v>69.900000000000006</v>
       </c>
+      <c r="CM49">
+        <v>4617</v>
+      </c>
+      <c r="CN49">
+        <v>0.80051981806367767</v>
+      </c>
     </row>
-    <row r="50" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -15128,8 +15431,14 @@
       <c r="CL50">
         <v>73.5</v>
       </c>
+      <c r="CM50">
+        <v>131</v>
+      </c>
+      <c r="CN50">
+        <v>0.74045801526717558</v>
+      </c>
     </row>
-    <row r="51" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -15400,8 +15709,14 @@
       <c r="CL51">
         <v>29.9</v>
       </c>
+      <c r="CM51">
+        <v>954</v>
+      </c>
+      <c r="CN51">
+        <v>0.80922431865828093</v>
+      </c>
     </row>
-    <row r="52" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -15672,8 +15987,14 @@
       <c r="CL52">
         <v>83.9</v>
       </c>
+      <c r="CM52">
+        <v>4162</v>
+      </c>
+      <c r="CN52">
+        <v>0.82316194137433929</v>
+      </c>
     </row>
-    <row r="53" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -15944,8 +16265,14 @@
       <c r="CL53">
         <v>63.9</v>
       </c>
+      <c r="CM53">
+        <v>2337</v>
+      </c>
+      <c r="CN53">
+        <v>0.7227214377406932</v>
+      </c>
     </row>
-    <row r="54" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -16216,8 +16543,14 @@
       <c r="CL54">
         <v>57.6</v>
       </c>
+      <c r="CM54">
+        <v>4967</v>
+      </c>
+      <c r="CN54">
+        <v>0.80893899738272601</v>
+      </c>
     </row>
-    <row r="55" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -16488,8 +16821,14 @@
       <c r="CL55">
         <v>75.7</v>
       </c>
+      <c r="CM55">
+        <v>2771</v>
+      </c>
+      <c r="CN55">
+        <v>0.80476362324070727</v>
+      </c>
     </row>
-    <row r="56" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -16760,8 +17099,14 @@
       <c r="CL56">
         <v>80.7</v>
       </c>
+      <c r="CM56">
+        <v>6154</v>
+      </c>
+      <c r="CN56">
+        <v>0.75885602859928503</v>
+      </c>
     </row>
-    <row r="57" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -17032,8 +17377,14 @@
       <c r="CL57">
         <v>66.900000000000006</v>
       </c>
+      <c r="CM57">
+        <v>6479</v>
+      </c>
+      <c r="CN57">
+        <v>0.77959561660750121</v>
+      </c>
     </row>
-    <row r="58" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -17304,8 +17655,14 @@
       <c r="CL58">
         <v>79.599999999999994</v>
       </c>
+      <c r="CM58">
+        <v>8407</v>
+      </c>
+      <c r="CN58">
+        <v>0.72451528488164629</v>
+      </c>
     </row>
-    <row r="59" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -17576,8 +17933,14 @@
       <c r="CL59">
         <v>62.6</v>
       </c>
+      <c r="CM59">
+        <v>8575</v>
+      </c>
+      <c r="CN59">
+        <v>0.88746355685131195</v>
+      </c>
     </row>
-    <row r="60" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -17848,8 +18211,14 @@
       <c r="CL60">
         <v>58.8</v>
       </c>
+      <c r="CM60">
+        <v>364</v>
+      </c>
+      <c r="CN60">
+        <v>0.63461538461538458</v>
+      </c>
     </row>
-    <row r="61" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -18120,8 +18489,14 @@
       <c r="CL61">
         <v>64.2</v>
       </c>
+      <c r="CM61">
+        <v>1069</v>
+      </c>
+      <c r="CN61">
+        <v>0.70439663236669781</v>
+      </c>
     </row>
-    <row r="62" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -18392,8 +18767,14 @@
       <c r="CL62">
         <v>69</v>
       </c>
+      <c r="CM62">
+        <v>10679</v>
+      </c>
+      <c r="CN62">
+        <v>0.85663451634048127</v>
+      </c>
     </row>
-    <row r="63" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -18664,8 +19045,14 @@
       <c r="CL63">
         <v>78.7</v>
       </c>
+      <c r="CM63">
+        <v>2598</v>
+      </c>
+      <c r="CN63">
+        <v>0.73672055427251737</v>
+      </c>
     </row>
-    <row r="64" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -18936,8 +19323,14 @@
       <c r="CL64">
         <v>73.8</v>
       </c>
+      <c r="CM64">
+        <v>2459</v>
+      </c>
+      <c r="CN64">
+        <v>0.84993899959333064</v>
+      </c>
     </row>
-    <row r="65" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -19208,8 +19601,14 @@
       <c r="CL65">
         <v>74.8</v>
       </c>
+      <c r="CM65">
+        <v>2077</v>
+      </c>
+      <c r="CN65">
+        <v>0.70582571015888296</v>
+      </c>
     </row>
-    <row r="66" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -19480,8 +19879,14 @@
       <c r="CL66">
         <v>73</v>
       </c>
+      <c r="CM66">
+        <v>238</v>
+      </c>
+      <c r="CN66">
+        <v>0.75630252100840334</v>
+      </c>
     </row>
-    <row r="67" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -19752,8 +20157,14 @@
       <c r="CL67">
         <v>55.6</v>
       </c>
+      <c r="CM67">
+        <v>6369</v>
+      </c>
+      <c r="CN67">
+        <v>0.81362851311037843</v>
+      </c>
     </row>
-    <row r="68" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -20024,8 +20435,14 @@
       <c r="CL68">
         <v>63</v>
       </c>
+      <c r="CM68">
+        <v>1810</v>
+      </c>
+      <c r="CN68">
+        <v>0.69171270718232047</v>
+      </c>
     </row>
-    <row r="69" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -20296,8 +20713,14 @@
       <c r="CL69">
         <v>70.400000000000006</v>
       </c>
+      <c r="CM69">
+        <v>2057</v>
+      </c>
+      <c r="CN69">
+        <v>0.87506076810889644</v>
+      </c>
     </row>
-    <row r="70" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -20568,8 +20991,14 @@
       <c r="CL70">
         <v>94.8</v>
       </c>
+      <c r="CM70">
+        <v>23097</v>
+      </c>
+      <c r="CN70">
+        <v>0.78707191410139843</v>
+      </c>
     </row>
-    <row r="71" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -20840,8 +21269,14 @@
       <c r="CL71">
         <v>68.3</v>
       </c>
+      <c r="CM71">
+        <v>1036</v>
+      </c>
+      <c r="CN71">
+        <v>0.76930501930501927</v>
+      </c>
     </row>
-    <row r="72" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -21112,8 +21547,14 @@
       <c r="CL72">
         <v>83.4</v>
       </c>
+      <c r="CM72">
+        <v>632</v>
+      </c>
+      <c r="CN72">
+        <v>0.48101265822784811</v>
+      </c>
     </row>
-    <row r="73" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -21384,8 +21825,14 @@
       <c r="CL73">
         <v>63.6</v>
       </c>
+      <c r="CM73">
+        <v>1402</v>
+      </c>
+      <c r="CN73">
+        <v>0.7168330955777461</v>
+      </c>
     </row>
-    <row r="74" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -21656,8 +22103,14 @@
       <c r="CL74">
         <v>74.599999999999994</v>
       </c>
+      <c r="CM74">
+        <v>21317</v>
+      </c>
+      <c r="CN74">
+        <v>0.88534972088004882</v>
+      </c>
     </row>
-    <row r="75" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -21928,8 +22381,14 @@
       <c r="CL75">
         <v>74.8</v>
       </c>
+      <c r="CM75">
+        <v>4156</v>
+      </c>
+      <c r="CN75">
+        <v>0.6179018286814244</v>
+      </c>
     </row>
-    <row r="76" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -22200,8 +22659,14 @@
       <c r="CL76">
         <v>59.3</v>
       </c>
+      <c r="CM76">
+        <v>1257</v>
+      </c>
+      <c r="CN76">
+        <v>0.82895783611774065</v>
+      </c>
     </row>
-    <row r="77" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -22472,8 +22937,14 @@
       <c r="CL77">
         <v>64</v>
       </c>
+      <c r="CM77">
+        <v>10515</v>
+      </c>
+      <c r="CN77">
+        <v>0.78925344745601522</v>
+      </c>
     </row>
-    <row r="78" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -22744,8 +23215,14 @@
       <c r="CL78">
         <v>72.8</v>
       </c>
+      <c r="CM78">
+        <v>2050</v>
+      </c>
+      <c r="CN78">
+        <v>0.79268292682926833</v>
+      </c>
     </row>
-    <row r="79" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -23016,8 +23493,14 @@
       <c r="CL79">
         <v>69.7</v>
       </c>
+      <c r="CM79">
+        <v>653</v>
+      </c>
+      <c r="CN79">
+        <v>0.72128637059724354</v>
+      </c>
     </row>
-    <row r="80" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -23288,8 +23771,14 @@
       <c r="CL80">
         <v>44.7</v>
       </c>
+      <c r="CM80">
+        <v>5594</v>
+      </c>
+      <c r="CN80">
+        <v>0.78852341794780123</v>
+      </c>
     </row>
-    <row r="81" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -23560,8 +24049,14 @@
       <c r="CL81">
         <v>69.400000000000006</v>
       </c>
+      <c r="CM81">
+        <v>3287</v>
+      </c>
+      <c r="CN81">
+        <v>0.8119866139336781</v>
+      </c>
     </row>
-    <row r="82" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -23832,8 +24327,14 @@
       <c r="CL82">
         <v>69</v>
       </c>
+      <c r="CM82">
+        <v>4853</v>
+      </c>
+      <c r="CN82">
+        <v>0.7739542550999382</v>
+      </c>
     </row>
-    <row r="83" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -24104,8 +24605,14 @@
       <c r="CL83">
         <v>52.2</v>
       </c>
+      <c r="CM83">
+        <v>6008</v>
+      </c>
+      <c r="CN83">
+        <v>0.82123834886817582</v>
+      </c>
     </row>
-    <row r="84" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -24376,8 +24883,14 @@
       <c r="CL84">
         <v>79.099999999999994</v>
       </c>
+      <c r="CM84">
+        <v>129816</v>
+      </c>
+      <c r="CN84">
+        <v>0.82244099340605159</v>
+      </c>
     </row>
-    <row r="85" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -24648,8 +25161,14 @@
       <c r="CL85">
         <v>67.7</v>
       </c>
+      <c r="CM85">
+        <v>1025</v>
+      </c>
+      <c r="CN85">
+        <v>0.75219512195121951</v>
+      </c>
     </row>
-    <row r="86" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -24920,8 +25439,14 @@
       <c r="CL86">
         <v>78.400000000000006</v>
       </c>
+      <c r="CM86">
+        <v>4886</v>
+      </c>
+      <c r="CN86">
+        <v>0.77261563651248466</v>
+      </c>
     </row>
-    <row r="87" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -25192,8 +25717,14 @@
       <c r="CL87">
         <v>72.599999999999994</v>
       </c>
+      <c r="CM87">
+        <v>1251</v>
+      </c>
+      <c r="CN87">
+        <v>0.8840927258193445</v>
+      </c>
     </row>
-    <row r="88" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -25464,8 +25995,14 @@
       <c r="CL88">
         <v>93.4</v>
       </c>
+      <c r="CM88">
+        <v>4985</v>
+      </c>
+      <c r="CN88">
+        <v>0.86359077231695081</v>
+      </c>
     </row>
-    <row r="89" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -25736,8 +26273,14 @@
       <c r="CL89">
         <v>81.7</v>
       </c>
+      <c r="CM89">
+        <v>1390</v>
+      </c>
+      <c r="CN89">
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="90" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -26008,8 +26551,14 @@
       <c r="CL90">
         <v>80.099999999999994</v>
       </c>
+      <c r="CM90">
+        <v>823</v>
+      </c>
+      <c r="CN90">
+        <v>0.69137302551640345</v>
+      </c>
     </row>
-    <row r="91" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -26280,8 +26829,14 @@
       <c r="CL91">
         <v>64.2</v>
       </c>
+      <c r="CM91">
+        <v>1227</v>
+      </c>
+      <c r="CN91">
+        <v>0.81581092094539531</v>
+      </c>
     </row>
-    <row r="92" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -26552,8 +27107,14 @@
       <c r="CL92">
         <v>66.7</v>
       </c>
+      <c r="CM92">
+        <v>603</v>
+      </c>
+      <c r="CN92">
+        <v>0.71641791044776115</v>
+      </c>
     </row>
-    <row r="93" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -26824,8 +27385,14 @@
       <c r="CL93">
         <v>83.1</v>
       </c>
+      <c r="CM93">
+        <v>1939</v>
+      </c>
+      <c r="CN93">
+        <v>0.81536874677668902</v>
+      </c>
     </row>
-    <row r="94" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -27096,8 +27663,14 @@
       <c r="CL94">
         <v>78.599999999999994</v>
       </c>
+      <c r="CM94">
+        <v>1818</v>
+      </c>
+      <c r="CN94">
+        <v>0.74697469746974698</v>
+      </c>
     </row>
-    <row r="95" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -27368,8 +27941,14 @@
       <c r="CL95">
         <v>72.2</v>
       </c>
+      <c r="CM95">
+        <v>969</v>
+      </c>
+      <c r="CN95">
+        <v>0.72445820433436536</v>
+      </c>
     </row>
-    <row r="96" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -27640,8 +28219,14 @@
       <c r="CL96">
         <v>68.400000000000006</v>
       </c>
+      <c r="CM96">
+        <v>52893</v>
+      </c>
+      <c r="CN96">
+        <v>0.82755752178927267</v>
+      </c>
     </row>
-    <row r="97" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -27912,8 +28497,14 @@
       <c r="CL97">
         <v>58.8</v>
       </c>
+      <c r="CM97">
+        <v>1374</v>
+      </c>
+      <c r="CN97">
+        <v>0.86171761280931591</v>
+      </c>
     </row>
-    <row r="98" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -28184,8 +28775,14 @@
       <c r="CL98">
         <v>67.599999999999994</v>
       </c>
+      <c r="CM98">
+        <v>5983</v>
+      </c>
+      <c r="CN98">
+        <v>0.86010362694300513</v>
+      </c>
     </row>
-    <row r="99" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -28456,8 +29053,14 @@
       <c r="CL99">
         <v>80.599999999999994</v>
       </c>
+      <c r="CM99">
+        <v>2856</v>
+      </c>
+      <c r="CN99">
+        <v>0.85784313725490191</v>
+      </c>
     </row>
-    <row r="100" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -28728,8 +29331,14 @@
       <c r="CL100">
         <v>78.400000000000006</v>
       </c>
+      <c r="CM100">
+        <v>3390</v>
+      </c>
+      <c r="CN100">
+        <v>0.74631268436578169</v>
+      </c>
     </row>
-    <row r="101" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -29000,8 +29609,14 @@
       <c r="CL101">
         <v>67.599999999999994</v>
       </c>
+      <c r="CM101">
+        <v>1522</v>
+      </c>
+      <c r="CN101">
+        <v>0.85676741130091982</v>
+      </c>
     </row>
-    <row r="102" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -29272,8 +29887,14 @@
       <c r="CL102">
         <v>68.5</v>
       </c>
+      <c r="CM102">
+        <v>2427</v>
+      </c>
+      <c r="CN102">
+        <v>0.87474248042851255</v>
+      </c>
     </row>
-    <row r="103" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -29544,8 +30165,14 @@
       <c r="CL103">
         <v>76.2</v>
       </c>
+      <c r="CM103">
+        <v>2026</v>
+      </c>
+      <c r="CN103">
+        <v>0.79615004935834155</v>
+      </c>
     </row>
-    <row r="104" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -29816,8 +30443,14 @@
       <c r="CL104">
         <v>74.099999999999994</v>
       </c>
+      <c r="CM104">
+        <v>1199</v>
+      </c>
+      <c r="CN104">
+        <v>0.76146788990825687</v>
+      </c>
     </row>
-    <row r="105" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -30088,8 +30721,14 @@
       <c r="CL105">
         <v>74.8</v>
       </c>
+      <c r="CM105">
+        <v>1156</v>
+      </c>
+      <c r="CN105">
+        <v>0.74134948096885811</v>
+      </c>
     </row>
-    <row r="106" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -30360,8 +30999,14 @@
       <c r="CL106">
         <v>69.2</v>
       </c>
+      <c r="CM106">
+        <v>1715</v>
+      </c>
+      <c r="CN106">
+        <v>0.76793002915451891</v>
+      </c>
     </row>
-    <row r="107" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -30632,8 +31277,14 @@
       <c r="CL107">
         <v>80.599999999999994</v>
       </c>
+      <c r="CM107">
+        <v>1403</v>
+      </c>
+      <c r="CN107">
+        <v>0.73342836778332143</v>
+      </c>
     </row>
-    <row r="108" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -30904,8 +31555,14 @@
       <c r="CL108">
         <v>77.400000000000006</v>
       </c>
+      <c r="CM108">
+        <v>1821</v>
+      </c>
+      <c r="CN108">
+        <v>0.80230642504118621</v>
+      </c>
     </row>
-    <row r="109" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -31176,8 +31833,14 @@
       <c r="CL109">
         <v>89.3</v>
       </c>
+      <c r="CM109">
+        <v>3376</v>
+      </c>
+      <c r="CN109">
+        <v>0.60545023696682465</v>
+      </c>
     </row>
-    <row r="110" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -31448,8 +32111,14 @@
       <c r="CL110">
         <v>66.099999999999994</v>
       </c>
+      <c r="CM110">
+        <v>1671</v>
+      </c>
+      <c r="CN110">
+        <v>0.78096947935368044</v>
+      </c>
     </row>
-    <row r="111" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -31720,8 +32389,14 @@
       <c r="CL111">
         <v>84.6</v>
       </c>
+      <c r="CM111">
+        <v>7899</v>
+      </c>
+      <c r="CN111">
+        <v>0.85770350677300922</v>
+      </c>
     </row>
-    <row r="112" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -31992,8 +32667,14 @@
       <c r="CL112">
         <v>70.599999999999994</v>
       </c>
+      <c r="CM112">
+        <v>1301</v>
+      </c>
+      <c r="CN112">
+        <v>0.84780937740199847</v>
+      </c>
     </row>
-    <row r="113" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -32264,8 +32945,14 @@
       <c r="CL113">
         <v>71.099999999999994</v>
       </c>
+      <c r="CM113">
+        <v>1661</v>
+      </c>
+      <c r="CN113">
+        <v>0.8892233594220349</v>
+      </c>
     </row>
-    <row r="114" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -32536,8 +33223,14 @@
       <c r="CL114">
         <v>86.6</v>
       </c>
+      <c r="CM114">
+        <v>965</v>
+      </c>
+      <c r="CN114">
+        <v>0.81554404145077719</v>
+      </c>
     </row>
-    <row r="115" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -32808,8 +33501,14 @@
       <c r="CL115">
         <v>68</v>
       </c>
+      <c r="CM115">
+        <v>13409</v>
+      </c>
+      <c r="CN115">
+        <v>0.83182936833470056</v>
+      </c>
     </row>
-    <row r="116" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -33080,8 +33779,14 @@
       <c r="CL116">
         <v>75.2</v>
       </c>
+      <c r="CM116">
+        <v>14041</v>
+      </c>
+      <c r="CN116">
+        <v>0.8449540631009187</v>
+      </c>
     </row>
-    <row r="117" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -33352,8 +34057,14 @@
       <c r="CL117">
         <v>76.900000000000006</v>
       </c>
+      <c r="CM117">
+        <v>510</v>
+      </c>
+      <c r="CN117">
+        <v>0.86862745098039218</v>
+      </c>
     </row>
-    <row r="118" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -33624,8 +34335,14 @@
       <c r="CL118">
         <v>69.599999999999994</v>
       </c>
+      <c r="CM118">
+        <v>1482</v>
+      </c>
+      <c r="CN118">
+        <v>0.82253711201079627</v>
+      </c>
     </row>
-    <row r="119" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -33896,8 +34613,14 @@
       <c r="CL119">
         <v>75.400000000000006</v>
       </c>
+      <c r="CM119">
+        <v>5203</v>
+      </c>
+      <c r="CN119">
+        <v>0.76551989236978668</v>
+      </c>
     </row>
-    <row r="120" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -34168,8 +34891,14 @@
       <c r="CL120">
         <v>71.3</v>
       </c>
+      <c r="CM120">
+        <v>238</v>
+      </c>
+      <c r="CN120">
+        <v>0.55882352941176472</v>
+      </c>
     </row>
-    <row r="121" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -34440,8 +35169,14 @@
       <c r="CL121">
         <v>33.200000000000003</v>
       </c>
+      <c r="CM121">
+        <v>2912</v>
+      </c>
+      <c r="CN121">
+        <v>0.77026098901098905</v>
+      </c>
     </row>
-    <row r="122" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -34712,8 +35447,14 @@
       <c r="CL122">
         <v>63.8</v>
       </c>
+      <c r="CM122">
+        <v>10493</v>
+      </c>
+      <c r="CN122">
+        <v>0.64366720670923472</v>
+      </c>
     </row>
-    <row r="123" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -34984,8 +35725,14 @@
       <c r="CL123">
         <v>53.3</v>
       </c>
+      <c r="CM123">
+        <v>2666</v>
+      </c>
+      <c r="CN123">
+        <v>0.76106526631657911</v>
+      </c>
     </row>
-    <row r="124" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -35256,8 +36003,14 @@
       <c r="CL124">
         <v>77.099999999999994</v>
       </c>
+      <c r="CM124">
+        <v>1992</v>
+      </c>
+      <c r="CN124">
+        <v>0.57530120481927716</v>
+      </c>
     </row>
-    <row r="125" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -35528,8 +36281,14 @@
       <c r="CL125">
         <v>63.9</v>
       </c>
+      <c r="CM125">
+        <v>1087</v>
+      </c>
+      <c r="CN125">
+        <v>0.60533578656853726</v>
+      </c>
     </row>
-    <row r="126" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -35800,8 +36559,14 @@
       <c r="CL126">
         <v>54.2</v>
       </c>
+      <c r="CM126">
+        <v>1034</v>
+      </c>
+      <c r="CN126">
+        <v>0.78046421663442944</v>
+      </c>
     </row>
-    <row r="127" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -36072,8 +36837,14 @@
       <c r="CL127">
         <v>69.400000000000006</v>
       </c>
+      <c r="CM127">
+        <v>1823</v>
+      </c>
+      <c r="CN127">
+        <v>0.79978058145913333</v>
+      </c>
     </row>
-    <row r="128" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -36344,8 +37115,14 @@
       <c r="CL128">
         <v>69.2</v>
       </c>
+      <c r="CM128">
+        <v>2349</v>
+      </c>
+      <c r="CN128">
+        <v>0.84716900808854834</v>
+      </c>
     </row>
-    <row r="129" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -36616,8 +37393,14 @@
       <c r="CL129">
         <v>88.4</v>
       </c>
+      <c r="CM129">
+        <v>6717</v>
+      </c>
+      <c r="CN129">
+        <v>0.82879261575107932</v>
+      </c>
     </row>
-    <row r="130" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -36888,8 +37671,14 @@
       <c r="CL130">
         <v>67</v>
       </c>
+      <c r="CM130">
+        <v>2070</v>
+      </c>
+      <c r="CN130">
+        <v>0.82270531400966185</v>
+      </c>
     </row>
-    <row r="131" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -37160,8 +37949,14 @@
       <c r="CL131">
         <v>72.900000000000006</v>
       </c>
+      <c r="CM131">
+        <v>1381</v>
+      </c>
+      <c r="CN131">
+        <v>0.80448950036205646</v>
+      </c>
     </row>
-    <row r="132" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -37432,8 +38227,14 @@
       <c r="CL132">
         <v>88.5</v>
       </c>
+      <c r="CM132">
+        <v>2568</v>
+      </c>
+      <c r="CN132">
+        <v>0.84852024922118385</v>
+      </c>
     </row>
-    <row r="133" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -37704,8 +38505,14 @@
       <c r="CL133">
         <v>74.7</v>
       </c>
+      <c r="CM133">
+        <v>10107</v>
+      </c>
+      <c r="CN133">
+        <v>0.82111407935094494</v>
+      </c>
     </row>
-    <row r="134" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -37976,8 +38783,14 @@
       <c r="CL134">
         <v>65.8</v>
       </c>
+      <c r="CM134">
+        <v>2488</v>
+      </c>
+      <c r="CN134">
+        <v>0.75281350482315113</v>
+      </c>
     </row>
-    <row r="135" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -38248,8 +39061,14 @@
       <c r="CL135">
         <v>61.6</v>
       </c>
+      <c r="CM135">
+        <v>3053</v>
+      </c>
+      <c r="CN135">
+        <v>0.83164100884376024</v>
+      </c>
     </row>
-    <row r="136" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -38520,8 +39339,14 @@
       <c r="CL136">
         <v>75.8</v>
       </c>
+      <c r="CM136">
+        <v>1878</v>
+      </c>
+      <c r="CN136">
+        <v>0.78700745473908418</v>
+      </c>
     </row>
-    <row r="137" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -38792,8 +39617,14 @@
       <c r="CL137">
         <v>72.3</v>
       </c>
+      <c r="CM137">
+        <v>2217</v>
+      </c>
+      <c r="CN137">
+        <v>0.79070816418583667</v>
+      </c>
     </row>
-    <row r="138" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -39064,8 +39895,14 @@
       <c r="CL138">
         <v>64.599999999999994</v>
       </c>
+      <c r="CM138">
+        <v>2266</v>
+      </c>
+      <c r="CN138">
+        <v>0.83406884377758161</v>
+      </c>
     </row>
-    <row r="139" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -39336,8 +40173,14 @@
       <c r="CL139">
         <v>76.900000000000006</v>
       </c>
+      <c r="CM139">
+        <v>7439</v>
+      </c>
+      <c r="CN139">
+        <v>0.85334050275574669</v>
+      </c>
     </row>
-    <row r="140" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -39608,8 +40451,14 @@
       <c r="CL140">
         <v>75</v>
       </c>
+      <c r="CM140">
+        <v>4651</v>
+      </c>
+      <c r="CN140">
+        <v>0.89120619221672759</v>
+      </c>
     </row>
-    <row r="141" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -39880,8 +40729,14 @@
       <c r="CL141">
         <v>76.099999999999994</v>
       </c>
+      <c r="CM141">
+        <v>476</v>
+      </c>
+      <c r="CN141">
+        <v>0.8214285714285714</v>
+      </c>
     </row>
-    <row r="142" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -40152,8 +41007,14 @@
       <c r="CL142">
         <v>63</v>
       </c>
+      <c r="CM142">
+        <v>831</v>
+      </c>
+      <c r="CN142">
+        <v>0.8038507821901324</v>
+      </c>
     </row>
-    <row r="143" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -40424,8 +41285,14 @@
       <c r="CL143">
         <v>71.400000000000006</v>
       </c>
+      <c r="CM143">
+        <v>1596</v>
+      </c>
+      <c r="CN143">
+        <v>0.83583959899749372</v>
+      </c>
     </row>
-    <row r="144" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -40696,8 +41563,14 @@
       <c r="CL144">
         <v>75.099999999999994</v>
       </c>
+      <c r="CM144">
+        <v>3418</v>
+      </c>
+      <c r="CN144">
+        <v>0.82533645406670564</v>
+      </c>
     </row>
-    <row r="145" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -40968,8 +41841,14 @@
       <c r="CL145">
         <v>69</v>
       </c>
+      <c r="CM145">
+        <v>554</v>
+      </c>
+      <c r="CN145">
+        <v>0.68231046931407946</v>
+      </c>
     </row>
-    <row r="146" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -41240,8 +42119,14 @@
       <c r="CL146">
         <v>78.900000000000006</v>
       </c>
+      <c r="CM146">
+        <v>4377</v>
+      </c>
+      <c r="CN146">
+        <v>0.78958190541466755</v>
+      </c>
     </row>
-    <row r="147" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>146</v>
       </c>
@@ -41512,8 +42397,14 @@
       <c r="CL147">
         <v>75.3</v>
       </c>
+      <c r="CM147">
+        <v>1198</v>
+      </c>
+      <c r="CN147">
+        <v>0.77796327212020033</v>
+      </c>
     </row>
-    <row r="148" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>147</v>
       </c>
@@ -41784,8 +42675,14 @@
       <c r="CL148">
         <v>50.5</v>
       </c>
+      <c r="CM148">
+        <v>1127</v>
+      </c>
+      <c r="CN148">
+        <v>0.82076308784383323</v>
+      </c>
     </row>
-    <row r="149" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>148</v>
       </c>
@@ -42056,8 +42953,14 @@
       <c r="CL149">
         <v>62.9</v>
       </c>
+      <c r="CM149">
+        <v>3174</v>
+      </c>
+      <c r="CN149">
+        <v>0.8412098298676749</v>
+      </c>
     </row>
-    <row r="150" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>149</v>
       </c>
@@ -42328,8 +43231,14 @@
       <c r="CL150">
         <v>71.3</v>
       </c>
+      <c r="CM150">
+        <v>1706</v>
+      </c>
+      <c r="CN150">
+        <v>0.83001172332942552</v>
+      </c>
     </row>
-    <row r="151" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>150</v>
       </c>
@@ -42600,8 +43509,14 @@
       <c r="CL151">
         <v>68.3</v>
       </c>
+      <c r="CM151">
+        <v>1796</v>
+      </c>
+      <c r="CN151">
+        <v>0.7048997772828508</v>
+      </c>
     </row>
-    <row r="152" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>151</v>
       </c>
@@ -42872,8 +43787,14 @@
       <c r="CL152">
         <v>63.3</v>
       </c>
+      <c r="CM152">
+        <v>7348</v>
+      </c>
+      <c r="CN152">
+        <v>0.76769188894937401</v>
+      </c>
     </row>
-    <row r="153" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>152</v>
       </c>
@@ -43144,8 +44065,14 @@
       <c r="CL153">
         <v>70.2</v>
       </c>
+      <c r="CM153">
+        <v>5943</v>
+      </c>
+      <c r="CN153">
+        <v>0.79538953390543499</v>
+      </c>
     </row>
-    <row r="154" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>153</v>
       </c>
@@ -43416,8 +44343,14 @@
       <c r="CL154">
         <v>64.3</v>
       </c>
+      <c r="CM154">
+        <v>6176</v>
+      </c>
+      <c r="CN154">
+        <v>0.852979274611399</v>
+      </c>
     </row>
-    <row r="155" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>154</v>
       </c>
@@ -43688,8 +44621,14 @@
       <c r="CL155">
         <v>80.599999999999994</v>
       </c>
+      <c r="CM155">
+        <v>10252</v>
+      </c>
+      <c r="CN155">
+        <v>0.82588763168162305</v>
+      </c>
     </row>
-    <row r="156" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>155</v>
       </c>
@@ -43960,8 +44899,14 @@
       <c r="CL156">
         <v>75.7</v>
       </c>
+      <c r="CM156">
+        <v>5708</v>
+      </c>
+      <c r="CN156">
+        <v>0.83759635599159077</v>
+      </c>
     </row>
-    <row r="157" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>156</v>
       </c>
@@ -44232,8 +45177,14 @@
       <c r="CL157">
         <v>76.7</v>
       </c>
+      <c r="CM157">
+        <v>914</v>
+      </c>
+      <c r="CN157">
+        <v>0.7286652078774617</v>
+      </c>
     </row>
-    <row r="158" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>157</v>
       </c>
@@ -44504,8 +45455,14 @@
       <c r="CL158">
         <v>83.2</v>
       </c>
+      <c r="CM158">
+        <v>248</v>
+      </c>
+      <c r="CN158">
+        <v>0.63709677419354838</v>
+      </c>
     </row>
-    <row r="159" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>158</v>
       </c>
@@ -44776,8 +45733,14 @@
       <c r="CL159">
         <v>81.7</v>
       </c>
+      <c r="CM159">
+        <v>801</v>
+      </c>
+      <c r="CN159">
+        <v>0.80149812734082393</v>
+      </c>
     </row>
-    <row r="160" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>159</v>
       </c>
@@ -45048,8 +46011,14 @@
       <c r="CL160">
         <v>61</v>
       </c>
+      <c r="CM160">
+        <v>1499</v>
+      </c>
+      <c r="CN160">
+        <v>0.83455637091394264</v>
+      </c>
     </row>
-    <row r="161" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>160</v>
       </c>
@@ -45320,8 +46289,14 @@
       <c r="CL161">
         <v>74.2</v>
       </c>
+      <c r="CM161">
+        <v>1397</v>
+      </c>
+      <c r="CN161">
+        <v>0.83679312813171081</v>
+      </c>
     </row>
-    <row r="162" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>161</v>
       </c>
@@ -45592,8 +46567,14 @@
       <c r="CL162">
         <v>83.2</v>
       </c>
+      <c r="CM162">
+        <v>883</v>
+      </c>
+      <c r="CN162">
+        <v>0.77916194790486981</v>
+      </c>
     </row>
-    <row r="163" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>162</v>
       </c>
@@ -45864,8 +46845,14 @@
       <c r="CL163">
         <v>67.900000000000006</v>
       </c>
+      <c r="CM163">
+        <v>822</v>
+      </c>
+      <c r="CN163">
+        <v>0.81021897810218979</v>
+      </c>
     </row>
-    <row r="164" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>163</v>
       </c>
@@ -46136,8 +47123,14 @@
       <c r="CL164">
         <v>54.9</v>
       </c>
+      <c r="CM164">
+        <v>442</v>
+      </c>
+      <c r="CN164">
+        <v>0.79411764705882348</v>
+      </c>
     </row>
-    <row r="165" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>164</v>
       </c>
@@ -46408,8 +47401,14 @@
       <c r="CL165">
         <v>67.900000000000006</v>
       </c>
+      <c r="CM165">
+        <v>1275</v>
+      </c>
+      <c r="CN165">
+        <v>0.71607843137254901</v>
+      </c>
     </row>
-    <row r="166" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>165</v>
       </c>
@@ -46680,8 +47679,14 @@
       <c r="CL166">
         <v>73.3</v>
       </c>
+      <c r="CM166">
+        <v>775</v>
+      </c>
+      <c r="CN166">
+        <v>0.7870967741935484</v>
+      </c>
     </row>
-    <row r="167" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>166</v>
       </c>
@@ -46952,8 +47957,14 @@
       <c r="CL167">
         <v>77.3</v>
       </c>
+      <c r="CM167">
+        <v>904</v>
+      </c>
+      <c r="CN167">
+        <v>0.73119469026548678</v>
+      </c>
     </row>
-    <row r="168" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>167</v>
       </c>
@@ -47224,8 +48235,14 @@
       <c r="CL168">
         <v>65.7</v>
       </c>
+      <c r="CM168">
+        <v>752</v>
+      </c>
+      <c r="CN168">
+        <v>0.67420212765957444</v>
+      </c>
     </row>
-    <row r="169" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>168</v>
       </c>
@@ -47496,8 +48513,14 @@
       <c r="CL169">
         <v>43.3</v>
       </c>
+      <c r="CM169">
+        <v>2494</v>
+      </c>
+      <c r="CN169">
+        <v>0.85846030473135526</v>
+      </c>
     </row>
-    <row r="170" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>169</v>
       </c>
@@ -47768,8 +48791,14 @@
       <c r="CL170">
         <v>68.2</v>
       </c>
+      <c r="CM170">
+        <v>2814</v>
+      </c>
+      <c r="CN170">
+        <v>0.88841506751954513</v>
+      </c>
     </row>
-    <row r="171" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>170</v>
       </c>
@@ -48040,8 +49069,14 @@
       <c r="CL171">
         <v>89.4</v>
       </c>
+      <c r="CM171">
+        <v>3281</v>
+      </c>
+      <c r="CN171">
+        <v>0.82657726302956414</v>
+      </c>
     </row>
-    <row r="172" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>171</v>
       </c>
@@ -48312,8 +49347,14 @@
       <c r="CL172">
         <v>64.7</v>
       </c>
+      <c r="CM172">
+        <v>2638</v>
+      </c>
+      <c r="CN172">
+        <v>0.78658074298711145</v>
+      </c>
     </row>
-    <row r="173" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>172</v>
       </c>
@@ -48584,8 +49625,14 @@
       <c r="CL173">
         <v>76.099999999999994</v>
       </c>
+      <c r="CM173">
+        <v>7504</v>
+      </c>
+      <c r="CN173">
+        <v>0.79677505330490406</v>
+      </c>
     </row>
-    <row r="174" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>173</v>
       </c>
@@ -48856,8 +49903,14 @@
       <c r="CL174">
         <v>78.8</v>
       </c>
+      <c r="CM174">
+        <v>1170</v>
+      </c>
+      <c r="CN174">
+        <v>0.69401709401709399</v>
+      </c>
     </row>
-    <row r="175" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>174</v>
       </c>
@@ -49128,8 +50181,14 @@
       <c r="CL175">
         <v>71.099999999999994</v>
       </c>
+      <c r="CM175">
+        <v>1369</v>
+      </c>
+      <c r="CN175">
+        <v>0.69539810080350617</v>
+      </c>
     </row>
-    <row r="176" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>175</v>
       </c>
@@ -49400,8 +50459,14 @@
       <c r="CL176">
         <v>76.099999999999994</v>
       </c>
+      <c r="CM176">
+        <v>8364</v>
+      </c>
+      <c r="CN176">
+        <v>0.86358201817312286</v>
+      </c>
     </row>
-    <row r="177" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>176</v>
       </c>
@@ -49672,8 +50737,14 @@
       <c r="CL177">
         <v>80.7</v>
       </c>
+      <c r="CM177">
+        <v>4098</v>
+      </c>
+      <c r="CN177">
+        <v>0.84016593460224498</v>
+      </c>
     </row>
-    <row r="178" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>177</v>
       </c>
@@ -49944,8 +51015,14 @@
       <c r="CL178">
         <v>85.9</v>
       </c>
+      <c r="CM178">
+        <v>4269</v>
+      </c>
+      <c r="CN178">
+        <v>0.77465448582806273</v>
+      </c>
     </row>
-    <row r="179" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>178</v>
       </c>
@@ -50216,8 +51293,14 @@
       <c r="CL179">
         <v>83.8</v>
       </c>
+      <c r="CM179">
+        <v>1559</v>
+      </c>
+      <c r="CN179">
+        <v>0.70942912123155866</v>
+      </c>
     </row>
-    <row r="180" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>179</v>
       </c>
@@ -50488,8 +51571,14 @@
       <c r="CL180">
         <v>83.7</v>
       </c>
+      <c r="CM180">
+        <v>1246</v>
+      </c>
+      <c r="CN180">
+        <v>0.80658105939004821</v>
+      </c>
     </row>
-    <row r="181" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>180</v>
       </c>
@@ -50760,8 +51849,14 @@
       <c r="CL181">
         <v>73.900000000000006</v>
       </c>
+      <c r="CM181">
+        <v>2027</v>
+      </c>
+      <c r="CN181">
+        <v>0.76221016280217069</v>
+      </c>
     </row>
-    <row r="182" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>181</v>
       </c>
@@ -51032,8 +52127,14 @@
       <c r="CL182">
         <v>78.900000000000006</v>
       </c>
+      <c r="CM182">
+        <v>3090</v>
+      </c>
+      <c r="CN182">
+        <v>0.85177993527508089</v>
+      </c>
     </row>
-    <row r="183" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>182</v>
       </c>
@@ -51304,8 +52405,14 @@
       <c r="CL183">
         <v>71.5</v>
       </c>
+      <c r="CM183">
+        <v>1683</v>
+      </c>
+      <c r="CN183">
+        <v>0.81937017231134879</v>
+      </c>
     </row>
-    <row r="184" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>183</v>
       </c>
@@ -51576,8 +52683,14 @@
       <c r="CL184">
         <v>65.8</v>
       </c>
+      <c r="CM184">
+        <v>653</v>
+      </c>
+      <c r="CN184">
+        <v>0.75957120980091886</v>
+      </c>
     </row>
-    <row r="185" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>184</v>
       </c>
@@ -51848,8 +52961,14 @@
       <c r="CL185">
         <v>72.900000000000006</v>
       </c>
+      <c r="CM185">
+        <v>1379</v>
+      </c>
+      <c r="CN185">
+        <v>0.87164612037708489</v>
+      </c>
     </row>
-    <row r="186" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>185</v>
       </c>
@@ -52120,8 +53239,14 @@
       <c r="CL186">
         <v>67.900000000000006</v>
       </c>
+      <c r="CM186">
+        <v>5320</v>
+      </c>
+      <c r="CN186">
+        <v>0.73853383458646615</v>
+      </c>
     </row>
-    <row r="187" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>186</v>
       </c>
@@ -52392,8 +53517,14 @@
       <c r="CL187">
         <v>72.7</v>
       </c>
+      <c r="CM187">
+        <v>7573</v>
+      </c>
+      <c r="CN187">
+        <v>0.83890136009507466</v>
+      </c>
     </row>
-    <row r="188" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>187</v>
       </c>
@@ -52664,8 +53795,14 @@
       <c r="CL188">
         <v>59.8</v>
       </c>
+      <c r="CM188">
+        <v>5073</v>
+      </c>
+      <c r="CN188">
+        <v>0.76995860437610886</v>
+      </c>
     </row>
-    <row r="189" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>188</v>
       </c>
@@ -52936,8 +54073,14 @@
       <c r="CL189">
         <v>72.099999999999994</v>
       </c>
+      <c r="CM189">
+        <v>492</v>
+      </c>
+      <c r="CN189">
+        <v>0.82926829268292679</v>
+      </c>
     </row>
-    <row r="190" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>189</v>
       </c>
@@ -53208,8 +54351,14 @@
       <c r="CL190">
         <v>81</v>
       </c>
+      <c r="CM190">
+        <v>1453</v>
+      </c>
+      <c r="CN190">
+        <v>0.85891259463179626</v>
+      </c>
     </row>
-    <row r="191" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>190</v>
       </c>
@@ -53480,8 +54629,14 @@
       <c r="CL191">
         <v>93.7</v>
       </c>
+      <c r="CM191">
+        <v>5889</v>
+      </c>
+      <c r="CN191">
+        <v>0.85073866530820175</v>
+      </c>
     </row>
-    <row r="192" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>191</v>
       </c>
@@ -53752,8 +54907,14 @@
       <c r="CL192">
         <v>66.7</v>
       </c>
+      <c r="CM192">
+        <v>1095</v>
+      </c>
+      <c r="CN192">
+        <v>0.84748858447488584</v>
+      </c>
     </row>
-    <row r="193" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>192</v>
       </c>
@@ -54024,8 +55185,14 @@
       <c r="CL193">
         <v>68</v>
       </c>
+      <c r="CM193">
+        <v>12375</v>
+      </c>
+      <c r="CN193">
+        <v>0.91991919191919191</v>
+      </c>
     </row>
-    <row r="194" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>193</v>
       </c>
@@ -54296,8 +55463,14 @@
       <c r="CL194">
         <v>69.599999999999994</v>
       </c>
+      <c r="CM194">
+        <v>511</v>
+      </c>
+      <c r="CN194">
+        <v>0.80821917808219179</v>
+      </c>
     </row>
-    <row r="195" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>194</v>
       </c>
@@ -54568,8 +55741,14 @@
       <c r="CL195">
         <v>60.5</v>
       </c>
+      <c r="CM195">
+        <v>1885</v>
+      </c>
+      <c r="CN195">
+        <v>0.75066312997347484</v>
+      </c>
     </row>
-    <row r="196" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>195</v>
       </c>
@@ -54840,8 +56019,14 @@
       <c r="CL196">
         <v>84.3</v>
       </c>
+      <c r="CM196">
+        <v>596</v>
+      </c>
+      <c r="CN196">
+        <v>0.72315436241610742</v>
+      </c>
     </row>
-    <row r="197" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>196</v>
       </c>
@@ -55112,8 +56297,14 @@
       <c r="CL197">
         <v>57.7</v>
       </c>
+      <c r="CM197">
+        <v>2575</v>
+      </c>
+      <c r="CN197">
+        <v>0.69475728155339811</v>
+      </c>
     </row>
-    <row r="198" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>197</v>
       </c>
@@ -55384,8 +56575,14 @@
       <c r="CL198">
         <v>63.3</v>
       </c>
+      <c r="CM198">
+        <v>2259</v>
+      </c>
+      <c r="CN198">
+        <v>0.76715360779105801</v>
+      </c>
     </row>
-    <row r="199" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>198</v>
       </c>
@@ -55656,8 +56853,14 @@
       <c r="CL199">
         <v>83.9</v>
       </c>
+      <c r="CM199">
+        <v>863</v>
+      </c>
+      <c r="CN199">
+        <v>0.7404403244495944</v>
+      </c>
     </row>
-    <row r="200" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -55928,8 +57131,14 @@
       <c r="CL200">
         <v>84</v>
       </c>
+      <c r="CM200">
+        <v>1640</v>
+      </c>
+      <c r="CN200">
+        <v>0.85792682926829267</v>
+      </c>
     </row>
-    <row r="201" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>200</v>
       </c>
@@ -56200,8 +57409,14 @@
       <c r="CL201">
         <v>102.3</v>
       </c>
+      <c r="CM201">
+        <v>3545</v>
+      </c>
+      <c r="CN201">
+        <v>0.79548660084626233</v>
+      </c>
     </row>
-    <row r="202" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>201</v>
       </c>
@@ -56472,8 +57687,14 @@
       <c r="CL202">
         <v>80.900000000000006</v>
       </c>
+      <c r="CM202">
+        <v>1012</v>
+      </c>
+      <c r="CN202">
+        <v>0.77865612648221338</v>
+      </c>
     </row>
-    <row r="203" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>202</v>
       </c>
@@ -56744,8 +57965,14 @@
       <c r="CL203">
         <v>73.8</v>
       </c>
+      <c r="CM203">
+        <v>6107</v>
+      </c>
+      <c r="CN203">
+        <v>0.87211396757818893</v>
+      </c>
     </row>
-    <row r="204" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>203</v>
       </c>
@@ -57016,8 +58243,14 @@
       <c r="CL204">
         <v>82.9</v>
       </c>
+      <c r="CM204">
+        <v>982</v>
+      </c>
+      <c r="CN204">
+        <v>0.82586558044806513</v>
+      </c>
     </row>
-    <row r="205" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>204</v>
       </c>
@@ -57288,8 +58521,14 @@
       <c r="CL205">
         <v>65.2</v>
       </c>
+      <c r="CM205">
+        <v>6276</v>
+      </c>
+      <c r="CN205">
+        <v>0.84257488846398976</v>
+      </c>
     </row>
-    <row r="206" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>205</v>
       </c>
@@ -57560,8 +58799,14 @@
       <c r="CL206">
         <v>77.8</v>
       </c>
+      <c r="CM206">
+        <v>831</v>
+      </c>
+      <c r="CN206">
+        <v>0.56558363417569191</v>
+      </c>
     </row>
-    <row r="207" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>206</v>
       </c>
@@ -57832,8 +59077,14 @@
       <c r="CL207">
         <v>65.400000000000006</v>
       </c>
+      <c r="CM207">
+        <v>2670</v>
+      </c>
+      <c r="CN207">
+        <v>0.74831460674157302</v>
+      </c>
     </row>
-    <row r="208" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>207</v>
       </c>
@@ -58104,8 +59355,14 @@
       <c r="CL208">
         <v>76</v>
       </c>
+      <c r="CM208">
+        <v>8590</v>
+      </c>
+      <c r="CN208">
+        <v>0.82980209545983707</v>
+      </c>
     </row>
-    <row r="209" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>208</v>
       </c>
@@ -58376,8 +59633,14 @@
       <c r="CL209">
         <v>74.400000000000006</v>
       </c>
+      <c r="CM209">
+        <v>2228</v>
+      </c>
+      <c r="CN209">
+        <v>0.82181328545780974</v>
+      </c>
     </row>
-    <row r="210" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>209</v>
       </c>
@@ -58648,8 +59911,14 @@
       <c r="CL210">
         <v>87.6</v>
       </c>
+      <c r="CM210">
+        <v>562</v>
+      </c>
+      <c r="CN210">
+        <v>0.69395017793594305</v>
+      </c>
     </row>
-    <row r="211" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>210</v>
       </c>
@@ -58920,8 +60189,14 @@
       <c r="CL211">
         <v>61.9</v>
       </c>
+      <c r="CM211">
+        <v>1727</v>
+      </c>
+      <c r="CN211">
+        <v>0.83497394325419805</v>
+      </c>
     </row>
-    <row r="212" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>211</v>
       </c>
@@ -59192,8 +60467,14 @@
       <c r="CL212">
         <v>87.6</v>
       </c>
+      <c r="CM212">
+        <v>1591</v>
+      </c>
+      <c r="CN212">
+        <v>0.85229415461973601</v>
+      </c>
     </row>
-    <row r="213" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>212</v>
       </c>
@@ -59464,8 +60745,14 @@
       <c r="CL213">
         <v>73.3</v>
       </c>
+      <c r="CM213">
+        <v>2122</v>
+      </c>
+      <c r="CN213">
+        <v>0.67624882186616397</v>
+      </c>
     </row>
-    <row r="214" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>213</v>
       </c>
@@ -59739,6 +61026,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94DDDA7-DAEF-3947-BF50-F00B1B973273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB18B771-5C64-AE42-A6CE-93063DDD2D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="14380" windowWidth="49940" windowHeight="34980" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
+    <workbookView xWindow="21920" yWindow="4560" windowWidth="49940" windowHeight="34980" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Skupna Tabela" sheetId="1" r:id="rId1"/>
@@ -2088,10 +2088,10 @@
         <v>78.3</v>
       </c>
       <c r="CM2">
-        <v>7322</v>
+        <v>698747</v>
       </c>
       <c r="CN2">
-        <v>0.81876536465446603</v>
+        <v>0.8084327271170616</v>
       </c>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.2">
@@ -2366,10 +2366,10 @@
         <v>81.099999999999994</v>
       </c>
       <c r="CM3">
-        <v>1891</v>
+        <v>5995</v>
       </c>
       <c r="CN3">
-        <v>0.68746694870438918</v>
+        <v>0.81876536465446603</v>
       </c>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.2">
@@ -2644,10 +2644,10 @@
         <v>67.7</v>
       </c>
       <c r="CM4">
-        <v>1464</v>
+        <v>1300</v>
       </c>
       <c r="CN4">
-        <v>0.80259562841530052</v>
+        <v>0.68746694870438918</v>
       </c>
     </row>
     <row r="5" spans="1:92" x14ac:dyDescent="0.2">
@@ -2922,10 +2922,10 @@
         <v>61.3</v>
       </c>
       <c r="CM5">
-        <v>2866</v>
+        <v>1175</v>
       </c>
       <c r="CN5">
-        <v>0.85729239357990228</v>
+        <v>0.80259562841530052</v>
       </c>
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.2">
@@ -3200,10 +3200,10 @@
         <v>68.8</v>
       </c>
       <c r="CM6">
-        <v>1041</v>
+        <v>2457</v>
       </c>
       <c r="CN6">
-        <v>0.78770413064361189</v>
+        <v>0.85729239357990228</v>
       </c>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.2">
@@ -3478,10 +3478,10 @@
         <v>78.099999999999994</v>
       </c>
       <c r="CM7">
-        <v>620</v>
+        <v>820</v>
       </c>
       <c r="CN7">
-        <v>0.7129032258064516</v>
+        <v>0.78770413064361189</v>
       </c>
     </row>
     <row r="8" spans="1:92" x14ac:dyDescent="0.2">
@@ -3756,10 +3756,10 @@
         <v>72.7</v>
       </c>
       <c r="CM8">
-        <v>3799</v>
+        <v>442</v>
       </c>
       <c r="CN8">
-        <v>0.7341405633061332</v>
+        <v>0.7129032258064516</v>
       </c>
     </row>
     <row r="9" spans="1:92" x14ac:dyDescent="0.2">
@@ -4034,10 +4034,10 @@
         <v>65.400000000000006</v>
       </c>
       <c r="CM9">
-        <v>805</v>
+        <v>2789</v>
       </c>
       <c r="CN9">
-        <v>0.67577639751552798</v>
+        <v>0.7341405633061332</v>
       </c>
     </row>
     <row r="10" spans="1:92" x14ac:dyDescent="0.2">
@@ -4312,10 +4312,10 @@
         <v>66.7</v>
       </c>
       <c r="CM10">
-        <v>3387</v>
+        <v>544</v>
       </c>
       <c r="CN10">
-        <v>0.55683495718925302</v>
+        <v>0.67577639751552798</v>
       </c>
     </row>
     <row r="11" spans="1:92" x14ac:dyDescent="0.2">
@@ -4590,10 +4590,10 @@
         <v>65.8</v>
       </c>
       <c r="CM11">
-        <v>1572</v>
+        <v>1886</v>
       </c>
       <c r="CN11">
-        <v>0.87786259541984735</v>
+        <v>0.55683495718925302</v>
       </c>
     </row>
     <row r="12" spans="1:92" x14ac:dyDescent="0.2">
@@ -4868,10 +4868,10 @@
         <v>72.2</v>
       </c>
       <c r="CM12">
-        <v>2666</v>
+        <v>1380</v>
       </c>
       <c r="CN12">
-        <v>0.49699924981245314</v>
+        <v>0.87786259541984735</v>
       </c>
     </row>
     <row r="13" spans="1:92" x14ac:dyDescent="0.2">
@@ -5146,10 +5146,10 @@
         <v>57</v>
       </c>
       <c r="CM13">
-        <v>2167</v>
+        <v>1325</v>
       </c>
       <c r="CN13">
-        <v>0.82418089524688509</v>
+        <v>0.49699924981245314</v>
       </c>
     </row>
     <row r="14" spans="1:92" x14ac:dyDescent="0.2">
@@ -5424,10 +5424,10 @@
         <v>80.400000000000006</v>
       </c>
       <c r="CM14">
-        <v>2339</v>
+        <v>1786</v>
       </c>
       <c r="CN14">
-        <v>0.74476271911073111</v>
+        <v>0.82418089524688509</v>
       </c>
     </row>
     <row r="15" spans="1:92" x14ac:dyDescent="0.2">
@@ -5702,10 +5702,10 @@
         <v>71.099999999999994</v>
       </c>
       <c r="CM15">
-        <v>4316</v>
+        <v>1742</v>
       </c>
       <c r="CN15">
-        <v>0.84708063021316038</v>
+        <v>0.74476271911073111</v>
       </c>
     </row>
     <row r="16" spans="1:92" x14ac:dyDescent="0.2">
@@ -5980,10 +5980,10 @@
         <v>92.7</v>
       </c>
       <c r="CM16">
-        <v>10515</v>
+        <v>3656</v>
       </c>
       <c r="CN16">
-        <v>0.76966238706609602</v>
+        <v>0.84708063021316038</v>
       </c>
     </row>
     <row r="17" spans="1:92" x14ac:dyDescent="0.2">
@@ -6258,10 +6258,10 @@
         <v>65.400000000000006</v>
       </c>
       <c r="CM17">
-        <v>786</v>
+        <v>8093</v>
       </c>
       <c r="CN17">
-        <v>0.71755725190839692</v>
+        <v>0.76966238706609602</v>
       </c>
     </row>
     <row r="18" spans="1:92" x14ac:dyDescent="0.2">
@@ -6536,10 +6536,10 @@
         <v>54.1</v>
       </c>
       <c r="CM18">
-        <v>21321</v>
+        <v>564</v>
       </c>
       <c r="CN18">
-        <v>0.84967872051029503</v>
+        <v>0.71755725190839692</v>
       </c>
     </row>
     <row r="19" spans="1:92" x14ac:dyDescent="0.2">
@@ -6814,10 +6814,10 @@
         <v>69.900000000000006</v>
       </c>
       <c r="CM19">
-        <v>2721</v>
+        <v>18116</v>
       </c>
       <c r="CN19">
-        <v>0.78868063212054396</v>
+        <v>0.84967872051029503</v>
       </c>
     </row>
     <row r="20" spans="1:92" x14ac:dyDescent="0.2">
@@ -7092,10 +7092,10 @@
         <v>86.7</v>
       </c>
       <c r="CM20">
-        <v>4541</v>
+        <v>2146</v>
       </c>
       <c r="CN20">
-        <v>0.82426778242677823</v>
+        <v>0.78868063212054396</v>
       </c>
     </row>
     <row r="21" spans="1:92" x14ac:dyDescent="0.2">
@@ -7370,10 +7370,10 @@
         <v>77.900000000000006</v>
       </c>
       <c r="CM21">
-        <v>1997</v>
+        <v>3743</v>
       </c>
       <c r="CN21">
-        <v>0.74211316975463193</v>
+        <v>0.82426778242677823</v>
       </c>
     </row>
     <row r="22" spans="1:92" x14ac:dyDescent="0.2">
@@ -7648,10 +7648,10 @@
         <v>78.900000000000006</v>
       </c>
       <c r="CM22">
-        <v>866</v>
+        <v>1482</v>
       </c>
       <c r="CN22">
-        <v>0.74018475750577373</v>
+        <v>0.74211316975463193</v>
       </c>
     </row>
     <row r="23" spans="1:92" x14ac:dyDescent="0.2">
@@ -7926,10 +7926,10 @@
         <v>54.2</v>
       </c>
       <c r="CM23">
-        <v>1527</v>
+        <v>641</v>
       </c>
       <c r="CN23">
-        <v>0.53176162409954153</v>
+        <v>0.74018475750577373</v>
       </c>
     </row>
     <row r="24" spans="1:92" x14ac:dyDescent="0.2">
@@ -8204,10 +8204,10 @@
         <v>61.9</v>
       </c>
       <c r="CM24">
-        <v>1483</v>
+        <v>812</v>
       </c>
       <c r="CN24">
-        <v>0.78624409979770737</v>
+        <v>0.53176162409954153</v>
       </c>
     </row>
     <row r="25" spans="1:92" x14ac:dyDescent="0.2">
@@ -8482,10 +8482,10 @@
         <v>70.3</v>
       </c>
       <c r="CM25">
-        <v>1420</v>
+        <v>1166</v>
       </c>
       <c r="CN25">
-        <v>0.78169014084507038</v>
+        <v>0.78624409979770737</v>
       </c>
     </row>
     <row r="26" spans="1:92" x14ac:dyDescent="0.2">
@@ -8760,10 +8760,10 @@
         <v>65.5</v>
       </c>
       <c r="CM26">
-        <v>5950</v>
+        <v>1110</v>
       </c>
       <c r="CN26">
-        <v>0.75344537815126056</v>
+        <v>0.78169014084507038</v>
       </c>
     </row>
     <row r="27" spans="1:92" x14ac:dyDescent="0.2">
@@ -9038,10 +9038,10 @@
         <v>66</v>
       </c>
       <c r="CM27">
-        <v>1076</v>
+        <v>4483</v>
       </c>
       <c r="CN27">
-        <v>0.79182156133828996</v>
+        <v>0.75344537815126056</v>
       </c>
     </row>
     <row r="28" spans="1:92" x14ac:dyDescent="0.2">
@@ -9316,10 +9316,10 @@
         <v>70.400000000000006</v>
       </c>
       <c r="CM28">
-        <v>1942</v>
+        <v>852</v>
       </c>
       <c r="CN28">
-        <v>0.7646755921730175</v>
+        <v>0.79182156133828996</v>
       </c>
     </row>
     <row r="29" spans="1:92" x14ac:dyDescent="0.2">
@@ -9594,10 +9594,10 @@
         <v>56.8</v>
       </c>
       <c r="CM29">
-        <v>402</v>
+        <v>1485</v>
       </c>
       <c r="CN29">
-        <v>0.70646766169154229</v>
+        <v>0.7646755921730175</v>
       </c>
     </row>
     <row r="30" spans="1:92" x14ac:dyDescent="0.2">
@@ -9872,10 +9872,10 @@
         <v>86.6</v>
       </c>
       <c r="CM30">
-        <v>1449</v>
+        <v>284</v>
       </c>
       <c r="CN30">
-        <v>0.77639751552795033</v>
+        <v>0.70646766169154229</v>
       </c>
     </row>
     <row r="31" spans="1:92" x14ac:dyDescent="0.2">
@@ -10150,10 +10150,10 @@
         <v>78.400000000000006</v>
       </c>
       <c r="CM31">
-        <v>890</v>
+        <v>1125</v>
       </c>
       <c r="CN31">
-        <v>0.77078651685393262</v>
+        <v>0.77639751552795033</v>
       </c>
     </row>
     <row r="32" spans="1:92" x14ac:dyDescent="0.2">
@@ -10428,10 +10428,10 @@
         <v>63.1</v>
       </c>
       <c r="CM32">
-        <v>2714</v>
+        <v>686</v>
       </c>
       <c r="CN32">
-        <v>0.79624170965364771</v>
+        <v>0.77078651685393262</v>
       </c>
     </row>
     <row r="33" spans="1:92" x14ac:dyDescent="0.2">
@@ -10706,10 +10706,10 @@
         <v>95.4</v>
       </c>
       <c r="CM33">
-        <v>585</v>
+        <v>2161</v>
       </c>
       <c r="CN33">
-        <v>0.74358974358974361</v>
+        <v>0.79624170965364771</v>
       </c>
     </row>
     <row r="34" spans="1:92" x14ac:dyDescent="0.2">
@@ -10984,10 +10984,10 @@
         <v>65.2</v>
       </c>
       <c r="CM34">
-        <v>2186</v>
+        <v>435</v>
       </c>
       <c r="CN34">
-        <v>0.86276303751143646</v>
+        <v>0.74358974358974361</v>
       </c>
     </row>
     <row r="35" spans="1:92" x14ac:dyDescent="0.2">
@@ -11262,10 +11262,10 @@
         <v>89.4</v>
       </c>
       <c r="CM35">
-        <v>1468</v>
+        <v>1886</v>
       </c>
       <c r="CN35">
-        <v>0.75544959128065392</v>
+        <v>0.86276303751143646</v>
       </c>
     </row>
     <row r="36" spans="1:92" x14ac:dyDescent="0.2">
@@ -11540,10 +11540,10 @@
         <v>83.4</v>
       </c>
       <c r="CM36">
-        <v>12824</v>
+        <v>1109</v>
       </c>
       <c r="CN36">
-        <v>0.8792108546475359</v>
+        <v>0.75544959128065392</v>
       </c>
     </row>
     <row r="37" spans="1:92" x14ac:dyDescent="0.2">
@@ -11818,10 +11818,10 @@
         <v>83</v>
       </c>
       <c r="CM37">
-        <v>1063</v>
+        <v>11275</v>
       </c>
       <c r="CN37">
-        <v>0.78833490122295391</v>
+        <v>0.8792108546475359</v>
       </c>
     </row>
     <row r="38" spans="1:92" x14ac:dyDescent="0.2">
@@ -12096,10 +12096,10 @@
         <v>64.099999999999994</v>
       </c>
       <c r="CM38">
-        <v>3116</v>
+        <v>838</v>
       </c>
       <c r="CN38">
-        <v>0.85654685494223359</v>
+        <v>0.78833490122295391</v>
       </c>
     </row>
     <row r="39" spans="1:92" x14ac:dyDescent="0.2">
@@ -12374,10 +12374,10 @@
         <v>71.400000000000006</v>
       </c>
       <c r="CM39">
-        <v>2605</v>
+        <v>2669</v>
       </c>
       <c r="CN39">
-        <v>0.83685220729366605</v>
+        <v>0.85654685494223359</v>
       </c>
     </row>
     <row r="40" spans="1:92" x14ac:dyDescent="0.2">
@@ -12652,10 +12652,10 @@
         <v>68.7</v>
       </c>
       <c r="CM40">
-        <v>2599</v>
+        <v>2180</v>
       </c>
       <c r="CN40">
-        <v>0.75836860330896494</v>
+        <v>0.83685220729366605</v>
       </c>
     </row>
     <row r="41" spans="1:92" x14ac:dyDescent="0.2">
@@ -12930,10 +12930,10 @@
         <v>96.6</v>
       </c>
       <c r="CM41">
-        <v>1435</v>
+        <v>1971</v>
       </c>
       <c r="CN41">
-        <v>0.83344947735191632</v>
+        <v>0.75836860330896494</v>
       </c>
     </row>
     <row r="42" spans="1:92" x14ac:dyDescent="0.2">
@@ -13208,10 +13208,10 @@
         <v>72.5</v>
       </c>
       <c r="CM42">
-        <v>1151</v>
+        <v>1196</v>
       </c>
       <c r="CN42">
-        <v>0.77584708948740222</v>
+        <v>0.83344947735191632</v>
       </c>
     </row>
     <row r="43" spans="1:92" x14ac:dyDescent="0.2">
@@ -13486,10 +13486,10 @@
         <v>74.099999999999994</v>
       </c>
       <c r="CM43">
-        <v>3745</v>
+        <v>893</v>
       </c>
       <c r="CN43">
-        <v>0.7965287049399199</v>
+        <v>0.77584708948740222</v>
       </c>
     </row>
     <row r="44" spans="1:92" x14ac:dyDescent="0.2">
@@ -13764,10 +13764,10 @@
         <v>60.9</v>
       </c>
       <c r="CM44">
-        <v>953</v>
+        <v>2983</v>
       </c>
       <c r="CN44">
-        <v>0.77334732423924446</v>
+        <v>0.7965287049399199</v>
       </c>
     </row>
     <row r="45" spans="1:92" x14ac:dyDescent="0.2">
@@ -14042,10 +14042,10 @@
         <v>69.7</v>
       </c>
       <c r="CM45">
-        <v>1104</v>
+        <v>737</v>
       </c>
       <c r="CN45">
-        <v>0.65489130434782605</v>
+        <v>0.77334732423924446</v>
       </c>
     </row>
     <row r="46" spans="1:92" x14ac:dyDescent="0.2">
@@ -14320,10 +14320,10 @@
         <v>44.4</v>
       </c>
       <c r="CM46">
-        <v>897</v>
+        <v>723</v>
       </c>
       <c r="CN46">
-        <v>0.75027870680044595</v>
+        <v>0.65489130434782605</v>
       </c>
     </row>
     <row r="47" spans="1:92" x14ac:dyDescent="0.2">
@@ -14598,10 +14598,10 @@
         <v>51.9</v>
       </c>
       <c r="CM47">
-        <v>6916</v>
+        <v>673</v>
       </c>
       <c r="CN47">
-        <v>0.86871023713128981</v>
+        <v>0.75027870680044595</v>
       </c>
     </row>
     <row r="48" spans="1:92" x14ac:dyDescent="0.2">
@@ -14876,10 +14876,10 @@
         <v>88</v>
       </c>
       <c r="CM48">
-        <v>1374</v>
+        <v>6008</v>
       </c>
       <c r="CN48">
-        <v>0.86171761280931591</v>
+        <v>0.86871023713128981</v>
       </c>
     </row>
     <row r="49" spans="1:92" x14ac:dyDescent="0.2">
@@ -15154,10 +15154,10 @@
         <v>69.900000000000006</v>
       </c>
       <c r="CM49">
-        <v>4617</v>
+        <v>1184</v>
       </c>
       <c r="CN49">
-        <v>0.80051981806367767</v>
+        <v>0.86171761280931591</v>
       </c>
     </row>
     <row r="50" spans="1:92" x14ac:dyDescent="0.2">
@@ -15432,10 +15432,10 @@
         <v>73.5</v>
       </c>
       <c r="CM50">
-        <v>131</v>
+        <v>3696</v>
       </c>
       <c r="CN50">
-        <v>0.74045801526717558</v>
+        <v>0.80051981806367767</v>
       </c>
     </row>
     <row r="51" spans="1:92" x14ac:dyDescent="0.2">
@@ -15710,10 +15710,10 @@
         <v>29.9</v>
       </c>
       <c r="CM51">
-        <v>954</v>
+        <v>97</v>
       </c>
       <c r="CN51">
-        <v>0.80922431865828093</v>
+        <v>0.74045801526717558</v>
       </c>
     </row>
     <row r="52" spans="1:92" x14ac:dyDescent="0.2">
@@ -15988,10 +15988,10 @@
         <v>83.9</v>
       </c>
       <c r="CM52">
-        <v>4162</v>
+        <v>772</v>
       </c>
       <c r="CN52">
-        <v>0.82316194137433929</v>
+        <v>0.80922431865828093</v>
       </c>
     </row>
     <row r="53" spans="1:92" x14ac:dyDescent="0.2">
@@ -16266,10 +16266,10 @@
         <v>63.9</v>
       </c>
       <c r="CM53">
-        <v>2337</v>
+        <v>3426</v>
       </c>
       <c r="CN53">
-        <v>0.7227214377406932</v>
+        <v>0.82316194137433929</v>
       </c>
     </row>
     <row r="54" spans="1:92" x14ac:dyDescent="0.2">
@@ -16544,10 +16544,10 @@
         <v>57.6</v>
       </c>
       <c r="CM54">
-        <v>4967</v>
+        <v>1689</v>
       </c>
       <c r="CN54">
-        <v>0.80893899738272601</v>
+        <v>0.7227214377406932</v>
       </c>
     </row>
     <row r="55" spans="1:92" x14ac:dyDescent="0.2">
@@ -16822,10 +16822,10 @@
         <v>75.7</v>
       </c>
       <c r="CM55">
-        <v>2771</v>
+        <v>4018</v>
       </c>
       <c r="CN55">
-        <v>0.80476362324070727</v>
+        <v>0.80893899738272601</v>
       </c>
     </row>
     <row r="56" spans="1:92" x14ac:dyDescent="0.2">
@@ -17100,10 +17100,10 @@
         <v>80.7</v>
       </c>
       <c r="CM56">
-        <v>6154</v>
+        <v>2230</v>
       </c>
       <c r="CN56">
-        <v>0.75885602859928503</v>
+        <v>0.80476362324070727</v>
       </c>
     </row>
     <row r="57" spans="1:92" x14ac:dyDescent="0.2">
@@ -17378,10 +17378,10 @@
         <v>66.900000000000006</v>
       </c>
       <c r="CM57">
-        <v>6479</v>
+        <v>4670</v>
       </c>
       <c r="CN57">
-        <v>0.77959561660750121</v>
+        <v>0.75885602859928503</v>
       </c>
     </row>
     <row r="58" spans="1:92" x14ac:dyDescent="0.2">
@@ -17656,10 +17656,10 @@
         <v>79.599999999999994</v>
       </c>
       <c r="CM58">
-        <v>8407</v>
+        <v>5051</v>
       </c>
       <c r="CN58">
-        <v>0.72451528488164629</v>
+        <v>0.77959561660750121</v>
       </c>
     </row>
     <row r="59" spans="1:92" x14ac:dyDescent="0.2">
@@ -17934,10 +17934,10 @@
         <v>62.6</v>
       </c>
       <c r="CM59">
-        <v>8575</v>
+        <v>6091</v>
       </c>
       <c r="CN59">
-        <v>0.88746355685131195</v>
+        <v>0.72451528488164629</v>
       </c>
     </row>
     <row r="60" spans="1:92" x14ac:dyDescent="0.2">
@@ -18212,10 +18212,10 @@
         <v>58.8</v>
       </c>
       <c r="CM60">
-        <v>364</v>
+        <v>7610</v>
       </c>
       <c r="CN60">
-        <v>0.63461538461538458</v>
+        <v>0.88746355685131195</v>
       </c>
     </row>
     <row r="61" spans="1:92" x14ac:dyDescent="0.2">
@@ -18490,10 +18490,10 @@
         <v>64.2</v>
       </c>
       <c r="CM61">
-        <v>1069</v>
+        <v>231</v>
       </c>
       <c r="CN61">
-        <v>0.70439663236669781</v>
+        <v>0.63461538461538458</v>
       </c>
     </row>
     <row r="62" spans="1:92" x14ac:dyDescent="0.2">
@@ -18768,10 +18768,10 @@
         <v>69</v>
       </c>
       <c r="CM62">
-        <v>10679</v>
+        <v>753</v>
       </c>
       <c r="CN62">
-        <v>0.85663451634048127</v>
+        <v>0.70439663236669781</v>
       </c>
     </row>
     <row r="63" spans="1:92" x14ac:dyDescent="0.2">
@@ -19046,10 +19046,10 @@
         <v>78.7</v>
       </c>
       <c r="CM63">
-        <v>2598</v>
+        <v>9148</v>
       </c>
       <c r="CN63">
-        <v>0.73672055427251737</v>
+        <v>0.85663451634048127</v>
       </c>
     </row>
     <row r="64" spans="1:92" x14ac:dyDescent="0.2">
@@ -19324,10 +19324,10 @@
         <v>73.8</v>
       </c>
       <c r="CM64">
-        <v>2459</v>
+        <v>1914</v>
       </c>
       <c r="CN64">
-        <v>0.84993899959333064</v>
+        <v>0.73672055427251737</v>
       </c>
     </row>
     <row r="65" spans="1:92" x14ac:dyDescent="0.2">
@@ -19602,10 +19602,10 @@
         <v>74.8</v>
       </c>
       <c r="CM65">
-        <v>2077</v>
+        <v>2090</v>
       </c>
       <c r="CN65">
-        <v>0.70582571015888296</v>
+        <v>0.84993899959333064</v>
       </c>
     </row>
     <row r="66" spans="1:92" x14ac:dyDescent="0.2">
@@ -19880,10 +19880,10 @@
         <v>73</v>
       </c>
       <c r="CM66">
-        <v>238</v>
+        <v>1466</v>
       </c>
       <c r="CN66">
-        <v>0.75630252100840334</v>
+        <v>0.70582571015888296</v>
       </c>
     </row>
     <row r="67" spans="1:92" x14ac:dyDescent="0.2">
@@ -20158,10 +20158,10 @@
         <v>55.6</v>
       </c>
       <c r="CM67">
-        <v>6369</v>
+        <v>180</v>
       </c>
       <c r="CN67">
-        <v>0.81362851311037843</v>
+        <v>0.75630252100840334</v>
       </c>
     </row>
     <row r="68" spans="1:92" x14ac:dyDescent="0.2">
@@ -20436,10 +20436,10 @@
         <v>63</v>
       </c>
       <c r="CM68">
-        <v>1810</v>
+        <v>5182</v>
       </c>
       <c r="CN68">
-        <v>0.69171270718232047</v>
+        <v>0.81362851311037843</v>
       </c>
     </row>
     <row r="69" spans="1:92" x14ac:dyDescent="0.2">
@@ -20714,10 +20714,10 @@
         <v>70.400000000000006</v>
       </c>
       <c r="CM69">
-        <v>2057</v>
+        <v>1252</v>
       </c>
       <c r="CN69">
-        <v>0.87506076810889644</v>
+        <v>0.69171270718232047</v>
       </c>
     </row>
     <row r="70" spans="1:92" x14ac:dyDescent="0.2">
@@ -20992,10 +20992,10 @@
         <v>94.8</v>
       </c>
       <c r="CM70">
-        <v>23097</v>
+        <v>1800</v>
       </c>
       <c r="CN70">
-        <v>0.78707191410139843</v>
+        <v>0.87506076810889644</v>
       </c>
     </row>
     <row r="71" spans="1:92" x14ac:dyDescent="0.2">
@@ -21270,10 +21270,10 @@
         <v>68.3</v>
       </c>
       <c r="CM71">
-        <v>1036</v>
+        <v>18179</v>
       </c>
       <c r="CN71">
-        <v>0.76930501930501927</v>
+        <v>0.78707191410139843</v>
       </c>
     </row>
     <row r="72" spans="1:92" x14ac:dyDescent="0.2">
@@ -21548,10 +21548,10 @@
         <v>83.4</v>
       </c>
       <c r="CM72">
-        <v>632</v>
+        <v>797</v>
       </c>
       <c r="CN72">
-        <v>0.48101265822784811</v>
+        <v>0.76930501930501927</v>
       </c>
     </row>
     <row r="73" spans="1:92" x14ac:dyDescent="0.2">
@@ -21826,10 +21826,10 @@
         <v>63.6</v>
       </c>
       <c r="CM73">
-        <v>1402</v>
+        <v>304</v>
       </c>
       <c r="CN73">
-        <v>0.7168330955777461</v>
+        <v>0.48101265822784811</v>
       </c>
     </row>
     <row r="74" spans="1:92" x14ac:dyDescent="0.2">
@@ -22104,10 +22104,10 @@
         <v>74.599999999999994</v>
       </c>
       <c r="CM74">
-        <v>21317</v>
+        <v>1005</v>
       </c>
       <c r="CN74">
-        <v>0.88534972088004882</v>
+        <v>0.7168330955777461</v>
       </c>
     </row>
     <row r="75" spans="1:92" x14ac:dyDescent="0.2">
@@ -22382,10 +22382,10 @@
         <v>74.8</v>
       </c>
       <c r="CM75">
-        <v>4156</v>
+        <v>18873</v>
       </c>
       <c r="CN75">
-        <v>0.6179018286814244</v>
+        <v>0.88534972088004882</v>
       </c>
     </row>
     <row r="76" spans="1:92" x14ac:dyDescent="0.2">
@@ -22660,10 +22660,10 @@
         <v>59.3</v>
       </c>
       <c r="CM76">
-        <v>1257</v>
+        <v>2568</v>
       </c>
       <c r="CN76">
-        <v>0.82895783611774065</v>
+        <v>0.6179018286814244</v>
       </c>
     </row>
     <row r="77" spans="1:92" x14ac:dyDescent="0.2">
@@ -22938,10 +22938,10 @@
         <v>64</v>
       </c>
       <c r="CM77">
-        <v>10515</v>
+        <v>1042</v>
       </c>
       <c r="CN77">
-        <v>0.78925344745601522</v>
+        <v>0.82895783611774065</v>
       </c>
     </row>
     <row r="78" spans="1:92" x14ac:dyDescent="0.2">
@@ -23216,10 +23216,10 @@
         <v>72.8</v>
       </c>
       <c r="CM78">
-        <v>2050</v>
+        <v>8299</v>
       </c>
       <c r="CN78">
-        <v>0.79268292682926833</v>
+        <v>0.78925344745601522</v>
       </c>
     </row>
     <row r="79" spans="1:92" x14ac:dyDescent="0.2">
@@ -23494,10 +23494,10 @@
         <v>69.7</v>
       </c>
       <c r="CM79">
-        <v>653</v>
+        <v>1625</v>
       </c>
       <c r="CN79">
-        <v>0.72128637059724354</v>
+        <v>0.79268292682926833</v>
       </c>
     </row>
     <row r="80" spans="1:92" x14ac:dyDescent="0.2">
@@ -23772,10 +23772,10 @@
         <v>44.7</v>
       </c>
       <c r="CM80">
-        <v>5594</v>
+        <v>471</v>
       </c>
       <c r="CN80">
-        <v>0.78852341794780123</v>
+        <v>0.72128637059724354</v>
       </c>
     </row>
     <row r="81" spans="1:92" x14ac:dyDescent="0.2">
@@ -24050,10 +24050,10 @@
         <v>69.400000000000006</v>
       </c>
       <c r="CM81">
-        <v>3287</v>
+        <v>4411</v>
       </c>
       <c r="CN81">
-        <v>0.8119866139336781</v>
+        <v>0.78852341794780123</v>
       </c>
     </row>
     <row r="82" spans="1:92" x14ac:dyDescent="0.2">
@@ -24328,10 +24328,10 @@
         <v>69</v>
       </c>
       <c r="CM82">
-        <v>4853</v>
+        <v>2669</v>
       </c>
       <c r="CN82">
-        <v>0.7739542550999382</v>
+        <v>0.8119866139336781</v>
       </c>
     </row>
     <row r="83" spans="1:92" x14ac:dyDescent="0.2">
@@ -24606,10 +24606,10 @@
         <v>52.2</v>
       </c>
       <c r="CM83">
-        <v>6008</v>
+        <v>3756</v>
       </c>
       <c r="CN83">
-        <v>0.82123834886817582</v>
+        <v>0.7739542550999382</v>
       </c>
     </row>
     <row r="84" spans="1:92" x14ac:dyDescent="0.2">
@@ -24884,10 +24884,10 @@
         <v>79.099999999999994</v>
       </c>
       <c r="CM84">
-        <v>129816</v>
+        <v>4934</v>
       </c>
       <c r="CN84">
-        <v>0.82244099340605159</v>
+        <v>0.82123834886817582</v>
       </c>
     </row>
     <row r="85" spans="1:92" x14ac:dyDescent="0.2">
@@ -25162,10 +25162,10 @@
         <v>67.7</v>
       </c>
       <c r="CM85">
-        <v>1025</v>
+        <v>106766</v>
       </c>
       <c r="CN85">
-        <v>0.75219512195121951</v>
+        <v>0.82244099340605159</v>
       </c>
     </row>
     <row r="86" spans="1:92" x14ac:dyDescent="0.2">
@@ -25440,10 +25440,10 @@
         <v>78.400000000000006</v>
       </c>
       <c r="CM86">
-        <v>4886</v>
+        <v>771</v>
       </c>
       <c r="CN86">
-        <v>0.77261563651248466</v>
+        <v>0.75219512195121951</v>
       </c>
     </row>
     <row r="87" spans="1:92" x14ac:dyDescent="0.2">
@@ -25718,10 +25718,10 @@
         <v>72.599999999999994</v>
       </c>
       <c r="CM87">
-        <v>1251</v>
+        <v>3775</v>
       </c>
       <c r="CN87">
-        <v>0.8840927258193445</v>
+        <v>0.77261563651248466</v>
       </c>
     </row>
     <row r="88" spans="1:92" x14ac:dyDescent="0.2">
@@ -25996,10 +25996,10 @@
         <v>93.4</v>
       </c>
       <c r="CM88">
-        <v>4985</v>
+        <v>1106</v>
       </c>
       <c r="CN88">
-        <v>0.86359077231695081</v>
+        <v>0.8840927258193445</v>
       </c>
     </row>
     <row r="89" spans="1:92" x14ac:dyDescent="0.2">
@@ -26274,10 +26274,10 @@
         <v>81.7</v>
       </c>
       <c r="CM89">
-        <v>1390</v>
+        <v>4305</v>
       </c>
       <c r="CN89">
-        <v>0.8</v>
+        <v>0.86359077231695081</v>
       </c>
     </row>
     <row r="90" spans="1:92" x14ac:dyDescent="0.2">
@@ -26552,10 +26552,10 @@
         <v>80.099999999999994</v>
       </c>
       <c r="CM90">
-        <v>823</v>
+        <v>1112</v>
       </c>
       <c r="CN90">
-        <v>0.69137302551640345</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="91" spans="1:92" x14ac:dyDescent="0.2">
@@ -26830,10 +26830,10 @@
         <v>64.2</v>
       </c>
       <c r="CM91">
-        <v>1227</v>
+        <v>569</v>
       </c>
       <c r="CN91">
-        <v>0.81581092094539531</v>
+        <v>0.69137302551640345</v>
       </c>
     </row>
     <row r="92" spans="1:92" x14ac:dyDescent="0.2">
@@ -27108,10 +27108,10 @@
         <v>66.7</v>
       </c>
       <c r="CM92">
-        <v>603</v>
+        <v>1001</v>
       </c>
       <c r="CN92">
-        <v>0.71641791044776115</v>
+        <v>0.81581092094539531</v>
       </c>
     </row>
     <row r="93" spans="1:92" x14ac:dyDescent="0.2">
@@ -27386,10 +27386,10 @@
         <v>83.1</v>
       </c>
       <c r="CM93">
-        <v>1939</v>
+        <v>432</v>
       </c>
       <c r="CN93">
-        <v>0.81536874677668902</v>
+        <v>0.71641791044776115</v>
       </c>
     </row>
     <row r="94" spans="1:92" x14ac:dyDescent="0.2">
@@ -27664,10 +27664,10 @@
         <v>78.599999999999994</v>
       </c>
       <c r="CM94">
-        <v>1818</v>
+        <v>1581</v>
       </c>
       <c r="CN94">
-        <v>0.74697469746974698</v>
+        <v>0.81536874677668902</v>
       </c>
     </row>
     <row r="95" spans="1:92" x14ac:dyDescent="0.2">
@@ -27942,10 +27942,10 @@
         <v>72.2</v>
       </c>
       <c r="CM95">
-        <v>969</v>
+        <v>1358</v>
       </c>
       <c r="CN95">
-        <v>0.72445820433436536</v>
+        <v>0.74697469746974698</v>
       </c>
     </row>
     <row r="96" spans="1:92" x14ac:dyDescent="0.2">
@@ -28220,10 +28220,10 @@
         <v>68.400000000000006</v>
       </c>
       <c r="CM96">
-        <v>52893</v>
+        <v>702</v>
       </c>
       <c r="CN96">
-        <v>0.82755752178927267</v>
+        <v>0.72445820433436536</v>
       </c>
     </row>
     <row r="97" spans="1:92" x14ac:dyDescent="0.2">
@@ -28498,10 +28498,10 @@
         <v>58.8</v>
       </c>
       <c r="CM97">
-        <v>1374</v>
+        <v>43772</v>
       </c>
       <c r="CN97">
-        <v>0.86171761280931591</v>
+        <v>0.82755752178927267</v>
       </c>
     </row>
     <row r="98" spans="1:92" x14ac:dyDescent="0.2">
@@ -28776,10 +28776,10 @@
         <v>67.599999999999994</v>
       </c>
       <c r="CM98">
-        <v>5983</v>
+        <v>1184</v>
       </c>
       <c r="CN98">
-        <v>0.86010362694300513</v>
+        <v>0.86171761280931591</v>
       </c>
     </row>
     <row r="99" spans="1:92" x14ac:dyDescent="0.2">
@@ -29054,10 +29054,10 @@
         <v>80.599999999999994</v>
       </c>
       <c r="CM99">
-        <v>2856</v>
+        <v>5146</v>
       </c>
       <c r="CN99">
-        <v>0.85784313725490191</v>
+        <v>0.86010362694300513</v>
       </c>
     </row>
     <row r="100" spans="1:92" x14ac:dyDescent="0.2">
@@ -29332,10 +29332,10 @@
         <v>78.400000000000006</v>
       </c>
       <c r="CM100">
-        <v>3390</v>
+        <v>2450</v>
       </c>
       <c r="CN100">
-        <v>0.74631268436578169</v>
+        <v>0.85784313725490191</v>
       </c>
     </row>
     <row r="101" spans="1:92" x14ac:dyDescent="0.2">
@@ -29610,10 +29610,10 @@
         <v>67.599999999999994</v>
       </c>
       <c r="CM101">
-        <v>1522</v>
+        <v>2530</v>
       </c>
       <c r="CN101">
-        <v>0.85676741130091982</v>
+        <v>0.74631268436578169</v>
       </c>
     </row>
     <row r="102" spans="1:92" x14ac:dyDescent="0.2">
@@ -29888,10 +29888,10 @@
         <v>68.5</v>
       </c>
       <c r="CM102">
-        <v>2427</v>
+        <v>1304</v>
       </c>
       <c r="CN102">
-        <v>0.87474248042851255</v>
+        <v>0.85676741130091982</v>
       </c>
     </row>
     <row r="103" spans="1:92" x14ac:dyDescent="0.2">
@@ -30166,10 +30166,10 @@
         <v>76.2</v>
       </c>
       <c r="CM103">
-        <v>2026</v>
+        <v>2123</v>
       </c>
       <c r="CN103">
-        <v>0.79615004935834155</v>
+        <v>0.87474248042851255</v>
       </c>
     </row>
     <row r="104" spans="1:92" x14ac:dyDescent="0.2">
@@ -30444,10 +30444,10 @@
         <v>74.099999999999994</v>
       </c>
       <c r="CM104">
-        <v>1199</v>
+        <v>1613</v>
       </c>
       <c r="CN104">
-        <v>0.76146788990825687</v>
+        <v>0.79615004935834155</v>
       </c>
     </row>
     <row r="105" spans="1:92" x14ac:dyDescent="0.2">
@@ -30722,10 +30722,10 @@
         <v>74.8</v>
       </c>
       <c r="CM105">
-        <v>1156</v>
+        <v>913</v>
       </c>
       <c r="CN105">
-        <v>0.74134948096885811</v>
+        <v>0.76146788990825687</v>
       </c>
     </row>
     <row r="106" spans="1:92" x14ac:dyDescent="0.2">
@@ -31000,10 +31000,10 @@
         <v>69.2</v>
       </c>
       <c r="CM106">
-        <v>1715</v>
+        <v>857</v>
       </c>
       <c r="CN106">
-        <v>0.76793002915451891</v>
+        <v>0.74134948096885811</v>
       </c>
     </row>
     <row r="107" spans="1:92" x14ac:dyDescent="0.2">
@@ -31278,10 +31278,10 @@
         <v>80.599999999999994</v>
       </c>
       <c r="CM107">
-        <v>1403</v>
+        <v>1317</v>
       </c>
       <c r="CN107">
-        <v>0.73342836778332143</v>
+        <v>0.76793002915451891</v>
       </c>
     </row>
     <row r="108" spans="1:92" x14ac:dyDescent="0.2">
@@ -31556,10 +31556,10 @@
         <v>77.400000000000006</v>
       </c>
       <c r="CM108">
-        <v>1821</v>
+        <v>1029</v>
       </c>
       <c r="CN108">
-        <v>0.80230642504118621</v>
+        <v>0.73342836778332143</v>
       </c>
     </row>
     <row r="109" spans="1:92" x14ac:dyDescent="0.2">
@@ -31834,10 +31834,10 @@
         <v>89.3</v>
       </c>
       <c r="CM109">
-        <v>3376</v>
+        <v>1461</v>
       </c>
       <c r="CN109">
-        <v>0.60545023696682465</v>
+        <v>0.80230642504118621</v>
       </c>
     </row>
     <row r="110" spans="1:92" x14ac:dyDescent="0.2">
@@ -32112,10 +32112,10 @@
         <v>66.099999999999994</v>
       </c>
       <c r="CM110">
-        <v>1671</v>
+        <v>2044</v>
       </c>
       <c r="CN110">
-        <v>0.78096947935368044</v>
+        <v>0.60545023696682465</v>
       </c>
     </row>
     <row r="111" spans="1:92" x14ac:dyDescent="0.2">
@@ -32390,10 +32390,10 @@
         <v>84.6</v>
       </c>
       <c r="CM111">
-        <v>7899</v>
+        <v>1305</v>
       </c>
       <c r="CN111">
-        <v>0.85770350677300922</v>
+        <v>0.78096947935368044</v>
       </c>
     </row>
     <row r="112" spans="1:92" x14ac:dyDescent="0.2">
@@ -32668,10 +32668,10 @@
         <v>70.599999999999994</v>
       </c>
       <c r="CM112">
-        <v>1301</v>
+        <v>6775</v>
       </c>
       <c r="CN112">
-        <v>0.84780937740199847</v>
+        <v>0.85770350677300922</v>
       </c>
     </row>
     <row r="113" spans="1:92" x14ac:dyDescent="0.2">
@@ -32946,10 +32946,10 @@
         <v>71.099999999999994</v>
       </c>
       <c r="CM113">
-        <v>1661</v>
+        <v>1103</v>
       </c>
       <c r="CN113">
-        <v>0.8892233594220349</v>
+        <v>0.84780937740199847</v>
       </c>
     </row>
     <row r="114" spans="1:92" x14ac:dyDescent="0.2">
@@ -33224,10 +33224,10 @@
         <v>86.6</v>
       </c>
       <c r="CM114">
-        <v>965</v>
+        <v>1477</v>
       </c>
       <c r="CN114">
-        <v>0.81554404145077719</v>
+        <v>0.8892233594220349</v>
       </c>
     </row>
     <row r="115" spans="1:92" x14ac:dyDescent="0.2">
@@ -33502,10 +33502,10 @@
         <v>68</v>
       </c>
       <c r="CM115">
-        <v>13409</v>
+        <v>787</v>
       </c>
       <c r="CN115">
-        <v>0.83182936833470056</v>
+        <v>0.81554404145077719</v>
       </c>
     </row>
     <row r="116" spans="1:92" x14ac:dyDescent="0.2">
@@ -33780,10 +33780,10 @@
         <v>75.2</v>
       </c>
       <c r="CM116">
-        <v>14041</v>
+        <v>11154</v>
       </c>
       <c r="CN116">
-        <v>0.8449540631009187</v>
+        <v>0.83182936833470056</v>
       </c>
     </row>
     <row r="117" spans="1:92" x14ac:dyDescent="0.2">
@@ -34058,10 +34058,10 @@
         <v>76.900000000000006</v>
       </c>
       <c r="CM117">
-        <v>510</v>
+        <v>11864</v>
       </c>
       <c r="CN117">
-        <v>0.86862745098039218</v>
+        <v>0.8449540631009187</v>
       </c>
     </row>
     <row r="118" spans="1:92" x14ac:dyDescent="0.2">
@@ -34336,10 +34336,10 @@
         <v>69.599999999999994</v>
       </c>
       <c r="CM118">
-        <v>1482</v>
+        <v>443</v>
       </c>
       <c r="CN118">
-        <v>0.82253711201079627</v>
+        <v>0.86862745098039218</v>
       </c>
     </row>
     <row r="119" spans="1:92" x14ac:dyDescent="0.2">
@@ -34614,10 +34614,10 @@
         <v>75.400000000000006</v>
       </c>
       <c r="CM119">
-        <v>5203</v>
+        <v>1219</v>
       </c>
       <c r="CN119">
-        <v>0.76551989236978668</v>
+        <v>0.82253711201079627</v>
       </c>
     </row>
     <row r="120" spans="1:92" x14ac:dyDescent="0.2">
@@ -34892,10 +34892,10 @@
         <v>71.3</v>
       </c>
       <c r="CM120">
-        <v>238</v>
+        <v>3983</v>
       </c>
       <c r="CN120">
-        <v>0.55882352941176472</v>
+        <v>0.76551989236978668</v>
       </c>
     </row>
     <row r="121" spans="1:92" x14ac:dyDescent="0.2">
@@ -35170,10 +35170,10 @@
         <v>33.200000000000003</v>
       </c>
       <c r="CM121">
-        <v>2912</v>
+        <v>133</v>
       </c>
       <c r="CN121">
-        <v>0.77026098901098905</v>
+        <v>0.55882352941176472</v>
       </c>
     </row>
     <row r="122" spans="1:92" x14ac:dyDescent="0.2">
@@ -35448,10 +35448,10 @@
         <v>63.8</v>
       </c>
       <c r="CM122">
-        <v>10493</v>
+        <v>2243</v>
       </c>
       <c r="CN122">
-        <v>0.64366720670923472</v>
+        <v>0.77026098901098905</v>
       </c>
     </row>
     <row r="123" spans="1:92" x14ac:dyDescent="0.2">
@@ -35726,10 +35726,10 @@
         <v>53.3</v>
       </c>
       <c r="CM123">
-        <v>2666</v>
+        <v>6754</v>
       </c>
       <c r="CN123">
-        <v>0.76106526631657911</v>
+        <v>0.64366720670923472</v>
       </c>
     </row>
     <row r="124" spans="1:92" x14ac:dyDescent="0.2">
@@ -36004,10 +36004,10 @@
         <v>77.099999999999994</v>
       </c>
       <c r="CM124">
-        <v>1992</v>
+        <v>2029</v>
       </c>
       <c r="CN124">
-        <v>0.57530120481927716</v>
+        <v>0.76106526631657911</v>
       </c>
     </row>
     <row r="125" spans="1:92" x14ac:dyDescent="0.2">
@@ -36282,10 +36282,10 @@
         <v>63.9</v>
       </c>
       <c r="CM125">
-        <v>1087</v>
+        <v>1146</v>
       </c>
       <c r="CN125">
-        <v>0.60533578656853726</v>
+        <v>0.57530120481927716</v>
       </c>
     </row>
     <row r="126" spans="1:92" x14ac:dyDescent="0.2">
@@ -36560,10 +36560,10 @@
         <v>54.2</v>
       </c>
       <c r="CM126">
-        <v>1034</v>
+        <v>658</v>
       </c>
       <c r="CN126">
-        <v>0.78046421663442944</v>
+        <v>0.60533578656853726</v>
       </c>
     </row>
     <row r="127" spans="1:92" x14ac:dyDescent="0.2">
@@ -36838,10 +36838,10 @@
         <v>69.400000000000006</v>
       </c>
       <c r="CM127">
-        <v>1823</v>
+        <v>807</v>
       </c>
       <c r="CN127">
-        <v>0.79978058145913333</v>
+        <v>0.78046421663442944</v>
       </c>
     </row>
     <row r="128" spans="1:92" x14ac:dyDescent="0.2">
@@ -37116,10 +37116,10 @@
         <v>69.2</v>
       </c>
       <c r="CM128">
-        <v>2349</v>
+        <v>1458</v>
       </c>
       <c r="CN128">
-        <v>0.84716900808854834</v>
+        <v>0.79978058145913333</v>
       </c>
     </row>
     <row r="129" spans="1:92" x14ac:dyDescent="0.2">
@@ -37394,10 +37394,10 @@
         <v>88.4</v>
       </c>
       <c r="CM129">
-        <v>6717</v>
+        <v>1990</v>
       </c>
       <c r="CN129">
-        <v>0.82879261575107932</v>
+        <v>0.84716900808854834</v>
       </c>
     </row>
     <row r="130" spans="1:92" x14ac:dyDescent="0.2">
@@ -37672,10 +37672,10 @@
         <v>67</v>
       </c>
       <c r="CM130">
-        <v>2070</v>
+        <v>5567</v>
       </c>
       <c r="CN130">
-        <v>0.82270531400966185</v>
+        <v>0.82879261575107932</v>
       </c>
     </row>
     <row r="131" spans="1:92" x14ac:dyDescent="0.2">
@@ -37950,10 +37950,10 @@
         <v>72.900000000000006</v>
       </c>
       <c r="CM131">
-        <v>1381</v>
+        <v>1703</v>
       </c>
       <c r="CN131">
-        <v>0.80448950036205646</v>
+        <v>0.82270531400966185</v>
       </c>
     </row>
     <row r="132" spans="1:92" x14ac:dyDescent="0.2">
@@ -38228,10 +38228,10 @@
         <v>88.5</v>
       </c>
       <c r="CM132">
-        <v>2568</v>
+        <v>1111</v>
       </c>
       <c r="CN132">
-        <v>0.84852024922118385</v>
+        <v>0.80448950036205646</v>
       </c>
     </row>
     <row r="133" spans="1:92" x14ac:dyDescent="0.2">
@@ -38506,10 +38506,10 @@
         <v>74.7</v>
       </c>
       <c r="CM133">
-        <v>10107</v>
+        <v>2179</v>
       </c>
       <c r="CN133">
-        <v>0.82111407935094494</v>
+        <v>0.84852024922118385</v>
       </c>
     </row>
     <row r="134" spans="1:92" x14ac:dyDescent="0.2">
@@ -38784,10 +38784,10 @@
         <v>65.8</v>
       </c>
       <c r="CM134">
-        <v>2488</v>
+        <v>8299</v>
       </c>
       <c r="CN134">
-        <v>0.75281350482315113</v>
+        <v>0.82111407935094494</v>
       </c>
     </row>
     <row r="135" spans="1:92" x14ac:dyDescent="0.2">
@@ -39062,10 +39062,10 @@
         <v>61.6</v>
       </c>
       <c r="CM135">
-        <v>3053</v>
+        <v>1873</v>
       </c>
       <c r="CN135">
-        <v>0.83164100884376024</v>
+        <v>0.75281350482315113</v>
       </c>
     </row>
     <row r="136" spans="1:92" x14ac:dyDescent="0.2">
@@ -39340,10 +39340,10 @@
         <v>75.8</v>
       </c>
       <c r="CM136">
-        <v>1878</v>
+        <v>2539</v>
       </c>
       <c r="CN136">
-        <v>0.78700745473908418</v>
+        <v>0.83164100884376024</v>
       </c>
     </row>
     <row r="137" spans="1:92" x14ac:dyDescent="0.2">
@@ -39618,10 +39618,10 @@
         <v>72.3</v>
       </c>
       <c r="CM137">
-        <v>2217</v>
+        <v>1478</v>
       </c>
       <c r="CN137">
-        <v>0.79070816418583667</v>
+        <v>0.78700745473908418</v>
       </c>
     </row>
     <row r="138" spans="1:92" x14ac:dyDescent="0.2">
@@ -39896,10 +39896,10 @@
         <v>64.599999999999994</v>
       </c>
       <c r="CM138">
-        <v>2266</v>
+        <v>1753</v>
       </c>
       <c r="CN138">
-        <v>0.83406884377758161</v>
+        <v>0.79070816418583667</v>
       </c>
     </row>
     <row r="139" spans="1:92" x14ac:dyDescent="0.2">
@@ -40174,10 +40174,10 @@
         <v>76.900000000000006</v>
       </c>
       <c r="CM139">
-        <v>7439</v>
+        <v>1890</v>
       </c>
       <c r="CN139">
-        <v>0.85334050275574669</v>
+        <v>0.83406884377758161</v>
       </c>
     </row>
     <row r="140" spans="1:92" x14ac:dyDescent="0.2">
@@ -40452,10 +40452,10 @@
         <v>75</v>
       </c>
       <c r="CM140">
-        <v>4651</v>
+        <v>6348</v>
       </c>
       <c r="CN140">
-        <v>0.89120619221672759</v>
+        <v>0.85334050275574669</v>
       </c>
     </row>
     <row r="141" spans="1:92" x14ac:dyDescent="0.2">
@@ -40730,10 +40730,10 @@
         <v>76.099999999999994</v>
       </c>
       <c r="CM141">
-        <v>476</v>
+        <v>4145</v>
       </c>
       <c r="CN141">
-        <v>0.8214285714285714</v>
+        <v>0.89120619221672759</v>
       </c>
     </row>
     <row r="142" spans="1:92" x14ac:dyDescent="0.2">
@@ -41008,10 +41008,10 @@
         <v>63</v>
       </c>
       <c r="CM142">
-        <v>831</v>
+        <v>391</v>
       </c>
       <c r="CN142">
-        <v>0.8038507821901324</v>
+        <v>0.8214285714285714</v>
       </c>
     </row>
     <row r="143" spans="1:92" x14ac:dyDescent="0.2">
@@ -41286,10 +41286,10 @@
         <v>71.400000000000006</v>
       </c>
       <c r="CM143">
-        <v>1596</v>
+        <v>668</v>
       </c>
       <c r="CN143">
-        <v>0.83583959899749372</v>
+        <v>0.8038507821901324</v>
       </c>
     </row>
     <row r="144" spans="1:92" x14ac:dyDescent="0.2">
@@ -41564,10 +41564,10 @@
         <v>75.099999999999994</v>
       </c>
       <c r="CM144">
-        <v>3418</v>
+        <v>1334</v>
       </c>
       <c r="CN144">
-        <v>0.82533645406670564</v>
+        <v>0.83583959899749372</v>
       </c>
     </row>
     <row r="145" spans="1:92" x14ac:dyDescent="0.2">
@@ -41842,10 +41842,10 @@
         <v>69</v>
       </c>
       <c r="CM145">
-        <v>554</v>
+        <v>2821</v>
       </c>
       <c r="CN145">
-        <v>0.68231046931407946</v>
+        <v>0.82533645406670564</v>
       </c>
     </row>
     <row r="146" spans="1:92" x14ac:dyDescent="0.2">
@@ -42120,10 +42120,10 @@
         <v>78.900000000000006</v>
       </c>
       <c r="CM146">
-        <v>4377</v>
+        <v>378</v>
       </c>
       <c r="CN146">
-        <v>0.78958190541466755</v>
+        <v>0.68231046931407946</v>
       </c>
     </row>
     <row r="147" spans="1:92" x14ac:dyDescent="0.2">
@@ -42398,10 +42398,10 @@
         <v>75.3</v>
       </c>
       <c r="CM147">
-        <v>1198</v>
+        <v>3456</v>
       </c>
       <c r="CN147">
-        <v>0.77796327212020033</v>
+        <v>0.78958190541466755</v>
       </c>
     </row>
     <row r="148" spans="1:92" x14ac:dyDescent="0.2">
@@ -42676,10 +42676,10 @@
         <v>50.5</v>
       </c>
       <c r="CM148">
-        <v>1127</v>
+        <v>932</v>
       </c>
       <c r="CN148">
-        <v>0.82076308784383323</v>
+        <v>0.77796327212020033</v>
       </c>
     </row>
     <row r="149" spans="1:92" x14ac:dyDescent="0.2">
@@ -42954,10 +42954,10 @@
         <v>62.9</v>
       </c>
       <c r="CM149">
-        <v>3174</v>
+        <v>925</v>
       </c>
       <c r="CN149">
-        <v>0.8412098298676749</v>
+        <v>0.82076308784383323</v>
       </c>
     </row>
     <row r="150" spans="1:92" x14ac:dyDescent="0.2">
@@ -43232,10 +43232,10 @@
         <v>71.3</v>
       </c>
       <c r="CM150">
-        <v>1706</v>
+        <v>2670</v>
       </c>
       <c r="CN150">
-        <v>0.83001172332942552</v>
+        <v>0.8412098298676749</v>
       </c>
     </row>
     <row r="151" spans="1:92" x14ac:dyDescent="0.2">
@@ -43510,10 +43510,10 @@
         <v>68.3</v>
       </c>
       <c r="CM151">
-        <v>1796</v>
+        <v>1416</v>
       </c>
       <c r="CN151">
-        <v>0.7048997772828508</v>
+        <v>0.83001172332942552</v>
       </c>
     </row>
     <row r="152" spans="1:92" x14ac:dyDescent="0.2">
@@ -43788,10 +43788,10 @@
         <v>63.3</v>
       </c>
       <c r="CM152">
-        <v>7348</v>
+        <v>1266</v>
       </c>
       <c r="CN152">
-        <v>0.76769188894937401</v>
+        <v>0.7048997772828508</v>
       </c>
     </row>
     <row r="153" spans="1:92" x14ac:dyDescent="0.2">
@@ -44066,10 +44066,10 @@
         <v>70.2</v>
       </c>
       <c r="CM153">
-        <v>5943</v>
+        <v>5641</v>
       </c>
       <c r="CN153">
-        <v>0.79538953390543499</v>
+        <v>0.76769188894937401</v>
       </c>
     </row>
     <row r="154" spans="1:92" x14ac:dyDescent="0.2">
@@ -44344,10 +44344,10 @@
         <v>64.3</v>
       </c>
       <c r="CM154">
-        <v>6176</v>
+        <v>4727</v>
       </c>
       <c r="CN154">
-        <v>0.852979274611399</v>
+        <v>0.79538953390543499</v>
       </c>
     </row>
     <row r="155" spans="1:92" x14ac:dyDescent="0.2">
@@ -44622,10 +44622,10 @@
         <v>80.599999999999994</v>
       </c>
       <c r="CM155">
-        <v>10252</v>
+        <v>5268</v>
       </c>
       <c r="CN155">
-        <v>0.82588763168162305</v>
+        <v>0.852979274611399</v>
       </c>
     </row>
     <row r="156" spans="1:92" x14ac:dyDescent="0.2">
@@ -44900,10 +44900,10 @@
         <v>75.7</v>
       </c>
       <c r="CM156">
-        <v>5708</v>
+        <v>8467</v>
       </c>
       <c r="CN156">
-        <v>0.83759635599159077</v>
+        <v>0.82588763168162305</v>
       </c>
     </row>
     <row r="157" spans="1:92" x14ac:dyDescent="0.2">
@@ -45178,10 +45178,10 @@
         <v>76.7</v>
       </c>
       <c r="CM157">
-        <v>914</v>
+        <v>4781</v>
       </c>
       <c r="CN157">
-        <v>0.7286652078774617</v>
+        <v>0.83759635599159077</v>
       </c>
     </row>
     <row r="158" spans="1:92" x14ac:dyDescent="0.2">
@@ -45456,10 +45456,10 @@
         <v>83.2</v>
       </c>
       <c r="CM158">
-        <v>248</v>
+        <v>666</v>
       </c>
       <c r="CN158">
-        <v>0.63709677419354838</v>
+        <v>0.7286652078774617</v>
       </c>
     </row>
     <row r="159" spans="1:92" x14ac:dyDescent="0.2">
@@ -45734,10 +45734,10 @@
         <v>81.7</v>
       </c>
       <c r="CM159">
-        <v>801</v>
+        <v>158</v>
       </c>
       <c r="CN159">
-        <v>0.80149812734082393</v>
+        <v>0.63709677419354838</v>
       </c>
     </row>
     <row r="160" spans="1:92" x14ac:dyDescent="0.2">
@@ -46012,10 +46012,10 @@
         <v>61</v>
       </c>
       <c r="CM160">
-        <v>1499</v>
+        <v>642</v>
       </c>
       <c r="CN160">
-        <v>0.83455637091394264</v>
+        <v>0.80149812734082393</v>
       </c>
     </row>
     <row r="161" spans="1:92" x14ac:dyDescent="0.2">
@@ -46290,10 +46290,10 @@
         <v>74.2</v>
       </c>
       <c r="CM161">
-        <v>1397</v>
+        <v>1251</v>
       </c>
       <c r="CN161">
-        <v>0.83679312813171081</v>
+        <v>0.83455637091394264</v>
       </c>
     </row>
     <row r="162" spans="1:92" x14ac:dyDescent="0.2">
@@ -46568,10 +46568,10 @@
         <v>83.2</v>
       </c>
       <c r="CM162">
-        <v>883</v>
+        <v>1169</v>
       </c>
       <c r="CN162">
-        <v>0.77916194790486981</v>
+        <v>0.83679312813171081</v>
       </c>
     </row>
     <row r="163" spans="1:92" x14ac:dyDescent="0.2">
@@ -46846,10 +46846,10 @@
         <v>67.900000000000006</v>
       </c>
       <c r="CM163">
-        <v>822</v>
+        <v>688</v>
       </c>
       <c r="CN163">
-        <v>0.81021897810218979</v>
+        <v>0.77916194790486981</v>
       </c>
     </row>
     <row r="164" spans="1:92" x14ac:dyDescent="0.2">
@@ -47124,10 +47124,10 @@
         <v>54.9</v>
       </c>
       <c r="CM164">
-        <v>442</v>
+        <v>666</v>
       </c>
       <c r="CN164">
-        <v>0.79411764705882348</v>
+        <v>0.81021897810218979</v>
       </c>
     </row>
     <row r="165" spans="1:92" x14ac:dyDescent="0.2">
@@ -47402,10 +47402,10 @@
         <v>67.900000000000006</v>
       </c>
       <c r="CM165">
-        <v>1275</v>
+        <v>351</v>
       </c>
       <c r="CN165">
-        <v>0.71607843137254901</v>
+        <v>0.79411764705882348</v>
       </c>
     </row>
     <row r="166" spans="1:92" x14ac:dyDescent="0.2">
@@ -47680,10 +47680,10 @@
         <v>73.3</v>
       </c>
       <c r="CM166">
-        <v>775</v>
+        <v>913</v>
       </c>
       <c r="CN166">
-        <v>0.7870967741935484</v>
+        <v>0.71607843137254901</v>
       </c>
     </row>
     <row r="167" spans="1:92" x14ac:dyDescent="0.2">
@@ -47958,10 +47958,10 @@
         <v>77.3</v>
       </c>
       <c r="CM167">
-        <v>904</v>
+        <v>610</v>
       </c>
       <c r="CN167">
-        <v>0.73119469026548678</v>
+        <v>0.7870967741935484</v>
       </c>
     </row>
     <row r="168" spans="1:92" x14ac:dyDescent="0.2">
@@ -48236,10 +48236,10 @@
         <v>65.7</v>
       </c>
       <c r="CM168">
-        <v>752</v>
+        <v>661</v>
       </c>
       <c r="CN168">
-        <v>0.67420212765957444</v>
+        <v>0.73119469026548678</v>
       </c>
     </row>
     <row r="169" spans="1:92" x14ac:dyDescent="0.2">
@@ -48514,10 +48514,10 @@
         <v>43.3</v>
       </c>
       <c r="CM169">
-        <v>2494</v>
+        <v>507</v>
       </c>
       <c r="CN169">
-        <v>0.85846030473135526</v>
+        <v>0.67420212765957444</v>
       </c>
     </row>
     <row r="170" spans="1:92" x14ac:dyDescent="0.2">
@@ -48792,10 +48792,10 @@
         <v>68.2</v>
       </c>
       <c r="CM170">
-        <v>2814</v>
+        <v>2141</v>
       </c>
       <c r="CN170">
-        <v>0.88841506751954513</v>
+        <v>0.85846030473135526</v>
       </c>
     </row>
     <row r="171" spans="1:92" x14ac:dyDescent="0.2">
@@ -49070,10 +49070,10 @@
         <v>89.4</v>
       </c>
       <c r="CM171">
-        <v>3281</v>
+        <v>2500</v>
       </c>
       <c r="CN171">
-        <v>0.82657726302956414</v>
+        <v>0.88841506751954513</v>
       </c>
     </row>
     <row r="172" spans="1:92" x14ac:dyDescent="0.2">
@@ -49348,10 +49348,10 @@
         <v>64.7</v>
       </c>
       <c r="CM172">
-        <v>2638</v>
+        <v>2712</v>
       </c>
       <c r="CN172">
-        <v>0.78658074298711145</v>
+        <v>0.82657726302956414</v>
       </c>
     </row>
     <row r="173" spans="1:92" x14ac:dyDescent="0.2">
@@ -49626,10 +49626,10 @@
         <v>76.099999999999994</v>
       </c>
       <c r="CM173">
-        <v>7504</v>
+        <v>2075</v>
       </c>
       <c r="CN173">
-        <v>0.79677505330490406</v>
+        <v>0.78658074298711145</v>
       </c>
     </row>
     <row r="174" spans="1:92" x14ac:dyDescent="0.2">
@@ -49904,10 +49904,10 @@
         <v>78.8</v>
       </c>
       <c r="CM174">
-        <v>1170</v>
+        <v>5979</v>
       </c>
       <c r="CN174">
-        <v>0.69401709401709399</v>
+        <v>0.79677505330490406</v>
       </c>
     </row>
     <row r="175" spans="1:92" x14ac:dyDescent="0.2">
@@ -50182,10 +50182,10 @@
         <v>71.099999999999994</v>
       </c>
       <c r="CM175">
-        <v>1369</v>
+        <v>812</v>
       </c>
       <c r="CN175">
-        <v>0.69539810080350617</v>
+        <v>0.69401709401709399</v>
       </c>
     </row>
     <row r="176" spans="1:92" x14ac:dyDescent="0.2">
@@ -50460,10 +50460,10 @@
         <v>76.099999999999994</v>
       </c>
       <c r="CM176">
-        <v>8364</v>
+        <v>952</v>
       </c>
       <c r="CN176">
-        <v>0.86358201817312286</v>
+        <v>0.69539810080350617</v>
       </c>
     </row>
     <row r="177" spans="1:92" x14ac:dyDescent="0.2">
@@ -50738,10 +50738,10 @@
         <v>80.7</v>
       </c>
       <c r="CM177">
-        <v>4098</v>
+        <v>7223</v>
       </c>
       <c r="CN177">
-        <v>0.84016593460224498</v>
+        <v>0.86358201817312286</v>
       </c>
     </row>
     <row r="178" spans="1:92" x14ac:dyDescent="0.2">
@@ -51016,10 +51016,10 @@
         <v>85.9</v>
       </c>
       <c r="CM178">
-        <v>4269</v>
+        <v>3443</v>
       </c>
       <c r="CN178">
-        <v>0.77465448582806273</v>
+        <v>0.84016593460224498</v>
       </c>
     </row>
     <row r="179" spans="1:92" x14ac:dyDescent="0.2">
@@ -51294,10 +51294,10 @@
         <v>83.8</v>
       </c>
       <c r="CM179">
-        <v>1559</v>
+        <v>3307</v>
       </c>
       <c r="CN179">
-        <v>0.70942912123155866</v>
+        <v>0.77465448582806273</v>
       </c>
     </row>
     <row r="180" spans="1:92" x14ac:dyDescent="0.2">
@@ -51572,10 +51572,10 @@
         <v>83.7</v>
       </c>
       <c r="CM180">
-        <v>1246</v>
+        <v>1106</v>
       </c>
       <c r="CN180">
-        <v>0.80658105939004821</v>
+        <v>0.70942912123155866</v>
       </c>
     </row>
     <row r="181" spans="1:92" x14ac:dyDescent="0.2">
@@ -51850,10 +51850,10 @@
         <v>73.900000000000006</v>
       </c>
       <c r="CM181">
-        <v>2027</v>
+        <v>1005</v>
       </c>
       <c r="CN181">
-        <v>0.76221016280217069</v>
+        <v>0.80658105939004821</v>
       </c>
     </row>
     <row r="182" spans="1:92" x14ac:dyDescent="0.2">
@@ -52128,10 +52128,10 @@
         <v>78.900000000000006</v>
       </c>
       <c r="CM182">
-        <v>3090</v>
+        <v>1545</v>
       </c>
       <c r="CN182">
-        <v>0.85177993527508089</v>
+        <v>0.76221016280217069</v>
       </c>
     </row>
     <row r="183" spans="1:92" x14ac:dyDescent="0.2">
@@ -52406,10 +52406,10 @@
         <v>71.5</v>
       </c>
       <c r="CM183">
-        <v>1683</v>
+        <v>2632</v>
       </c>
       <c r="CN183">
-        <v>0.81937017231134879</v>
+        <v>0.85177993527508089</v>
       </c>
     </row>
     <row r="184" spans="1:92" x14ac:dyDescent="0.2">
@@ -52684,10 +52684,10 @@
         <v>65.8</v>
       </c>
       <c r="CM184">
-        <v>653</v>
+        <v>1379</v>
       </c>
       <c r="CN184">
-        <v>0.75957120980091886</v>
+        <v>0.81937017231134879</v>
       </c>
     </row>
     <row r="185" spans="1:92" x14ac:dyDescent="0.2">
@@ -52962,10 +52962,10 @@
         <v>72.900000000000006</v>
       </c>
       <c r="CM185">
-        <v>1379</v>
+        <v>496</v>
       </c>
       <c r="CN185">
-        <v>0.87164612037708489</v>
+        <v>0.75957120980091886</v>
       </c>
     </row>
     <row r="186" spans="1:92" x14ac:dyDescent="0.2">
@@ -53240,10 +53240,10 @@
         <v>67.900000000000006</v>
       </c>
       <c r="CM186">
-        <v>5320</v>
+        <v>1202</v>
       </c>
       <c r="CN186">
-        <v>0.73853383458646615</v>
+        <v>0.87164612037708489</v>
       </c>
     </row>
     <row r="187" spans="1:92" x14ac:dyDescent="0.2">
@@ -53518,10 +53518,10 @@
         <v>72.7</v>
       </c>
       <c r="CM187">
-        <v>7573</v>
+        <v>3929</v>
       </c>
       <c r="CN187">
-        <v>0.83890136009507466</v>
+        <v>0.73853383458646615</v>
       </c>
     </row>
     <row r="188" spans="1:92" x14ac:dyDescent="0.2">
@@ -53796,10 +53796,10 @@
         <v>59.8</v>
       </c>
       <c r="CM188">
-        <v>5073</v>
+        <v>6353</v>
       </c>
       <c r="CN188">
-        <v>0.76995860437610886</v>
+        <v>0.83890136009507466</v>
       </c>
     </row>
     <row r="189" spans="1:92" x14ac:dyDescent="0.2">
@@ -54074,10 +54074,10 @@
         <v>72.099999999999994</v>
       </c>
       <c r="CM189">
-        <v>492</v>
+        <v>3906</v>
       </c>
       <c r="CN189">
-        <v>0.82926829268292679</v>
+        <v>0.76995860437610886</v>
       </c>
     </row>
     <row r="190" spans="1:92" x14ac:dyDescent="0.2">
@@ -54352,10 +54352,10 @@
         <v>81</v>
       </c>
       <c r="CM190">
-        <v>1453</v>
+        <v>408</v>
       </c>
       <c r="CN190">
-        <v>0.85891259463179626</v>
+        <v>0.82926829268292679</v>
       </c>
     </row>
     <row r="191" spans="1:92" x14ac:dyDescent="0.2">
@@ -54630,10 +54630,10 @@
         <v>93.7</v>
       </c>
       <c r="CM191">
-        <v>5889</v>
+        <v>1248</v>
       </c>
       <c r="CN191">
-        <v>0.85073866530820175</v>
+        <v>0.85891259463179626</v>
       </c>
     </row>
     <row r="192" spans="1:92" x14ac:dyDescent="0.2">
@@ -54908,10 +54908,10 @@
         <v>66.7</v>
       </c>
       <c r="CM192">
-        <v>1095</v>
+        <v>5010</v>
       </c>
       <c r="CN192">
-        <v>0.84748858447488584</v>
+        <v>0.85073866530820175</v>
       </c>
     </row>
     <row r="193" spans="1:92" x14ac:dyDescent="0.2">
@@ -55186,10 +55186,10 @@
         <v>68</v>
       </c>
       <c r="CM193">
-        <v>12375</v>
+        <v>928</v>
       </c>
       <c r="CN193">
-        <v>0.91991919191919191</v>
+        <v>0.84748858447488584</v>
       </c>
     </row>
     <row r="194" spans="1:92" x14ac:dyDescent="0.2">
@@ -55464,10 +55464,10 @@
         <v>69.599999999999994</v>
       </c>
       <c r="CM194">
-        <v>511</v>
+        <v>11384</v>
       </c>
       <c r="CN194">
-        <v>0.80821917808219179</v>
+        <v>0.91991919191919191</v>
       </c>
     </row>
     <row r="195" spans="1:92" x14ac:dyDescent="0.2">
@@ -55742,10 +55742,10 @@
         <v>60.5</v>
       </c>
       <c r="CM195">
-        <v>1885</v>
+        <v>413</v>
       </c>
       <c r="CN195">
-        <v>0.75066312997347484</v>
+        <v>0.80821917808219179</v>
       </c>
     </row>
     <row r="196" spans="1:92" x14ac:dyDescent="0.2">
@@ -56020,10 +56020,10 @@
         <v>84.3</v>
       </c>
       <c r="CM196">
-        <v>596</v>
+        <v>1415</v>
       </c>
       <c r="CN196">
-        <v>0.72315436241610742</v>
+        <v>0.75066312997347484</v>
       </c>
     </row>
     <row r="197" spans="1:92" x14ac:dyDescent="0.2">
@@ -56298,10 +56298,10 @@
         <v>57.7</v>
       </c>
       <c r="CM197">
-        <v>2575</v>
+        <v>431</v>
       </c>
       <c r="CN197">
-        <v>0.69475728155339811</v>
+        <v>0.72315436241610742</v>
       </c>
     </row>
     <row r="198" spans="1:92" x14ac:dyDescent="0.2">
@@ -56576,10 +56576,10 @@
         <v>63.3</v>
       </c>
       <c r="CM198">
-        <v>2259</v>
+        <v>1789</v>
       </c>
       <c r="CN198">
-        <v>0.76715360779105801</v>
+        <v>0.69475728155339811</v>
       </c>
     </row>
     <row r="199" spans="1:92" x14ac:dyDescent="0.2">
@@ -56854,10 +56854,10 @@
         <v>83.9</v>
       </c>
       <c r="CM199">
-        <v>863</v>
+        <v>1733</v>
       </c>
       <c r="CN199">
-        <v>0.7404403244495944</v>
+        <v>0.76715360779105801</v>
       </c>
     </row>
     <row r="200" spans="1:92" x14ac:dyDescent="0.2">
@@ -57132,10 +57132,10 @@
         <v>84</v>
       </c>
       <c r="CM200">
-        <v>1640</v>
+        <v>639</v>
       </c>
       <c r="CN200">
-        <v>0.85792682926829267</v>
+        <v>0.7404403244495944</v>
       </c>
     </row>
     <row r="201" spans="1:92" x14ac:dyDescent="0.2">
@@ -57410,10 +57410,10 @@
         <v>102.3</v>
       </c>
       <c r="CM201">
-        <v>3545</v>
+        <v>1407</v>
       </c>
       <c r="CN201">
-        <v>0.79548660084626233</v>
+        <v>0.85792682926829267</v>
       </c>
     </row>
     <row r="202" spans="1:92" x14ac:dyDescent="0.2">
@@ -57688,10 +57688,10 @@
         <v>80.900000000000006</v>
       </c>
       <c r="CM202">
-        <v>1012</v>
+        <v>2820</v>
       </c>
       <c r="CN202">
-        <v>0.77865612648221338</v>
+        <v>0.79548660084626233</v>
       </c>
     </row>
     <row r="203" spans="1:92" x14ac:dyDescent="0.2">
@@ -57966,10 +57966,10 @@
         <v>73.8</v>
       </c>
       <c r="CM203">
-        <v>6107</v>
+        <v>788</v>
       </c>
       <c r="CN203">
-        <v>0.87211396757818893</v>
+        <v>0.77865612648221338</v>
       </c>
     </row>
     <row r="204" spans="1:92" x14ac:dyDescent="0.2">
@@ -58244,10 +58244,10 @@
         <v>82.9</v>
       </c>
       <c r="CM204">
-        <v>982</v>
+        <v>5326</v>
       </c>
       <c r="CN204">
-        <v>0.82586558044806513</v>
+        <v>0.87211396757818893</v>
       </c>
     </row>
     <row r="205" spans="1:92" x14ac:dyDescent="0.2">
@@ -58522,10 +58522,10 @@
         <v>65.2</v>
       </c>
       <c r="CM205">
-        <v>6276</v>
+        <v>811</v>
       </c>
       <c r="CN205">
-        <v>0.84257488846398976</v>
+        <v>0.82586558044806513</v>
       </c>
     </row>
     <row r="206" spans="1:92" x14ac:dyDescent="0.2">
@@ -58800,10 +58800,10 @@
         <v>77.8</v>
       </c>
       <c r="CM206">
-        <v>831</v>
+        <v>5288</v>
       </c>
       <c r="CN206">
-        <v>0.56558363417569191</v>
+        <v>0.84257488846398976</v>
       </c>
     </row>
     <row r="207" spans="1:92" x14ac:dyDescent="0.2">
@@ -59078,10 +59078,10 @@
         <v>65.400000000000006</v>
       </c>
       <c r="CM207">
-        <v>2670</v>
+        <v>470</v>
       </c>
       <c r="CN207">
-        <v>0.74831460674157302</v>
+        <v>0.56558363417569191</v>
       </c>
     </row>
     <row r="208" spans="1:92" x14ac:dyDescent="0.2">
@@ -59356,10 +59356,10 @@
         <v>76</v>
       </c>
       <c r="CM208">
-        <v>8590</v>
+        <v>1998</v>
       </c>
       <c r="CN208">
-        <v>0.82980209545983707</v>
+        <v>0.74831460674157302</v>
       </c>
     </row>
     <row r="209" spans="1:92" x14ac:dyDescent="0.2">
@@ -59634,10 +59634,10 @@
         <v>74.400000000000006</v>
       </c>
       <c r="CM209">
-        <v>2228</v>
+        <v>7128</v>
       </c>
       <c r="CN209">
-        <v>0.82181328545780974</v>
+        <v>0.82980209545983707</v>
       </c>
     </row>
     <row r="210" spans="1:92" x14ac:dyDescent="0.2">
@@ -59912,10 +59912,10 @@
         <v>87.6</v>
       </c>
       <c r="CM210">
-        <v>562</v>
+        <v>1831</v>
       </c>
       <c r="CN210">
-        <v>0.69395017793594305</v>
+        <v>0.82181328545780974</v>
       </c>
     </row>
     <row r="211" spans="1:92" x14ac:dyDescent="0.2">
@@ -60190,10 +60190,10 @@
         <v>61.9</v>
       </c>
       <c r="CM211">
-        <v>1727</v>
+        <v>390</v>
       </c>
       <c r="CN211">
-        <v>0.83497394325419805</v>
+        <v>0.69395017793594305</v>
       </c>
     </row>
     <row r="212" spans="1:92" x14ac:dyDescent="0.2">
@@ -60468,10 +60468,10 @@
         <v>87.6</v>
       </c>
       <c r="CM212">
-        <v>1591</v>
+        <v>1442</v>
       </c>
       <c r="CN212">
-        <v>0.85229415461973601</v>
+        <v>0.83497394325419805</v>
       </c>
     </row>
     <row r="213" spans="1:92" x14ac:dyDescent="0.2">
@@ -60746,10 +60746,10 @@
         <v>73.3</v>
       </c>
       <c r="CM213">
-        <v>2122</v>
+        <v>1356</v>
       </c>
       <c r="CN213">
-        <v>0.67624882186616397</v>
+        <v>0.85229415461973601</v>
       </c>
     </row>
     <row r="214" spans="1:92" x14ac:dyDescent="0.2">
@@ -61022,6 +61022,12 @@
       </c>
       <c r="CL214">
         <v>80.099999999999994</v>
+      </c>
+      <c r="CM214">
+        <v>1435</v>
+      </c>
+      <c r="CN214">
+        <v>0.67624882186616397</v>
       </c>
     </row>
   </sheetData>

--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/Test folder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit_turisticne_regije_app_v4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44610FAE-0E3B-EA47-A3D7-5BD06BDF5558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC10E226-E67D-E046-9B6B-2695295A8D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8540" yWindow="11380" windowWidth="49940" windowHeight="34980" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
+    <workbookView xWindow="25460" yWindow="7280" windowWidth="49880" windowHeight="34240" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Skupna Tabela" sheetId="1" r:id="rId1"/>
@@ -1165,7 +1165,22 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="21">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -1240,9 +1255,9 @@
     <tableColumn id="4" xr3:uid="{6A516117-D02C-9042-BED8-A834718FD32E}" name="Število prebivalcev (H2/2024)"/>
     <tableColumn id="5" xr3:uid="{91CEC2B5-9950-E340-9265-15A390DF7689}" name="Povprečna starost prebivalcev"/>
     <tableColumn id="6" xr3:uid="{FB5CAD11-15F3-A24F-9CAF-8E64EAD3A48D}" name="Naravni prirast /1000 prebival."/>
-    <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov_x0009_Tuji" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov_x0009_Tuji" dataDxfId="18"/>
     <tableColumn id="10" xr3:uid="{AE7EC853-0402-A44C-9F12-18D82AF38827}" name="Delež tujih prenočitev"/>
     <tableColumn id="100" xr3:uid="{646738F1-12E5-3D42-B08F-732CB4BD71FB}" name="Delež vseh prenočitev - Domači trg"/>
     <tableColumn id="101" xr3:uid="{E13F778E-7B5E-764D-A93E-CE2E6F497E0A}" name="Delež vseh prenočitev - DACH trgi"/>
@@ -1252,33 +1267,33 @@
     <tableColumn id="96" xr3:uid="{BE355046-C01C-9644-BF5E-989C542937E5}" name="Delež vseh prenočitev - Prekomorski trgi (ZDA, VB, CAN, AU, Azija)"/>
     <tableColumn id="95" xr3:uid="{D5614879-03D8-BE4D-8BB9-B1493690172E}" name="Delež vseh prenočitev - Trgi JV Evrope"/>
     <tableColumn id="94" xr3:uid="{5E5059F9-5ABE-A940-B1FB-98129F4C2C53}" name="Delež vseh prenočitev - Vsi drugi tuji trgi"/>
-    <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji" dataDxfId="10"/>
-    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji" dataDxfId="15"/>
+    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev" dataDxfId="14"/>
     <tableColumn id="14" xr3:uid="{494C63A2-19AC-0544-861F-B7FA12714240}" name="PDB turistov_x0009_SKUPAJ"/>
     <tableColumn id="15" xr3:uid="{A743FB1C-E3E3-8340-BA42-61AD9082C50D}" name="PDB turistov_x0009_Domači"/>
     <tableColumn id="16" xr3:uid="{D6397E34-AE62-1B40-8641-B68E90F526C0}" name="PDB turistov_x0009_Tuji"/>
     <tableColumn id="17" xr3:uid="{FF46E309-259F-F74C-B4E3-7DF480EC498E}" name="Nastanitvene kapacitete - Nedeljive enote"/>
     <tableColumn id="18" xr3:uid="{DFA7A743-7B9B-AC4B-B555-AB008106AD20}" name="Nastanitvene kapacitete - vsa ležišča"/>
     <tableColumn id="19" xr3:uid="{978F1FBB-9333-EE42-8F86-066AF03E32F3}" name="Nastanitvene kapacitete - stalna ležišča"/>
-    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="4"/>
-    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="10"/>
+    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="9"/>
+    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="8"/>
     <tableColumn id="26" xr3:uid="{6B98A6DD-4A64-EE45-AE54-458C05388214}" name="Delež stalnih ležišč v Hotelih ipd."/>
     <tableColumn id="27" xr3:uid="{CC3F87E6-B3CD-E841-BCED-E5C77DFA385B}" name="Povprečna letna zasedenost staln. ležišč"/>
     <tableColumn id="28" xr3:uid="{36E12EEC-F431-7640-B38F-3F28A52A27A2}" name="Ocenjena povp. Letna zased. sob (nedeljivih enot)"/>
     <tableColumn id="29" xr3:uid="{E32E1653-4218-8144-AE1B-7DA0234BDD6B}" name="Pritisk turizma na družbeni prostor (število stalnih ležišč / 100 prebivalcev)"/>
     <tableColumn id="30" xr3:uid="{6235832E-2F71-6247-9BC2-BB497EF940F1}" name="Gostota turizma"/>
     <tableColumn id="31" xr3:uid="{6059D037-013F-3443-92BE-556256221BB9}" name="Intenzivnost turizma (število nočitev na dan / 100 prebivalcev)"/>
-    <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)"/>
-    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)"/>
-    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="1"/>
-    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="0"/>
+    <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" dataDxfId="3"/>
+    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="7"/>
+    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="6"/>
+    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="5"/>
     <tableColumn id="37" xr3:uid="{52A7F38A-5C90-964D-B065-B17C7BA263D5}" name="Delež delovno aktivnih v turizmu (OECD/WTO)"/>
     <tableColumn id="38" xr3:uid="{C0F240E5-648C-7342-B26C-C8B4E0C3F6B4}" name="Število vseh vrst podjetij na območju"/>
     <tableColumn id="39" xr3:uid="{36A2CDB3-CA3D-9043-ADE8-DD7F31F3FE73}" name="Prihodek (v 1000 EUR) vseh podjetij na območju"/>
@@ -1287,7 +1302,7 @@
     <tableColumn id="42" xr3:uid="{B0D87609-1D6D-C14B-ACCF-6C1B464628BA}" name="Dodana vrednost reg.podjetij v Gostinstvu (I)"/>
     <tableColumn id="43" xr3:uid="{607A8E1A-ADB4-DE4D-8BAE-A85043CB1032}" name="Dodana vrednost/zaposl. reg.podjetij Gostinstvu (I)"/>
     <tableColumn id="44" xr3:uid="{868E97D0-55BC-434A-905F-BF7484D746C8}" name="Ocenjeni stroški dela v reg. podj. v Gostinski (I) dejavnosti"/>
-    <tableColumn id="45" xr3:uid="{338734FE-BF0A-3E4F-A3B5-2D41980F97B6}" name="Stroški dela na zaposl. na leto v reg. podj. v Gostinski (I) dejavnosti"/>
+    <tableColumn id="45" xr3:uid="{338734FE-BF0A-3E4F-A3B5-2D41980F97B6}" name="Stroški dela na zaposl. na leto v reg. podj. v Gostinski (I) dejavnosti" dataDxfId="2"/>
     <tableColumn id="46" xr3:uid="{49EE83EE-AD75-6A45-A4EA-AA7A2C93AD25}" name="Delež stroškov dela v prihodkih v reg. podj. v Gostinstvu (I)"/>
     <tableColumn id="47" xr3:uid="{31239E64-8BC6-F640-A167-9AFF156CFDD7}" name="Delež stroškov dela v dod vredn. v reg. podj. v Gostinstvu (I)"/>
     <tableColumn id="48" xr3:uid="{33891302-7793-7844-A25D-3A2BD436AE77}" name="EBITDA v reg.podjetjih in s.p. v Gostinstvu (I)"/>
@@ -1301,9 +1316,9 @@
     <tableColumn id="56" xr3:uid="{F3FBED48-E964-884C-83EF-540A4CB997DE}" name="Število reg. podjetij in s.p. v nastanitveni dejav. (I 55)"/>
     <tableColumn id="57" xr3:uid="{7E9C06A6-EE05-5A4B-BFC4-1470DA5C6480}" name="Prihodki reg.podjetij in s.p. v nastanitveni dejav. (I 55)"/>
     <tableColumn id="58" xr3:uid="{594A7048-030B-7641-B062-ED36E3B0A3D9}" name="Dodana vrednost reg.podjetij v nastanitveni dejav. (I 55)"/>
-    <tableColumn id="59" xr3:uid="{09081719-5307-4548-8093-CB520C468E59}" name="Dodana vrednost/zaposl. V reg.podjetjih v nast.dejav. (I 55)"/>
+    <tableColumn id="59" xr3:uid="{09081719-5307-4548-8093-CB520C468E59}" name="Dodana vrednost/zaposl. V reg.podjetjih v nast.dejav. (I 55)" dataDxfId="1"/>
     <tableColumn id="60" xr3:uid="{DB8C5AB7-2761-3A43-9547-30F272D35A19}" name="Ocenjeni stroški dela v reg. podj. v nastan.gost. (I 55) dejavnosti"/>
-    <tableColumn id="61" xr3:uid="{C40A32FF-D555-5543-9E84-A6DEFFEAA3D9}" name="Stroški dela na zaposl. na leto v reg. podj. v nast.gost. (I 55) dejavnosti"/>
+    <tableColumn id="61" xr3:uid="{C40A32FF-D555-5543-9E84-A6DEFFEAA3D9}" name="Stroški dela na zaposl. na leto v reg. podj. v nast.gost. (I 55) dejavnosti" dataDxfId="0"/>
     <tableColumn id="62" xr3:uid="{D0F52755-EE67-9D44-8FB1-80277D4514B0}" name="Delež stroškov dela v prihodkih v reg. podj. v nast.gost.dej. (I 55)"/>
     <tableColumn id="63" xr3:uid="{901DFC53-DFEE-1A4A-8CD7-EE7638EC34CF}" name="Delež stroškov dela v dod vredn. v reg. podj. v nast.gost.dej. (I 55)"/>
     <tableColumn id="64" xr3:uid="{8B14609D-EBDD-BD49-B52D-3A5DF542F21A}" name="EBITDA v reg.podjetjih in s.p. v nastanitveni dejav. (I 55)"/>
@@ -1691,8 +1706,8 @@
     <col min="41" max="41" width="32.5" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="17" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="36.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="58.5" style="1" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="45.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="27.5" style="1" customWidth="1"/>
     <col min="48" max="48" width="29.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -1704,7 +1719,7 @@
     <col min="54" max="54" width="33.1640625" customWidth="1"/>
     <col min="55" max="55" width="63.5" customWidth="1"/>
     <col min="56" max="56" width="23.6640625" customWidth="1"/>
-    <col min="57" max="57" width="32.6640625" customWidth="1"/>
+    <col min="57" max="57" width="32.6640625" style="1" customWidth="1"/>
     <col min="58" max="58" width="24.83203125" customWidth="1"/>
     <col min="59" max="59" width="26.83203125" customWidth="1"/>
     <col min="60" max="60" width="17.83203125" customWidth="1"/>
@@ -1715,9 +1730,9 @@
     <col min="66" max="67" width="30.5" customWidth="1"/>
     <col min="68" max="68" width="24.5" customWidth="1"/>
     <col min="69" max="70" width="26.5" customWidth="1"/>
-    <col min="71" max="71" width="28.83203125" customWidth="1"/>
+    <col min="71" max="71" width="28.83203125" style="1" customWidth="1"/>
     <col min="72" max="72" width="28.33203125" customWidth="1"/>
-    <col min="73" max="73" width="30.6640625" customWidth="1"/>
+    <col min="73" max="73" width="30.6640625" style="1" customWidth="1"/>
     <col min="74" max="74" width="29.5" customWidth="1"/>
     <col min="75" max="75" width="27.1640625" customWidth="1"/>
     <col min="76" max="83" width="26.5" customWidth="1"/>
@@ -1871,10 +1886,10 @@
       <c r="AQ1" t="s">
         <v>305</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>301</v>
       </c>
       <c r="AT1" s="1" t="s">
@@ -1910,7 +1925,7 @@
       <c r="BD1" t="s">
         <v>242</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>243</v>
       </c>
       <c r="BF1" t="s">
@@ -1952,13 +1967,13 @@
       <c r="BR1" t="s">
         <v>255</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>256</v>
       </c>
       <c r="BT1" t="s">
         <v>257</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>258</v>
       </c>
       <c r="BV1" t="s">
@@ -2173,10 +2188,10 @@
       <c r="AQ2">
         <v>2.1714850709100819</v>
       </c>
-      <c r="AR2">
+      <c r="AR2" s="1">
         <v>64820</v>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="1">
         <v>44149</v>
       </c>
       <c r="AT2" s="1">
@@ -2212,7 +2227,7 @@
       <c r="BD2">
         <v>791516130</v>
       </c>
-      <c r="BE2">
+      <c r="BE2" s="1">
         <v>25555.558325602102</v>
       </c>
       <c r="BF2">
@@ -2254,13 +2269,13 @@
       <c r="BR2">
         <v>519607832</v>
       </c>
-      <c r="BS2">
+      <c r="BS2" s="1">
         <v>53260.389975799495</v>
       </c>
       <c r="BT2">
         <v>319880016</v>
       </c>
-      <c r="BU2">
+      <c r="BU2" s="1">
         <v>32788.063128395996</v>
       </c>
       <c r="BV2">
@@ -2487,10 +2502,10 @@
       <c r="AQ3">
         <v>0.60434040920557841</v>
       </c>
-      <c r="AR3">
+      <c r="AR3" s="1">
         <v>303.5</v>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="1">
         <v>181.69238103133813</v>
       </c>
       <c r="AT3" s="1">
@@ -2526,7 +2541,7 @@
       <c r="BD3">
         <v>3189611</v>
       </c>
-      <c r="BE3">
+      <c r="BE3" s="1">
         <v>25746.049010922467</v>
       </c>
       <c r="BF3">
@@ -2568,13 +2583,13 @@
       <c r="BR3">
         <v>1988597</v>
       </c>
-      <c r="BS3">
+      <c r="BS3" s="1">
         <v>46867.711524864484</v>
       </c>
       <c r="BT3">
         <v>1242626</v>
       </c>
-      <c r="BU3">
+      <c r="BU3" s="1">
         <v>29286.495404195146</v>
       </c>
       <c r="BV3">
@@ -2801,10 +2816,10 @@
       <c r="AQ4">
         <v>28.213565532530737</v>
       </c>
-      <c r="AR4">
+      <c r="AR4" s="1">
         <v>173.08333333333331</v>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="1">
         <v>147.1198742103513</v>
       </c>
       <c r="AT4" s="1">
@@ -2840,7 +2855,7 @@
       <c r="BD4">
         <v>3789203</v>
       </c>
-      <c r="BE4">
+      <c r="BE4" s="1">
         <v>34632.699027965849</v>
       </c>
       <c r="BF4">
@@ -2882,13 +2897,13 @@
       <c r="BR4">
         <v>4809195</v>
       </c>
-      <c r="BS4">
+      <c r="BS4" s="1">
         <v>69850.326797385613</v>
       </c>
       <c r="BT4">
         <v>2709226</v>
       </c>
-      <c r="BU4">
+      <c r="BU4" s="1">
         <v>39349.687726942626</v>
       </c>
       <c r="BV4">
@@ -3115,10 +3130,10 @@
       <c r="AQ5">
         <v>6.132825775510993E-2</v>
       </c>
-      <c r="AR5">
+      <c r="AR5" s="1">
         <v>32</v>
       </c>
-      <c r="AS5">
+      <c r="AS5" s="1">
         <v>22.204602068333156</v>
       </c>
       <c r="AT5" s="1">
@@ -3154,7 +3169,7 @@
       <c r="BD5">
         <v>126437</v>
       </c>
-      <c r="BE5">
+      <c r="BE5" s="1">
         <v>11939.36654061956</v>
       </c>
       <c r="BF5">
@@ -3196,13 +3211,13 @@
       <c r="BR5">
         <v>0</v>
       </c>
-      <c r="BS5" t="s">
+      <c r="BS5" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT5">
         <v>0</v>
       </c>
-      <c r="BU5" t="s">
+      <c r="BU5" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV5" t="s">
@@ -3429,10 +3444,10 @@
       <c r="AQ6">
         <v>3.4664680035880989E-2</v>
       </c>
-      <c r="AR6">
+      <c r="AR6" s="1">
         <v>99.625</v>
       </c>
-      <c r="AS6">
+      <c r="AS6" s="1">
         <v>69.129171283052827</v>
       </c>
       <c r="AT6" s="1">
@@ -3468,7 +3483,7 @@
       <c r="BD6">
         <v>1580462</v>
       </c>
-      <c r="BE6">
+      <c r="BE6" s="1">
         <v>22249.215078019628</v>
       </c>
       <c r="BF6">
@@ -3510,13 +3525,13 @@
       <c r="BR6">
         <v>94758</v>
       </c>
-      <c r="BS6" t="s">
+      <c r="BS6" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT6">
         <v>0</v>
       </c>
-      <c r="BU6" t="s">
+      <c r="BU6" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV6" t="s">
@@ -3743,10 +3758,10 @@
       <c r="AQ7">
         <v>0.15135618924495936</v>
       </c>
-      <c r="AR7">
+      <c r="AR7" s="1">
         <v>38.666666666666664</v>
       </c>
-      <c r="AS7">
+      <c r="AS7" s="1">
         <v>25.712417428437977</v>
       </c>
       <c r="AT7" s="1">
@@ -3782,7 +3797,7 @@
       <c r="BD7">
         <v>446704</v>
       </c>
-      <c r="BE7">
+      <c r="BE7" s="1">
         <v>18648.300717402315</v>
       </c>
       <c r="BF7">
@@ -3824,13 +3839,13 @@
       <c r="BR7">
         <v>369459</v>
       </c>
-      <c r="BS7">
+      <c r="BS7" s="1">
         <v>34920.510396975427</v>
       </c>
       <c r="BT7">
         <v>233422</v>
       </c>
-      <c r="BU7">
+      <c r="BU7" s="1">
         <v>22062.57088846881</v>
       </c>
       <c r="BV7">
@@ -4057,10 +4072,10 @@
       <c r="AQ8">
         <v>0.79855739183000185</v>
       </c>
-      <c r="AR8">
+      <c r="AR8" s="1">
         <v>26</v>
       </c>
-      <c r="AS8">
+      <c r="AS8" s="1">
         <v>22.297965915338096</v>
       </c>
       <c r="AT8" s="1">
@@ -4096,7 +4111,7 @@
       <c r="BD8">
         <v>408994</v>
       </c>
-      <c r="BE8">
+      <c r="BE8" s="1">
         <v>19704.560802472442</v>
       </c>
       <c r="BF8">
@@ -4138,13 +4153,13 @@
       <c r="BR8">
         <v>4491</v>
       </c>
-      <c r="BS8">
+      <c r="BS8" s="1">
         <v>34546.153846153844</v>
       </c>
       <c r="BT8">
         <v>4007</v>
       </c>
-      <c r="BU8">
+      <c r="BU8" s="1">
         <v>30823.076923076922</v>
       </c>
       <c r="BV8">
@@ -4371,10 +4386,10 @@
       <c r="AQ9">
         <v>38.816395173682977</v>
       </c>
-      <c r="AR9">
+      <c r="AR9" s="1">
         <v>1062.625</v>
       </c>
-      <c r="AS9">
+      <c r="AS9" s="1">
         <v>715.14185526512904</v>
       </c>
       <c r="AT9" s="1">
@@ -4410,7 +4425,7 @@
       <c r="BD9">
         <v>14172663</v>
       </c>
-      <c r="BE9">
+      <c r="BE9" s="1">
         <v>28292.829098600574</v>
       </c>
       <c r="BF9">
@@ -4452,13 +4467,13 @@
       <c r="BR9">
         <v>18589500</v>
       </c>
-      <c r="BS9">
+      <c r="BS9" s="1">
         <v>68245.89742648408</v>
       </c>
       <c r="BT9">
         <v>9191455</v>
       </c>
-      <c r="BU9">
+      <c r="BU9" s="1">
         <v>33743.731414515947</v>
       </c>
       <c r="BV9">
@@ -4685,10 +4700,10 @@
       <c r="AQ10">
         <v>1.3028531541750286</v>
       </c>
-      <c r="AR10">
+      <c r="AR10" s="1">
         <v>15.75</v>
       </c>
-      <c r="AS10">
+      <c r="AS10" s="1">
         <v>10.231689320388348</v>
       </c>
       <c r="AT10" s="1">
@@ -4724,7 +4739,7 @@
       <c r="BD10">
         <v>345480</v>
       </c>
-      <c r="BE10">
+      <c r="BE10" s="1">
         <v>23450.591462690019</v>
       </c>
       <c r="BF10">
@@ -4766,13 +4781,13 @@
       <c r="BR10">
         <v>0</v>
       </c>
-      <c r="BS10" t="s">
+      <c r="BS10" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT10">
         <v>0</v>
       </c>
-      <c r="BU10" t="s">
+      <c r="BU10" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV10" t="s">
@@ -4999,10 +5014,10 @@
       <c r="AQ11">
         <v>43.961232955124636</v>
       </c>
-      <c r="AR11">
+      <c r="AR11" s="1">
         <v>470.54166666666669</v>
       </c>
-      <c r="AS11">
+      <c r="AS11" s="1">
         <v>316.67242957726944</v>
       </c>
       <c r="AT11" s="1">
@@ -5038,7 +5053,7 @@
       <c r="BD11">
         <v>7392146</v>
       </c>
-      <c r="BE11">
+      <c r="BE11" s="1">
         <v>27233.586071575392</v>
       </c>
       <c r="BF11">
@@ -5080,13 +5095,13 @@
       <c r="BR11">
         <v>10709846</v>
       </c>
-      <c r="BS11">
+      <c r="BS11" s="1">
         <v>54221.577561765902</v>
       </c>
       <c r="BT11">
         <v>6726357</v>
       </c>
-      <c r="BU11">
+      <c r="BU11" s="1">
         <v>34054.055285540708</v>
       </c>
       <c r="BV11">
@@ -5313,10 +5328,10 @@
       <c r="AQ12">
         <v>7.0415410453046279E-2</v>
       </c>
-      <c r="AR12">
+      <c r="AR12" s="1">
         <v>25.208333333333332</v>
       </c>
-      <c r="AS12">
+      <c r="AS12" s="1">
         <v>15.309462656112309</v>
       </c>
       <c r="AT12" s="1">
@@ -5352,7 +5367,7 @@
       <c r="BD12">
         <v>516258</v>
       </c>
-      <c r="BE12">
+      <c r="BE12" s="1">
         <v>24194.044425622571</v>
       </c>
       <c r="BF12">
@@ -5394,13 +5409,13 @@
       <c r="BR12">
         <v>0</v>
       </c>
-      <c r="BS12" t="s">
+      <c r="BS12" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT12">
         <v>0</v>
       </c>
-      <c r="BU12" t="s">
+      <c r="BU12" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV12" t="s">
@@ -5627,10 +5642,10 @@
       <c r="AQ13">
         <v>50.130275287598678</v>
       </c>
-      <c r="AR13">
+      <c r="AR13" s="1">
         <v>366.54166666666663</v>
       </c>
-      <c r="AS13">
+      <c r="AS13" s="1">
         <v>219.43271223677667</v>
       </c>
       <c r="AT13" s="1">
@@ -5666,7 +5681,7 @@
       <c r="BD13">
         <v>4253908</v>
       </c>
-      <c r="BE13">
+      <c r="BE13" s="1">
         <v>26718.787746669856</v>
       </c>
       <c r="BF13">
@@ -5708,13 +5723,13 @@
       <c r="BR13">
         <v>5861935</v>
       </c>
-      <c r="BS13">
+      <c r="BS13" s="1">
         <v>61958.936687453759</v>
       </c>
       <c r="BT13">
         <v>2812366</v>
       </c>
-      <c r="BU13">
+      <c r="BU13" s="1">
         <v>29725.8852129796</v>
       </c>
       <c r="BV13">
@@ -5941,10 +5956,10 @@
       <c r="AQ14">
         <v>9.1469373024993611E-2</v>
       </c>
-      <c r="AR14">
+      <c r="AR14" s="1">
         <v>71.833333333333343</v>
       </c>
-      <c r="AS14">
+      <c r="AS14" s="1">
         <v>54.139909195564471</v>
       </c>
       <c r="AT14" s="1">
@@ -5980,7 +5995,7 @@
       <c r="BD14">
         <v>625897</v>
       </c>
-      <c r="BE14">
+      <c r="BE14" s="1">
         <v>21697.414940261137</v>
       </c>
       <c r="BF14">
@@ -6022,13 +6037,13 @@
       <c r="BR14">
         <v>15703</v>
       </c>
-      <c r="BS14" t="s">
+      <c r="BS14" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT14">
         <v>0</v>
       </c>
-      <c r="BU14" t="s">
+      <c r="BU14" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV14" t="s">
@@ -6255,10 +6270,10 @@
       <c r="AQ15">
         <v>2.7635304467394599</v>
       </c>
-      <c r="AR15">
+      <c r="AR15" s="1">
         <v>213.375</v>
       </c>
-      <c r="AS15">
+      <c r="AS15" s="1">
         <v>127.73842439064833</v>
       </c>
       <c r="AT15" s="1">
@@ -6294,7 +6309,7 @@
       <c r="BD15">
         <v>1871196</v>
       </c>
-      <c r="BE15">
+      <c r="BE15" s="1">
         <v>19471.429902369709</v>
       </c>
       <c r="BF15">
@@ -6336,13 +6351,13 @@
       <c r="BR15">
         <v>721926</v>
       </c>
-      <c r="BS15">
+      <c r="BS15" s="1">
         <v>49788</v>
       </c>
       <c r="BT15">
         <v>413033</v>
       </c>
-      <c r="BU15">
+      <c r="BU15" s="1">
         <v>28485.03448275862</v>
       </c>
       <c r="BV15">
@@ -6569,10 +6584,10 @@
       <c r="AQ16">
         <v>0.30674575443500518</v>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="1">
         <v>254.29166666666666</v>
       </c>
-      <c r="AS16">
+      <c r="AS16" s="1">
         <v>154.43578609959246</v>
       </c>
       <c r="AT16" s="1">
@@ -6608,7 +6623,7 @@
       <c r="BD16">
         <v>3264297</v>
       </c>
-      <c r="BE16">
+      <c r="BE16" s="1">
         <v>21522.627712727561</v>
       </c>
       <c r="BF16">
@@ -6650,13 +6665,13 @@
       <c r="BR16">
         <v>404920</v>
       </c>
-      <c r="BS16">
+      <c r="BS16" s="1">
         <v>48726.835138387483</v>
       </c>
       <c r="BT16">
         <v>208520</v>
       </c>
-      <c r="BU16">
+      <c r="BU16" s="1">
         <v>25092.659446450059</v>
       </c>
       <c r="BV16">
@@ -6883,10 +6898,10 @@
       <c r="AQ17">
         <v>7.4797142402560013</v>
       </c>
-      <c r="AR17">
+      <c r="AR17" s="1">
         <v>768.54166666666663</v>
       </c>
-      <c r="AS17">
+      <c r="AS17" s="1">
         <v>659.11214953271019</v>
       </c>
       <c r="AT17" s="1">
@@ -6922,7 +6937,7 @@
       <c r="BD17">
         <v>15045962</v>
       </c>
-      <c r="BE17">
+      <c r="BE17" s="1">
         <v>28849.858543887512</v>
       </c>
       <c r="BF17">
@@ -6964,13 +6979,13 @@
       <c r="BR17">
         <v>23805053</v>
       </c>
-      <c r="BS17">
+      <c r="BS17" s="1">
         <v>58410.141086983196</v>
       </c>
       <c r="BT17">
         <v>12889255</v>
       </c>
-      <c r="BU17">
+      <c r="BU17" s="1">
         <v>31626.193105140475</v>
       </c>
       <c r="BV17">
@@ -7197,10 +7212,10 @@
       <c r="AQ18">
         <v>0.15576107363882902</v>
       </c>
-      <c r="AR18">
+      <c r="AR18" s="1">
         <v>24.958333333333332</v>
       </c>
-      <c r="AS18">
+      <c r="AS18" s="1">
         <v>17.318433123608806</v>
       </c>
       <c r="AT18" s="1">
@@ -7236,7 +7251,7 @@
       <c r="BD18">
         <v>314305</v>
       </c>
-      <c r="BE18">
+      <c r="BE18" s="1">
         <v>20483.484591155262</v>
       </c>
       <c r="BF18">
@@ -7278,13 +7293,13 @@
       <c r="BR18">
         <v>0</v>
       </c>
-      <c r="BS18" t="s">
+      <c r="BS18" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT18">
         <v>0</v>
       </c>
-      <c r="BU18" t="s">
+      <c r="BU18" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV18" t="s">
@@ -7511,10 +7526,10 @@
       <c r="AQ19">
         <v>0.35607146649676114</v>
       </c>
-      <c r="AR19">
+      <c r="AR19" s="1">
         <v>2323.125</v>
       </c>
-      <c r="AS19">
+      <c r="AS19" s="1">
         <v>1750.9110424586408</v>
       </c>
       <c r="AT19" s="1">
@@ -7550,7 +7565,7 @@
       <c r="BD19">
         <v>20626890</v>
       </c>
-      <c r="BE19">
+      <c r="BE19" s="1">
         <v>25525.106718210693</v>
       </c>
       <c r="BF19">
@@ -7592,13 +7607,13 @@
       <c r="BR19">
         <v>10960133</v>
       </c>
-      <c r="BS19">
+      <c r="BS19" s="1">
         <v>59588.609797205456</v>
       </c>
       <c r="BT19">
         <v>6347253</v>
       </c>
-      <c r="BU19">
+      <c r="BU19" s="1">
         <v>34509.068667427826</v>
       </c>
       <c r="BV19">
@@ -7825,10 +7840,10 @@
       <c r="AQ20">
         <v>2.8651068590587911</v>
       </c>
-      <c r="AR20">
+      <c r="AR20" s="1">
         <v>848.83333333333337</v>
       </c>
-      <c r="AS20">
+      <c r="AS20" s="1">
         <v>571.26102323103987</v>
       </c>
       <c r="AT20" s="1">
@@ -7864,7 +7879,7 @@
       <c r="BD20">
         <v>3592535</v>
       </c>
-      <c r="BE20">
+      <c r="BE20" s="1">
         <v>28193.965841095414</v>
       </c>
       <c r="BF20">
@@ -7906,13 +7921,13 @@
       <c r="BR20">
         <v>1084285</v>
       </c>
-      <c r="BS20">
+      <c r="BS20" s="1">
         <v>43774.121921679449</v>
       </c>
       <c r="BT20">
         <v>668930</v>
       </c>
-      <c r="BU20">
+      <c r="BU20" s="1">
         <v>27005.651998385143</v>
       </c>
       <c r="BV20">
@@ -8139,10 +8154,10 @@
       <c r="AQ21">
         <v>0.63288847476898913</v>
       </c>
-      <c r="AR21">
+      <c r="AR21" s="1">
         <v>163.625</v>
       </c>
-      <c r="AS21">
+      <c r="AS21" s="1">
         <v>106.29588349514562</v>
       </c>
       <c r="AT21" s="1">
@@ -8178,7 +8193,7 @@
       <c r="BD21">
         <v>1631939</v>
       </c>
-      <c r="BE21">
+      <c r="BE21" s="1">
         <v>19813.010243887304</v>
       </c>
       <c r="BF21">
@@ -8220,13 +8235,13 @@
       <c r="BR21">
         <v>400994</v>
       </c>
-      <c r="BS21">
+      <c r="BS21" s="1">
         <v>31824.920634920636</v>
       </c>
       <c r="BT21">
         <v>266315</v>
       </c>
-      <c r="BU21">
+      <c r="BU21" s="1">
         <v>21136.111111111113</v>
       </c>
       <c r="BV21">
@@ -8453,10 +8468,10 @@
       <c r="AQ22">
         <v>1.850628381781718</v>
       </c>
-      <c r="AR22">
+      <c r="AR22" s="1">
         <v>65.333333333333329</v>
       </c>
-      <c r="AS22">
+      <c r="AS22" s="1">
         <v>39.112253357652136</v>
       </c>
       <c r="AT22" s="1">
@@ -8492,7 +8507,7 @@
       <c r="BD22">
         <v>582020</v>
       </c>
-      <c r="BE22">
+      <c r="BE22" s="1">
         <v>21807.726057871085</v>
       </c>
       <c r="BF22">
@@ -8534,13 +8549,13 @@
       <c r="BR22">
         <v>67134</v>
       </c>
-      <c r="BS22">
+      <c r="BS22" s="1">
         <v>101718.18181818181</v>
       </c>
       <c r="BT22">
         <v>17026</v>
       </c>
-      <c r="BU22">
+      <c r="BU22" s="1">
         <v>25796.969696969696</v>
       </c>
       <c r="BV22">
@@ -8767,10 +8782,10 @@
       <c r="AQ23">
         <v>0.24767612524461843</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="1">
         <v>48.166666666666664</v>
       </c>
-      <c r="AS23">
+      <c r="AS23" s="1">
         <v>32.029692400080073</v>
       </c>
       <c r="AT23" s="1">
@@ -8806,7 +8821,7 @@
       <c r="BD23">
         <v>127970</v>
       </c>
-      <c r="BE23">
+      <c r="BE23" s="1">
         <v>3507.2947018883146</v>
       </c>
       <c r="BF23">
@@ -8848,13 +8863,13 @@
       <c r="BR23">
         <v>-68</v>
       </c>
-      <c r="BS23" t="s">
+      <c r="BS23" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT23">
         <v>0</v>
       </c>
-      <c r="BU23" t="s">
+      <c r="BU23" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV23" t="s">
@@ -9081,10 +9096,10 @@
       <c r="AQ24">
         <v>0.26498989445317767</v>
       </c>
-      <c r="AR24">
+      <c r="AR24" s="1">
         <v>16.25</v>
       </c>
-      <c r="AS24">
+      <c r="AS24" s="1">
         <v>10.805865083071996</v>
       </c>
       <c r="AT24" s="1">
@@ -9120,7 +9135,7 @@
       <c r="BD24">
         <v>166412</v>
       </c>
-      <c r="BE24">
+      <c r="BE24" s="1">
         <v>11775.754481928412</v>
       </c>
       <c r="BF24">
@@ -9162,13 +9177,13 @@
       <c r="BR24">
         <v>5296</v>
       </c>
-      <c r="BS24" t="s">
+      <c r="BS24" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT24">
         <v>0</v>
       </c>
-      <c r="BU24" t="s">
+      <c r="BU24" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV24" t="s">
@@ -9395,10 +9410,10 @@
       <c r="AQ25">
         <v>0.12532440342794501</v>
       </c>
-      <c r="AR25">
+      <c r="AR25" s="1">
         <v>67.333333333333329</v>
       </c>
-      <c r="AS25">
+      <c r="AS25" s="1">
         <v>46.722183518784348</v>
       </c>
       <c r="AT25" s="1">
@@ -9434,7 +9449,7 @@
       <c r="BD25">
         <v>1001585</v>
       </c>
-      <c r="BE25">
+      <c r="BE25" s="1">
         <v>22368.76667690363</v>
       </c>
       <c r="BF25">
@@ -9476,13 +9491,13 @@
       <c r="BR25">
         <v>9749</v>
       </c>
-      <c r="BS25" t="s">
+      <c r="BS25" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT25">
         <v>0</v>
       </c>
-      <c r="BU25" t="s">
+      <c r="BU25" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV25" t="s">
@@ -9709,10 +9724,10 @@
       <c r="AQ26">
         <v>8.5060413773069346E-2</v>
       </c>
-      <c r="AR26">
+      <c r="AR26" s="1">
         <v>28.916666666666668</v>
       </c>
-      <c r="AS26">
+      <c r="AS26" s="1">
         <v>20.34229353337501</v>
       </c>
       <c r="AT26" s="1">
@@ -9748,7 +9763,7 @@
       <c r="BD26">
         <v>23226</v>
       </c>
-      <c r="BE26">
+      <c r="BE26" s="1">
         <v>7742</v>
       </c>
       <c r="BF26">
@@ -9790,13 +9805,13 @@
       <c r="BR26">
         <v>355</v>
       </c>
-      <c r="BS26" t="s">
+      <c r="BS26" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT26">
         <v>0</v>
       </c>
-      <c r="BU26" t="s">
+      <c r="BU26" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV26" t="s">
@@ -10023,10 +10038,10 @@
       <c r="AQ27">
         <v>0.96011433774586363</v>
       </c>
-      <c r="AR27">
+      <c r="AR27" s="1">
         <v>248.625</v>
       </c>
-      <c r="AS27">
+      <c r="AS27" s="1">
         <v>195.63621254884194</v>
       </c>
       <c r="AT27" s="1">
@@ -10062,7 +10077,7 @@
       <c r="BD27">
         <v>2370472</v>
       </c>
-      <c r="BE27">
+      <c r="BE27" s="1">
         <v>17991.457671319749</v>
       </c>
       <c r="BF27">
@@ -10104,13 +10119,13 @@
       <c r="BR27">
         <v>2149888</v>
       </c>
-      <c r="BS27">
+      <c r="BS27" s="1">
         <v>45298.946481247367</v>
       </c>
       <c r="BT27">
         <v>1353266</v>
       </c>
-      <c r="BU27">
+      <c r="BU27" s="1">
         <v>28513.822166034555</v>
       </c>
       <c r="BV27">
@@ -10337,10 +10352,10 @@
       <c r="AQ28">
         <v>0.48858783981587106</v>
       </c>
-      <c r="AR28">
+      <c r="AR28" s="1">
         <v>23.75</v>
       </c>
-      <c r="AS28">
+      <c r="AS28" s="1">
         <v>15.793187429105224</v>
       </c>
       <c r="AT28" s="1">
@@ -10376,7 +10391,7 @@
       <c r="BD28">
         <v>131108</v>
       </c>
-      <c r="BE28">
+      <c r="BE28" s="1">
         <v>22682.756218848925</v>
       </c>
       <c r="BF28">
@@ -10418,13 +10433,13 @@
       <c r="BR28">
         <v>5832</v>
       </c>
-      <c r="BS28" t="s">
+      <c r="BS28" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT28">
         <v>0</v>
       </c>
-      <c r="BU28" t="s">
+      <c r="BU28" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV28" t="s">
@@ -10651,10 +10666,10 @@
       <c r="AQ29">
         <v>1.4183178723417127</v>
       </c>
-      <c r="AR29">
+      <c r="AR29" s="1">
         <v>166.66666666666666</v>
       </c>
-      <c r="AS29">
+      <c r="AS29" s="1">
         <v>141.66574310096419</v>
       </c>
       <c r="AT29" s="1">
@@ -10690,7 +10705,7 @@
       <c r="BD29">
         <v>1973624</v>
       </c>
-      <c r="BE29">
+      <c r="BE29" s="1">
         <v>23418.223345568389</v>
       </c>
       <c r="BF29">
@@ -10732,13 +10747,13 @@
       <c r="BR29">
         <v>105117</v>
       </c>
-      <c r="BS29">
+      <c r="BS29" s="1">
         <v>61471.929824561405</v>
       </c>
       <c r="BT29">
         <v>42383</v>
       </c>
-      <c r="BU29">
+      <c r="BU29" s="1">
         <v>24785.380116959066</v>
       </c>
       <c r="BV29">
@@ -10965,10 +10980,10 @@
       <c r="AQ30">
         <v>0.27469886724098524</v>
       </c>
-      <c r="AR30">
+      <c r="AR30" s="1">
         <v>2.5</v>
       </c>
-      <c r="AS30">
+      <c r="AS30" s="1">
         <v>1.8842195775718491</v>
       </c>
       <c r="AT30" s="1">
@@ -11004,7 +11019,7 @@
       <c r="BD30" t="s">
         <v>218</v>
       </c>
-      <c r="BE30" t="s">
+      <c r="BE30" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF30" t="s">
@@ -11043,13 +11058,13 @@
       <c r="BR30">
         <v>22057</v>
       </c>
-      <c r="BS30">
+      <c r="BS30" s="1">
         <v>44114</v>
       </c>
       <c r="BT30">
         <v>11987</v>
       </c>
-      <c r="BU30">
+      <c r="BU30" s="1">
         <v>23974</v>
       </c>
       <c r="BV30">
@@ -11276,10 +11291,10 @@
       <c r="AQ31">
         <v>1.9036463838227026E-2</v>
       </c>
-      <c r="AR31">
+      <c r="AR31" s="1">
         <v>25.083333333333332</v>
       </c>
-      <c r="AS31">
+      <c r="AS31" s="1">
         <v>15.233547965255553</v>
       </c>
       <c r="AT31" s="1">
@@ -11315,7 +11330,7 @@
       <c r="BD31">
         <v>131039</v>
       </c>
-      <c r="BE31">
+      <c r="BE31" s="1">
         <v>15461.974570823444</v>
       </c>
       <c r="BF31">
@@ -11357,13 +11372,13 @@
       <c r="BR31">
         <v>238438</v>
       </c>
-      <c r="BS31">
+      <c r="BS31" s="1">
         <v>38028.38915470495</v>
       </c>
       <c r="BT31">
         <v>169391</v>
       </c>
-      <c r="BU31">
+      <c r="BU31" s="1">
         <v>27016.108452950561</v>
       </c>
       <c r="BV31">
@@ -11590,10 +11605,10 @@
       <c r="AQ32">
         <v>12.900192323575569</v>
       </c>
-      <c r="AR32">
+      <c r="AR32" s="1">
         <v>233.25</v>
       </c>
-      <c r="AS32">
+      <c r="AS32" s="1">
         <v>175.79768658745354</v>
       </c>
       <c r="AT32" s="1">
@@ -11629,7 +11644,7 @@
       <c r="BD32">
         <v>7248111</v>
       </c>
-      <c r="BE32">
+      <c r="BE32" s="1">
         <v>35252.600868349888</v>
       </c>
       <c r="BF32">
@@ -11671,13 +11686,13 @@
       <c r="BR32">
         <v>9945334</v>
       </c>
-      <c r="BS32">
+      <c r="BS32" s="1">
         <v>50196.002624539447</v>
       </c>
       <c r="BT32">
         <v>7105386</v>
       </c>
-      <c r="BU32">
+      <c r="BU32" s="1">
         <v>35862.241962347951</v>
       </c>
       <c r="BV32">
@@ -11904,10 +11919,10 @@
       <c r="AQ33">
         <v>0.1869263868841744</v>
       </c>
-      <c r="AR33">
+      <c r="AR33" s="1">
         <v>89.375</v>
       </c>
-      <c r="AS33">
+      <c r="AS33" s="1">
         <v>54.279003962580013</v>
       </c>
       <c r="AT33" s="1">
@@ -11943,7 +11958,7 @@
       <c r="BD33">
         <v>391321</v>
       </c>
-      <c r="BE33">
+      <c r="BE33" s="1">
         <v>19338.339611393938</v>
       </c>
       <c r="BF33">
@@ -11985,13 +12000,13 @@
       <c r="BR33">
         <v>0</v>
       </c>
-      <c r="BS33" t="s">
+      <c r="BS33" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT33">
         <v>0</v>
       </c>
-      <c r="BU33" t="s">
+      <c r="BU33" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV33" t="s">
@@ -12218,10 +12233,10 @@
       <c r="AQ34">
         <v>0.25908040690735079</v>
       </c>
-      <c r="AR34">
+      <c r="AR34" s="1">
         <v>23.75</v>
       </c>
-      <c r="AS34">
+      <c r="AS34" s="1">
         <v>16.479978097591015</v>
       </c>
       <c r="AT34" s="1">
@@ -12257,7 +12272,7 @@
       <c r="BD34">
         <v>211771</v>
       </c>
-      <c r="BE34">
+      <c r="BE34" s="1">
         <v>16361.677399719827</v>
       </c>
       <c r="BF34">
@@ -12299,13 +12314,13 @@
       <c r="BR34">
         <v>49598</v>
       </c>
-      <c r="BS34">
+      <c r="BS34" s="1">
         <v>38748.4375</v>
       </c>
       <c r="BT34">
         <v>39311</v>
       </c>
-      <c r="BU34">
+      <c r="BU34" s="1">
         <v>30711.71875</v>
       </c>
       <c r="BV34">
@@ -12532,10 +12547,10 @@
       <c r="AQ35">
         <v>0.18603130387519212</v>
       </c>
-      <c r="AR35">
+      <c r="AR35" s="1">
         <v>53.333333333333329</v>
       </c>
-      <c r="AS35">
+      <c r="AS35" s="1">
         <v>32.390268098882238</v>
       </c>
       <c r="AT35" s="1">
@@ -12571,7 +12586,7 @@
       <c r="BD35">
         <v>380490</v>
       </c>
-      <c r="BE35">
+      <c r="BE35" s="1">
         <v>17200.247130265332</v>
       </c>
       <c r="BF35">
@@ -12613,13 +12628,13 @@
       <c r="BR35">
         <v>160949</v>
       </c>
-      <c r="BS35">
+      <c r="BS35" s="1">
         <v>27372.278911564626</v>
       </c>
       <c r="BT35">
         <v>144047</v>
       </c>
-      <c r="BU35">
+      <c r="BU35" s="1">
         <v>24497.789115646257</v>
       </c>
       <c r="BV35">
@@ -12846,10 +12861,10 @@
       <c r="AQ36">
         <v>9.7162292540271888</v>
       </c>
-      <c r="AR36">
+      <c r="AR36" s="1">
         <v>213.83333333333334</v>
       </c>
-      <c r="AS36">
+      <c r="AS36" s="1">
         <v>168.25960160895875</v>
       </c>
       <c r="AT36" s="1">
@@ -12885,7 +12900,7 @@
       <c r="BD36">
         <v>271477</v>
       </c>
-      <c r="BE36">
+      <c r="BE36" s="1">
         <v>15430.067470677732</v>
       </c>
       <c r="BF36">
@@ -12927,13 +12942,13 @@
       <c r="BR36">
         <v>124996</v>
       </c>
-      <c r="BS36">
+      <c r="BS36" s="1">
         <v>114675.22935779818</v>
       </c>
       <c r="BT36">
         <v>29847</v>
       </c>
-      <c r="BU36">
+      <c r="BU36" s="1">
         <v>27382.568807339452</v>
       </c>
       <c r="BV36">
@@ -13160,10 +13175,10 @@
       <c r="AQ37">
         <v>0.35435087890079264</v>
       </c>
-      <c r="AR37">
+      <c r="AR37" s="1">
         <v>711.75</v>
       </c>
-      <c r="AS37">
+      <c r="AS37" s="1">
         <v>432.25824973836444</v>
       </c>
       <c r="AT37" s="1">
@@ -13199,7 +13214,7 @@
       <c r="BD37">
         <v>5792015</v>
       </c>
-      <c r="BE37">
+      <c r="BE37" s="1">
         <v>20253.739722537095</v>
       </c>
       <c r="BF37">
@@ -13241,13 +13256,13 @@
       <c r="BR37">
         <v>1475061</v>
       </c>
-      <c r="BS37">
+      <c r="BS37" s="1">
         <v>62982.963279248514</v>
       </c>
       <c r="BT37">
         <v>829672</v>
       </c>
-      <c r="BU37">
+      <c r="BU37" s="1">
         <v>35425.789923142613</v>
       </c>
       <c r="BV37">
@@ -13474,10 +13489,10 @@
       <c r="AQ38">
         <v>0</v>
       </c>
-      <c r="AR38">
+      <c r="AR38" s="1">
         <v>10.833333333333332</v>
       </c>
-      <c r="AS38">
+      <c r="AS38" s="1">
         <v>7.2039100553813293</v>
       </c>
       <c r="AT38" s="1">
@@ -13513,7 +13528,7 @@
       <c r="BD38">
         <v>50069</v>
       </c>
-      <c r="BE38">
+      <c r="BE38" s="1">
         <v>13151.148379416272</v>
       </c>
       <c r="BF38">
@@ -13555,13 +13570,13 @@
       <c r="BR38">
         <v>0</v>
       </c>
-      <c r="BS38" t="s">
+      <c r="BS38" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT38">
         <v>0</v>
       </c>
-      <c r="BU38" t="s">
+      <c r="BU38" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV38" t="s">
@@ -13788,10 +13803,10 @@
       <c r="AQ39">
         <v>0.47945205479452058</v>
       </c>
-      <c r="AR39">
+      <c r="AR39" s="1">
         <v>137.95833333333331</v>
       </c>
-      <c r="AS39">
+      <c r="AS39" s="1">
         <v>97.050913384732922</v>
       </c>
       <c r="AT39" s="1">
@@ -13827,7 +13842,7 @@
       <c r="BD39">
         <v>1019431</v>
       </c>
-      <c r="BE39">
+      <c r="BE39" s="1">
         <v>23698.164561510701</v>
       </c>
       <c r="BF39">
@@ -13869,13 +13884,13 @@
       <c r="BR39">
         <v>216080</v>
       </c>
-      <c r="BS39">
+      <c r="BS39" s="1">
         <v>187895.65217391305</v>
       </c>
       <c r="BT39">
         <v>37550</v>
       </c>
-      <c r="BU39">
+      <c r="BU39" s="1">
         <v>32652.17391304348</v>
       </c>
       <c r="BV39">
@@ -14102,10 +14117,10 @@
       <c r="AQ40">
         <v>2.4874750376624743E-2</v>
       </c>
-      <c r="AR40">
+      <c r="AR40" s="1">
         <v>59.5</v>
       </c>
-      <c r="AS40">
+      <c r="AS40" s="1">
         <v>39.566090611863615</v>
       </c>
       <c r="AT40" s="1">
@@ -14141,7 +14156,7 @@
       <c r="BD40">
         <v>610549</v>
       </c>
-      <c r="BE40">
+      <c r="BE40" s="1">
         <v>21846.485068780614</v>
       </c>
       <c r="BF40">
@@ -14183,13 +14198,13 @@
       <c r="BR40">
         <v>166948</v>
       </c>
-      <c r="BS40">
+      <c r="BS40" s="1">
         <v>157498.11320754717</v>
       </c>
       <c r="BT40">
         <v>32058</v>
       </c>
-      <c r="BU40">
+      <c r="BU40" s="1">
         <v>30243.396226415094</v>
       </c>
       <c r="BV40">
@@ -14416,10 +14431,10 @@
       <c r="AQ41">
         <v>0.52935331872288316</v>
       </c>
-      <c r="AR41">
+      <c r="AR41" s="1">
         <v>106.875</v>
       </c>
-      <c r="AS41">
+      <c r="AS41" s="1">
         <v>71.926395277224486</v>
       </c>
       <c r="AT41" s="1">
@@ -14455,7 +14470,7 @@
       <c r="BD41">
         <v>1069804</v>
       </c>
-      <c r="BE41">
+      <c r="BE41" s="1">
         <v>21358.893317137754</v>
       </c>
       <c r="BF41">
@@ -14497,13 +14512,13 @@
       <c r="BR41">
         <v>95117</v>
       </c>
-      <c r="BS41">
+      <c r="BS41" s="1">
         <v>32574.31506849315</v>
       </c>
       <c r="BT41">
         <v>56890</v>
       </c>
-      <c r="BU41">
+      <c r="BU41" s="1">
         <v>19482.876712328769</v>
       </c>
       <c r="BV41">
@@ -14730,10 +14745,10 @@
       <c r="AQ42">
         <v>6.5024106715477994E-2</v>
       </c>
-      <c r="AR42">
+      <c r="AR42" s="1">
         <v>22.75</v>
       </c>
-      <c r="AS42">
+      <c r="AS42" s="1">
         <v>15.128211116300795</v>
       </c>
       <c r="AT42" s="1">
@@ -14769,7 +14784,7 @@
       <c r="BD42" t="s">
         <v>218</v>
       </c>
-      <c r="BE42" t="s">
+      <c r="BE42" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF42" t="s">
@@ -14808,13 +14823,13 @@
       <c r="BR42">
         <v>0</v>
       </c>
-      <c r="BS42" t="s">
+      <c r="BS42" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT42">
         <v>0</v>
       </c>
-      <c r="BU42" t="s">
+      <c r="BU42" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV42" t="s">
@@ -15041,10 +15056,10 @@
       <c r="AQ43">
         <v>6.2132108569515179</v>
       </c>
-      <c r="AR43">
+      <c r="AR43" s="1">
         <v>88.583333333333343</v>
       </c>
-      <c r="AS43">
+      <c r="AS43" s="1">
         <v>59.616185715157613</v>
       </c>
       <c r="AT43" s="1">
@@ -15080,7 +15095,7 @@
       <c r="BD43">
         <v>1300819</v>
       </c>
-      <c r="BE43">
+      <c r="BE43" s="1">
         <v>22022.019195727451</v>
       </c>
       <c r="BF43">
@@ -15122,13 +15137,13 @@
       <c r="BR43">
         <v>1170005</v>
       </c>
-      <c r="BS43">
+      <c r="BS43" s="1">
         <v>53182.045454545463</v>
       </c>
       <c r="BT43">
         <v>634579</v>
       </c>
-      <c r="BU43">
+      <c r="BU43" s="1">
         <v>28844.500000000004</v>
       </c>
       <c r="BV43">
@@ -15355,10 +15370,10 @@
       <c r="AQ44">
         <v>0.11730676006690402</v>
       </c>
-      <c r="AR44">
+      <c r="AR44" s="1">
         <v>192.08333333333331</v>
       </c>
-      <c r="AS44">
+      <c r="AS44" s="1">
         <v>133.28543689455188</v>
       </c>
       <c r="AT44" s="1">
@@ -15394,7 +15409,7 @@
       <c r="BD44">
         <v>1842811</v>
       </c>
-      <c r="BE44">
+      <c r="BE44" s="1">
         <v>20725.327197393282</v>
       </c>
       <c r="BF44">
@@ -15436,13 +15451,13 @@
       <c r="BR44">
         <v>790576</v>
       </c>
-      <c r="BS44">
+      <c r="BS44" s="1">
         <v>63962.459546925573</v>
       </c>
       <c r="BT44">
         <v>335467</v>
       </c>
-      <c r="BU44">
+      <c r="BU44" s="1">
         <v>27141.343042071199</v>
       </c>
       <c r="BV44">
@@ -15669,10 +15684,10 @@
       <c r="AQ45">
         <v>0.23613930305960867</v>
       </c>
-      <c r="AR45">
+      <c r="AR45" s="1">
         <v>25.958333333333336</v>
       </c>
-      <c r="AS45">
+      <c r="AS45" s="1">
         <v>19.564479947121036</v>
       </c>
       <c r="AT45" s="1">
@@ -15708,7 +15723,7 @@
       <c r="BD45">
         <v>231097</v>
       </c>
-      <c r="BE45">
+      <c r="BE45" s="1">
         <v>19884.211124180998</v>
       </c>
       <c r="BF45">
@@ -15750,13 +15765,13 @@
       <c r="BR45">
         <v>359532</v>
       </c>
-      <c r="BS45">
+      <c r="BS45" s="1">
         <v>57989.032258064515</v>
       </c>
       <c r="BT45">
         <v>296839</v>
       </c>
-      <c r="BU45">
+      <c r="BU45" s="1">
         <v>47877.258064516129</v>
       </c>
       <c r="BV45">
@@ -15983,10 +15998,10 @@
       <c r="AQ46">
         <v>0.33791791846972247</v>
       </c>
-      <c r="AR46">
+      <c r="AR46" s="1">
         <v>48.75</v>
       </c>
-      <c r="AS46">
+      <c r="AS46" s="1">
         <v>33.827323463476297</v>
       </c>
       <c r="AT46" s="1">
@@ -16022,7 +16037,7 @@
       <c r="BD46">
         <v>740902</v>
       </c>
-      <c r="BE46">
+      <c r="BE46" s="1">
         <v>21175.88610062141</v>
       </c>
       <c r="BF46">
@@ -16064,13 +16079,13 @@
       <c r="BR46">
         <v>714946</v>
       </c>
-      <c r="BS46">
+      <c r="BS46" s="1">
         <v>26887.777359909742</v>
       </c>
       <c r="BT46">
         <v>724513</v>
       </c>
-      <c r="BU46">
+      <c r="BU46" s="1">
         <v>27247.574276043626</v>
       </c>
       <c r="BV46">
@@ -16297,10 +16312,10 @@
       <c r="AQ47">
         <v>0.13271838645281198</v>
       </c>
-      <c r="AR47">
+      <c r="AR47" s="1">
         <v>49.333333333333336</v>
       </c>
-      <c r="AS47">
+      <c r="AS47" s="1">
         <v>34.232094855346951</v>
       </c>
       <c r="AT47" s="1">
@@ -16336,7 +16351,7 @@
       <c r="BD47">
         <v>260413</v>
       </c>
-      <c r="BE47">
+      <c r="BE47" s="1">
         <v>19602.881370324943</v>
       </c>
       <c r="BF47">
@@ -16378,13 +16393,13 @@
       <c r="BR47">
         <v>0</v>
       </c>
-      <c r="BS47" t="s">
+      <c r="BS47" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT47">
         <v>0</v>
       </c>
-      <c r="BU47" t="s">
+      <c r="BU47" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV47" t="s">
@@ -16611,10 +16626,10 @@
       <c r="AQ48">
         <v>0.28489505705890139</v>
       </c>
-      <c r="AR48">
+      <c r="AR48" s="1">
         <v>351.95833333333337</v>
       </c>
-      <c r="AS48">
+      <c r="AS48" s="1">
         <v>213.75046455567062</v>
       </c>
       <c r="AT48" s="1">
@@ -16650,7 +16665,7 @@
       <c r="BD48">
         <v>4150496</v>
       </c>
-      <c r="BE48">
+      <c r="BE48" s="1">
         <v>27440.747595831013</v>
       </c>
       <c r="BF48">
@@ -16692,13 +16707,13 @@
       <c r="BR48">
         <v>1513323</v>
       </c>
-      <c r="BS48">
+      <c r="BS48" s="1">
         <v>39327.520790020782</v>
       </c>
       <c r="BT48">
         <v>1137035</v>
       </c>
-      <c r="BU48">
+      <c r="BU48" s="1">
         <v>29548.726611226608</v>
       </c>
       <c r="BV48">
@@ -16925,10 +16940,10 @@
       <c r="AQ49">
         <v>0.66756030338054562</v>
       </c>
-      <c r="AR49">
+      <c r="AR49" s="1">
         <v>74.041666666666657</v>
       </c>
-      <c r="AS49">
+      <c r="AS49" s="1">
         <v>49.235954493894702</v>
       </c>
       <c r="AT49" s="1">
@@ -16964,7 +16979,7 @@
       <c r="BD49">
         <v>896337</v>
       </c>
-      <c r="BE49">
+      <c r="BE49" s="1">
         <v>21247.152674480407</v>
       </c>
       <c r="BF49">
@@ -17006,13 +17021,13 @@
       <c r="BR49">
         <v>530306</v>
       </c>
-      <c r="BS49">
+      <c r="BS49" s="1">
         <v>42560.674157303365</v>
       </c>
       <c r="BT49">
         <v>262934</v>
       </c>
-      <c r="BU49">
+      <c r="BU49" s="1">
         <v>21102.247191011236</v>
       </c>
       <c r="BV49">
@@ -17239,10 +17254,10 @@
       <c r="AQ50">
         <v>1.3901147598951133</v>
       </c>
-      <c r="AR50">
+      <c r="AR50" s="1">
         <v>193.95833333333331</v>
       </c>
-      <c r="AS50">
+      <c r="AS50" s="1">
         <v>128.97769733769266</v>
       </c>
       <c r="AT50" s="1">
@@ -17278,7 +17293,7 @@
       <c r="BD50">
         <v>1894610</v>
       </c>
-      <c r="BE50">
+      <c r="BE50" s="1">
         <v>19869.350510783697</v>
       </c>
       <c r="BF50">
@@ -17320,13 +17335,13 @@
       <c r="BR50">
         <v>92681</v>
       </c>
-      <c r="BS50">
+      <c r="BS50" s="1">
         <v>26480.285714285714</v>
       </c>
       <c r="BT50">
         <v>63012</v>
       </c>
-      <c r="BU50">
+      <c r="BU50" s="1">
         <v>18003.428571428572</v>
       </c>
       <c r="BV50">
@@ -17553,10 +17568,10 @@
       <c r="AQ51">
         <v>1.0824719007370813</v>
       </c>
-      <c r="AR51">
+      <c r="AR51" s="1">
         <v>1.0918727806362312</v>
       </c>
-      <c r="AS51">
+      <c r="AS51" s="1">
         <v>0.75764376885224805</v>
       </c>
       <c r="AT51" s="1">
@@ -17592,7 +17607,7 @@
       <c r="BD51">
         <v>21520</v>
       </c>
-      <c r="BE51">
+      <c r="BE51" s="1">
         <v>21520</v>
       </c>
       <c r="BF51">
@@ -17634,13 +17649,13 @@
       <c r="BR51">
         <v>0</v>
       </c>
-      <c r="BS51" t="s">
+      <c r="BS51" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT51">
         <v>0</v>
       </c>
-      <c r="BU51" t="s">
+      <c r="BU51" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV51" t="s">
@@ -17867,10 +17882,10 @@
       <c r="AQ52">
         <v>0</v>
       </c>
-      <c r="AR52">
+      <c r="AR52" s="1">
         <v>12.5</v>
       </c>
-      <c r="AS52">
+      <c r="AS52" s="1">
         <v>7.5914690856755271</v>
       </c>
       <c r="AT52" s="1">
@@ -17906,7 +17921,7 @@
       <c r="BD52">
         <v>531740</v>
       </c>
-      <c r="BE52">
+      <c r="BE52" s="1">
         <v>21344.752785824458</v>
       </c>
       <c r="BF52">
@@ -17948,13 +17963,13 @@
       <c r="BR52">
         <v>0</v>
       </c>
-      <c r="BS52" t="s">
+      <c r="BS52" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT52">
         <v>0</v>
       </c>
-      <c r="BU52" t="s">
+      <c r="BU52" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV52" t="s">
@@ -18181,10 +18196,10 @@
       <c r="AQ53">
         <v>8.3139921832413768E-2</v>
       </c>
-      <c r="AR53">
+      <c r="AR53" s="1">
         <v>90.666666666666657</v>
       </c>
-      <c r="AS53">
+      <c r="AS53" s="1">
         <v>59.455180442374854</v>
       </c>
       <c r="AT53" s="1">
@@ -18220,7 +18235,7 @@
       <c r="BD53">
         <v>633180</v>
       </c>
-      <c r="BE53">
+      <c r="BE53" s="1">
         <v>20092.750807520639</v>
       </c>
       <c r="BF53">
@@ -18262,13 +18277,13 @@
       <c r="BR53">
         <v>6475</v>
       </c>
-      <c r="BS53" t="s">
+      <c r="BS53" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT53">
         <v>5113</v>
       </c>
-      <c r="BU53" t="s">
+      <c r="BU53" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV53">
@@ -18495,10 +18510,10 @@
       <c r="AQ54">
         <v>1.6668873192271449</v>
       </c>
-      <c r="AR54">
+      <c r="AR54" s="1">
         <v>183.91666666666666</v>
       </c>
-      <c r="AS54">
+      <c r="AS54" s="1">
         <v>156.32814751191398</v>
       </c>
       <c r="AT54" s="1">
@@ -18534,7 +18549,7 @@
       <c r="BD54">
         <v>3811411</v>
       </c>
-      <c r="BE54">
+      <c r="BE54" s="1">
         <v>26246.894025186411</v>
       </c>
       <c r="BF54">
@@ -18576,13 +18591,13 @@
       <c r="BR54">
         <v>2098929</v>
       </c>
-      <c r="BS54">
+      <c r="BS54" s="1">
         <v>48575.075214070814</v>
       </c>
       <c r="BT54">
         <v>1600983</v>
       </c>
-      <c r="BU54">
+      <c r="BU54" s="1">
         <v>37051.214996528579</v>
       </c>
       <c r="BV54">
@@ -18809,10 +18824,10 @@
       <c r="AQ55">
         <v>0.58672703549121508</v>
       </c>
-      <c r="AR55">
+      <c r="AR55" s="1">
         <v>170.75</v>
       </c>
-      <c r="AS55">
+      <c r="AS55" s="1">
         <v>102.22067235947607</v>
       </c>
       <c r="AT55" s="1">
@@ -18848,7 +18863,7 @@
       <c r="BD55">
         <v>2421671</v>
       </c>
-      <c r="BE55">
+      <c r="BE55" s="1">
         <v>25826.114025802526</v>
       </c>
       <c r="BF55">
@@ -18890,13 +18905,13 @@
       <c r="BR55">
         <v>284648</v>
       </c>
-      <c r="BS55">
+      <c r="BS55" s="1">
         <v>55813.333333333336</v>
       </c>
       <c r="BT55">
         <v>128307</v>
       </c>
-      <c r="BU55">
+      <c r="BU55" s="1">
         <v>25158.23529411765</v>
       </c>
       <c r="BV55">
@@ -19123,10 +19138,10 @@
       <c r="AQ56">
         <v>0.20041235672351132</v>
       </c>
-      <c r="AR56">
+      <c r="AR56" s="1">
         <v>64.375</v>
       </c>
-      <c r="AS56">
+      <c r="AS56" s="1">
         <v>39.096065791228959</v>
       </c>
       <c r="AT56" s="1">
@@ -19162,7 +19177,7 @@
       <c r="BD56">
         <v>100927</v>
       </c>
-      <c r="BE56">
+      <c r="BE56" s="1">
         <v>5901.4624695168768</v>
       </c>
       <c r="BF56">
@@ -19204,13 +19219,13 @@
       <c r="BR56">
         <v>316497</v>
       </c>
-      <c r="BS56">
+      <c r="BS56" s="1">
         <v>72591.055045871573</v>
       </c>
       <c r="BT56">
         <v>150571</v>
       </c>
-      <c r="BU56">
+      <c r="BU56" s="1">
         <v>34534.633027522941</v>
       </c>
       <c r="BV56">
@@ -19437,10 +19452,10 @@
       <c r="AQ57">
         <v>0.29423404334258119</v>
       </c>
-      <c r="AR57">
+      <c r="AR57" s="1">
         <v>178.66666666666669</v>
       </c>
-      <c r="AS57">
+      <c r="AS57" s="1">
         <v>116.06741747572816</v>
       </c>
       <c r="AT57" s="1">
@@ -19476,7 +19491,7 @@
       <c r="BD57">
         <v>1401359</v>
       </c>
-      <c r="BE57">
+      <c r="BE57" s="1">
         <v>17009.393334446304</v>
       </c>
       <c r="BF57">
@@ -19518,13 +19533,13 @@
       <c r="BR57">
         <v>115120</v>
       </c>
-      <c r="BS57">
+      <c r="BS57" s="1">
         <v>24971.800433839482</v>
       </c>
       <c r="BT57">
         <v>108479</v>
       </c>
-      <c r="BU57">
+      <c r="BU57" s="1">
         <v>23531.23644251627</v>
       </c>
       <c r="BV57">
@@ -19751,10 +19766,10 @@
       <c r="AQ58">
         <v>0.17375523940438381</v>
       </c>
-      <c r="AR58">
+      <c r="AR58" s="1">
         <v>234.375</v>
       </c>
-      <c r="AS58">
+      <c r="AS58" s="1">
         <v>142.34004535641611</v>
       </c>
       <c r="AT58" s="1">
@@ -19790,7 +19805,7 @@
       <c r="BD58">
         <v>2264452</v>
       </c>
-      <c r="BE58">
+      <c r="BE58" s="1">
         <v>19329.949071704039</v>
       </c>
       <c r="BF58">
@@ -19832,13 +19847,13 @@
       <c r="BR58">
         <v>524441</v>
       </c>
-      <c r="BS58">
+      <c r="BS58" s="1">
         <v>52235.159362549806</v>
       </c>
       <c r="BT58">
         <v>229355</v>
       </c>
-      <c r="BU58">
+      <c r="BU58" s="1">
         <v>22844.123505976098</v>
       </c>
       <c r="BV58">
@@ -20065,10 +20080,10 @@
       <c r="AQ59">
         <v>9.4146782675780241</v>
       </c>
-      <c r="AR59">
+      <c r="AR59" s="1">
         <v>781.91666666666663</v>
       </c>
-      <c r="AS59">
+      <c r="AS59" s="1">
         <v>664.62483375817362</v>
       </c>
       <c r="AT59" s="1">
@@ -20104,7 +20119,7 @@
       <c r="BD59">
         <v>12877165</v>
       </c>
-      <c r="BE59">
+      <c r="BE59" s="1">
         <v>27718.179075210166</v>
       </c>
       <c r="BF59">
@@ -20146,13 +20161,13 @@
       <c r="BR59">
         <v>11536810</v>
       </c>
-      <c r="BS59">
+      <c r="BS59" s="1">
         <v>54329.220626324473</v>
       </c>
       <c r="BT59">
         <v>7543644</v>
       </c>
-      <c r="BU59">
+      <c r="BU59" s="1">
         <v>35524.577348716746</v>
       </c>
       <c r="BV59">
@@ -20379,10 +20394,10 @@
       <c r="AQ60">
         <v>0.49618120029429286</v>
       </c>
-      <c r="AR60">
+      <c r="AR60" s="1">
         <v>337.91666666666663</v>
       </c>
-      <c r="AS60">
+      <c r="AS60" s="1">
         <v>227.41639988237446</v>
       </c>
       <c r="AT60" s="1">
@@ -20418,7 +20433,7 @@
       <c r="BD60">
         <v>1650163</v>
       </c>
-      <c r="BE60">
+      <c r="BE60" s="1">
         <v>14387.481524388957</v>
       </c>
       <c r="BF60">
@@ -20460,13 +20475,13 @@
       <c r="BR60">
         <v>142592</v>
       </c>
-      <c r="BS60">
+      <c r="BS60" s="1">
         <v>128461.26126126124</v>
       </c>
       <c r="BT60">
         <v>18935</v>
       </c>
-      <c r="BU60">
+      <c r="BU60" s="1">
         <v>17058.558558558558</v>
       </c>
       <c r="BV60">
@@ -20693,10 +20708,10 @@
       <c r="AQ61">
         <v>13.126076613895499</v>
       </c>
-      <c r="AR61">
+      <c r="AR61" s="1">
         <v>27.625</v>
       </c>
-      <c r="AS61">
+      <c r="AS61" s="1">
         <v>18.591501001481415</v>
       </c>
       <c r="AT61" s="1">
@@ -20732,7 +20747,7 @@
       <c r="BD61">
         <v>471370</v>
       </c>
-      <c r="BE61">
+      <c r="BE61" s="1">
         <v>24123.453970784351</v>
       </c>
       <c r="BF61">
@@ -20774,13 +20789,13 @@
       <c r="BR61">
         <v>230803</v>
       </c>
-      <c r="BS61">
+      <c r="BS61" s="1">
         <v>33353.034682080928</v>
       </c>
       <c r="BT61">
         <v>153891</v>
       </c>
-      <c r="BU61">
+      <c r="BU61" s="1">
         <v>22238.583815028902</v>
       </c>
       <c r="BV61">
@@ -21007,10 +21022,10 @@
       <c r="AQ62">
         <v>8.1915242225853224E-2</v>
       </c>
-      <c r="AR62">
+      <c r="AR62" s="1">
         <v>27.666666666666668</v>
       </c>
-      <c r="AS62">
+      <c r="AS62" s="1">
         <v>18.397677987589244</v>
       </c>
       <c r="AT62" s="1">
@@ -21046,7 +21061,7 @@
       <c r="BD62">
         <v>307277</v>
       </c>
-      <c r="BE62">
+      <c r="BE62" s="1">
         <v>21932.865477563137</v>
       </c>
       <c r="BF62">
@@ -21088,13 +21103,13 @@
       <c r="BR62">
         <v>0</v>
       </c>
-      <c r="BS62" t="s">
+      <c r="BS62" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT62">
         <v>0</v>
       </c>
-      <c r="BU62" t="s">
+      <c r="BU62" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV62" t="s">
@@ -21321,10 +21336,10 @@
       <c r="AQ63">
         <v>0.80981375896809327</v>
       </c>
-      <c r="AR63">
+      <c r="AR63" s="1">
         <v>649.125</v>
       </c>
-      <c r="AS63">
+      <c r="AS63" s="1">
         <v>394.22498961913004</v>
       </c>
       <c r="AT63" s="1">
@@ -21360,7 +21375,7 @@
       <c r="BD63">
         <v>5654597</v>
       </c>
-      <c r="BE63">
+      <c r="BE63" s="1">
         <v>22666.586612805098</v>
       </c>
       <c r="BF63">
@@ -21402,13 +21417,13 @@
       <c r="BR63">
         <v>2899145</v>
       </c>
-      <c r="BS63">
+      <c r="BS63" s="1">
         <v>54960.094786729867</v>
       </c>
       <c r="BT63">
         <v>1617844</v>
       </c>
-      <c r="BU63">
+      <c r="BU63" s="1">
         <v>30670.028436018962</v>
       </c>
       <c r="BV63">
@@ -21635,10 +21650,10 @@
       <c r="AQ64">
         <v>0.71440888955950976</v>
       </c>
-      <c r="AR64">
+      <c r="AR64" s="1">
         <v>85.666666666666671</v>
       </c>
-      <c r="AS64">
+      <c r="AS64" s="1">
         <v>51.284944453656124</v>
       </c>
       <c r="AT64" s="1">
@@ -21674,7 +21689,7 @@
       <c r="BD64">
         <v>828282</v>
       </c>
-      <c r="BE64">
+      <c r="BE64" s="1">
         <v>21894.256690621889</v>
       </c>
       <c r="BF64">
@@ -21716,13 +21731,13 @@
       <c r="BR64">
         <v>104805</v>
       </c>
-      <c r="BS64">
+      <c r="BS64" s="1">
         <v>30915.929203539821</v>
       </c>
       <c r="BT64">
         <v>85613</v>
       </c>
-      <c r="BU64">
+      <c r="BU64" s="1">
         <v>25254.572271386431</v>
       </c>
       <c r="BV64">
@@ -21949,10 +21964,10 @@
       <c r="AQ65">
         <v>4.3595626488890669E-2</v>
       </c>
-      <c r="AR65">
+      <c r="AR65" s="1">
         <v>131.29166666666669</v>
       </c>
-      <c r="AS65">
+      <c r="AS65" s="1">
         <v>87.305848401948367</v>
       </c>
       <c r="AT65" s="1">
@@ -21988,7 +22003,7 @@
       <c r="BD65">
         <v>2486590</v>
       </c>
-      <c r="BE65">
+      <c r="BE65" s="1">
         <v>26724.23083784401</v>
       </c>
       <c r="BF65">
@@ -22030,13 +22045,13 @@
       <c r="BR65">
         <v>18635</v>
       </c>
-      <c r="BS65" t="s">
+      <c r="BS65" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT65">
         <v>0</v>
       </c>
-      <c r="BU65" t="s">
+      <c r="BU65" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV65" t="s">
@@ -22263,10 +22278,10 @@
       <c r="AQ66">
         <v>15.189038383961654</v>
       </c>
-      <c r="AR66">
+      <c r="AR66" s="1">
         <v>218.625</v>
       </c>
-      <c r="AS66">
+      <c r="AS66" s="1">
         <v>130.88137332117395</v>
       </c>
       <c r="AT66" s="1">
@@ -22302,7 +22317,7 @@
       <c r="BD66">
         <v>3520280</v>
       </c>
-      <c r="BE66">
+      <c r="BE66" s="1">
         <v>27799.318704128178</v>
       </c>
       <c r="BF66">
@@ -22344,13 +22359,13 @@
       <c r="BR66">
         <v>2738474</v>
       </c>
-      <c r="BS66">
+      <c r="BS66" s="1">
         <v>54002.642476829009</v>
       </c>
       <c r="BT66">
         <v>1603262</v>
       </c>
-      <c r="BU66">
+      <c r="BU66" s="1">
         <v>31616.288700453551</v>
       </c>
       <c r="BV66">
@@ -22577,10 +22592,10 @@
       <c r="AQ67">
         <v>0.1482234589041096</v>
       </c>
-      <c r="AR67">
+      <c r="AR67" s="1">
         <v>7</v>
       </c>
-      <c r="AS67">
+      <c r="AS67" s="1">
         <v>4.8572567024478781</v>
       </c>
       <c r="AT67" s="1">
@@ -22616,7 +22631,7 @@
       <c r="BD67">
         <v>92287</v>
       </c>
-      <c r="BE67">
+      <c r="BE67" s="1">
         <v>26069.915122621474</v>
       </c>
       <c r="BF67">
@@ -22658,13 +22673,13 @@
       <c r="BR67">
         <v>0</v>
       </c>
-      <c r="BS67" t="s">
+      <c r="BS67" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT67">
         <v>0</v>
       </c>
-      <c r="BU67" t="s">
+      <c r="BU67" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV67" t="s">
@@ -22891,10 +22906,10 @@
       <c r="AQ68">
         <v>0.53010105259467655</v>
       </c>
-      <c r="AR68">
+      <c r="AR68" s="1">
         <v>210.33333333333331</v>
       </c>
-      <c r="AS68">
+      <c r="AS68" s="1">
         <v>165.50554733476687</v>
       </c>
       <c r="AT68" s="1">
@@ -22930,7 +22945,7 @@
       <c r="BD68">
         <v>2118716</v>
       </c>
-      <c r="BE68">
+      <c r="BE68" s="1">
         <v>22301.318358380686</v>
       </c>
       <c r="BF68">
@@ -22972,13 +22987,13 @@
       <c r="BR68">
         <v>156610</v>
       </c>
-      <c r="BS68">
+      <c r="BS68" s="1">
         <v>31638.383838383837</v>
       </c>
       <c r="BT68">
         <v>140231</v>
       </c>
-      <c r="BU68">
+      <c r="BU68" s="1">
         <v>28329.494949494947</v>
       </c>
       <c r="BV68">
@@ -23205,10 +23220,10 @@
       <c r="AQ69">
         <v>1.2686497064579256</v>
       </c>
-      <c r="AR69">
+      <c r="AR69" s="1">
         <v>33.791666666666671</v>
       </c>
-      <c r="AS69">
+      <c r="AS69" s="1">
         <v>28.722729413720497</v>
       </c>
       <c r="AT69" s="1">
@@ -23244,7 +23259,7 @@
       <c r="BD69">
         <v>217116</v>
       </c>
-      <c r="BE69">
+      <c r="BE69" s="1">
         <v>11839.091859282587</v>
       </c>
       <c r="BF69">
@@ -23286,13 +23301,13 @@
       <c r="BR69">
         <v>344765</v>
       </c>
-      <c r="BS69">
+      <c r="BS69" s="1">
         <v>47292.866941015091</v>
       </c>
       <c r="BT69">
         <v>158457</v>
       </c>
-      <c r="BU69">
+      <c r="BU69" s="1">
         <v>21736.213991769546</v>
       </c>
       <c r="BV69">
@@ -23519,10 +23534,10 @@
       <c r="AQ70">
         <v>0.12548611647289737</v>
       </c>
-      <c r="AR70">
+      <c r="AR70" s="1">
         <v>102</v>
       </c>
-      <c r="AS70">
+      <c r="AS70" s="1">
         <v>61.946387739112296</v>
       </c>
       <c r="AT70" s="1">
@@ -23558,7 +23573,7 @@
       <c r="BD70">
         <v>1516687</v>
       </c>
-      <c r="BE70">
+      <c r="BE70" s="1">
         <v>23162.934843516421</v>
       </c>
       <c r="BF70">
@@ -23600,13 +23615,13 @@
       <c r="BR70">
         <v>504585</v>
       </c>
-      <c r="BS70">
+      <c r="BS70" s="1">
         <v>43312.017167381971</v>
       </c>
       <c r="BT70">
         <v>277768</v>
       </c>
-      <c r="BU70">
+      <c r="BU70" s="1">
         <v>23842.746781115879</v>
       </c>
       <c r="BV70">
@@ -23833,10 +23848,10 @@
       <c r="AQ71">
         <v>1.873887712667317</v>
       </c>
-      <c r="AR71">
+      <c r="AR71" s="1">
         <v>1726.8333333333333</v>
       </c>
-      <c r="AS71">
+      <c r="AS71" s="1">
         <v>1467.79876426909</v>
       </c>
       <c r="AT71" s="1">
@@ -23872,7 +23887,7 @@
       <c r="BD71">
         <v>16252941</v>
       </c>
-      <c r="BE71">
+      <c r="BE71" s="1">
         <v>21291.857823824288</v>
       </c>
       <c r="BF71">
@@ -23914,13 +23929,13 @@
       <c r="BR71">
         <v>9088919</v>
       </c>
-      <c r="BS71">
+      <c r="BS71" s="1">
         <v>61048.623052122508</v>
       </c>
       <c r="BT71">
         <v>4494200</v>
       </c>
-      <c r="BU71">
+      <c r="BU71" s="1">
         <v>30186.727565824822</v>
       </c>
       <c r="BV71">
@@ -24147,10 +24162,10 @@
       <c r="AQ72">
         <v>0.39405945026412387</v>
       </c>
-      <c r="AR72">
+      <c r="AR72" s="1">
         <v>60.166666666666664</v>
       </c>
-      <c r="AS72">
+      <c r="AS72" s="1">
         <v>51.599780098955456</v>
       </c>
       <c r="AT72" s="1">
@@ -24186,7 +24201,7 @@
       <c r="BD72">
         <v>689275</v>
       </c>
-      <c r="BE72">
+      <c r="BE72" s="1">
         <v>23842.596029824203</v>
       </c>
       <c r="BF72">
@@ -24228,13 +24243,13 @@
       <c r="BR72">
         <v>5524</v>
       </c>
-      <c r="BS72" t="s">
+      <c r="BS72" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT72">
         <v>0</v>
       </c>
-      <c r="BU72" t="s">
+      <c r="BU72" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV72" t="s">
@@ -24461,10 +24476,10 @@
       <c r="AQ73">
         <v>5.4537394157024428</v>
       </c>
-      <c r="AR73">
+      <c r="AR73" s="1">
         <v>3.5</v>
       </c>
-      <c r="AS73">
+      <c r="AS73" s="1">
         <v>2.7540542741918426</v>
       </c>
       <c r="AT73" s="1">
@@ -24500,7 +24515,7 @@
       <c r="BD73" t="s">
         <v>218</v>
       </c>
-      <c r="BE73" t="s">
+      <c r="BE73" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF73" t="s">
@@ -24542,13 +24557,13 @@
       <c r="BR73">
         <v>16419</v>
       </c>
-      <c r="BS73">
+      <c r="BS73" s="1">
         <v>42100</v>
       </c>
       <c r="BT73">
         <v>9120</v>
       </c>
-      <c r="BU73">
+      <c r="BU73" s="1">
         <v>23384.615384615383</v>
       </c>
       <c r="BV73">
@@ -24775,10 +24790,10 @@
       <c r="AQ74">
         <v>0.76441286352648163</v>
       </c>
-      <c r="AR74">
+      <c r="AR74" s="1">
         <v>57.208333333333329</v>
       </c>
-      <c r="AS74">
+      <c r="AS74" s="1">
         <v>43.117224666769147</v>
       </c>
       <c r="AT74" s="1">
@@ -24814,7 +24829,7 @@
       <c r="BD74">
         <v>325274</v>
       </c>
-      <c r="BE74">
+      <c r="BE74" s="1">
         <v>17764.959711327308</v>
       </c>
       <c r="BF74">
@@ -24856,13 +24871,13 @@
       <c r="BR74">
         <v>104533</v>
       </c>
-      <c r="BS74">
+      <c r="BS74" s="1">
         <v>96789.814814814803</v>
       </c>
       <c r="BT74">
         <v>24483</v>
       </c>
-      <c r="BU74">
+      <c r="BU74" s="1">
         <v>22669.444444444442</v>
       </c>
       <c r="BV74">
@@ -25089,10 +25104,10 @@
       <c r="AQ75">
         <v>0.63684816110650111</v>
       </c>
-      <c r="AR75">
+      <c r="AR75" s="1">
         <v>1737.75</v>
       </c>
-      <c r="AS75">
+      <c r="AS75" s="1">
         <v>1169.497949875994</v>
       </c>
       <c r="AT75" s="1">
@@ -25128,7 +25143,7 @@
       <c r="BD75">
         <v>17123389</v>
       </c>
-      <c r="BE75">
+      <c r="BE75" s="1">
         <v>24298.272312250454</v>
       </c>
       <c r="BF75">
@@ -25170,13 +25185,13 @@
       <c r="BR75">
         <v>10690289</v>
       </c>
-      <c r="BS75">
+      <c r="BS75" s="1">
         <v>39636.235215601941</v>
       </c>
       <c r="BT75">
         <v>8104787</v>
       </c>
-      <c r="BU75">
+      <c r="BU75" s="1">
         <v>30050.005561529044</v>
       </c>
       <c r="BV75">
@@ -25403,10 +25418,10 @@
       <c r="AQ76">
         <v>50.112434892567791</v>
       </c>
-      <c r="AR76">
+      <c r="AR76" s="1">
         <v>860.95833333333326</v>
       </c>
-      <c r="AS76">
+      <c r="AS76" s="1">
         <v>579.42109380635065</v>
       </c>
       <c r="AT76" s="1">
@@ -25442,7 +25457,7 @@
       <c r="BD76">
         <v>13421546</v>
       </c>
-      <c r="BE76">
+      <c r="BE76" s="1">
         <v>31235.600340643701</v>
       </c>
       <c r="BF76">
@@ -25484,13 +25499,13 @@
       <c r="BR76">
         <v>12413938</v>
       </c>
-      <c r="BS76">
+      <c r="BS76" s="1">
         <v>49989.683082994408</v>
       </c>
       <c r="BT76">
         <v>7927765</v>
       </c>
-      <c r="BU76">
+      <c r="BU76" s="1">
         <v>31924.314420327795</v>
       </c>
       <c r="BV76">
@@ -25717,10 +25732,10 @@
       <c r="AQ77">
         <v>0.23888366040410378</v>
       </c>
-      <c r="AR77">
+      <c r="AR77" s="1">
         <v>37.916666666666664</v>
       </c>
-      <c r="AS77">
+      <c r="AS77" s="1">
         <v>26.310140471592671</v>
       </c>
       <c r="AT77" s="1">
@@ -25756,7 +25771,7 @@
       <c r="BD77">
         <v>702061</v>
       </c>
-      <c r="BE77">
+      <c r="BE77" s="1">
         <v>23535.236371249368</v>
       </c>
       <c r="BF77">
@@ -25798,13 +25813,13 @@
       <c r="BR77">
         <v>89024</v>
       </c>
-      <c r="BS77">
+      <c r="BS77" s="1">
         <v>54282.926829268297</v>
       </c>
       <c r="BT77">
         <v>48570</v>
       </c>
-      <c r="BU77">
+      <c r="BU77" s="1">
         <v>29615.853658536587</v>
       </c>
       <c r="BV77">
@@ -26031,10 +26046,10 @@
       <c r="AQ78">
         <v>0.2096494229044123</v>
       </c>
-      <c r="AR78">
+      <c r="AR78" s="1">
         <v>396.29166666666663</v>
       </c>
-      <c r="AS78">
+      <c r="AS78" s="1">
         <v>339.86531061022538</v>
       </c>
       <c r="AT78" s="1">
@@ -26070,7 +26085,7 @@
       <c r="BD78">
         <v>5011554</v>
       </c>
-      <c r="BE78">
+      <c r="BE78" s="1">
         <v>23450.353611293798</v>
       </c>
       <c r="BF78">
@@ -26112,13 +26127,13 @@
       <c r="BR78">
         <v>641566</v>
       </c>
-      <c r="BS78">
+      <c r="BS78" s="1">
         <v>41047.088931541904</v>
       </c>
       <c r="BT78">
         <v>415120</v>
       </c>
-      <c r="BU78">
+      <c r="BU78" s="1">
         <v>26559.181062060139</v>
       </c>
       <c r="BV78">
@@ -26345,10 +26360,10 @@
       <c r="AQ79">
         <v>0.77590258027538517</v>
       </c>
-      <c r="AR79">
+      <c r="AR79" s="1">
         <v>127.75</v>
       </c>
-      <c r="AS79">
+      <c r="AS79" s="1">
         <v>84.950723960765998</v>
       </c>
       <c r="AT79" s="1">
@@ -26384,7 +26399,7 @@
       <c r="BD79">
         <v>1558859</v>
       </c>
-      <c r="BE79">
+      <c r="BE79" s="1">
         <v>24256.101176292726</v>
       </c>
       <c r="BF79">
@@ -26426,13 +26441,13 @@
       <c r="BR79">
         <v>569391</v>
       </c>
-      <c r="BS79">
+      <c r="BS79" s="1">
         <v>73564.728682170535</v>
       </c>
       <c r="BT79">
         <v>227880</v>
       </c>
-      <c r="BU79">
+      <c r="BU79" s="1">
         <v>29441.860465116279</v>
       </c>
       <c r="BV79">
@@ -26659,10 +26674,10 @@
       <c r="AQ80">
         <v>0.2185417155106005</v>
       </c>
-      <c r="AR80">
+      <c r="AR80" s="1">
         <v>19.583333333333332</v>
       </c>
-      <c r="AS80">
+      <c r="AS80" s="1">
         <v>13.588753869943469</v>
       </c>
       <c r="AT80" s="1">
@@ -26698,7 +26713,7 @@
       <c r="BD80">
         <v>159130</v>
       </c>
-      <c r="BE80">
+      <c r="BE80" s="1">
         <v>17216.061339843407</v>
       </c>
       <c r="BF80">
@@ -26740,13 +26755,13 @@
       <c r="BR80">
         <v>1591</v>
       </c>
-      <c r="BS80">
+      <c r="BS80" s="1">
         <v>9358.823529411764</v>
       </c>
       <c r="BT80">
         <v>3121</v>
       </c>
-      <c r="BU80">
+      <c r="BU80" s="1">
         <v>18358.823529411762</v>
       </c>
       <c r="BV80">
@@ -26973,10 +26988,10 @@
       <c r="AQ81">
         <v>5.8104497737898706</v>
       </c>
-      <c r="AR81">
+      <c r="AR81" s="1">
         <v>760.125</v>
       </c>
-      <c r="AS81">
+      <c r="AS81" s="1">
         <v>572.89696256072068</v>
       </c>
       <c r="AT81" s="1">
@@ -27012,7 +27027,7 @@
       <c r="BD81">
         <v>20996655</v>
       </c>
-      <c r="BE81">
+      <c r="BE81" s="1">
         <v>31627.646158372434</v>
       </c>
       <c r="BF81">
@@ -27054,13 +27069,13 @@
       <c r="BR81">
         <v>26128120</v>
       </c>
-      <c r="BS81">
+      <c r="BS81" s="1">
         <v>45886.303366642671</v>
       </c>
       <c r="BT81">
         <v>18630195</v>
       </c>
-      <c r="BU81">
+      <c r="BU81" s="1">
         <v>32718.419065348346</v>
       </c>
       <c r="BV81">
@@ -27287,10 +27302,10 @@
       <c r="AQ82">
         <v>0.11168695768617018</v>
       </c>
-      <c r="AR82">
+      <c r="AR82" s="1">
         <v>160.5</v>
       </c>
-      <c r="AS82">
+      <c r="AS82" s="1">
         <v>106.72869820511109</v>
       </c>
       <c r="AT82" s="1">
@@ -27326,7 +27341,7 @@
       <c r="BD82">
         <v>2306228</v>
       </c>
-      <c r="BE82">
+      <c r="BE82" s="1">
         <v>23489.031102783803</v>
       </c>
       <c r="BF82">
@@ -27368,13 +27383,13 @@
       <c r="BR82">
         <v>46052</v>
       </c>
-      <c r="BS82">
+      <c r="BS82" s="1">
         <v>46052</v>
       </c>
       <c r="BT82">
         <v>38494</v>
       </c>
-      <c r="BU82">
+      <c r="BU82" s="1">
         <v>38494</v>
       </c>
       <c r="BV82">
@@ -27601,10 +27616,10 @@
       <c r="AQ83">
         <v>2.5019328942228687</v>
       </c>
-      <c r="AR83">
+      <c r="AR83" s="1">
         <v>267.875</v>
       </c>
-      <c r="AS83">
+      <c r="AS83" s="1">
         <v>185.87680559546078</v>
       </c>
       <c r="AT83" s="1">
@@ -27640,7 +27655,7 @@
       <c r="BD83">
         <v>5090436</v>
       </c>
-      <c r="BE83">
+      <c r="BE83" s="1">
         <v>27683.096037054034</v>
       </c>
       <c r="BF83">
@@ -27682,13 +27697,13 @@
       <c r="BR83">
         <v>2311067</v>
       </c>
-      <c r="BS83">
+      <c r="BS83" s="1">
         <v>27169.844815424407</v>
       </c>
       <c r="BT83">
         <v>2807853</v>
       </c>
-      <c r="BU83">
+      <c r="BU83" s="1">
         <v>33010.263343522216</v>
       </c>
       <c r="BV83">
@@ -27915,10 +27930,10 @@
       <c r="AQ84">
         <v>6.760273108117687E-2</v>
       </c>
-      <c r="AR84">
+      <c r="AR84" s="1">
         <v>147.625</v>
       </c>
-      <c r="AS84">
+      <c r="AS84" s="1">
         <v>96.805930288296935</v>
       </c>
       <c r="AT84" s="1">
@@ -27954,7 +27969,7 @@
       <c r="BD84">
         <v>1279329</v>
       </c>
-      <c r="BE84">
+      <c r="BE84" s="1">
         <v>21947.504405519499</v>
       </c>
       <c r="BF84">
@@ -27996,13 +28011,13 @@
       <c r="BR84">
         <v>66017</v>
       </c>
-      <c r="BS84">
+      <c r="BS84" s="1">
         <v>33008.5</v>
       </c>
       <c r="BT84">
         <v>41454</v>
       </c>
-      <c r="BU84">
+      <c r="BU84" s="1">
         <v>20727</v>
       </c>
       <c r="BV84">
@@ -28229,10 +28244,10 @@
       <c r="AQ85">
         <v>2.3801837811236095</v>
       </c>
-      <c r="AR85">
+      <c r="AR85" s="1">
         <v>18004.166666666668</v>
       </c>
-      <c r="AS85">
+      <c r="AS85" s="1">
         <v>10934.245973067984</v>
       </c>
       <c r="AT85" s="1">
@@ -28268,7 +28283,7 @@
       <c r="BD85">
         <v>238679081</v>
       </c>
-      <c r="BE85">
+      <c r="BE85" s="1">
         <v>28322.537930239843</v>
       </c>
       <c r="BF85">
@@ -28310,13 +28325,13 @@
       <c r="BR85">
         <v>135885297</v>
       </c>
-      <c r="BS85">
+      <c r="BS85" s="1">
         <v>59345.03635768099</v>
       </c>
       <c r="BT85">
         <v>77535595</v>
       </c>
-      <c r="BU85">
+      <c r="BU85" s="1">
         <v>33862.035156676509</v>
       </c>
       <c r="BV85">
@@ -28543,10 +28558,10 @@
       <c r="AQ86">
         <v>1.9792121106360701</v>
       </c>
-      <c r="AR86">
+      <c r="AR86" s="1">
         <v>49.791666666666671</v>
       </c>
-      <c r="AS86">
+      <c r="AS86" s="1">
         <v>37.527373253305996</v>
       </c>
       <c r="AT86" s="1">
@@ -28582,7 +28597,7 @@
       <c r="BD86">
         <v>464748</v>
       </c>
-      <c r="BE86">
+      <c r="BE86" s="1">
         <v>16535.811755378512</v>
       </c>
       <c r="BF86">
@@ -28624,13 +28639,13 @@
       <c r="BR86">
         <v>218564</v>
       </c>
-      <c r="BS86">
+      <c r="BS86" s="1">
         <v>39380.900900900902</v>
       </c>
       <c r="BT86">
         <v>117997</v>
       </c>
-      <c r="BU86">
+      <c r="BU86" s="1">
         <v>21260.720720720721</v>
       </c>
       <c r="BV86">
@@ -28857,10 +28872,10 @@
       <c r="AQ87">
         <v>1.7702193400487145</v>
       </c>
-      <c r="AR87">
+      <c r="AR87" s="1">
         <v>156.70833333333331</v>
       </c>
-      <c r="AS87">
+      <c r="AS87" s="1">
         <v>108.73894320182421</v>
       </c>
       <c r="AT87" s="1">
@@ -28896,7 +28911,7 @@
       <c r="BD87">
         <v>5296476</v>
       </c>
-      <c r="BE87">
+      <c r="BE87" s="1">
         <v>26305.944051265076</v>
       </c>
       <c r="BF87">
@@ -28938,13 +28953,13 @@
       <c r="BR87">
         <v>5511825</v>
       </c>
-      <c r="BS87">
+      <c r="BS87" s="1">
         <v>43880.463338906142</v>
       </c>
       <c r="BT87">
         <v>4305433</v>
       </c>
-      <c r="BU87">
+      <c r="BU87" s="1">
         <v>34276.196162725901</v>
       </c>
       <c r="BV87">
@@ -29171,10 +29186,10 @@
       <c r="AQ88">
         <v>0</v>
       </c>
-      <c r="AR88">
+      <c r="AR88" s="1">
         <v>43.333333333333336</v>
       </c>
-      <c r="AS88">
+      <c r="AS88" s="1">
         <v>26.317092830341824</v>
       </c>
       <c r="AT88" s="1">
@@ -29210,7 +29225,7 @@
       <c r="BD88">
         <v>159497</v>
       </c>
-      <c r="BE88">
+      <c r="BE88" s="1">
         <v>15500.030919160896</v>
       </c>
       <c r="BF88">
@@ -29252,13 +29267,13 @@
       <c r="BR88">
         <v>113937</v>
       </c>
-      <c r="BS88">
+      <c r="BS88" s="1">
         <v>24293.603411513857</v>
       </c>
       <c r="BT88">
         <v>110738</v>
       </c>
-      <c r="BU88">
+      <c r="BU88" s="1">
         <v>23611.513859275052</v>
       </c>
       <c r="BV88">
@@ -29485,10 +29500,10 @@
       <c r="AQ89">
         <v>0.36239617481852832</v>
       </c>
-      <c r="AR89">
+      <c r="AR89" s="1">
         <v>221.91666666666666</v>
       </c>
-      <c r="AS89">
+      <c r="AS89" s="1">
         <v>134.77388116769282</v>
       </c>
       <c r="AT89" s="1">
@@ -29524,7 +29539,7 @@
       <c r="BD89">
         <v>5394425</v>
       </c>
-      <c r="BE89">
+      <c r="BE89" s="1">
         <v>26372.619276292557</v>
       </c>
       <c r="BF89">
@@ -29566,13 +29581,13 @@
       <c r="BR89">
         <v>97828</v>
       </c>
-      <c r="BS89">
+      <c r="BS89" s="1">
         <v>25084.102564102566</v>
       </c>
       <c r="BT89">
         <v>72471</v>
       </c>
-      <c r="BU89">
+      <c r="BU89" s="1">
         <v>18582.307692307691</v>
       </c>
       <c r="BV89">
@@ -29799,10 +29814,10 @@
       <c r="AQ90">
         <v>0.56692641643365005</v>
       </c>
-      <c r="AR90">
+      <c r="AR90" s="1">
         <v>42.416666666666671</v>
       </c>
-      <c r="AS90">
+      <c r="AS90" s="1">
         <v>27.555184466019419</v>
       </c>
       <c r="AT90" s="1">
@@ -29838,7 +29853,7 @@
       <c r="BD90">
         <v>111523</v>
       </c>
-      <c r="BE90">
+      <c r="BE90" s="1">
         <v>7723.8534246439267</v>
       </c>
       <c r="BF90">
@@ -29880,13 +29895,13 @@
       <c r="BR90">
         <v>206015</v>
       </c>
-      <c r="BS90">
+      <c r="BS90" s="1">
         <v>34335.833333333336</v>
       </c>
       <c r="BT90">
         <v>167468</v>
       </c>
-      <c r="BU90">
+      <c r="BU90" s="1">
         <v>27911.333333333332</v>
       </c>
       <c r="BV90">
@@ -30113,10 +30128,10 @@
       <c r="AQ91">
         <v>0.19296808662523765</v>
       </c>
-      <c r="AR91">
+      <c r="AR91" s="1">
         <v>15.791666666666666</v>
       </c>
-      <c r="AS91">
+      <c r="AS91" s="1">
         <v>12.426030594270337</v>
       </c>
       <c r="AT91" s="1">
@@ -30152,7 +30167,7 @@
       <c r="BD91" t="s">
         <v>218</v>
       </c>
-      <c r="BE91" t="s">
+      <c r="BE91" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF91" t="s">
@@ -30194,13 +30209,13 @@
       <c r="BR91">
         <v>122165</v>
       </c>
-      <c r="BS91">
+      <c r="BS91" s="1">
         <v>24433</v>
       </c>
       <c r="BT91">
         <v>79199</v>
       </c>
-      <c r="BU91">
+      <c r="BU91" s="1">
         <v>15839.8</v>
       </c>
       <c r="BV91">
@@ -30427,10 +30442,10 @@
       <c r="AQ92">
         <v>0.19445916915436764</v>
       </c>
-      <c r="AR92">
+      <c r="AR92" s="1">
         <v>15.625</v>
       </c>
-      <c r="AS92">
+      <c r="AS92" s="1">
         <v>10.390254887569226</v>
       </c>
       <c r="AT92" s="1">
@@ -30466,7 +30481,7 @@
       <c r="BD92">
         <v>85024</v>
       </c>
-      <c r="BE92">
+      <c r="BE92" s="1">
         <v>10563.53017394842</v>
       </c>
       <c r="BF92">
@@ -30508,13 +30523,13 @@
       <c r="BR92">
         <v>0</v>
       </c>
-      <c r="BS92" t="s">
+      <c r="BS92" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT92">
         <v>0</v>
       </c>
-      <c r="BU92" t="s">
+      <c r="BU92" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV92" t="s">
@@ -30741,10 +30756,10 @@
       <c r="AQ93">
         <v>3.5287440357087889</v>
       </c>
-      <c r="AR93">
+      <c r="AR93" s="1">
         <v>40.25</v>
       </c>
-      <c r="AS93">
+      <c r="AS93" s="1">
         <v>30.335935198906768</v>
       </c>
       <c r="AT93" s="1">
@@ -30780,7 +30795,7 @@
       <c r="BD93">
         <v>176950</v>
       </c>
-      <c r="BE93">
+      <c r="BE93" s="1">
         <v>8699.3465960346512</v>
       </c>
       <c r="BF93">
@@ -30822,13 +30837,13 @@
       <c r="BR93">
         <v>0</v>
       </c>
-      <c r="BS93" t="s">
+      <c r="BS93" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT93">
         <v>0</v>
       </c>
-      <c r="BU93" t="s">
+      <c r="BU93" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV93" t="s">
@@ -31055,10 +31070,10 @@
       <c r="AQ94">
         <v>4.4124755539985003E-2</v>
       </c>
-      <c r="AR94">
+      <c r="AR94" s="1">
         <v>156.79166666666669</v>
       </c>
-      <c r="AS94">
+      <c r="AS94" s="1">
         <v>95.222327231323362</v>
       </c>
       <c r="AT94" s="1">
@@ -31094,7 +31109,7 @@
       <c r="BD94">
         <v>4881403</v>
       </c>
-      <c r="BE94">
+      <c r="BE94" s="1">
         <v>42374.123430944026</v>
       </c>
       <c r="BF94">
@@ -31136,13 +31151,13 @@
       <c r="BR94">
         <v>83610</v>
       </c>
-      <c r="BS94">
+      <c r="BS94" s="1">
         <v>9654.7344110854501</v>
       </c>
       <c r="BT94">
         <v>240804</v>
       </c>
-      <c r="BU94">
+      <c r="BU94" s="1">
         <v>27806.466512702078</v>
       </c>
       <c r="BV94">
@@ -31369,10 +31384,10 @@
       <c r="AQ95">
         <v>2.0328537996326192E-2</v>
       </c>
-      <c r="AR95">
+      <c r="AR95" s="1">
         <v>39.166666666666664</v>
       </c>
-      <c r="AS95">
+      <c r="AS95" s="1">
         <v>26.044905584840194</v>
       </c>
       <c r="AT95" s="1">
@@ -31408,7 +31423,7 @@
       <c r="BD95">
         <v>300669</v>
       </c>
-      <c r="BE95">
+      <c r="BE95" s="1">
         <v>13077.095398644426</v>
       </c>
       <c r="BF95">
@@ -31450,13 +31465,13 @@
       <c r="BR95">
         <v>0</v>
       </c>
-      <c r="BS95" t="s">
+      <c r="BS95" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT95">
         <v>0</v>
       </c>
-      <c r="BU95" t="s">
+      <c r="BU95" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV95" t="s">
@@ -31683,10 +31698,10 @@
       <c r="AQ96">
         <v>0.12780922396757882</v>
       </c>
-      <c r="AR96">
+      <c r="AR96" s="1">
         <v>15</v>
       </c>
-      <c r="AS96">
+      <c r="AS96" s="1">
         <v>9.9746446920664571</v>
       </c>
       <c r="AT96" s="1">
@@ -31722,7 +31737,7 @@
       <c r="BD96">
         <v>127228</v>
       </c>
-      <c r="BE96">
+      <c r="BE96" s="1">
         <v>22146.864760522531</v>
       </c>
       <c r="BF96">
@@ -31764,13 +31779,13 @@
       <c r="BR96">
         <v>-11713</v>
       </c>
-      <c r="BS96">
+      <c r="BS96" s="1">
         <v>-11713</v>
       </c>
       <c r="BT96">
         <v>19679</v>
       </c>
-      <c r="BU96">
+      <c r="BU96" s="1">
         <v>19679</v>
       </c>
       <c r="BV96">
@@ -31997,10 +32012,10 @@
       <c r="AQ97">
         <v>1.2369080307317659</v>
       </c>
-      <c r="AR97">
+      <c r="AR97" s="1">
         <v>4130.458333333333</v>
       </c>
-      <c r="AS97">
+      <c r="AS97" s="1">
         <v>2746.6569526923331</v>
       </c>
       <c r="AT97" s="1">
@@ -32036,7 +32051,7 @@
       <c r="BD97">
         <v>38018386</v>
       </c>
-      <c r="BE97">
+      <c r="BE97" s="1">
         <v>23417.338053792155</v>
       </c>
       <c r="BF97">
@@ -32078,13 +32093,13 @@
       <c r="BR97">
         <v>11670345</v>
       </c>
-      <c r="BS97">
+      <c r="BS97" s="1">
         <v>44625.057356989906</v>
       </c>
       <c r="BT97">
         <v>7956107</v>
       </c>
-      <c r="BU97">
+      <c r="BU97" s="1">
         <v>30422.556592230041</v>
       </c>
       <c r="BV97">
@@ -32311,10 +32326,10 @@
       <c r="AQ98">
         <v>0.15092053448217832</v>
       </c>
-      <c r="AR98">
+      <c r="AR98" s="1">
         <v>41.416666666666664</v>
       </c>
-      <c r="AS98">
+      <c r="AS98" s="1">
         <v>27.541102288650162</v>
       </c>
       <c r="AT98" s="1">
@@ -32350,7 +32365,7 @@
       <c r="BD98">
         <v>389999</v>
       </c>
-      <c r="BE98">
+      <c r="BE98" s="1">
         <v>12471.634332216452</v>
       </c>
       <c r="BF98">
@@ -32392,13 +32407,13 @@
       <c r="BR98">
         <v>0</v>
       </c>
-      <c r="BS98" t="s">
+      <c r="BS98" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT98">
         <v>0</v>
       </c>
-      <c r="BU98" t="s">
+      <c r="BU98" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV98" t="s">
@@ -32625,10 +32640,10 @@
       <c r="AQ99">
         <v>0.28200447626152791</v>
       </c>
-      <c r="AR99">
+      <c r="AR99" s="1">
         <v>259.66666666666663</v>
       </c>
-      <c r="AS99">
+      <c r="AS99" s="1">
         <v>157.7001178064329</v>
       </c>
       <c r="AT99" s="1">
@@ -32664,7 +32679,7 @@
       <c r="BD99">
         <v>5622426</v>
       </c>
-      <c r="BE99">
+      <c r="BE99" s="1">
         <v>27053.751289436666</v>
       </c>
       <c r="BF99">
@@ -32706,13 +32721,13 @@
       <c r="BR99">
         <v>1801056</v>
       </c>
-      <c r="BS99">
+      <c r="BS99" s="1">
         <v>76251.312447078744</v>
       </c>
       <c r="BT99">
         <v>832998</v>
       </c>
-      <c r="BU99">
+      <c r="BU99" s="1">
         <v>35266.638441998308</v>
       </c>
       <c r="BV99">
@@ -32939,10 +32954,10 @@
       <c r="AQ100">
         <v>0.16341838070395126</v>
       </c>
-      <c r="AR100">
+      <c r="AR100" s="1">
         <v>117.20833333333334</v>
       </c>
-      <c r="AS100">
+      <c r="AS100" s="1">
         <v>71.182675126684188</v>
       </c>
       <c r="AT100" s="1">
@@ -32978,7 +32993,7 @@
       <c r="BD100">
         <v>986764</v>
       </c>
-      <c r="BE100">
+      <c r="BE100" s="1">
         <v>22221.378416926356</v>
       </c>
       <c r="BF100">
@@ -33020,13 +33035,13 @@
       <c r="BR100">
         <v>57417</v>
       </c>
-      <c r="BS100">
+      <c r="BS100" s="1">
         <v>57417</v>
       </c>
       <c r="BT100">
         <v>18462</v>
       </c>
-      <c r="BU100">
+      <c r="BU100" s="1">
         <v>18462</v>
       </c>
       <c r="BV100">
@@ -33253,10 +33268,10 @@
       <c r="AQ101">
         <v>1.3201318005984495</v>
       </c>
-      <c r="AR101">
+      <c r="AR101" s="1">
         <v>145.08333333333334</v>
       </c>
-      <c r="AS101">
+      <c r="AS101" s="1">
         <v>114.16210693733328</v>
       </c>
       <c r="AT101" s="1">
@@ -33292,7 +33307,7 @@
       <c r="BD101">
         <v>2041618</v>
       </c>
-      <c r="BE101">
+      <c r="BE101" s="1">
         <v>23371.278640887016</v>
       </c>
       <c r="BF101">
@@ -33334,13 +33349,13 @@
       <c r="BR101">
         <v>1227882</v>
       </c>
-      <c r="BS101">
+      <c r="BS101" s="1">
         <v>60546.449704142011</v>
       </c>
       <c r="BT101">
         <v>706793</v>
       </c>
-      <c r="BU101">
+      <c r="BU101" s="1">
         <v>34851.725838264298</v>
       </c>
       <c r="BV101">
@@ -33567,10 +33582,10 @@
       <c r="AQ102">
         <v>0.75414034422595588</v>
       </c>
-      <c r="AR102">
+      <c r="AR102" s="1">
         <v>34.458333333333336</v>
       </c>
-      <c r="AS102">
+      <c r="AS102" s="1">
         <v>24.240744599569357</v>
       </c>
       <c r="AT102" s="1">
@@ -33606,7 +33621,7 @@
       <c r="BD102">
         <v>90578</v>
       </c>
-      <c r="BE102">
+      <c r="BE102" s="1">
         <v>7520.4761850599598</v>
       </c>
       <c r="BF102">
@@ -33648,13 +33663,13 @@
       <c r="BR102">
         <v>123496</v>
       </c>
-      <c r="BS102">
+      <c r="BS102" s="1">
         <v>140336.36363636365</v>
       </c>
       <c r="BT102">
         <v>58096</v>
       </c>
-      <c r="BU102">
+      <c r="BU102" s="1">
         <v>66018.181818181823</v>
       </c>
       <c r="BV102">
@@ -33881,10 +33896,10 @@
       <c r="AQ103">
         <v>3.8933546225545929E-2</v>
       </c>
-      <c r="AR103">
+      <c r="AR103" s="1">
         <v>99.125</v>
       </c>
-      <c r="AS103">
+      <c r="AS103" s="1">
         <v>65.915777006739177</v>
       </c>
       <c r="AT103" s="1">
@@ -33920,7 +33935,7 @@
       <c r="BD103">
         <v>1729191</v>
       </c>
-      <c r="BE103">
+      <c r="BE103" s="1">
         <v>21449.441139698502</v>
       </c>
       <c r="BF103">
@@ -33962,13 +33977,13 @@
       <c r="BR103">
         <v>516825</v>
       </c>
-      <c r="BS103">
+      <c r="BS103" s="1">
         <v>34455</v>
       </c>
       <c r="BT103">
         <v>417396</v>
       </c>
-      <c r="BU103">
+      <c r="BU103" s="1">
         <v>27826.400000000001</v>
       </c>
       <c r="BV103">
@@ -34195,10 +34210,10 @@
       <c r="AQ104">
         <v>0.58899242330010981</v>
       </c>
-      <c r="AR104">
+      <c r="AR104" s="1">
         <v>60.583333333333336</v>
       </c>
-      <c r="AS104">
+      <c r="AS104" s="1">
         <v>36.268632896700389</v>
       </c>
       <c r="AT104" s="1">
@@ -34234,7 +34249,7 @@
       <c r="BD104">
         <v>133920</v>
       </c>
-      <c r="BE104">
+      <c r="BE104" s="1">
         <v>14304.873315162104</v>
       </c>
       <c r="BF104">
@@ -34276,13 +34291,13 @@
       <c r="BR104">
         <v>36660</v>
       </c>
-      <c r="BS104" t="s">
+      <c r="BS104" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT104">
         <v>0</v>
       </c>
-      <c r="BU104" t="s">
+      <c r="BU104" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV104" t="s">
@@ -34509,10 +34524,10 @@
       <c r="AQ105">
         <v>0.10022430218461494</v>
       </c>
-      <c r="AR105">
+      <c r="AR105" s="1">
         <v>43.75</v>
       </c>
-      <c r="AS105">
+      <c r="AS105" s="1">
         <v>34.425678427398033</v>
       </c>
       <c r="AT105" s="1">
@@ -34548,7 +34563,7 @@
       <c r="BD105">
         <v>249647</v>
       </c>
-      <c r="BE105">
+      <c r="BE105" s="1">
         <v>21447.224804584992</v>
       </c>
       <c r="BF105">
@@ -34590,13 +34605,13 @@
       <c r="BR105">
         <v>0</v>
       </c>
-      <c r="BS105" t="s">
+      <c r="BS105" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT105">
         <v>0</v>
       </c>
-      <c r="BU105" t="s">
+      <c r="BU105" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV105" t="s">
@@ -34823,10 +34838,10 @@
       <c r="AQ106">
         <v>0.17765688654709647</v>
       </c>
-      <c r="AR106">
+      <c r="AR106" s="1">
         <v>13.041666666666668</v>
       </c>
-      <c r="AS106">
+      <c r="AS106" s="1">
         <v>10.262130807405317</v>
       </c>
       <c r="AT106" s="1">
@@ -34862,7 +34877,7 @@
       <c r="BD106">
         <v>117942</v>
       </c>
-      <c r="BE106">
+      <c r="BE106" s="1">
         <v>19625.934115266788</v>
       </c>
       <c r="BF106">
@@ -34904,13 +34919,13 @@
       <c r="BR106">
         <v>1151</v>
       </c>
-      <c r="BS106" t="s">
+      <c r="BS106" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT106">
         <v>0</v>
       </c>
-      <c r="BU106" t="s">
+      <c r="BU106" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV106" t="s">
@@ -35137,10 +35152,10 @@
       <c r="AQ107">
         <v>2.1559564096245052</v>
       </c>
-      <c r="AR107">
+      <c r="AR107" s="1">
         <v>81.083333333333329</v>
       </c>
-      <c r="AS107">
+      <c r="AS107" s="1">
         <v>57.04049454747517</v>
       </c>
       <c r="AT107" s="1">
@@ -35176,7 +35191,7 @@
       <c r="BD107">
         <v>160036</v>
       </c>
-      <c r="BE107">
+      <c r="BE107" s="1">
         <v>8724.7611748943818</v>
       </c>
       <c r="BF107">
@@ -35218,13 +35233,13 @@
       <c r="BR107">
         <v>30650</v>
       </c>
-      <c r="BS107" t="s">
+      <c r="BS107" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT107">
         <v>0</v>
       </c>
-      <c r="BU107" t="s">
+      <c r="BU107" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV107" t="s">
@@ -35451,10 +35466,10 @@
       <c r="AQ108">
         <v>9.0595177510188807E-2</v>
       </c>
-      <c r="AR108">
+      <c r="AR108" s="1">
         <v>24</v>
       </c>
-      <c r="AS108">
+      <c r="AS108" s="1">
         <v>18.884943594458345</v>
       </c>
       <c r="AT108" s="1">
@@ -35490,7 +35505,7 @@
       <c r="BD108">
         <v>310905</v>
       </c>
-      <c r="BE108">
+      <c r="BE108" s="1">
         <v>29396.945559189317</v>
       </c>
       <c r="BF108">
@@ -35532,13 +35547,13 @@
       <c r="BR108">
         <v>0</v>
       </c>
-      <c r="BS108" t="s">
+      <c r="BS108" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT108">
         <v>0</v>
       </c>
-      <c r="BU108" t="s">
+      <c r="BU108" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV108" t="s">
@@ -35765,10 +35780,10 @@
       <c r="AQ109">
         <v>6.6464530606351713E-2</v>
       </c>
-      <c r="AR109">
+      <c r="AR109" s="1">
         <v>45.583333333333329</v>
       </c>
-      <c r="AS109">
+      <c r="AS109" s="1">
         <v>27.683557265763415</v>
       </c>
       <c r="AT109" s="1">
@@ -35804,7 +35819,7 @@
       <c r="BD109">
         <v>588403</v>
       </c>
-      <c r="BE109">
+      <c r="BE109" s="1">
         <v>20719.008295242813</v>
       </c>
       <c r="BF109">
@@ -35846,13 +35861,13 @@
       <c r="BR109">
         <v>0</v>
       </c>
-      <c r="BS109" t="s">
+      <c r="BS109" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT109">
         <v>0</v>
       </c>
-      <c r="BU109" t="s">
+      <c r="BU109" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV109" t="s">
@@ -36079,10 +36094,10 @@
       <c r="AQ110">
         <v>24.705979779855767</v>
       </c>
-      <c r="AR110">
+      <c r="AR110" s="1">
         <v>561.79166666666674</v>
       </c>
-      <c r="AS110">
+      <c r="AS110" s="1">
         <v>389.82376261371877</v>
       </c>
       <c r="AT110" s="1">
@@ -36118,7 +36133,7 @@
       <c r="BD110">
         <v>5883333</v>
       </c>
-      <c r="BE110">
+      <c r="BE110" s="1">
         <v>27426.580657761697</v>
       </c>
       <c r="BF110">
@@ -36160,13 +36175,13 @@
       <c r="BR110">
         <v>6451313</v>
       </c>
-      <c r="BS110">
+      <c r="BS110" s="1">
         <v>47745.063647128474</v>
       </c>
       <c r="BT110">
         <v>3790140</v>
       </c>
-      <c r="BU110">
+      <c r="BU110" s="1">
         <v>28050.177619893428</v>
       </c>
       <c r="BV110">
@@ -36393,10 +36408,10 @@
       <c r="AQ111">
         <v>3.0210885610532472</v>
       </c>
-      <c r="AR111">
+      <c r="AR111" s="1">
         <v>98</v>
       </c>
-      <c r="AS111">
+      <c r="AS111" s="1">
         <v>73.861407440816492</v>
       </c>
       <c r="AT111" s="1">
@@ -36432,7 +36447,7 @@
       <c r="BD111">
         <v>830135</v>
       </c>
-      <c r="BE111">
+      <c r="BE111" s="1">
         <v>21419.752884531095</v>
       </c>
       <c r="BF111">
@@ -36474,13 +36489,13 @@
       <c r="BR111">
         <v>55182</v>
       </c>
-      <c r="BS111">
+      <c r="BS111" s="1">
         <v>131385.71428571429</v>
       </c>
       <c r="BT111">
         <v>8339</v>
       </c>
-      <c r="BU111">
+      <c r="BU111" s="1">
         <v>19854.761904761905</v>
       </c>
       <c r="BV111">
@@ -36707,10 +36722,10 @@
       <c r="AQ112">
         <v>0.38559930950717852</v>
       </c>
-      <c r="AR112">
+      <c r="AR112" s="1">
         <v>675.41666666666663</v>
       </c>
-      <c r="AS112">
+      <c r="AS112" s="1">
         <v>468.66744730166727</v>
       </c>
       <c r="AT112" s="1">
@@ -36746,7 +36761,7 @@
       <c r="BD112">
         <v>6129193</v>
       </c>
-      <c r="BE112">
+      <c r="BE112" s="1">
         <v>22162.586374495164</v>
       </c>
       <c r="BF112">
@@ -36788,13 +36803,13 @@
       <c r="BR112">
         <v>1520250</v>
       </c>
-      <c r="BS112">
+      <c r="BS112" s="1">
         <v>53304.698457223007</v>
       </c>
       <c r="BT112">
         <v>864549</v>
       </c>
-      <c r="BU112">
+      <c r="BU112" s="1">
         <v>30313.779803646568</v>
       </c>
       <c r="BV112">
@@ -37021,10 +37036,10 @@
       <c r="AQ113">
         <v>0.13213614669476223</v>
       </c>
-      <c r="AR113">
+      <c r="AR113" s="1">
         <v>22.166666666666668</v>
       </c>
-      <c r="AS113">
+      <c r="AS113" s="1">
         <v>15.593804264777386</v>
       </c>
       <c r="AT113" s="1">
@@ -37060,7 +37075,7 @@
       <c r="BD113">
         <v>141744</v>
       </c>
-      <c r="BE113">
+      <c r="BE113" s="1">
         <v>14366.115004257179</v>
       </c>
       <c r="BF113">
@@ -37102,13 +37117,13 @@
       <c r="BR113">
         <v>-5743</v>
       </c>
-      <c r="BS113">
+      <c r="BS113" s="1">
         <v>-7003.6585365853662</v>
       </c>
       <c r="BT113">
         <v>15244</v>
       </c>
-      <c r="BU113">
+      <c r="BU113" s="1">
         <v>18590.243902439026</v>
       </c>
       <c r="BV113">
@@ -37335,10 +37350,10 @@
       <c r="AQ114">
         <v>1.3048678657669655</v>
       </c>
-      <c r="AR114">
+      <c r="AR114" s="1">
         <v>104.16666666666667</v>
       </c>
-      <c r="AS114">
+      <c r="AS114" s="1">
         <v>70.103699100608665</v>
       </c>
       <c r="AT114" s="1">
@@ -37374,7 +37389,7 @@
       <c r="BD114">
         <v>1484372</v>
       </c>
-      <c r="BE114">
+      <c r="BE114" s="1">
         <v>18539.475739584668</v>
       </c>
       <c r="BF114">
@@ -37416,13 +37431,13 @@
       <c r="BR114">
         <v>0</v>
       </c>
-      <c r="BS114" t="s">
+      <c r="BS114" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT114">
         <v>0</v>
       </c>
-      <c r="BU114" t="s">
+      <c r="BU114" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV114" t="s">
@@ -37649,10 +37664,10 @@
       <c r="AQ115">
         <v>0.10190813148265748</v>
       </c>
-      <c r="AR115">
+      <c r="AR115" s="1">
         <v>50.166666666666671</v>
       </c>
-      <c r="AS115">
+      <c r="AS115" s="1">
         <v>37.810006189941774</v>
       </c>
       <c r="AT115" s="1">
@@ -37688,7 +37703,7 @@
       <c r="BD115">
         <v>571410</v>
       </c>
-      <c r="BE115">
+      <c r="BE115" s="1">
         <v>23019.337674530252</v>
       </c>
       <c r="BF115">
@@ -37730,13 +37745,13 @@
       <c r="BR115">
         <v>477662</v>
       </c>
-      <c r="BS115">
+      <c r="BS115" s="1">
         <v>56328.066037735844</v>
       </c>
       <c r="BT115">
         <v>210715</v>
       </c>
-      <c r="BU115">
+      <c r="BU115" s="1">
         <v>24848.466981132075</v>
       </c>
       <c r="BV115">
@@ -37963,10 +37978,10 @@
       <c r="AQ116">
         <v>1.3575967375828648</v>
       </c>
-      <c r="AR116">
+      <c r="AR116" s="1">
         <v>1988.9583333333333</v>
       </c>
-      <c r="AS116">
+      <c r="AS116" s="1">
         <v>1190.7037079257173</v>
       </c>
       <c r="AT116" s="1">
@@ -38002,7 +38017,7 @@
       <c r="BD116">
         <v>7766147</v>
       </c>
-      <c r="BE116">
+      <c r="BE116" s="1">
         <v>24267.512930040473</v>
       </c>
       <c r="BF116">
@@ -38044,13 +38059,13 @@
       <c r="BR116">
         <v>1429006</v>
       </c>
-      <c r="BS116">
+      <c r="BS116" s="1">
         <v>95267.06666666668</v>
       </c>
       <c r="BT116">
         <v>428200</v>
       </c>
-      <c r="BU116">
+      <c r="BU116" s="1">
         <v>28546.666666666672</v>
       </c>
       <c r="BV116">
@@ -38277,10 +38292,10 @@
       <c r="AQ117">
         <v>0.43820128528339503</v>
       </c>
-      <c r="AR117">
+      <c r="AR117" s="1">
         <v>1066.0833333333333</v>
       </c>
-      <c r="AS117">
+      <c r="AS117" s="1">
         <v>838.87181737467222</v>
       </c>
       <c r="AT117" s="1">
@@ -38316,7 +38331,7 @@
       <c r="BD117">
         <v>31026363</v>
       </c>
-      <c r="BE117">
+      <c r="BE117" s="1">
         <v>33832.082673074561</v>
       </c>
       <c r="BF117">
@@ -38358,13 +38373,13 @@
       <c r="BR117">
         <v>31391469</v>
       </c>
-      <c r="BS117">
+      <c r="BS117" s="1">
         <v>47788.014736104975</v>
       </c>
       <c r="BT117">
         <v>24967130</v>
       </c>
-      <c r="BU117">
+      <c r="BU117" s="1">
         <v>38008.083545190209</v>
       </c>
       <c r="BV117">
@@ -38591,10 +38606,10 @@
       <c r="AQ118">
         <v>0</v>
       </c>
-      <c r="AR118">
+      <c r="AR118" s="1">
         <v>22.916666666666668</v>
       </c>
-      <c r="AS118">
+      <c r="AS118" s="1">
         <v>15.901733252061508</v>
       </c>
       <c r="AT118" s="1">
@@ -38630,7 +38645,7 @@
       <c r="BD118">
         <v>378884</v>
       </c>
-      <c r="BE118">
+      <c r="BE118" s="1">
         <v>22194.541453502694</v>
       </c>
       <c r="BF118">
@@ -38672,13 +38687,13 @@
       <c r="BR118">
         <v>0</v>
       </c>
-      <c r="BS118" t="s">
+      <c r="BS118" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT118">
         <v>0</v>
       </c>
-      <c r="BU118" t="s">
+      <c r="BU118" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV118" t="s">
@@ -38905,10 +38920,10 @@
       <c r="AQ119">
         <v>2.1566431841963562E-2</v>
       </c>
-      <c r="AR119">
+      <c r="AR119" s="1">
         <v>42.25</v>
       </c>
-      <c r="AS119">
+      <c r="AS119" s="1">
         <v>28.095249215987188</v>
       </c>
       <c r="AT119" s="1">
@@ -38944,7 +38959,7 @@
       <c r="BD119">
         <v>350369</v>
       </c>
-      <c r="BE119">
+      <c r="BE119" s="1">
         <v>22363.567903665265</v>
       </c>
       <c r="BF119">
@@ -38986,13 +39001,13 @@
       <c r="BR119">
         <v>507943</v>
       </c>
-      <c r="BS119">
+      <c r="BS119" s="1">
         <v>60977.551020408166</v>
       </c>
       <c r="BT119">
         <v>304004</v>
       </c>
-      <c r="BU119">
+      <c r="BU119" s="1">
         <v>36495.078031212484</v>
       </c>
       <c r="BV119">
@@ -39219,10 +39234,10 @@
       <c r="AQ120">
         <v>0.38088648268376979</v>
       </c>
-      <c r="AR120">
+      <c r="AR120" s="1">
         <v>139.04166666666669</v>
       </c>
-      <c r="AS120">
+      <c r="AS120" s="1">
         <v>92.459414826182694</v>
       </c>
       <c r="AT120" s="1">
@@ -39258,7 +39273,7 @@
       <c r="BD120">
         <v>1734141</v>
       </c>
-      <c r="BE120">
+      <c r="BE120" s="1">
         <v>17239.074288015952</v>
       </c>
       <c r="BF120">
@@ -39300,13 +39315,13 @@
       <c r="BR120">
         <v>66247</v>
       </c>
-      <c r="BS120">
+      <c r="BS120" s="1">
         <v>11421.896551724138</v>
       </c>
       <c r="BT120">
         <v>122450</v>
       </c>
-      <c r="BU120">
+      <c r="BU120" s="1">
         <v>21112.068965517243</v>
       </c>
       <c r="BV120">
@@ -39533,10 +39548,10 @@
       <c r="AQ121">
         <v>8.8030006523157205</v>
       </c>
-      <c r="AR121">
+      <c r="AR121" s="1">
         <v>10.46333419316055</v>
       </c>
-      <c r="AS121">
+      <c r="AS121" s="1">
         <v>8.2333115019918477</v>
       </c>
       <c r="AT121" s="1">
@@ -39572,7 +39587,7 @@
       <c r="BD121">
         <v>219267</v>
       </c>
-      <c r="BE121">
+      <c r="BE121" s="1">
         <v>22682.674800340588</v>
       </c>
       <c r="BF121">
@@ -39614,13 +39629,13 @@
       <c r="BR121">
         <v>327351</v>
       </c>
-      <c r="BS121">
+      <c r="BS121" s="1">
         <v>33922.383419689118</v>
       </c>
       <c r="BT121">
         <v>219085</v>
       </c>
-      <c r="BU121">
+      <c r="BU121" s="1">
         <v>22703.108808290155</v>
       </c>
       <c r="BV121">
@@ -39847,10 +39862,10 @@
       <c r="AQ122">
         <v>0.17268190621598317</v>
       </c>
-      <c r="AR122">
+      <c r="AR122" s="1">
         <v>59.5</v>
       </c>
-      <c r="AS122">
+      <c r="AS122" s="1">
         <v>39.566090611863615</v>
       </c>
       <c r="AT122" s="1">
@@ -39886,7 +39901,7 @@
       <c r="BD122">
         <v>1310657</v>
       </c>
-      <c r="BE122">
+      <c r="BE122" s="1">
         <v>18812.129698682111</v>
       </c>
       <c r="BF122">
@@ -39928,13 +39943,13 @@
       <c r="BR122">
         <v>209808</v>
       </c>
-      <c r="BS122">
+      <c r="BS122" s="1">
         <v>68789.508196721319</v>
       </c>
       <c r="BT122">
         <v>70347</v>
       </c>
-      <c r="BU122">
+      <c r="BU122" s="1">
         <v>23064.590163934427</v>
       </c>
       <c r="BV122">
@@ -40161,10 +40176,10 @@
       <c r="AQ123">
         <v>28.237805372080118</v>
       </c>
-      <c r="AR123">
+      <c r="AR123" s="1">
         <v>2396.583333333333</v>
       </c>
-      <c r="AS123">
+      <c r="AS123" s="1">
         <v>2037.0825529203146</v>
       </c>
       <c r="AT123" s="1">
@@ -40200,7 +40215,7 @@
       <c r="BD123">
         <v>36228573</v>
       </c>
-      <c r="BE123">
+      <c r="BE123" s="1">
         <v>29071.569482501607</v>
       </c>
       <c r="BF123">
@@ -40242,13 +40257,13 @@
       <c r="BR123">
         <v>37951587</v>
       </c>
-      <c r="BS123">
+      <c r="BS123" s="1">
         <v>53438.63895577236</v>
       </c>
       <c r="BT123">
         <v>23458395</v>
       </c>
-      <c r="BU123">
+      <c r="BU123" s="1">
         <v>33031.153634942741</v>
       </c>
       <c r="BV123">
@@ -40475,10 +40490,10 @@
       <c r="AQ124">
         <v>1.0674315180009188</v>
       </c>
-      <c r="AR124">
+      <c r="AR124" s="1">
         <v>83.208333333333343</v>
       </c>
-      <c r="AS124">
+      <c r="AS124" s="1">
         <v>54.054718446601939</v>
       </c>
       <c r="AT124" s="1">
@@ -40514,7 +40529,7 @@
       <c r="BD124">
         <v>623274</v>
       </c>
-      <c r="BE124">
+      <c r="BE124" s="1">
         <v>19038.432818151399</v>
       </c>
       <c r="BF124">
@@ -40556,13 +40571,13 @@
       <c r="BR124">
         <v>191616</v>
       </c>
-      <c r="BS124">
+      <c r="BS124" s="1">
         <v>41746.405228758173</v>
       </c>
       <c r="BT124">
         <v>120904</v>
       </c>
-      <c r="BU124">
+      <c r="BU124" s="1">
         <v>26340.740740740741</v>
       </c>
       <c r="BV124">
@@ -40789,10 +40804,10 @@
       <c r="AQ125">
         <v>33.686290392789957</v>
       </c>
-      <c r="AR125">
+      <c r="AR125" s="1">
         <v>452.91666666666663</v>
       </c>
-      <c r="AS125">
+      <c r="AS125" s="1">
         <v>341.35778013676662</v>
       </c>
       <c r="AT125" s="1">
@@ -40828,7 +40843,7 @@
       <c r="BD125">
         <v>14247452</v>
       </c>
-      <c r="BE125">
+      <c r="BE125" s="1">
         <v>35661.027505936967</v>
       </c>
       <c r="BF125">
@@ -40870,13 +40885,13 @@
       <c r="BR125">
         <v>23303713</v>
       </c>
-      <c r="BS125">
+      <c r="BS125" s="1">
         <v>72448.277684511602</v>
       </c>
       <c r="BT125">
         <v>12479484</v>
       </c>
-      <c r="BU125">
+      <c r="BU125" s="1">
         <v>38797.127401604179</v>
       </c>
       <c r="BV125">
@@ -41103,10 +41118,10 @@
       <c r="AQ126">
         <v>0.3085207094810164</v>
       </c>
-      <c r="AR126">
+      <c r="AR126" s="1">
         <v>12.708333333333332</v>
       </c>
-      <c r="AS126">
+      <c r="AS126" s="1">
         <v>8.4507406418896363</v>
       </c>
       <c r="AT126" s="1">
@@ -41142,7 +41157,7 @@
       <c r="BD126">
         <v>81946</v>
       </c>
-      <c r="BE126">
+      <c r="BE126" s="1">
         <v>11706.6303606937</v>
       </c>
       <c r="BF126">
@@ -41184,13 +41199,13 @@
       <c r="BR126">
         <v>2930</v>
       </c>
-      <c r="BS126">
+      <c r="BS126" s="1">
         <v>5860</v>
       </c>
       <c r="BT126">
         <v>3631</v>
       </c>
-      <c r="BU126">
+      <c r="BU126" s="1">
         <v>7262</v>
       </c>
       <c r="BV126">
@@ -41417,10 +41432,10 @@
       <c r="AQ127">
         <v>8.2338814419094755E-2</v>
       </c>
-      <c r="AR127">
+      <c r="AR127" s="1">
         <v>18.25</v>
       </c>
-      <c r="AS127">
+      <c r="AS127" s="1">
         <v>12.838508022504689</v>
       </c>
       <c r="AT127" s="1">
@@ -41456,7 +41471,7 @@
       <c r="BD127">
         <v>46409</v>
       </c>
-      <c r="BE127">
+      <c r="BE127" s="1">
         <v>17670.08455401528</v>
       </c>
       <c r="BF127">
@@ -41498,13 +41513,13 @@
       <c r="BR127">
         <v>0</v>
       </c>
-      <c r="BS127" t="s">
+      <c r="BS127" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT127">
         <v>0</v>
       </c>
-      <c r="BU127" t="s">
+      <c r="BU127" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV127" t="s">
@@ -41731,10 +41746,10 @@
       <c r="AQ128">
         <v>2.2640591920539455E-2</v>
       </c>
-      <c r="AR128">
+      <c r="AR128" s="1">
         <v>49.333333333333329</v>
       </c>
-      <c r="AS128">
+      <c r="AS128" s="1">
         <v>32.805498098351897</v>
       </c>
       <c r="AT128" s="1">
@@ -41770,7 +41785,7 @@
       <c r="BD128">
         <v>489275</v>
       </c>
-      <c r="BE128">
+      <c r="BE128" s="1">
         <v>19841.545185458173</v>
       </c>
       <c r="BF128">
@@ -41812,13 +41827,13 @@
       <c r="BR128">
         <v>-410</v>
       </c>
-      <c r="BS128" t="s">
+      <c r="BS128" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT128">
         <v>0</v>
       </c>
-      <c r="BU128" t="s">
+      <c r="BU128" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV128" t="s">
@@ -42045,10 +42060,10 @@
       <c r="AQ129">
         <v>8.1559890444436539E-2</v>
       </c>
-      <c r="AR129">
+      <c r="AR129" s="1">
         <v>42.708333333333329</v>
       </c>
-      <c r="AS129">
+      <c r="AS129" s="1">
         <v>32.188751116852423</v>
       </c>
       <c r="AT129" s="1">
@@ -42084,7 +42099,7 @@
       <c r="BD129">
         <v>43063</v>
       </c>
-      <c r="BE129">
+      <c r="BE129" s="1">
         <v>5499.4032847231529</v>
       </c>
       <c r="BF129">
@@ -42126,13 +42141,13 @@
       <c r="BR129">
         <v>181704</v>
       </c>
-      <c r="BS129">
+      <c r="BS129" s="1">
         <v>70978.125</v>
       </c>
       <c r="BT129">
         <v>72045</v>
       </c>
-      <c r="BU129">
+      <c r="BU129" s="1">
         <v>28142.578125</v>
       </c>
       <c r="BV129">
@@ -42359,10 +42374,10 @@
       <c r="AQ130">
         <v>2.4245127349793991</v>
       </c>
-      <c r="AR130">
+      <c r="AR130" s="1">
         <v>589.25</v>
       </c>
-      <c r="AS130">
+      <c r="AS130" s="1">
         <v>382.7951067961165</v>
       </c>
       <c r="AT130" s="1">
@@ -42398,7 +42413,7 @@
       <c r="BD130" t="s">
         <v>218</v>
       </c>
-      <c r="BE130" t="s">
+      <c r="BE130" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF130" t="s">
@@ -42440,13 +42455,13 @@
       <c r="BR130">
         <v>1847524</v>
       </c>
-      <c r="BS130">
+      <c r="BS130" s="1">
         <v>89511.821705426351</v>
       </c>
       <c r="BT130">
         <v>318528</v>
       </c>
-      <c r="BU130">
+      <c r="BU130" s="1">
         <v>15432.558139534884</v>
       </c>
       <c r="BV130">
@@ -42673,10 +42688,10 @@
       <c r="AQ131">
         <v>0.47624853117793692</v>
       </c>
-      <c r="AR131">
+      <c r="AR131" s="1">
         <v>83.791666666666657</v>
       </c>
-      <c r="AS131">
+      <c r="AS131" s="1">
         <v>63.15275950828314</v>
       </c>
       <c r="AT131" s="1">
@@ -42712,7 +42727,7 @@
       <c r="BD131">
         <v>956783</v>
       </c>
-      <c r="BE131">
+      <c r="BE131" s="1">
         <v>19488.551050292506</v>
       </c>
       <c r="BF131">
@@ -42754,13 +42769,13 @@
       <c r="BR131">
         <v>208008</v>
       </c>
-      <c r="BS131">
+      <c r="BS131" s="1">
         <v>41189.702970297032</v>
       </c>
       <c r="BT131">
         <v>122904</v>
       </c>
-      <c r="BU131">
+      <c r="BU131" s="1">
         <v>24337.425742574258</v>
       </c>
       <c r="BV131">
@@ -42987,10 +43002,10 @@
       <c r="AQ132">
         <v>1.2100340195455213</v>
       </c>
-      <c r="AR132">
+      <c r="AR132" s="1">
         <v>44.666666666666671</v>
       </c>
-      <c r="AS132">
+      <c r="AS132" s="1">
         <v>30.060466174340998</v>
       </c>
       <c r="AT132" s="1">
@@ -43026,7 +43041,7 @@
       <c r="BD132">
         <v>583203</v>
       </c>
-      <c r="BE132">
+      <c r="BE132" s="1">
         <v>25025.587601303243</v>
       </c>
       <c r="BF132">
@@ -43068,13 +43083,13 @@
       <c r="BR132">
         <v>77531</v>
       </c>
-      <c r="BS132" t="s">
+      <c r="BS132" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT132">
         <v>0</v>
       </c>
-      <c r="BU132" t="s">
+      <c r="BU132" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV132" t="s">
@@ -43301,10 +43316,10 @@
       <c r="AQ133">
         <v>0.51210517420087931</v>
       </c>
-      <c r="AR133">
+      <c r="AR133" s="1">
         <v>117.54166666666666</v>
       </c>
-      <c r="AS133">
+      <c r="AS133" s="1">
         <v>82.688198930332703</v>
       </c>
       <c r="AT133" s="1">
@@ -43340,7 +43355,7 @@
       <c r="BD133">
         <v>1560479</v>
       </c>
-      <c r="BE133">
+      <c r="BE133" s="1">
         <v>25098.060762021272</v>
       </c>
       <c r="BF133">
@@ -43382,13 +43397,13 @@
       <c r="BR133">
         <v>0</v>
       </c>
-      <c r="BS133" t="s">
+      <c r="BS133" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT133">
         <v>0</v>
       </c>
-      <c r="BU133" t="s">
+      <c r="BU133" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV133" t="s">
@@ -43615,10 +43630,10 @@
       <c r="AQ134">
         <v>1.75660495111296</v>
       </c>
-      <c r="AR134">
+      <c r="AR134" s="1">
         <v>755.75</v>
       </c>
-      <c r="AS134">
+      <c r="AS134" s="1">
         <v>502.55584840194837</v>
       </c>
       <c r="AT134" s="1">
@@ -43654,7 +43669,7 @@
       <c r="BD134">
         <v>5750011</v>
       </c>
-      <c r="BE134">
+      <c r="BE134" s="1">
         <v>22095.370144224333</v>
       </c>
       <c r="BF134">
@@ -43696,13 +43711,13 @@
       <c r="BR134">
         <v>2219036</v>
       </c>
-      <c r="BS134">
+      <c r="BS134" s="1">
         <v>37464.730710788455</v>
       </c>
       <c r="BT134">
         <v>1586868</v>
       </c>
-      <c r="BU134">
+      <c r="BU134" s="1">
         <v>26791.625865270984</v>
       </c>
       <c r="BV134">
@@ -43929,10 +43944,10 @@
       <c r="AQ135">
         <v>0.11503022751719037</v>
       </c>
-      <c r="AR135">
+      <c r="AR135" s="1">
         <v>58.458333333333336</v>
       </c>
-      <c r="AS135">
+      <c r="AS135" s="1">
         <v>40.563875913895082</v>
       </c>
       <c r="AT135" s="1">
@@ -43968,7 +43983,7 @@
       <c r="BD135">
         <v>576468</v>
       </c>
-      <c r="BE135">
+      <c r="BE135" s="1">
         <v>18241.607523920517</v>
       </c>
       <c r="BF135">
@@ -44010,13 +44025,13 @@
       <c r="BR135">
         <v>278603</v>
       </c>
-      <c r="BS135">
+      <c r="BS135" s="1">
         <v>57090.778688524588</v>
       </c>
       <c r="BT135">
         <v>180471</v>
       </c>
-      <c r="BU135">
+      <c r="BU135" s="1">
         <v>36981.762295081971</v>
       </c>
       <c r="BV135">
@@ -44243,10 +44258,10 @@
       <c r="AQ136">
         <v>3.2536729420181036E-2</v>
       </c>
-      <c r="AR136">
+      <c r="AR136" s="1">
         <v>63.791666666666671</v>
       </c>
-      <c r="AS136">
+      <c r="AS136" s="1">
         <v>42.4199472876493</v>
       </c>
       <c r="AT136" s="1">
@@ -44282,7 +44297,7 @@
       <c r="BD136" t="s">
         <v>218</v>
       </c>
-      <c r="BE136" t="s">
+      <c r="BE136" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF136" t="s">
@@ -44324,13 +44339,13 @@
       <c r="BR136">
         <v>0</v>
       </c>
-      <c r="BS136" t="s">
+      <c r="BS136" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT136">
         <v>0</v>
       </c>
-      <c r="BU136" t="s">
+      <c r="BU136" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV136" t="s">
@@ -44557,10 +44572,10 @@
       <c r="AQ137">
         <v>0.10457226245956651</v>
       </c>
-      <c r="AR137">
+      <c r="AR137" s="1">
         <v>41.416666666666664</v>
       </c>
-      <c r="AS137">
+      <c r="AS137" s="1">
         <v>35.519516217702026</v>
       </c>
       <c r="AT137" s="1">
@@ -44596,7 +44611,7 @@
       <c r="BD137">
         <v>554993</v>
       </c>
-      <c r="BE137">
+      <c r="BE137" s="1">
         <v>24191.788540942835</v>
       </c>
       <c r="BF137">
@@ -44638,13 +44653,13 @@
       <c r="BR137">
         <v>0</v>
       </c>
-      <c r="BS137" t="s">
+      <c r="BS137" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT137">
         <v>0</v>
       </c>
-      <c r="BU137" t="s">
+      <c r="BU137" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV137" t="s">
@@ -44871,10 +44886,10 @@
       <c r="AQ138">
         <v>7.4243159495647513</v>
       </c>
-      <c r="AR138">
+      <c r="AR138" s="1">
         <v>199.16666666666666</v>
       </c>
-      <c r="AS138">
+      <c r="AS138" s="1">
         <v>138.20051808155273</v>
       </c>
       <c r="AT138" s="1">
@@ -44910,7 +44925,7 @@
       <c r="BD138">
         <v>370322</v>
       </c>
-      <c r="BE138">
+      <c r="BE138" s="1">
         <v>12690.659561741701</v>
       </c>
       <c r="BF138">
@@ -44952,13 +44967,13 @@
       <c r="BR138">
         <v>356706</v>
       </c>
-      <c r="BS138">
+      <c r="BS138" s="1">
         <v>33972</v>
       </c>
       <c r="BT138">
         <v>224383</v>
       </c>
-      <c r="BU138">
+      <c r="BU138" s="1">
         <v>21369.809523809523</v>
       </c>
       <c r="BV138">
@@ -45185,10 +45200,10 @@
       <c r="AQ139">
         <v>0.21930906510942533</v>
       </c>
-      <c r="AR139">
+      <c r="AR139" s="1">
         <v>96.833333333333329</v>
       </c>
-      <c r="AS139">
+      <c r="AS139" s="1">
         <v>68.120302840869627</v>
       </c>
       <c r="AT139" s="1">
@@ -45224,7 +45239,7 @@
       <c r="BD139">
         <v>1229611</v>
       </c>
-      <c r="BE139">
+      <c r="BE139" s="1">
         <v>26964.561294027135</v>
       </c>
       <c r="BF139">
@@ -45266,13 +45281,13 @@
       <c r="BR139">
         <v>233771</v>
       </c>
-      <c r="BS139">
+      <c r="BS139" s="1">
         <v>233771</v>
       </c>
       <c r="BT139">
         <v>146065</v>
       </c>
-      <c r="BU139">
+      <c r="BU139" s="1">
         <v>146065</v>
       </c>
       <c r="BV139">
@@ -45499,10 +45514,10 @@
       <c r="AQ140">
         <v>6.5501338193149401</v>
       </c>
-      <c r="AR140">
+      <c r="AR140" s="1">
         <v>627.83333333333326</v>
       </c>
-      <c r="AS140">
+      <c r="AS140" s="1">
         <v>422.52901521918847</v>
       </c>
       <c r="AT140" s="1">
@@ -45538,7 +45553,7 @@
       <c r="BD140">
         <v>8453409</v>
       </c>
-      <c r="BE140">
+      <c r="BE140" s="1">
         <v>24679.116520082691</v>
       </c>
       <c r="BF140">
@@ -45580,13 +45595,13 @@
       <c r="BR140">
         <v>5560312</v>
       </c>
-      <c r="BS140">
+      <c r="BS140" s="1">
         <v>74475.113849450849</v>
       </c>
       <c r="BT140">
         <v>2281913</v>
       </c>
-      <c r="BU140">
+      <c r="BU140" s="1">
         <v>30564.063755692474</v>
       </c>
       <c r="BV140">
@@ -45813,10 +45828,10 @@
       <c r="AQ141">
         <v>0.29976975552556201</v>
       </c>
-      <c r="AR141">
+      <c r="AR141" s="1">
         <v>214</v>
       </c>
-      <c r="AS141">
+      <c r="AS141" s="1">
         <v>150.54469681183582</v>
       </c>
       <c r="AT141" s="1">
@@ -45852,7 +45867,7 @@
       <c r="BD141">
         <v>2283306</v>
       </c>
-      <c r="BE141">
+      <c r="BE141" s="1">
         <v>25582.628680087251</v>
       </c>
       <c r="BF141">
@@ -45894,13 +45909,13 @@
       <c r="BR141">
         <v>225428</v>
       </c>
-      <c r="BS141">
+      <c r="BS141" s="1">
         <v>39828.268551236746</v>
       </c>
       <c r="BT141">
         <v>137349</v>
       </c>
-      <c r="BU141">
+      <c r="BU141" s="1">
         <v>24266.607773851589</v>
       </c>
       <c r="BV141">
@@ -46127,10 +46142,10 @@
       <c r="AQ142">
         <v>0.33411293017039767</v>
       </c>
-      <c r="AR142">
+      <c r="AR142" s="1">
         <v>20.5</v>
       </c>
-      <c r="AS142">
+      <c r="AS142" s="1">
         <v>14.224823200025929</v>
       </c>
       <c r="AT142" s="1">
@@ -46166,7 +46181,7 @@
       <c r="BD142" t="s">
         <v>218</v>
       </c>
-      <c r="BE142" t="s">
+      <c r="BE142" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF142" t="s">
@@ -46208,13 +46223,13 @@
       <c r="BR142">
         <v>31005</v>
       </c>
-      <c r="BS142">
+      <c r="BS142" s="1">
         <v>238500</v>
       </c>
       <c r="BT142">
         <v>2629</v>
       </c>
-      <c r="BU142">
+      <c r="BU142" s="1">
         <v>20223.076923076922</v>
       </c>
       <c r="BV142">
@@ -46441,10 +46456,10 @@
       <c r="AQ143">
         <v>7.8131518735328216</v>
       </c>
-      <c r="AR143">
+      <c r="AR143" s="1">
         <v>39.416666666666664</v>
       </c>
-      <c r="AS143">
+      <c r="AS143" s="1">
         <v>29.707862006382822</v>
       </c>
       <c r="AT143" s="1">
@@ -46480,7 +46495,7 @@
       <c r="BD143">
         <v>576102</v>
       </c>
-      <c r="BE143">
+      <c r="BE143" s="1">
         <v>20649.954482244048</v>
       </c>
       <c r="BF143">
@@ -46522,13 +46537,13 @@
       <c r="BR143">
         <v>654297</v>
       </c>
-      <c r="BS143">
+      <c r="BS143" s="1">
         <v>54208.533554266782</v>
       </c>
       <c r="BT143">
         <v>342311</v>
       </c>
-      <c r="BU143">
+      <c r="BU143" s="1">
         <v>28360.480530240267</v>
       </c>
       <c r="BV143">
@@ -46755,10 +46770,10 @@
       <c r="AQ144">
         <v>0.85125199687351105</v>
       </c>
-      <c r="AR144">
+      <c r="AR144" s="1">
         <v>90.541666666666657</v>
       </c>
-      <c r="AS144">
+      <c r="AS144" s="1">
         <v>54.203397032001334</v>
       </c>
       <c r="AT144" s="1">
@@ -46794,7 +46809,7 @@
       <c r="BD144">
         <v>2267666</v>
       </c>
-      <c r="BE144">
+      <c r="BE144" s="1">
         <v>25703.201346955288</v>
       </c>
       <c r="BF144">
@@ -46836,13 +46851,13 @@
       <c r="BR144">
         <v>1456800</v>
       </c>
-      <c r="BS144">
+      <c r="BS144" s="1">
         <v>32416.555407209613</v>
       </c>
       <c r="BT144">
         <v>1269125</v>
       </c>
-      <c r="BU144">
+      <c r="BU144" s="1">
         <v>28240.43168669337</v>
       </c>
       <c r="BV144">
@@ -47069,10 +47084,10 @@
       <c r="AQ145">
         <v>0.13288142738672074</v>
       </c>
-      <c r="AR145">
+      <c r="AR145" s="1">
         <v>137.79166666666669</v>
       </c>
-      <c r="AS145">
+      <c r="AS145" s="1">
         <v>108.42449386610028</v>
       </c>
       <c r="AT145" s="1">
@@ -47108,7 +47123,7 @@
       <c r="BD145">
         <v>1185038</v>
       </c>
-      <c r="BE145">
+      <c r="BE145" s="1">
         <v>20989.984896695358</v>
       </c>
       <c r="BF145">
@@ -47150,13 +47165,13 @@
       <c r="BR145">
         <v>57224</v>
       </c>
-      <c r="BS145">
+      <c r="BS145" s="1">
         <v>57224</v>
       </c>
       <c r="BT145">
         <v>23139</v>
       </c>
-      <c r="BU145">
+      <c r="BU145" s="1">
         <v>23139</v>
       </c>
       <c r="BV145">
@@ -47383,10 +47398,10 @@
       <c r="AQ146">
         <v>4.9094284710723066</v>
       </c>
-      <c r="AR146">
+      <c r="AR146" s="1">
         <v>12.583333333333332</v>
       </c>
-      <c r="AS146">
+      <c r="AS146" s="1">
         <v>8.8521219698548297</v>
       </c>
       <c r="AT146" s="1">
@@ -47422,7 +47437,7 @@
       <c r="BD146">
         <v>17907</v>
       </c>
-      <c r="BE146">
+      <c r="BE146" s="1">
         <v>2355.1998808982421</v>
       </c>
       <c r="BF146">
@@ -47464,13 +47479,13 @@
       <c r="BR146">
         <v>180340</v>
       </c>
-      <c r="BS146">
+      <c r="BS146" s="1">
         <v>60113.333333333336</v>
       </c>
       <c r="BT146">
         <v>82861</v>
       </c>
-      <c r="BU146">
+      <c r="BU146" s="1">
         <v>27620.333333333332</v>
       </c>
       <c r="BV146">
@@ -47697,10 +47712,10 @@
       <c r="AQ147">
         <v>4.662710644085025</v>
       </c>
-      <c r="AR147">
+      <c r="AR147" s="1">
         <v>576.36145969285894</v>
       </c>
-      <c r="AS147">
+      <c r="AS147" s="1">
         <v>434.39661844446925</v>
       </c>
       <c r="AT147" s="1">
@@ -47736,7 +47751,7 @@
       <c r="BD147">
         <v>10488677</v>
       </c>
-      <c r="BE147">
+      <c r="BE147" s="1">
         <v>24332.376769202237</v>
       </c>
       <c r="BF147">
@@ -47778,13 +47793,13 @@
       <c r="BR147">
         <v>13014760</v>
       </c>
-      <c r="BS147">
+      <c r="BS147" s="1">
         <v>38606.864228293438</v>
       </c>
       <c r="BT147">
         <v>9788273</v>
       </c>
-      <c r="BU147">
+      <c r="BU147" s="1">
         <v>29035.842899943644</v>
       </c>
       <c r="BV147">
@@ -48011,10 +48026,10 @@
       <c r="AQ148">
         <v>0.36240566543867803</v>
       </c>
-      <c r="AR148">
+      <c r="AR148" s="1">
         <v>24.666666666666668</v>
       </c>
-      <c r="AS148">
+      <c r="AS148" s="1">
         <v>17.116047427673475</v>
       </c>
       <c r="AT148" s="1">
@@ -48050,7 +48065,7 @@
       <c r="BD148">
         <v>319436</v>
       </c>
-      <c r="BE148">
+      <c r="BE148" s="1">
         <v>18877.252099479843</v>
       </c>
       <c r="BF148">
@@ -48092,13 +48107,13 @@
       <c r="BR148">
         <v>343157</v>
       </c>
-      <c r="BS148">
+      <c r="BS148" s="1">
         <v>41645.26699029126</v>
       </c>
       <c r="BT148">
         <v>247527</v>
       </c>
-      <c r="BU148">
+      <c r="BU148" s="1">
         <v>30039.684466019418</v>
       </c>
       <c r="BV148">
@@ -48325,10 +48340,10 @@
       <c r="AQ149">
         <v>0.5001242103768897</v>
       </c>
-      <c r="AR149">
+      <c r="AR149" s="1">
         <v>29.291666666666664</v>
       </c>
-      <c r="AS149">
+      <c r="AS149" s="1">
         <v>22.07677271721683</v>
       </c>
       <c r="AT149" s="1">
@@ -48364,7 +48379,7 @@
       <c r="BD149" t="s">
         <v>218</v>
       </c>
-      <c r="BE149" t="s">
+      <c r="BE149" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF149" t="s">
@@ -48406,13 +48421,13 @@
       <c r="BR149">
         <v>128709</v>
       </c>
-      <c r="BS149">
+      <c r="BS149" s="1">
         <v>52966.666666666672</v>
       </c>
       <c r="BT149">
         <v>55632</v>
       </c>
-      <c r="BU149">
+      <c r="BU149" s="1">
         <v>22893.827160493831</v>
       </c>
       <c r="BV149">
@@ -48639,10 +48654,10 @@
       <c r="AQ150">
         <v>0.25977141029643558</v>
       </c>
-      <c r="AR150">
+      <c r="AR150" s="1">
         <v>88.791666666666657</v>
       </c>
-      <c r="AS150">
+      <c r="AS150" s="1">
         <v>59.044355107760047</v>
       </c>
       <c r="AT150" s="1">
@@ -48678,7 +48693,7 @@
       <c r="BD150">
         <v>1022408</v>
       </c>
-      <c r="BE150">
+      <c r="BE150" s="1">
         <v>22085.499501995309</v>
       </c>
       <c r="BF150">
@@ -48720,13 +48735,13 @@
       <c r="BR150">
         <v>331540</v>
       </c>
-      <c r="BS150">
+      <c r="BS150" s="1">
         <v>25820.872274143301</v>
       </c>
       <c r="BT150">
         <v>303395</v>
       </c>
-      <c r="BU150">
+      <c r="BU150" s="1">
         <v>23628.894080996884</v>
       </c>
       <c r="BV150">
@@ -48953,10 +48968,10 @@
       <c r="AQ151">
         <v>0.6167011373789274</v>
       </c>
-      <c r="AR151">
+      <c r="AR151" s="1">
         <v>54.875</v>
       </c>
-      <c r="AS151">
+      <c r="AS151" s="1">
         <v>36.490575165143127</v>
       </c>
       <c r="AT151" s="1">
@@ -48992,7 +49007,7 @@
       <c r="BD151" t="s">
         <v>218</v>
       </c>
-      <c r="BE151" t="s">
+      <c r="BE151" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF151" t="s">
@@ -49034,13 +49049,13 @@
       <c r="BR151">
         <v>0</v>
       </c>
-      <c r="BS151" t="s">
+      <c r="BS151" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT151">
         <v>0</v>
       </c>
-      <c r="BU151" t="s">
+      <c r="BU151" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV151" t="s">
@@ -49267,10 +49282,10 @@
       <c r="AQ152">
         <v>1.1009108513232446</v>
       </c>
-      <c r="AR152">
+      <c r="AR152" s="1">
         <v>45.083333333333336</v>
       </c>
-      <c r="AS152">
+      <c r="AS152" s="1">
         <v>35.47484196042349</v>
       </c>
       <c r="AT152" s="1">
@@ -49306,7 +49321,7 @@
       <c r="BD152">
         <v>346241</v>
       </c>
-      <c r="BE152">
+      <c r="BE152" s="1">
         <v>17390.8380448057</v>
       </c>
       <c r="BF152">
@@ -49348,13 +49363,13 @@
       <c r="BR152">
         <v>32918</v>
       </c>
-      <c r="BS152">
+      <c r="BS152" s="1">
         <v>32918</v>
       </c>
       <c r="BT152">
         <v>32119</v>
       </c>
-      <c r="BU152">
+      <c r="BU152" s="1">
         <v>32119</v>
       </c>
       <c r="BV152">
@@ -49581,10 +49596,10 @@
       <c r="AQ153">
         <v>0.14702644633519096</v>
       </c>
-      <c r="AR153">
+      <c r="AR153" s="1">
         <v>223.41666666666669</v>
       </c>
-      <c r="AS153">
+      <c r="AS153" s="1">
         <v>191.60527762506871</v>
       </c>
       <c r="AT153" s="1">
@@ -49620,7 +49635,7 @@
       <c r="BD153">
         <v>2625759</v>
       </c>
-      <c r="BE153">
+      <c r="BE153" s="1">
         <v>21886.082683244651</v>
       </c>
       <c r="BF153">
@@ -49662,13 +49677,13 @@
       <c r="BR153">
         <v>151223</v>
       </c>
-      <c r="BS153">
+      <c r="BS153" s="1">
         <v>64625.213675213679</v>
       </c>
       <c r="BT153">
         <v>69276</v>
       </c>
-      <c r="BU153">
+      <c r="BU153" s="1">
         <v>29605.128205128207</v>
       </c>
       <c r="BV153">
@@ -49895,10 +49910,10 @@
       <c r="AQ154">
         <v>2.3787530476492691</v>
       </c>
-      <c r="AR154">
+      <c r="AR154" s="1">
         <v>552.54166666666674</v>
       </c>
-      <c r="AS154">
+      <c r="AS154" s="1">
         <v>469.65735481547165</v>
       </c>
       <c r="AT154" s="1">
@@ -49934,7 +49949,7 @@
       <c r="BD154">
         <v>9524818</v>
       </c>
-      <c r="BE154">
+      <c r="BE154" s="1">
         <v>29189.68208467084</v>
       </c>
       <c r="BF154">
@@ -49976,13 +49991,13 @@
       <c r="BR154">
         <v>4953428</v>
       </c>
-      <c r="BS154">
+      <c r="BS154" s="1">
         <v>36090.550091074678</v>
       </c>
       <c r="BT154">
         <v>4392160</v>
       </c>
-      <c r="BU154">
+      <c r="BU154" s="1">
         <v>32001.165755919854</v>
       </c>
       <c r="BV154">
@@ -50209,10 +50224,10 @@
       <c r="AQ155">
         <v>0.49330149259478223</v>
       </c>
-      <c r="AR155">
+      <c r="AR155" s="1">
         <v>412.375</v>
       </c>
-      <c r="AS155">
+      <c r="AS155" s="1">
         <v>290.09752031673264</v>
       </c>
       <c r="AT155" s="1">
@@ -50248,7 +50263,7 @@
       <c r="BD155">
         <v>5851284</v>
       </c>
-      <c r="BE155">
+      <c r="BE155" s="1">
         <v>21380.928330613602</v>
       </c>
       <c r="BF155">
@@ -50290,13 +50305,13 @@
       <c r="BR155">
         <v>7522976</v>
       </c>
-      <c r="BS155">
+      <c r="BS155" s="1">
         <v>60396.40333975594</v>
       </c>
       <c r="BT155">
         <v>3428946</v>
       </c>
-      <c r="BU155">
+      <c r="BU155" s="1">
         <v>27528.468208092487</v>
       </c>
       <c r="BV155">
@@ -50523,10 +50538,10 @@
       <c r="AQ156">
         <v>0.53049305215625808</v>
       </c>
-      <c r="AR156">
+      <c r="AR156" s="1">
         <v>474.58333333333337</v>
       </c>
-      <c r="AS156">
+      <c r="AS156" s="1">
         <v>315.58667511843601</v>
       </c>
       <c r="AT156" s="1">
@@ -50562,7 +50577,7 @@
       <c r="BD156">
         <v>2402038</v>
       </c>
-      <c r="BE156">
+      <c r="BE156" s="1">
         <v>11755.97366171855</v>
       </c>
       <c r="BF156">
@@ -50604,13 +50619,13 @@
       <c r="BR156">
         <v>879446</v>
       </c>
-      <c r="BS156">
+      <c r="BS156" s="1">
         <v>53235.230024213073</v>
       </c>
       <c r="BT156">
         <v>471072</v>
       </c>
-      <c r="BU156">
+      <c r="BU156" s="1">
         <v>28515.254237288136</v>
       </c>
       <c r="BV156">
@@ -50837,10 +50852,10 @@
       <c r="AQ157">
         <v>0.15920387470241956</v>
       </c>
-      <c r="AR157">
+      <c r="AR157" s="1">
         <v>236.08333333333331</v>
       </c>
-      <c r="AS157">
+      <c r="AS157" s="1">
         <v>177.93313544203494</v>
       </c>
       <c r="AT157" s="1">
@@ -50876,7 +50891,7 @@
       <c r="BD157">
         <v>2268699</v>
       </c>
-      <c r="BE157">
+      <c r="BE157" s="1">
         <v>19528.591643142561</v>
       </c>
       <c r="BF157">
@@ -50918,13 +50933,13 @@
       <c r="BR157">
         <v>90954</v>
       </c>
-      <c r="BS157">
+      <c r="BS157" s="1">
         <v>52880.232558139534</v>
       </c>
       <c r="BT157">
         <v>37708</v>
       </c>
-      <c r="BU157">
+      <c r="BU157" s="1">
         <v>21923.255813953489</v>
       </c>
       <c r="BV157">
@@ -51151,10 +51166,10 @@
       <c r="AQ158">
         <v>0.14969044208615917</v>
       </c>
-      <c r="AR158">
+      <c r="AR158" s="1">
         <v>53.958333333333329</v>
       </c>
-      <c r="AS158">
+      <c r="AS158" s="1">
         <v>42.458336727124234</v>
       </c>
       <c r="AT158" s="1">
@@ -51190,7 +51205,7 @@
       <c r="BD158">
         <v>527175</v>
       </c>
-      <c r="BE158">
+      <c r="BE158" s="1">
         <v>28189.824605933318</v>
       </c>
       <c r="BF158">
@@ -51232,13 +51247,13 @@
       <c r="BR158">
         <v>0</v>
       </c>
-      <c r="BS158" t="s">
+      <c r="BS158" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT158">
         <v>0</v>
       </c>
-      <c r="BU158" t="s">
+      <c r="BU158" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV158" t="s">
@@ -51465,10 +51480,10 @@
       <c r="AQ159">
         <v>17.675317955282008</v>
       </c>
-      <c r="AR159">
+      <c r="AR159" s="1">
         <v>55.5</v>
       </c>
-      <c r="AS159">
+      <c r="AS159" s="1">
         <v>41.829674622095048</v>
       </c>
       <c r="AT159" s="1">
@@ -51504,7 +51519,7 @@
       <c r="BD159">
         <v>1026151</v>
       </c>
-      <c r="BE159">
+      <c r="BE159" s="1">
         <v>26088.472323808648</v>
       </c>
       <c r="BF159">
@@ -51546,13 +51561,13 @@
       <c r="BR159">
         <v>1822410</v>
       </c>
-      <c r="BS159">
+      <c r="BS159" s="1">
         <v>54109.560570071248</v>
       </c>
       <c r="BT159">
         <v>975440</v>
       </c>
-      <c r="BU159">
+      <c r="BU159" s="1">
         <v>28961.995249406169</v>
       </c>
       <c r="BV159">
@@ -51779,10 +51794,10 @@
       <c r="AQ160">
         <v>0</v>
       </c>
-      <c r="AR160">
+      <c r="AR160" s="1">
         <v>8.75</v>
       </c>
-      <c r="AS160">
+      <c r="AS160" s="1">
         <v>5.8185427370387668</v>
       </c>
       <c r="AT160" s="1">
@@ -51818,7 +51833,7 @@
       <c r="BD160">
         <v>227039</v>
       </c>
-      <c r="BE160">
+      <c r="BE160" s="1">
         <v>29017.778737562501</v>
       </c>
       <c r="BF160">
@@ -51860,13 +51875,13 @@
       <c r="BR160">
         <v>0</v>
       </c>
-      <c r="BS160" t="s">
+      <c r="BS160" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT160">
         <v>0</v>
       </c>
-      <c r="BU160" t="s">
+      <c r="BU160" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV160" t="s">
@@ -52093,10 +52108,10 @@
       <c r="AQ161">
         <v>0.24987316083206493</v>
       </c>
-      <c r="AR161">
+      <c r="AR161" s="1">
         <v>30.541666666666668</v>
       </c>
-      <c r="AS161">
+      <c r="AS161" s="1">
         <v>20.309484886901981</v>
       </c>
       <c r="AT161" s="1">
@@ -52132,7 +52147,7 @@
       <c r="BD161" t="s">
         <v>218</v>
       </c>
-      <c r="BE161" t="s">
+      <c r="BE161" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF161" t="s">
@@ -52174,13 +52189,13 @@
       <c r="BR161">
         <v>15809</v>
       </c>
-      <c r="BS161">
+      <c r="BS161" s="1">
         <v>31618</v>
       </c>
       <c r="BT161">
         <v>12984</v>
       </c>
-      <c r="BU161">
+      <c r="BU161" s="1">
         <v>25968</v>
       </c>
       <c r="BV161">
@@ -52407,10 +52422,10 @@
       <c r="AQ162">
         <v>0.19471972477383678</v>
       </c>
-      <c r="AR162">
+      <c r="AR162" s="1">
         <v>36.333333333333336</v>
       </c>
-      <c r="AS162">
+      <c r="AS162" s="1">
         <v>28.589706274943886</v>
       </c>
       <c r="AT162" s="1">
@@ -52446,7 +52461,7 @@
       <c r="BD162">
         <v>334301</v>
       </c>
-      <c r="BE162">
+      <c r="BE162" s="1">
         <v>22151.8683743646</v>
       </c>
       <c r="BF162">
@@ -52488,13 +52503,13 @@
       <c r="BR162">
         <v>77224</v>
       </c>
-      <c r="BS162">
+      <c r="BS162" s="1">
         <v>77224</v>
       </c>
       <c r="BT162">
         <v>31421</v>
       </c>
-      <c r="BU162">
+      <c r="BU162" s="1">
         <v>31421</v>
       </c>
       <c r="BV162">
@@ -52721,10 +52736,10 @@
       <c r="AQ163">
         <v>0.37919563861489064</v>
       </c>
-      <c r="AR163">
+      <c r="AR163" s="1">
         <v>23.083333333333332</v>
       </c>
-      <c r="AS163">
+      <c r="AS163" s="1">
         <v>15.349869887235602</v>
       </c>
       <c r="AT163" s="1">
@@ -52760,7 +52775,7 @@
       <c r="BD163">
         <v>360474</v>
       </c>
-      <c r="BE163">
+      <c r="BE163" s="1">
         <v>24589.138035540476</v>
       </c>
       <c r="BF163">
@@ -52802,13 +52817,13 @@
       <c r="BR163">
         <v>60439</v>
       </c>
-      <c r="BS163">
+      <c r="BS163" s="1">
         <v>59253.921568627447</v>
       </c>
       <c r="BT163">
         <v>21005</v>
       </c>
-      <c r="BU163">
+      <c r="BU163" s="1">
         <v>20593.137254901962</v>
       </c>
       <c r="BV163">
@@ -53035,10 +53050,10 @@
       <c r="AQ164">
         <v>9.1486627237676407E-2</v>
       </c>
-      <c r="AR164">
+      <c r="AR164" s="1">
         <v>43.583333333333336</v>
       </c>
-      <c r="AS164">
+      <c r="AS164" s="1">
         <v>28.981884299726435</v>
       </c>
       <c r="AT164" s="1">
@@ -53074,7 +53089,7 @@
       <c r="BD164">
         <v>1023120</v>
       </c>
-      <c r="BE164">
+      <c r="BE164" s="1">
         <v>30195.054611933916</v>
       </c>
       <c r="BF164">
@@ -53116,13 +53131,13 @@
       <c r="BR164">
         <v>0</v>
       </c>
-      <c r="BS164" t="s">
+      <c r="BS164" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT164">
         <v>0</v>
       </c>
-      <c r="BU164" t="s">
+      <c r="BU164" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV164" t="s">
@@ -53349,10 +53364,10 @@
       <c r="AQ165">
         <v>0</v>
       </c>
-      <c r="AR165">
+      <c r="AR165" s="1">
         <v>11.5</v>
       </c>
-      <c r="AS165">
+      <c r="AS165" s="1">
         <v>7.6472275972509509</v>
       </c>
       <c r="AT165" s="1">
@@ -53388,7 +53403,7 @@
       <c r="BD165">
         <v>10676</v>
       </c>
-      <c r="BE165">
+      <c r="BE165" s="1">
         <v>4510.528712384119</v>
       </c>
       <c r="BF165">
@@ -53430,13 +53445,13 @@
       <c r="BR165">
         <v>0</v>
       </c>
-      <c r="BS165" t="s">
+      <c r="BS165" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT165">
         <v>0</v>
       </c>
-      <c r="BU165" t="s">
+      <c r="BU165" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV165" t="s">
@@ -53663,10 +53678,10 @@
       <c r="AQ166">
         <v>0.6945591562855844</v>
       </c>
-      <c r="AR166">
+      <c r="AR166" s="1">
         <v>22.083333333333332</v>
       </c>
-      <c r="AS166">
+      <c r="AS166" s="1">
         <v>15.323488406531995</v>
       </c>
       <c r="AT166" s="1">
@@ -53702,7 +53717,7 @@
       <c r="BD166" t="s">
         <v>218</v>
       </c>
-      <c r="BE166" t="s">
+      <c r="BE166" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF166" t="s">
@@ -53744,13 +53759,13 @@
       <c r="BR166">
         <v>0</v>
       </c>
-      <c r="BS166" t="s">
+      <c r="BS166" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT166">
         <v>0</v>
       </c>
-      <c r="BU166" t="s">
+      <c r="BU166" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV166" t="s">
@@ -53977,10 +53992,10 @@
       <c r="AQ167">
         <v>0</v>
       </c>
-      <c r="AR167">
+      <c r="AR167" s="1">
         <v>11.916666666666666</v>
       </c>
-      <c r="AS167">
+      <c r="AS167" s="1">
         <v>7.924301060919464</v>
       </c>
       <c r="AT167" s="1">
@@ -54016,7 +54031,7 @@
       <c r="BD167">
         <v>52119</v>
       </c>
-      <c r="BE167">
+      <c r="BE167" s="1">
         <v>6049.8567705207361</v>
       </c>
       <c r="BF167">
@@ -54058,13 +54073,13 @@
       <c r="BR167">
         <v>120518</v>
       </c>
-      <c r="BS167">
+      <c r="BS167" s="1">
         <v>49191.020408163262</v>
       </c>
       <c r="BT167">
         <v>62445</v>
       </c>
-      <c r="BU167">
+      <c r="BU167" s="1">
         <v>25487.755102040814</v>
       </c>
       <c r="BV167">
@@ -54291,10 +54306,10 @@
       <c r="AQ168">
         <v>4.4834388665866545E-2</v>
       </c>
-      <c r="AR168">
+      <c r="AR168" s="1">
         <v>5.666666666666667</v>
       </c>
-      <c r="AS168">
+      <c r="AS168" s="1">
         <v>3.7681991058917728</v>
       </c>
       <c r="AT168" s="1">
@@ -54330,7 +54345,7 @@
       <c r="BD168">
         <v>73343</v>
       </c>
-      <c r="BE168">
+      <c r="BE168" s="1">
         <v>29813.857158390158</v>
       </c>
       <c r="BF168">
@@ -54372,13 +54387,13 @@
       <c r="BR168">
         <v>0</v>
       </c>
-      <c r="BS168" t="s">
+      <c r="BS168" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT168">
         <v>0</v>
       </c>
-      <c r="BU168" t="s">
+      <c r="BU168" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV168" t="s">
@@ -54605,10 +54620,10 @@
       <c r="AQ169">
         <v>0.91894977168949765</v>
       </c>
-      <c r="AR169">
+      <c r="AR169" s="1">
         <v>14.916666666666668</v>
       </c>
-      <c r="AS169">
+      <c r="AS169" s="1">
         <v>10.350582734978218</v>
       </c>
       <c r="AT169" s="1">
@@ -54644,7 +54659,7 @@
       <c r="BD169">
         <v>210669</v>
       </c>
-      <c r="BE169">
+      <c r="BE169" s="1">
         <v>21236.60857551108</v>
       </c>
       <c r="BF169">
@@ -54686,13 +54701,13 @@
       <c r="BR169">
         <v>0</v>
       </c>
-      <c r="BS169" t="s">
+      <c r="BS169" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT169">
         <v>0</v>
       </c>
-      <c r="BU169" t="s">
+      <c r="BU169" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV169" t="s">
@@ -54919,10 +54934,10 @@
       <c r="AQ170">
         <v>0.39721496428085967</v>
       </c>
-      <c r="AR170">
+      <c r="AR170" s="1">
         <v>146</v>
       </c>
-      <c r="AS170">
+      <c r="AS170" s="1">
         <v>87.40391311556958</v>
       </c>
       <c r="AT170" s="1">
@@ -54958,7 +54973,7 @@
       <c r="BD170">
         <v>1061349</v>
       </c>
-      <c r="BE170">
+      <c r="BE170" s="1">
         <v>26562.136189845292</v>
       </c>
       <c r="BF170">
@@ -55000,13 +55015,13 @@
       <c r="BR170">
         <v>15934</v>
       </c>
-      <c r="BS170">
+      <c r="BS170" s="1">
         <v>15934</v>
       </c>
       <c r="BT170">
         <v>29653</v>
       </c>
-      <c r="BU170">
+      <c r="BU170" s="1">
         <v>29653</v>
       </c>
       <c r="BV170">
@@ -55233,10 +55248,10 @@
       <c r="AQ171">
         <v>0.91334602302867651</v>
       </c>
-      <c r="AR171">
+      <c r="AR171" s="1">
         <v>196.66666666666669</v>
       </c>
-      <c r="AS171">
+      <c r="AS171" s="1">
         <v>132.35578390194917</v>
       </c>
       <c r="AT171" s="1">
@@ -55272,7 +55287,7 @@
       <c r="BD171">
         <v>1261854</v>
       </c>
-      <c r="BE171">
+      <c r="BE171" s="1">
         <v>21775.288687847766</v>
       </c>
       <c r="BF171">
@@ -55314,13 +55329,13 @@
       <c r="BR171">
         <v>75167</v>
       </c>
-      <c r="BS171">
+      <c r="BS171" s="1">
         <v>75167</v>
       </c>
       <c r="BT171">
         <v>22604</v>
       </c>
-      <c r="BU171">
+      <c r="BU171" s="1">
         <v>22604</v>
       </c>
       <c r="BV171">
@@ -55547,10 +55562,10 @@
       <c r="AQ172">
         <v>0.67156857952082494</v>
       </c>
-      <c r="AR172">
+      <c r="AR172" s="1">
         <v>261.20833333333337</v>
       </c>
-      <c r="AS172">
+      <c r="AS172" s="1">
         <v>173.69735437379063</v>
       </c>
       <c r="AT172" s="1">
@@ -55586,7 +55601,7 @@
       <c r="BD172">
         <v>1529861</v>
       </c>
-      <c r="BE172">
+      <c r="BE172" s="1">
         <v>21950.325339453451</v>
       </c>
       <c r="BF172">
@@ -55628,13 +55643,13 @@
       <c r="BR172">
         <v>193951</v>
       </c>
-      <c r="BS172">
+      <c r="BS172" s="1">
         <v>30639.96840442338</v>
       </c>
       <c r="BT172">
         <v>152904</v>
       </c>
-      <c r="BU172">
+      <c r="BU172" s="1">
         <v>24155.450236966823</v>
       </c>
       <c r="BV172">
@@ -55861,10 +55876,10 @@
       <c r="AQ173">
         <v>2.936868384446021E-2</v>
       </c>
-      <c r="AR173">
+      <c r="AR173" s="1">
         <v>58.375</v>
       </c>
-      <c r="AS173">
+      <c r="AS173" s="1">
         <v>45.933690930271091</v>
       </c>
       <c r="AT173" s="1">
@@ -55900,7 +55915,7 @@
       <c r="BD173">
         <v>271679</v>
       </c>
-      <c r="BE173">
+      <c r="BE173" s="1">
         <v>12640.331526107711</v>
       </c>
       <c r="BF173">
@@ -55942,13 +55957,13 @@
       <c r="BR173">
         <v>681</v>
       </c>
-      <c r="BS173" t="s">
+      <c r="BS173" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT173">
         <v>0</v>
       </c>
-      <c r="BU173" t="s">
+      <c r="BU173" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV173" t="s">
@@ -56175,10 +56190,10 @@
       <c r="AQ174">
         <v>0.11025231814629456</v>
       </c>
-      <c r="AR174">
+      <c r="AR174" s="1">
         <v>215.91666666666669</v>
       </c>
-      <c r="AS174">
+      <c r="AS174" s="1">
         <v>162.73376418295538</v>
       </c>
       <c r="AT174" s="1">
@@ -56214,7 +56229,7 @@
       <c r="BD174">
         <v>1644618</v>
       </c>
-      <c r="BE174">
+      <c r="BE174" s="1">
         <v>19041.095945556117</v>
       </c>
       <c r="BF174">
@@ -56256,13 +56271,13 @@
       <c r="BR174">
         <v>193662</v>
       </c>
-      <c r="BS174">
+      <c r="BS174" s="1">
         <v>193662</v>
       </c>
       <c r="BT174">
         <v>96136</v>
       </c>
-      <c r="BU174">
+      <c r="BU174" s="1">
         <v>96136</v>
       </c>
       <c r="BV174">
@@ -56489,10 +56504,10 @@
       <c r="AQ175">
         <v>2.8677146335243538E-2</v>
       </c>
-      <c r="AR175">
+      <c r="AR175" s="1">
         <v>55.583333333333336</v>
       </c>
-      <c r="AS175">
+      <c r="AS175" s="1">
         <v>43.737004782999023</v>
       </c>
       <c r="AT175" s="1">
@@ -56528,7 +56543,7 @@
       <c r="BD175">
         <v>445062</v>
       </c>
-      <c r="BE175">
+      <c r="BE175" s="1">
         <v>23444.540577019437</v>
       </c>
       <c r="BF175">
@@ -56570,13 +56585,13 @@
       <c r="BR175">
         <v>0</v>
       </c>
-      <c r="BS175" t="s">
+      <c r="BS175" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT175">
         <v>0</v>
       </c>
-      <c r="BU175" t="s">
+      <c r="BU175" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV175" t="s">
@@ -56803,10 +56818,10 @@
       <c r="AQ176">
         <v>0.48727708329308111</v>
       </c>
-      <c r="AR176">
+      <c r="AR176" s="1">
         <v>21.416666666666664</v>
       </c>
-      <c r="AS176">
+      <c r="AS176" s="1">
         <v>16.85218924922151</v>
       </c>
       <c r="AT176" s="1">
@@ -56842,7 +56857,7 @@
       <c r="BD176">
         <v>419685</v>
       </c>
-      <c r="BE176">
+      <c r="BE176" s="1">
         <v>16298.221088134889</v>
       </c>
       <c r="BF176">
@@ -56884,13 +56899,13 @@
       <c r="BR176">
         <v>0</v>
       </c>
-      <c r="BS176" t="s">
+      <c r="BS176" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT176">
         <v>0</v>
       </c>
-      <c r="BU176" t="s">
+      <c r="BU176" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV176" t="s">
@@ -57117,10 +57132,10 @@
       <c r="AQ177">
         <v>0.45994146824033749</v>
       </c>
-      <c r="AR177">
+      <c r="AR177" s="1">
         <v>479.08333333333331</v>
       </c>
-      <c r="AS177">
+      <c r="AS177" s="1">
         <v>322.42093290351937</v>
       </c>
       <c r="AT177" s="1">
@@ -57156,7 +57171,7 @@
       <c r="BD177">
         <v>4619779</v>
       </c>
-      <c r="BE177">
+      <c r="BE177" s="1">
         <v>22956.617688275179</v>
       </c>
       <c r="BF177">
@@ -57198,13 +57213,13 @@
       <c r="BR177">
         <v>1350387</v>
       </c>
-      <c r="BS177">
+      <c r="BS177" s="1">
         <v>63697.499999999993</v>
       </c>
       <c r="BT177">
         <v>651359</v>
       </c>
-      <c r="BU177">
+      <c r="BU177" s="1">
         <v>30724.481132075467</v>
       </c>
       <c r="BV177">
@@ -57431,10 +57446,10 @@
       <c r="AQ178">
         <v>0.13525748056213976</v>
       </c>
-      <c r="AR178">
+      <c r="AR178" s="1">
         <v>179.95833333333334</v>
       </c>
-      <c r="AS178">
+      <c r="AS178" s="1">
         <v>109.29184993677532</v>
       </c>
       <c r="AT178" s="1">
@@ -57470,7 +57485,7 @@
       <c r="BD178">
         <v>1896234</v>
       </c>
-      <c r="BE178">
+      <c r="BE178" s="1">
         <v>24654.721994889813</v>
       </c>
       <c r="BF178">
@@ -57512,13 +57527,13 @@
       <c r="BR178">
         <v>328948</v>
       </c>
-      <c r="BS178">
+      <c r="BS178" s="1">
         <v>61716.322701688558</v>
       </c>
       <c r="BT178">
         <v>145909</v>
       </c>
-      <c r="BU178">
+      <c r="BU178" s="1">
         <v>27375.046904315197</v>
       </c>
       <c r="BV178">
@@ -57745,10 +57760,10 @@
       <c r="AQ179">
         <v>0.16289982438983899</v>
       </c>
-      <c r="AR179">
+      <c r="AR179" s="1">
         <v>121.04166666666666</v>
       </c>
-      <c r="AS179">
+      <c r="AS179" s="1">
         <v>91.227631214103681</v>
       </c>
       <c r="AT179" s="1">
@@ -57784,7 +57799,7 @@
       <c r="BD179">
         <v>1258805</v>
       </c>
-      <c r="BE179">
+      <c r="BE179" s="1">
         <v>22197.390405059465</v>
       </c>
       <c r="BF179">
@@ -57826,13 +57841,13 @@
       <c r="BR179">
         <v>303854</v>
       </c>
-      <c r="BS179">
+      <c r="BS179" s="1">
         <v>99951.973684210519</v>
       </c>
       <c r="BT179">
         <v>81113</v>
       </c>
-      <c r="BU179">
+      <c r="BU179" s="1">
         <v>26681.907894736843</v>
       </c>
       <c r="BV179">
@@ -58059,10 +58074,10 @@
       <c r="AQ180">
         <v>9.0667855863272884</v>
       </c>
-      <c r="AR180">
+      <c r="AR180" s="1">
         <v>217.5</v>
       </c>
-      <c r="AS180">
+      <c r="AS180" s="1">
         <v>171.14480132477877</v>
       </c>
       <c r="AT180" s="1">
@@ -58098,7 +58113,7 @@
       <c r="BD180">
         <v>161398</v>
       </c>
-      <c r="BE180">
+      <c r="BE180" s="1">
         <v>15427.809876429093</v>
       </c>
       <c r="BF180">
@@ -58140,13 +58155,13 @@
       <c r="BR180">
         <v>139669</v>
       </c>
-      <c r="BS180">
+      <c r="BS180" s="1">
         <v>40601.453488372092</v>
       </c>
       <c r="BT180">
         <v>99042</v>
       </c>
-      <c r="BU180">
+      <c r="BU180" s="1">
         <v>28791.279069767443</v>
       </c>
       <c r="BV180">
@@ -58373,10 +58388,10 @@
       <c r="AQ181">
         <v>5.3068581867159167E-2</v>
       </c>
-      <c r="AR181">
+      <c r="AR181" s="1">
         <v>25.416666666666668</v>
       </c>
-      <c r="AS181">
+      <c r="AS181" s="1">
         <v>19.156232371980469</v>
       </c>
       <c r="AT181" s="1">
@@ -58412,7 +58427,7 @@
       <c r="BD181">
         <v>144281</v>
       </c>
-      <c r="BE181">
+      <c r="BE181" s="1">
         <v>16205.377261427591</v>
       </c>
       <c r="BF181">
@@ -58454,13 +58469,13 @@
       <c r="BR181">
         <v>171849</v>
       </c>
-      <c r="BS181">
+      <c r="BS181" s="1">
         <v>46825.340599455041</v>
       </c>
       <c r="BT181">
         <v>96887</v>
       </c>
-      <c r="BU181">
+      <c r="BU181" s="1">
         <v>26399.727520435968</v>
       </c>
       <c r="BV181">
@@ -58687,10 +58702,10 @@
       <c r="AQ182">
         <v>2.3887459320366306E-2</v>
       </c>
-      <c r="AR182">
+      <c r="AR182" s="1">
         <v>52.833333333333336</v>
       </c>
-      <c r="AS182">
+      <c r="AS182" s="1">
         <v>32.086609335455229</v>
       </c>
       <c r="AT182" s="1">
@@ -58726,7 +58741,7 @@
       <c r="BD182">
         <v>353596</v>
       </c>
-      <c r="BE182">
+      <c r="BE182" s="1">
         <v>23340.186868616427</v>
       </c>
       <c r="BF182">
@@ -58768,13 +58783,13 @@
       <c r="BR182">
         <v>101213</v>
       </c>
-      <c r="BS182" t="s">
+      <c r="BS182" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT182">
         <v>0</v>
       </c>
-      <c r="BU182" t="s">
+      <c r="BU182" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV182" t="s">
@@ -59001,10 +59016,10 @@
       <c r="AQ183">
         <v>2.1207418269223419</v>
       </c>
-      <c r="AR183">
+      <c r="AR183" s="1">
         <v>187</v>
       </c>
-      <c r="AS183">
+      <c r="AS183" s="1">
         <v>140.93962440237431</v>
       </c>
       <c r="AT183" s="1">
@@ -59040,7 +59055,7 @@
       <c r="BD183">
         <v>2707119</v>
       </c>
-      <c r="BE183">
+      <c r="BE183" s="1">
         <v>20888.318397007501</v>
       </c>
       <c r="BF183">
@@ -59082,13 +59097,13 @@
       <c r="BR183">
         <v>2797866</v>
       </c>
-      <c r="BS183">
+      <c r="BS183" s="1">
         <v>32735.064935064936</v>
       </c>
       <c r="BT183">
         <v>2336952</v>
       </c>
-      <c r="BU183">
+      <c r="BU183" s="1">
         <v>27342.365742365742</v>
       </c>
       <c r="BV183">
@@ -59315,10 +59330,10 @@
       <c r="AQ184">
         <v>9.4988697703719246E-2</v>
       </c>
-      <c r="AR184">
+      <c r="AR184" s="1">
         <v>42.583333333333336</v>
       </c>
-      <c r="AS184">
+      <c r="AS184" s="1">
         <v>32.09454013797383</v>
       </c>
       <c r="AT184" s="1">
@@ -59354,7 +59369,7 @@
       <c r="BD184">
         <v>580647</v>
       </c>
-      <c r="BE184">
+      <c r="BE184" s="1">
         <v>22812.77424580017</v>
       </c>
       <c r="BF184">
@@ -59396,13 +59411,13 @@
       <c r="BR184">
         <v>-1702</v>
       </c>
-      <c r="BS184" t="s">
+      <c r="BS184" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT184">
         <v>0</v>
       </c>
-      <c r="BU184" t="s">
+      <c r="BU184" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV184" t="s">
@@ -59629,10 +59644,10 @@
       <c r="AQ185">
         <v>4.180367054575642E-2</v>
       </c>
-      <c r="AR185">
+      <c r="AR185" s="1">
         <v>28.083333333333336</v>
       </c>
-      <c r="AS185">
+      <c r="AS185" s="1">
         <v>21.166066588057106</v>
       </c>
       <c r="AT185" s="1">
@@ -59668,7 +59683,7 @@
       <c r="BD185">
         <v>464338</v>
       </c>
-      <c r="BE185">
+      <c r="BE185" s="1">
         <v>21863.399275715175</v>
       </c>
       <c r="BF185">
@@ -59710,13 +59725,13 @@
       <c r="BR185">
         <v>0</v>
       </c>
-      <c r="BS185" t="s">
+      <c r="BS185" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT185">
         <v>0</v>
       </c>
-      <c r="BU185" t="s">
+      <c r="BU185" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV185" t="s">
@@ -59943,10 +59958,10 @@
       <c r="AQ186">
         <v>1.6393766913317322E-2</v>
       </c>
-      <c r="AR186">
+      <c r="AR186" s="1">
         <v>38.75</v>
       </c>
-      <c r="AS186">
+      <c r="AS186" s="1">
         <v>26.888385317122182</v>
       </c>
       <c r="AT186" s="1">
@@ -59982,7 +59997,7 @@
       <c r="BD186">
         <v>570373</v>
       </c>
-      <c r="BE186">
+      <c r="BE186" s="1">
         <v>22894.164527977526</v>
       </c>
       <c r="BF186">
@@ -60024,13 +60039,13 @@
       <c r="BR186">
         <v>0</v>
       </c>
-      <c r="BS186" t="s">
+      <c r="BS186" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT186">
         <v>0</v>
       </c>
-      <c r="BU186" t="s">
+      <c r="BU186" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV186" t="s">
@@ -60257,10 +60272,10 @@
       <c r="AQ187">
         <v>4.9818428894617499</v>
       </c>
-      <c r="AR187">
+      <c r="AR187" s="1">
         <v>234.29166666666669</v>
       </c>
-      <c r="AS187">
+      <c r="AS187" s="1">
         <v>140.2603320344885</v>
       </c>
       <c r="AT187" s="1">
@@ -60296,7 +60311,7 @@
       <c r="BD187">
         <v>2118006</v>
       </c>
-      <c r="BE187">
+      <c r="BE187" s="1">
         <v>21298.48255512496</v>
       </c>
       <c r="BF187">
@@ -60338,13 +60353,13 @@
       <c r="BR187">
         <v>1827959</v>
       </c>
-      <c r="BS187">
+      <c r="BS187" s="1">
         <v>49511.34886240519</v>
       </c>
       <c r="BT187">
         <v>1146652</v>
       </c>
-      <c r="BU187">
+      <c r="BU187" s="1">
         <v>31057.746478873232</v>
       </c>
       <c r="BV187">
@@ -60571,10 +60586,10 @@
       <c r="AQ188">
         <v>6.3401866348660726E-2</v>
       </c>
-      <c r="AR188">
+      <c r="AR188" s="1">
         <v>214.45833333333331</v>
       </c>
-      <c r="AS188">
+      <c r="AS188" s="1">
         <v>140.63226734232694</v>
       </c>
       <c r="AT188" s="1">
@@ -60610,7 +60625,7 @@
       <c r="BD188">
         <v>112032</v>
       </c>
-      <c r="BE188">
+      <c r="BE188" s="1">
         <v>1587.188169723177</v>
       </c>
       <c r="BF188">
@@ -60652,13 +60667,13 @@
       <c r="BR188">
         <v>139522</v>
       </c>
-      <c r="BS188">
+      <c r="BS188" s="1">
         <v>30265.07592190889</v>
       </c>
       <c r="BT188">
         <v>109250</v>
       </c>
-      <c r="BU188">
+      <c r="BU188" s="1">
         <v>23698.481561822126</v>
       </c>
       <c r="BV188">
@@ -60885,10 +60900,10 @@
       <c r="AQ189">
         <v>0.42708145564183564</v>
       </c>
-      <c r="AR189">
+      <c r="AR189" s="1">
         <v>215.54166666666669</v>
       </c>
-      <c r="AS189">
+      <c r="AS189" s="1">
         <v>169.60384238564765</v>
       </c>
       <c r="AT189" s="1">
@@ -60924,7 +60939,7 @@
       <c r="BD189">
         <v>2949727</v>
       </c>
-      <c r="BE189">
+      <c r="BE189" s="1">
         <v>22861.650209193802</v>
       </c>
       <c r="BF189">
@@ -60966,13 +60981,13 @@
       <c r="BR189">
         <v>660983</v>
       </c>
-      <c r="BS189">
+      <c r="BS189" s="1">
         <v>30829.430970149257</v>
       </c>
       <c r="BT189">
         <v>466009</v>
       </c>
-      <c r="BU189">
+      <c r="BU189" s="1">
         <v>21735.494402985078</v>
       </c>
       <c r="BV189">
@@ -61199,10 +61214,10 @@
       <c r="AQ190">
         <v>0.20842592980141336</v>
       </c>
-      <c r="AR190">
+      <c r="AR190" s="1">
         <v>10.5</v>
       </c>
-      <c r="AS190">
+      <c r="AS190" s="1">
         <v>6.9822512844465203</v>
       </c>
       <c r="AT190" s="1">
@@ -61238,7 +61253,7 @@
       <c r="BD190">
         <v>127783</v>
       </c>
-      <c r="BE190">
+      <c r="BE190" s="1">
         <v>20444.781512211477</v>
       </c>
       <c r="BF190">
@@ -61280,13 +61295,13 @@
       <c r="BR190">
         <v>0</v>
       </c>
-      <c r="BS190" t="s">
+      <c r="BS190" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT190">
         <v>0</v>
       </c>
-      <c r="BU190" t="s">
+      <c r="BU190" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV190" t="s">
@@ -61513,10 +61528,10 @@
       <c r="AQ191">
         <v>0.35980835413995549</v>
       </c>
-      <c r="AR191">
+      <c r="AR191" s="1">
         <v>148.66666666666666</v>
       </c>
-      <c r="AS191">
+      <c r="AS191" s="1">
         <v>90.287872325634254</v>
       </c>
       <c r="AT191" s="1">
@@ -61552,7 +61567,7 @@
       <c r="BD191">
         <v>1463950</v>
       </c>
-      <c r="BE191">
+      <c r="BE191" s="1">
         <v>20714.941198692984</v>
       </c>
       <c r="BF191">
@@ -61594,13 +61609,13 @@
       <c r="BR191">
         <v>45633</v>
       </c>
-      <c r="BS191">
+      <c r="BS191" s="1">
         <v>8775.576923076922</v>
       </c>
       <c r="BT191">
         <v>104820</v>
       </c>
-      <c r="BU191">
+      <c r="BU191" s="1">
         <v>20157.692307692309</v>
       </c>
       <c r="BV191">
@@ -61827,10 +61842,10 @@
       <c r="AQ192">
         <v>0.49443549700512113</v>
       </c>
-      <c r="AR192">
+      <c r="AR192" s="1">
         <v>220.33333333333334</v>
       </c>
-      <c r="AS192">
+      <c r="AS192" s="1">
         <v>148.28334433760745</v>
       </c>
       <c r="AT192" s="1">
@@ -61866,7 +61881,7 @@
       <c r="BD192">
         <v>1530960</v>
       </c>
-      <c r="BE192">
+      <c r="BE192" s="1">
         <v>15641.066648364422</v>
       </c>
       <c r="BF192">
@@ -61908,13 +61923,13 @@
       <c r="BR192">
         <v>0</v>
       </c>
-      <c r="BS192" t="s">
+      <c r="BS192" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT192">
         <v>0</v>
       </c>
-      <c r="BU192" t="s">
+      <c r="BU192" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV192" t="s">
@@ -62141,10 +62156,10 @@
       <c r="AQ193">
         <v>0</v>
       </c>
-      <c r="AR193">
+      <c r="AR193" s="1">
         <v>20.75</v>
       </c>
-      <c r="AS193">
+      <c r="AS193" s="1">
         <v>14.398296653684783</v>
       </c>
       <c r="AT193" s="1">
@@ -62180,7 +62195,7 @@
       <c r="BD193">
         <v>205531</v>
       </c>
-      <c r="BE193">
+      <c r="BE193" s="1">
         <v>20567.455513535228</v>
       </c>
       <c r="BF193">
@@ -62222,13 +62237,13 @@
       <c r="BR193">
         <v>6752</v>
       </c>
-      <c r="BS193" t="s">
+      <c r="BS193" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT193">
         <v>0</v>
       </c>
-      <c r="BU193" t="s">
+      <c r="BU193" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV193" t="s">
@@ -62455,10 +62470,10 @@
       <c r="AQ194">
         <v>0.30740982339155853</v>
       </c>
-      <c r="AR194">
+      <c r="AR194" s="1">
         <v>642.79166666666674</v>
       </c>
-      <c r="AS194">
+      <c r="AS194" s="1">
         <v>484.46425705334866</v>
       </c>
       <c r="AT194" s="1">
@@ -62494,7 +62509,7 @@
       <c r="BD194">
         <v>7823324</v>
       </c>
-      <c r="BE194">
+      <c r="BE194" s="1">
         <v>23970.820009430881</v>
       </c>
       <c r="BF194">
@@ -62536,13 +62551,13 @@
       <c r="BR194">
         <v>371985</v>
       </c>
-      <c r="BS194">
+      <c r="BS194" s="1">
         <v>70719.581749049437</v>
       </c>
       <c r="BT194">
         <v>142221</v>
       </c>
-      <c r="BU194">
+      <c r="BU194" s="1">
         <v>27038.212927756656</v>
       </c>
       <c r="BV194">
@@ -62769,10 +62784,10 @@
       <c r="AQ195">
         <v>3.7192252193841285E-2</v>
       </c>
-      <c r="AR195">
+      <c r="AR195" s="1">
         <v>2.75</v>
       </c>
-      <c r="AS195">
+      <c r="AS195" s="1">
         <v>1.908207990247381</v>
       </c>
       <c r="AT195" s="1">
@@ -62808,7 +62823,7 @@
       <c r="BD195" t="s">
         <v>218</v>
       </c>
-      <c r="BE195" t="s">
+      <c r="BE195" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF195" t="s">
@@ -62850,13 +62865,13 @@
       <c r="BR195">
         <v>3130</v>
       </c>
-      <c r="BS195" t="s">
+      <c r="BS195" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT195">
         <v>0</v>
       </c>
-      <c r="BU195" t="s">
+      <c r="BU195" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV195" t="s">
@@ -63083,10 +63098,10 @@
       <c r="AQ196">
         <v>0.20928296326467047</v>
       </c>
-      <c r="AR196">
+      <c r="AR196" s="1">
         <v>51.25</v>
       </c>
-      <c r="AS196">
+      <c r="AS196" s="1">
         <v>31.12502325126966</v>
       </c>
       <c r="AT196" s="1">
@@ -63122,7 +63137,7 @@
       <c r="BD196">
         <v>146264</v>
       </c>
-      <c r="BE196">
+      <c r="BE196" s="1">
         <v>8719.4030626601543</v>
       </c>
       <c r="BF196">
@@ -63164,13 +63179,13 @@
       <c r="BR196">
         <v>172177</v>
       </c>
-      <c r="BS196">
+      <c r="BS196" s="1">
         <v>103100</v>
       </c>
       <c r="BT196">
         <v>48492</v>
       </c>
-      <c r="BU196">
+      <c r="BU196" s="1">
         <v>29037.125748502996</v>
       </c>
       <c r="BV196">
@@ -63397,10 +63412,10 @@
       <c r="AQ197">
         <v>20.508891223757509</v>
       </c>
-      <c r="AR197">
+      <c r="AR197" s="1">
         <v>82.583333333333329</v>
       </c>
-      <c r="AS197">
+      <c r="AS197" s="1">
         <v>57.304064191974369</v>
       </c>
       <c r="AT197" s="1">
@@ -63436,7 +63451,7 @@
       <c r="BD197">
         <v>1744377</v>
       </c>
-      <c r="BE197">
+      <c r="BE197" s="1">
         <v>26894.447327768099</v>
       </c>
       <c r="BF197">
@@ -63478,13 +63493,13 @@
       <c r="BR197">
         <v>2675506</v>
       </c>
-      <c r="BS197">
+      <c r="BS197" s="1">
         <v>47505.43323863636</v>
       </c>
       <c r="BT197">
         <v>1768034</v>
       </c>
-      <c r="BU197">
+      <c r="BU197" s="1">
         <v>31392.649147727272</v>
       </c>
       <c r="BV197">
@@ -63711,10 +63726,10 @@
       <c r="AQ198">
         <v>0.35007070417470493</v>
       </c>
-      <c r="AR198">
+      <c r="AR198" s="1">
         <v>58.208333333333336</v>
       </c>
-      <c r="AS198">
+      <c r="AS198" s="1">
         <v>38.707162874491225</v>
       </c>
       <c r="AT198" s="1">
@@ -63750,7 +63765,7 @@
       <c r="BD198">
         <v>117642</v>
       </c>
-      <c r="BE198">
+      <c r="BE198" s="1">
         <v>4040.5175988150459</v>
       </c>
       <c r="BF198">
@@ -63792,13 +63807,13 @@
       <c r="BR198">
         <v>138607</v>
       </c>
-      <c r="BS198">
+      <c r="BS198" s="1">
         <v>51719.029850746265</v>
       </c>
       <c r="BT198">
         <v>91802</v>
       </c>
-      <c r="BU198">
+      <c r="BU198" s="1">
         <v>34254.477611940296</v>
       </c>
       <c r="BV198">
@@ -64025,10 +64040,10 @@
       <c r="AQ199">
         <v>1.1077941447634074</v>
       </c>
-      <c r="AR199">
+      <c r="AR199" s="1">
         <v>76.5</v>
       </c>
-      <c r="AS199">
+      <c r="AS199" s="1">
         <v>45.79725584480186</v>
       </c>
       <c r="AT199" s="1">
@@ -64064,7 +64079,7 @@
       <c r="BD199">
         <v>1648074</v>
       </c>
-      <c r="BE199">
+      <c r="BE199" s="1">
         <v>31344.958923572125</v>
       </c>
       <c r="BF199">
@@ -64106,13 +64121,13 @@
       <c r="BR199">
         <v>417368</v>
       </c>
-      <c r="BS199">
+      <c r="BS199" s="1">
         <v>47918.254879448905</v>
       </c>
       <c r="BT199">
         <v>240301</v>
       </c>
-      <c r="BU199">
+      <c r="BU199" s="1">
         <v>27589.092996555679</v>
       </c>
       <c r="BV199">
@@ -64339,10 +64354,10 @@
       <c r="AQ200">
         <v>0.82725091003801388</v>
       </c>
-      <c r="AR200">
+      <c r="AR200" s="1">
         <v>8</v>
       </c>
-      <c r="AS200">
+      <c r="AS200" s="1">
         <v>6.0295026482299177</v>
       </c>
       <c r="AT200" s="1">
@@ -64378,7 +64393,7 @@
       <c r="BD200">
         <v>113452</v>
       </c>
-      <c r="BE200">
+      <c r="BE200" s="1">
         <v>18126.408020774154</v>
       </c>
       <c r="BF200">
@@ -64420,13 +64435,13 @@
       <c r="BR200">
         <v>0</v>
       </c>
-      <c r="BS200" t="s">
+      <c r="BS200" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT200">
         <v>0</v>
       </c>
-      <c r="BU200" t="s">
+      <c r="BU200" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV200" t="s">
@@ -64653,10 +64668,10 @@
       <c r="AQ201">
         <v>0.17230782217368482</v>
       </c>
-      <c r="AR201">
+      <c r="AR201" s="1">
         <v>38.666666666666664</v>
       </c>
-      <c r="AS201">
+      <c r="AS201" s="1">
         <v>23.482944371689626</v>
       </c>
       <c r="AT201" s="1">
@@ -64692,7 +64707,7 @@
       <c r="BD201">
         <v>426914</v>
       </c>
-      <c r="BE201">
+      <c r="BE201" s="1">
         <v>26027.721089031751</v>
       </c>
       <c r="BF201">
@@ -64734,13 +64749,13 @@
       <c r="BR201">
         <v>0</v>
       </c>
-      <c r="BS201" t="s">
+      <c r="BS201" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT201">
         <v>0</v>
       </c>
-      <c r="BU201" t="s">
+      <c r="BU201" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV201" t="s">
@@ -64967,10 +64982,10 @@
       <c r="AQ202">
         <v>0.1432263941136111</v>
       </c>
-      <c r="AR202">
+      <c r="AR202" s="1">
         <v>81.666666666666657</v>
       </c>
-      <c r="AS202">
+      <c r="AS202" s="1">
         <v>61.551172867347056</v>
       </c>
       <c r="AT202" s="1">
@@ -65006,7 +65021,7 @@
       <c r="BD202">
         <v>674412</v>
       </c>
-      <c r="BE202">
+      <c r="BE202" s="1">
         <v>13133.386277351374</v>
       </c>
       <c r="BF202">
@@ -65048,13 +65063,13 @@
       <c r="BR202">
         <v>69612</v>
       </c>
-      <c r="BS202">
+      <c r="BS202" s="1">
         <v>69612</v>
       </c>
       <c r="BT202">
         <v>26610</v>
       </c>
-      <c r="BU202">
+      <c r="BU202" s="1">
         <v>26610</v>
       </c>
       <c r="BV202">
@@ -65281,10 +65296,10 @@
       <c r="AQ203">
         <v>2.1428283642224013</v>
       </c>
-      <c r="AR203">
+      <c r="AR203" s="1">
         <v>118.29166666666666</v>
       </c>
-      <c r="AS203">
+      <c r="AS203" s="1">
         <v>89.154989678774655</v>
       </c>
       <c r="AT203" s="1">
@@ -65320,7 +65335,7 @@
       <c r="BD203">
         <v>3243662</v>
       </c>
-      <c r="BE203">
+      <c r="BE203" s="1">
         <v>31885.924677296807</v>
       </c>
       <c r="BF203">
@@ -65362,13 +65377,13 @@
       <c r="BR203">
         <v>61877</v>
       </c>
-      <c r="BS203">
+      <c r="BS203" s="1">
         <v>36613.609467455623</v>
       </c>
       <c r="BT203">
         <v>39709</v>
       </c>
-      <c r="BU203">
+      <c r="BU203" s="1">
         <v>23496.449704142011</v>
       </c>
       <c r="BV203">
@@ -65595,10 +65610,10 @@
       <c r="AQ204">
         <v>0.18937359421663544</v>
       </c>
-      <c r="AR204">
+      <c r="AR204" s="1">
         <v>282.79166666666663</v>
       </c>
-      <c r="AS204">
+      <c r="AS204" s="1">
         <v>171.74433561493262</v>
       </c>
       <c r="AT204" s="1">
@@ -65634,7 +65649,7 @@
       <c r="BD204">
         <v>3060498</v>
       </c>
-      <c r="BE204">
+      <c r="BE204" s="1">
         <v>25275.181124036895</v>
       </c>
       <c r="BF204">
@@ -65676,13 +65691,13 @@
       <c r="BR204">
         <v>1060904</v>
       </c>
-      <c r="BS204">
+      <c r="BS204" s="1">
         <v>38719.124087591241</v>
       </c>
       <c r="BT204">
         <v>729147</v>
       </c>
-      <c r="BU204">
+      <c r="BU204" s="1">
         <v>26611.204379562045</v>
       </c>
       <c r="BV204">
@@ -65909,10 +65924,10 @@
       <c r="AQ205">
         <v>8.5825258937520882E-2</v>
       </c>
-      <c r="AR205">
+      <c r="AR205" s="1">
         <v>23.583333333333332</v>
       </c>
-      <c r="AS205">
+      <c r="AS205" s="1">
         <v>16.590400777939848</v>
       </c>
       <c r="AT205" s="1">
@@ -65948,7 +65963,7 @@
       <c r="BD205">
         <v>198994</v>
       </c>
-      <c r="BE205">
+      <c r="BE205" s="1">
         <v>24476.566314472402</v>
       </c>
       <c r="BF205">
@@ -65990,13 +66005,13 @@
       <c r="BR205">
         <v>0</v>
       </c>
-      <c r="BS205" t="s">
+      <c r="BS205" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT205">
         <v>0</v>
       </c>
-      <c r="BU205" t="s">
+      <c r="BU205" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV205" t="s">
@@ -66223,10 +66238,10 @@
       <c r="AQ206">
         <v>0.20367151947984866</v>
       </c>
-      <c r="AR206">
+      <c r="AR206" s="1">
         <v>155.70833333333331</v>
       </c>
-      <c r="AS206">
+      <c r="AS206" s="1">
         <v>102.1066219270013</v>
       </c>
       <c r="AT206" s="1">
@@ -66262,7 +66277,7 @@
       <c r="BD206">
         <v>1395015</v>
       </c>
-      <c r="BE206">
+      <c r="BE206" s="1">
         <v>20212.565884361866</v>
       </c>
       <c r="BF206">
@@ -66304,13 +66319,13 @@
       <c r="BR206">
         <v>48602</v>
       </c>
-      <c r="BS206">
+      <c r="BS206" s="1">
         <v>17234.751773049647</v>
       </c>
       <c r="BT206">
         <v>48257</v>
       </c>
-      <c r="BU206">
+      <c r="BU206" s="1">
         <v>17112.411347517733</v>
       </c>
       <c r="BV206">
@@ -66537,10 +66552,10 @@
       <c r="AQ207">
         <v>0.32316145079259007</v>
       </c>
-      <c r="AR207">
+      <c r="AR207" s="1">
         <v>6.5</v>
       </c>
-      <c r="AS207">
+      <c r="AS207" s="1">
         <v>4.322346033228798</v>
       </c>
       <c r="AT207" s="1">
@@ -66576,7 +66591,7 @@
       <c r="BD207">
         <v>137538</v>
       </c>
-      <c r="BE207">
+      <c r="BE207" s="1">
         <v>29419.099277490124</v>
       </c>
       <c r="BF207">
@@ -66618,13 +66633,13 @@
       <c r="BR207">
         <v>170863</v>
       </c>
-      <c r="BS207">
+      <c r="BS207" s="1">
         <v>42715.75</v>
       </c>
       <c r="BT207">
         <v>130879</v>
       </c>
-      <c r="BU207">
+      <c r="BU207" s="1">
         <v>32719.75</v>
       </c>
       <c r="BV207">
@@ -66851,10 +66866,10 @@
       <c r="AQ208">
         <v>10.533008362571774</v>
       </c>
-      <c r="AR208">
+      <c r="AR208" s="1">
         <v>413.625</v>
       </c>
-      <c r="AS208">
+      <c r="AS208" s="1">
         <v>311.74412910926242</v>
       </c>
       <c r="AT208" s="1">
@@ -66890,7 +66905,7 @@
       <c r="BD208">
         <v>11243373</v>
       </c>
-      <c r="BE208">
+      <c r="BE208" s="1">
         <v>34136.849424808526</v>
       </c>
       <c r="BF208">
@@ -66932,13 +66947,13 @@
       <c r="BR208">
         <v>16939194</v>
       </c>
-      <c r="BS208">
+      <c r="BS208" s="1">
         <v>55969.58202544193</v>
       </c>
       <c r="BT208">
         <v>10709135</v>
       </c>
-      <c r="BU208">
+      <c r="BU208" s="1">
         <v>35384.553114158269</v>
       </c>
       <c r="BV208">
@@ -67165,10 +67180,10 @@
       <c r="AQ209">
         <v>0.39763538986333991</v>
       </c>
-      <c r="AR209">
+      <c r="AR209" s="1">
         <v>406.33333333333337</v>
       </c>
-      <c r="AS209">
+      <c r="AS209" s="1">
         <v>306.2484886746779</v>
       </c>
       <c r="AT209" s="1">
@@ -67204,7 +67219,7 @@
       <c r="BD209">
         <v>6262283</v>
       </c>
-      <c r="BE209">
+      <c r="BE209" s="1">
         <v>25339.935484170881</v>
       </c>
       <c r="BF209">
@@ -67246,13 +67261,13 @@
       <c r="BR209">
         <v>183060</v>
       </c>
-      <c r="BS209">
+      <c r="BS209" s="1">
         <v>27200.594353640416</v>
       </c>
       <c r="BT209">
         <v>170695</v>
       </c>
-      <c r="BU209">
+      <c r="BU209" s="1">
         <v>25363.298662704306</v>
       </c>
       <c r="BV209">
@@ -67479,10 +67494,10 @@
       <c r="AQ210">
         <v>1.1340875237186763</v>
       </c>
-      <c r="AR210">
+      <c r="AR210" s="1">
         <v>95.916666666666671</v>
       </c>
-      <c r="AS210">
+      <c r="AS210" s="1">
         <v>64.551486131840463</v>
       </c>
       <c r="AT210" s="1">
@@ -67518,7 +67533,7 @@
       <c r="BD210">
         <v>1137092</v>
       </c>
-      <c r="BE210">
+      <c r="BE210" s="1">
         <v>22882.448085784712</v>
       </c>
       <c r="BF210">
@@ -67560,13 +67575,13 @@
       <c r="BR210">
         <v>151610</v>
       </c>
-      <c r="BS210">
+      <c r="BS210" s="1">
         <v>47676.100628930813</v>
       </c>
       <c r="BT210">
         <v>82775</v>
       </c>
-      <c r="BU210">
+      <c r="BU210" s="1">
         <v>26029.874213836476</v>
       </c>
       <c r="BV210">
@@ -67793,10 +67808,10 @@
       <c r="AQ211">
         <v>0.14646996838777662</v>
       </c>
-      <c r="AR211">
+      <c r="AR211" s="1">
         <v>5.5</v>
       </c>
-      <c r="AS211">
+      <c r="AS211" s="1">
         <v>3.6573697204243678</v>
       </c>
       <c r="AT211" s="1">
@@ -67832,7 +67847,7 @@
       <c r="BD211">
         <v>0</v>
       </c>
-      <c r="BE211" t="s">
+      <c r="BE211" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BF211" t="s">
@@ -67874,13 +67889,13 @@
       <c r="BR211">
         <v>0</v>
       </c>
-      <c r="BS211" t="s">
+      <c r="BS211" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT211">
         <v>0</v>
       </c>
-      <c r="BU211" t="s">
+      <c r="BU211" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV211" t="s">
@@ -68107,10 +68122,10 @@
       <c r="AQ212">
         <v>7.7652589770608738E-2</v>
       </c>
-      <c r="AR212">
+      <c r="AR212" s="1">
         <v>93.458333333333343</v>
       </c>
-      <c r="AS212">
+      <c r="AS212" s="1">
         <v>62.897038833066091</v>
       </c>
       <c r="AT212" s="1">
@@ -68146,7 +68161,7 @@
       <c r="BD212">
         <v>573806</v>
       </c>
-      <c r="BE212">
+      <c r="BE212" s="1">
         <v>19166.749042666426</v>
       </c>
       <c r="BF212">
@@ -68188,13 +68203,13 @@
       <c r="BR212">
         <v>69216</v>
       </c>
-      <c r="BS212">
+      <c r="BS212" s="1">
         <v>34608</v>
       </c>
       <c r="BT212">
         <v>59369</v>
       </c>
-      <c r="BU212">
+      <c r="BU212" s="1">
         <v>29684.5</v>
       </c>
       <c r="BV212">
@@ -68421,10 +68436,10 @@
       <c r="AQ213">
         <v>2.2086799529499013</v>
       </c>
-      <c r="AR213">
+      <c r="AR213" s="1">
         <v>105.875</v>
       </c>
-      <c r="AS213">
+      <c r="AS213" s="1">
         <v>71.253399765858646</v>
       </c>
       <c r="AT213" s="1">
@@ -68460,7 +68475,7 @@
       <c r="BD213">
         <v>702639</v>
       </c>
-      <c r="BE213">
+      <c r="BE213" s="1">
         <v>22802.471306771553</v>
       </c>
       <c r="BF213">
@@ -68502,13 +68517,13 @@
       <c r="BR213">
         <v>0</v>
       </c>
-      <c r="BS213" t="s">
+      <c r="BS213" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT213">
         <v>0</v>
       </c>
-      <c r="BU213" t="s">
+      <c r="BU213" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV213" t="s">
@@ -68735,10 +68750,10 @@
       <c r="AQ214">
         <v>0.30816785587551287</v>
       </c>
-      <c r="AR214">
+      <c r="AR214" s="1">
         <v>79.25</v>
       </c>
-      <c r="AS214">
+      <c r="AS214" s="1">
         <v>62.359657494200995</v>
       </c>
       <c r="AT214" s="1">
@@ -68774,7 +68789,7 @@
       <c r="BD214">
         <v>1260624</v>
       </c>
-      <c r="BE214">
+      <c r="BE214" s="1">
         <v>24538.321810455051</v>
       </c>
       <c r="BF214">
@@ -68816,13 +68831,13 @@
       <c r="BR214">
         <v>9230</v>
       </c>
-      <c r="BS214" t="s">
+      <c r="BS214" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BT214">
         <v>0</v>
       </c>
-      <c r="BU214" t="s">
+      <c r="BU214" s="1" t="s">
         <v>218</v>
       </c>
       <c r="BV214" t="s">

--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit_turisticne_regije_app_v4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC10E226-E67D-E046-9B6B-2695295A8D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E6FDB2-0613-E448-A207-BBF1AE1E44B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25460" yWindow="7280" windowWidth="49880" windowHeight="34240" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
+    <workbookView xWindow="19920" yWindow="11520" windowWidth="49880" windowHeight="34240" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Skupna Tabela" sheetId="1" r:id="rId1"/>
@@ -1289,11 +1289,11 @@
     <tableColumn id="29" xr3:uid="{E32E1653-4218-8144-AE1B-7DA0234BDD6B}" name="Pritisk turizma na družbeni prostor (število stalnih ležišč / 100 prebivalcev)"/>
     <tableColumn id="30" xr3:uid="{6235832E-2F71-6247-9BC2-BB497EF940F1}" name="Gostota turizma"/>
     <tableColumn id="31" xr3:uid="{6059D037-013F-3443-92BE-556256221BB9}" name="Intenzivnost turizma (število nočitev na dan / 100 prebivalcev)"/>
-    <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)" dataDxfId="4"/>
-    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" dataDxfId="3"/>
-    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="7"/>
-    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="6"/>
-    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="5"/>
+    <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)" dataDxfId="7"/>
+    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" dataDxfId="6"/>
+    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="5"/>
+    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="3"/>
     <tableColumn id="37" xr3:uid="{52A7F38A-5C90-964D-B065-B17C7BA263D5}" name="Delež delovno aktivnih v turizmu (OECD/WTO)"/>
     <tableColumn id="38" xr3:uid="{C0F240E5-648C-7342-B26C-C8B4E0C3F6B4}" name="Število vseh vrst podjetij na območju"/>
     <tableColumn id="39" xr3:uid="{36A2CDB3-CA3D-9043-ADE8-DD7F31F3FE73}" name="Prihodek (v 1000 EUR) vseh podjetij na območju"/>

--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit_turisticne_regije_app_v4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E90F8AB-8A60-9B4C-B6F4-EEB31D46A587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A53F828-B1A1-2B47-BC99-65535C07792F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
@@ -1106,9 +1106,6 @@
     <t>Prenočitve turistov SKUPAJ - 2024</t>
   </si>
   <si>
-    <t>Prenočitve - povprečno število prenočitev na mesec - 2024</t>
-  </si>
-  <si>
     <t>Prenočitve turistov SKUPAJ - 2019</t>
   </si>
   <si>
@@ -1146,6 +1143,9 @@
   </si>
   <si>
     <t>GINI Indeks - sezonskost prenočitev - 2019</t>
+  </si>
+  <si>
+    <t>Prenočitve - povprečno število prenočitev na mesec</t>
   </si>
 </sst>
 </file>
@@ -1340,9 +1340,6 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
@@ -1374,6 +1371,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1431,7 +1431,7 @@
     <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ - 2024" dataDxfId="64" totalsRowDxfId="44"/>
     <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači - 2024" dataDxfId="63" totalsRowDxfId="43"/>
     <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov Tuji - 2024" dataDxfId="62" totalsRowDxfId="42"/>
-    <tableColumn id="105" xr3:uid="{3F73618F-8B9D-9C40-9ABE-1663CD0B4B36}" name="Prenočitve - povprečno število prenočitev na mesec - 2024" dataDxfId="61" totalsRowDxfId="41"/>
+    <tableColumn id="105" xr3:uid="{3F73618F-8B9D-9C40-9ABE-1663CD0B4B36}" name="Prenočitve - povprečno število prenočitev na mesec" dataDxfId="61" totalsRowDxfId="41"/>
     <tableColumn id="109" xr3:uid="{B1220855-9F1D-CF43-9E92-775EB008AA16}" name="Delež tujih prenočitev - 2019" dataDxfId="60" totalsRowDxfId="40"/>
     <tableColumn id="10" xr3:uid="{AE7EC853-0402-A44C-9F12-18D82AF38827}" name="Delež tujih prenočitev - 2024"/>
     <tableColumn id="110" xr3:uid="{A139B468-44D6-C04C-9966-6DB28C506A45}" name="Rast števila prenočitev 2024/2019 - SKUPAJ"/>
@@ -1448,21 +1448,21 @@
     <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ" dataDxfId="59" totalsRowDxfId="39"/>
     <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači" dataDxfId="58" totalsRowDxfId="38"/>
     <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji" dataDxfId="57" totalsRowDxfId="37"/>
-    <tableColumn id="114" xr3:uid="{7D3CB0D0-10CA-6240-8C96-33B71BD40FD8}" name="GINI Indeks - sezonskost prenočitev - 2019" dataDxfId="45" totalsRowDxfId="36"/>
-    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev - 2024" dataDxfId="56" totalsRowDxfId="35"/>
-    <tableColumn id="113" xr3:uid="{6F600461-C50A-4040-BD92-B01925DC3C2B}" name="Gibanje GINI Indeksa prenoč. 2024/2019" dataDxfId="55" totalsRowDxfId="34"/>
+    <tableColumn id="114" xr3:uid="{7D3CB0D0-10CA-6240-8C96-33B71BD40FD8}" name="GINI Indeks - sezonskost prenočitev - 2019" dataDxfId="56" totalsRowDxfId="36"/>
+    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev - 2024" dataDxfId="55" totalsRowDxfId="35"/>
+    <tableColumn id="113" xr3:uid="{6F600461-C50A-4040-BD92-B01925DC3C2B}" name="Gibanje GINI Indeksa prenoč. 2024/2019" dataDxfId="54" totalsRowDxfId="34"/>
     <tableColumn id="14" xr3:uid="{494C63A2-19AC-0544-861F-B7FA12714240}" name="PDB turistov_x0009_SKUPAJ"/>
     <tableColumn id="15" xr3:uid="{A743FB1C-E3E3-8340-BA42-61AD9082C50D}" name="PDB turistov_x0009_Domači"/>
     <tableColumn id="16" xr3:uid="{D6397E34-AE62-1B40-8641-B68E90F526C0}" name="PDB turistov_x0009_Tuji"/>
     <tableColumn id="17" xr3:uid="{FF46E309-259F-F74C-B4E3-7DF480EC498E}" name="Nastanitvene kapacitete - Nedeljive enote" totalsRowDxfId="33"/>
     <tableColumn id="18" xr3:uid="{DFA7A743-7B9B-AC4B-B555-AB008106AD20}" name="Nastanitvene kapacitete - vsa ležišča" totalsRowDxfId="32"/>
     <tableColumn id="19" xr3:uid="{978F1FBB-9333-EE42-8F86-066AF03E32F3}" name="Nastanitvene kapacitete - stalna ležišča" totalsRowDxfId="31"/>
-    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="54" totalsRowDxfId="30"/>
-    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="53" totalsRowDxfId="29"/>
-    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="52" totalsRowDxfId="28"/>
-    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="51" totalsRowDxfId="27"/>
-    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="50" totalsRowDxfId="26"/>
-    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="49" totalsRowDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="53" totalsRowDxfId="30"/>
+    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="52" totalsRowDxfId="29"/>
+    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="51" totalsRowDxfId="28"/>
+    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="50" totalsRowDxfId="27"/>
+    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="49" totalsRowDxfId="26"/>
+    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="48" totalsRowDxfId="25"/>
     <tableColumn id="26" xr3:uid="{6B98A6DD-4A64-EE45-AE54-458C05388214}" name="Delež stalnih ležišč v Hotelih ipd."/>
     <tableColumn id="27" xr3:uid="{CC3F87E6-B3CD-E841-BCED-E5C77DFA385B}" name="Povprečna letna zasedenost staln. ležišč"/>
     <tableColumn id="28" xr3:uid="{36E12EEC-F431-7640-B38F-3F28A52A27A2}" name="Ocenjena povp. Letna zased. sob (nedeljivih enot)"/>
@@ -1471,9 +1471,9 @@
     <tableColumn id="31" xr3:uid="{6059D037-013F-3443-92BE-556256221BB9}" name="Intenzivnost turizma (število nočitev na dan / 100 prebivalcev)"/>
     <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)" totalsRowDxfId="24"/>
     <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" totalsRowDxfId="23"/>
-    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="48" totalsRowDxfId="22"/>
-    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="47" totalsRowDxfId="21"/>
-    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="46" totalsRowDxfId="20"/>
+    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="47" totalsRowDxfId="22"/>
+    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="46" totalsRowDxfId="21"/>
+    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="45" totalsRowDxfId="20"/>
     <tableColumn id="37" xr3:uid="{52A7F38A-5C90-964D-B065-B17C7BA263D5}" name="Delež delovno aktivnih v turizmu (OECD/WTO)" totalsRowDxfId="19"/>
     <tableColumn id="38" xr3:uid="{C0F240E5-648C-7342-B26C-C8B4E0C3F6B4}" name="Število vseh vrst podjetij na območju" totalsRowDxfId="18"/>
     <tableColumn id="39" xr3:uid="{36A2CDB3-CA3D-9043-ADE8-DD7F31F3FE73}" name="Prihodek (v 1000 EUR) vseh podjetij na območju" totalsRowDxfId="17"/>
@@ -1968,40 +1968,40 @@
         <v>226</v>
       </c>
       <c r="J1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K1" t="s">
+        <v>358</v>
+      </c>
+      <c r="L1" t="s">
         <v>359</v>
-      </c>
-      <c r="L1" t="s">
-        <v>360</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>355</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="R1" t="s">
         <v>361</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" t="s">
         <v>363</v>
       </c>
-      <c r="R1" t="s">
-        <v>362</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
+        <v>365</v>
+      </c>
+      <c r="U1" t="s">
         <v>364</v>
-      </c>
-      <c r="T1" t="s">
-        <v>366</v>
-      </c>
-      <c r="U1" t="s">
-        <v>365</v>
       </c>
       <c r="V1" t="s">
         <v>314</v>
@@ -2037,13 +2037,13 @@
         <v>282</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AJ1" t="s">
         <v>283</v>

--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit_turisticne_regije_app_v4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57967CCE-6C5D-0B42-B71A-5BDE1DBB06AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2AEED2-5374-3D44-9976-6B011A65A8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="41720" windowHeight="27000" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
+    <workbookView xWindow="4020" yWindow="1680" windowWidth="41720" windowHeight="27000" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Skupna Tabela" sheetId="1" r:id="rId1"/>
@@ -1846,7 +1846,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="23.5" customWidth="1"/>
+    <col min="2" max="3" width="23.5" customWidth="1"/>
+    <col min="4" max="4" width="26.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27.6640625" bestFit="1" customWidth="1"/>

--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit_turisticne_regije_app_v4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4475D34-4B1B-5E45-86BB-44CCA90EC75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEACA9DC-E4AC-DF46-ABE5-8AD190A15280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11300" yWindow="9480" windowWidth="28800" windowHeight="16280" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
+    <workbookView xWindow="8640" yWindow="17520" windowWidth="28800" windowHeight="16280" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Skupna Tabela" sheetId="1" r:id="rId1"/>
@@ -1178,9 +1178,6 @@
     <t>Delež vseh prenočitev - Italijanski trg - 2024</t>
   </si>
   <si>
-    <t>Delež vseh prenočitev - Vzh.evropski trgi (PL,CZ,HU,SK,LIT,LTV,EST,RU,UKR) -2024</t>
-  </si>
-  <si>
     <t>Delež vseh prenočitev - Drugi zah.in sev. evropski trgi (ES,P, F,Benelux, Skandinavske države) - 2024</t>
   </si>
   <si>
@@ -1212,6 +1209,9 @@
   </si>
   <si>
     <t>Delež vseh prenočitev - Vsi drugi tuji trgi - 2025</t>
+  </si>
+  <si>
+    <t>Delež vseh prenočitev - Vzh.evropski trgi (PL,CZ,HU,SK,LIT,LTV,EST,RU,UKR) - 2024</t>
   </si>
 </sst>
 </file>
@@ -1436,27 +1436,6 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
@@ -1514,7 +1493,28 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1554,26 +1554,26 @@
     <tableColumn id="106" xr3:uid="{F7FF3683-D64C-B84C-B130-995DD9ED829C}" name="Prenočitve turistov SKUPAJ - 2019"/>
     <tableColumn id="107" xr3:uid="{DFFD75B6-E4A3-0C44-9D48-17B3516A305A}" name="Prenočitve turistov Domači - 2019"/>
     <tableColumn id="108" xr3:uid="{584DB04E-60D9-1744-B6A1-6952195DC361}" name="Prenočitve turistov Tuji - 2019"/>
-    <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ - 2024" dataDxfId="61" totalsRowDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači - 2024" dataDxfId="84" totalsRowDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov Tuji - 2024" dataDxfId="83" totalsRowDxfId="52"/>
-    <tableColumn id="122" xr3:uid="{552065FC-30CB-E140-83A3-C3991B55A8C6}" name="Prenočitve turistov SKUPAJ - 2025" dataDxfId="60" totalsRowDxfId="51"/>
-    <tableColumn id="123" xr3:uid="{AA739D98-B21D-8C4B-8209-6847B58DF8F4}" name="Prenočitve turistov Domači - 2025" dataDxfId="59" totalsRowDxfId="50"/>
-    <tableColumn id="124" xr3:uid="{0D52A3F1-C861-A84F-A614-D77C5FA49216}" name="Prenočitve turistov Tuji - 2025" dataDxfId="58" totalsRowDxfId="49"/>
-    <tableColumn id="105" xr3:uid="{3F73618F-8B9D-9C40-9ABE-1663CD0B4B36}" name="Prenočitve - povprečno število prenočitev na mesec" dataDxfId="82" totalsRowDxfId="48"/>
-    <tableColumn id="109" xr3:uid="{B1220855-9F1D-CF43-9E92-775EB008AA16}" name="Delež tujih prenočitev - 2019" dataDxfId="81" totalsRowDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ - 2024" dataDxfId="84" totalsRowDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači - 2024" dataDxfId="83" totalsRowDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov Tuji - 2024" dataDxfId="82" totalsRowDxfId="52"/>
+    <tableColumn id="122" xr3:uid="{552065FC-30CB-E140-83A3-C3991B55A8C6}" name="Prenočitve turistov SKUPAJ - 2025" dataDxfId="81" totalsRowDxfId="51"/>
+    <tableColumn id="123" xr3:uid="{AA739D98-B21D-8C4B-8209-6847B58DF8F4}" name="Prenočitve turistov Domači - 2025" dataDxfId="80" totalsRowDxfId="50"/>
+    <tableColumn id="124" xr3:uid="{0D52A3F1-C861-A84F-A614-D77C5FA49216}" name="Prenočitve turistov Tuji - 2025" dataDxfId="79" totalsRowDxfId="49"/>
+    <tableColumn id="105" xr3:uid="{3F73618F-8B9D-9C40-9ABE-1663CD0B4B36}" name="Prenočitve - povprečno število prenočitev na mesec" dataDxfId="78" totalsRowDxfId="48"/>
+    <tableColumn id="109" xr3:uid="{B1220855-9F1D-CF43-9E92-775EB008AA16}" name="Delež tujih prenočitev - 2019" dataDxfId="77" totalsRowDxfId="47"/>
     <tableColumn id="10" xr3:uid="{AE7EC853-0402-A44C-9F12-18D82AF38827}" name="Delež tujih prenočitev - 2024"/>
     <tableColumn id="125" xr3:uid="{8BC79AC6-F78F-4B4D-9748-B88B6AFF69EE}" name="Delež tujih prenočitev - 2025"/>
     <tableColumn id="110" xr3:uid="{A139B468-44D6-C04C-9966-6DB28C506A45}" name="Rast števila prenočitev 2024/2019 - SKUPAJ"/>
     <tableColumn id="111" xr3:uid="{9040517C-15E6-8C4D-8D7F-E856E27F299C}" name="Rast števila prenočitev 2024/2019 - Domači"/>
     <tableColumn id="112" xr3:uid="{9A1AC9F7-3946-384A-8284-60731B1A7003}" name="Rast števila prenočitev 2024/2019 - Tuji"/>
-    <tableColumn id="126" xr3:uid="{37DB623B-8FCA-2E46-BB4A-C8A36B9D3AEE}" name="Rast števila prenočitev 2025/2019 - SKUPAJ" dataDxfId="57" totalsRowDxfId="46"/>
-    <tableColumn id="127" xr3:uid="{FB1CE38A-E750-9246-972D-AB5C38B8E853}" name="Rast števila prenočitev 2025/2019 - Domači" dataDxfId="56" totalsRowDxfId="45"/>
-    <tableColumn id="128" xr3:uid="{C06A9023-037E-AE4C-AF11-D1DBF757480E}" name="Rast števila prenočitev 2025/2019 - Tuji" dataDxfId="55" totalsRowDxfId="44"/>
+    <tableColumn id="126" xr3:uid="{37DB623B-8FCA-2E46-BB4A-C8A36B9D3AEE}" name="Rast števila prenočitev 2025/2019 - SKUPAJ" dataDxfId="76" totalsRowDxfId="46"/>
+    <tableColumn id="127" xr3:uid="{FB1CE38A-E750-9246-972D-AB5C38B8E853}" name="Rast števila prenočitev 2025/2019 - Domači" dataDxfId="75" totalsRowDxfId="45"/>
+    <tableColumn id="128" xr3:uid="{C06A9023-037E-AE4C-AF11-D1DBF757480E}" name="Rast števila prenočitev 2025/2019 - Tuji" dataDxfId="74" totalsRowDxfId="44"/>
     <tableColumn id="100" xr3:uid="{646738F1-12E5-3D42-B08F-732CB4BD71FB}" name="Delež vseh prenočitev - Domači trg - 2024"/>
     <tableColumn id="101" xr3:uid="{E13F778E-7B5E-764D-A93E-CE2E6F497E0A}" name="Delež vseh prenočitev - DACH trgi - 2024"/>
     <tableColumn id="97" xr3:uid="{4353E62C-3E00-A742-97A0-09F93BE31459}" name="Delež vseh prenočitev - Italijanski trg - 2024"/>
-    <tableColumn id="98" xr3:uid="{610ECDE2-6D04-A047-91E5-67167D9D99DB}" name="Delež vseh prenočitev - Vzh.evropski trgi (PL,CZ,HU,SK,LIT,LTV,EST,RU,UKR) -2024"/>
+    <tableColumn id="98" xr3:uid="{610ECDE2-6D04-A047-91E5-67167D9D99DB}" name="Delež vseh prenočitev - Vzh.evropski trgi (PL,CZ,HU,SK,LIT,LTV,EST,RU,UKR) - 2024"/>
     <tableColumn id="99" xr3:uid="{CD8B1967-9DD5-D64C-8F1F-161A789F5F39}" name="Delež vseh prenočitev - Drugi zah.in sev. evropski trgi (ES,P, F,Benelux, Skandinavske države) - 2024"/>
     <tableColumn id="96" xr3:uid="{BE355046-C01C-9644-BF5E-989C542937E5}" name="Delež vseh prenočitev - Prekomorski trgi (ZDA, VB, CAN, AU, Azija) - 2024"/>
     <tableColumn id="95" xr3:uid="{D5614879-03D8-BE4D-8BB9-B1493690172E}" name="Delež vseh prenočitev - Trgi JV Evrope - 2024"/>
@@ -1586,16 +1586,16 @@
     <tableColumn id="134" xr3:uid="{47D138F1-3468-0446-A0A8-1298EA2CC048}" name="Delež vseh prenočitev - Prekomorski trgi (ZDA, VB, CAN, AU, Azija) - 2025"/>
     <tableColumn id="135" xr3:uid="{99963EE1-0660-E74E-B6D4-6DADD5F900F4}" name="Delež vseh prenočitev - Trgi JV Evrope - 2025"/>
     <tableColumn id="136" xr3:uid="{C21D36A1-E635-E346-9F0E-242FFBC2D5F9}" name="Delež vseh prenočitev - Vsi drugi tuji trgi - 2025"/>
-    <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ - 2024" dataDxfId="80" totalsRowDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači - 2024" dataDxfId="79" totalsRowDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji - 2024" dataDxfId="78" totalsRowDxfId="41"/>
-    <tableColumn id="114" xr3:uid="{79DBE021-6724-BA4B-A6CC-BF8D5E62986D}" name="Prihodi turistov SKUPAJ - 2025" dataDxfId="77" totalsRowDxfId="40"/>
-    <tableColumn id="115" xr3:uid="{7330AE28-8ABF-1442-912F-D54E4863351F}" name="Prihodi turistov Domači - 2025" dataDxfId="76" totalsRowDxfId="39"/>
-    <tableColumn id="116" xr3:uid="{677B102C-DD5D-C542-98A6-030FC27E5DCE}" name="Prihodi turistov Tuji - 2025" dataDxfId="75" totalsRowDxfId="38"/>
-    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev - 2024" dataDxfId="74" totalsRowDxfId="37"/>
-    <tableColumn id="113" xr3:uid="{6F600461-C50A-4040-BD92-B01925DC3C2B}" name="Gibanje GINI Indeksa prenoč. 2024/2019" dataDxfId="73" totalsRowDxfId="36"/>
-    <tableColumn id="120" xr3:uid="{78864389-753D-0644-96EE-43E33DC457C5}" name="GINI Indeks - sezonskost prenočitev - 2025" dataDxfId="72" totalsRowDxfId="35"/>
-    <tableColumn id="121" xr3:uid="{EB237473-7927-E543-9439-92CA8EF4944C}" name="Gibanje GINI Indeksa prenoč. 2025/2019" dataDxfId="71" totalsRowDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ - 2024" dataDxfId="73" totalsRowDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači - 2024" dataDxfId="72" totalsRowDxfId="42"/>
+    <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji - 2024" dataDxfId="71" totalsRowDxfId="41"/>
+    <tableColumn id="114" xr3:uid="{79DBE021-6724-BA4B-A6CC-BF8D5E62986D}" name="Prihodi turistov SKUPAJ - 2025" dataDxfId="70" totalsRowDxfId="40"/>
+    <tableColumn id="115" xr3:uid="{7330AE28-8ABF-1442-912F-D54E4863351F}" name="Prihodi turistov Domači - 2025" dataDxfId="69" totalsRowDxfId="39"/>
+    <tableColumn id="116" xr3:uid="{677B102C-DD5D-C542-98A6-030FC27E5DCE}" name="Prihodi turistov Tuji - 2025" dataDxfId="68" totalsRowDxfId="38"/>
+    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev - 2024" dataDxfId="67" totalsRowDxfId="37"/>
+    <tableColumn id="113" xr3:uid="{6F600461-C50A-4040-BD92-B01925DC3C2B}" name="Gibanje GINI Indeksa prenoč. 2024/2019" dataDxfId="66" totalsRowDxfId="36"/>
+    <tableColumn id="120" xr3:uid="{78864389-753D-0644-96EE-43E33DC457C5}" name="GINI Indeks - sezonskost prenočitev - 2025" dataDxfId="65" totalsRowDxfId="35"/>
+    <tableColumn id="121" xr3:uid="{EB237473-7927-E543-9439-92CA8EF4944C}" name="Gibanje GINI Indeksa prenoč. 2025/2019" dataDxfId="64" totalsRowDxfId="34"/>
     <tableColumn id="14" xr3:uid="{494C63A2-19AC-0544-861F-B7FA12714240}" name="PDB turistov SKUPAJ - 2024"/>
     <tableColumn id="15" xr3:uid="{A743FB1C-E3E3-8340-BA42-61AD9082C50D}" name="PDB turistov Domači - 2024"/>
     <tableColumn id="16" xr3:uid="{D6397E34-AE62-1B40-8641-B68E90F526C0}" name="PDB turistov Tuji - 2024"/>
@@ -1605,12 +1605,12 @@
     <tableColumn id="17" xr3:uid="{FF46E309-259F-F74C-B4E3-7DF480EC498E}" name="Nastanitvene kapacitete - Nedeljive enote" totalsRowDxfId="33"/>
     <tableColumn id="18" xr3:uid="{DFA7A743-7B9B-AC4B-B555-AB008106AD20}" name="Nastanitvene kapacitete - vsa ležišča" totalsRowDxfId="32"/>
     <tableColumn id="19" xr3:uid="{978F1FBB-9333-EE42-8F86-066AF03E32F3}" name="Nastanitvene kapacitete - stalna ležišča" totalsRowDxfId="31"/>
-    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="70" totalsRowDxfId="30"/>
-    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="69" totalsRowDxfId="29"/>
-    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="68" totalsRowDxfId="28"/>
-    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="67" totalsRowDxfId="27"/>
-    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="66" totalsRowDxfId="26"/>
-    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="65" totalsRowDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="63" totalsRowDxfId="30"/>
+    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="62" totalsRowDxfId="29"/>
+    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="61" totalsRowDxfId="28"/>
+    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="60" totalsRowDxfId="27"/>
+    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="59" totalsRowDxfId="26"/>
+    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="58" totalsRowDxfId="25"/>
     <tableColumn id="26" xr3:uid="{6B98A6DD-4A64-EE45-AE54-458C05388214}" name="Delež stalnih ležišč v Hotelih ipd."/>
     <tableColumn id="27" xr3:uid="{CC3F87E6-B3CD-E841-BCED-E5C77DFA385B}" name="Povprečna letna zasedenost staln. ležišč"/>
     <tableColumn id="28" xr3:uid="{36E12EEC-F431-7640-B38F-3F28A52A27A2}" name="Ocenjena povp. Letna zased. sob (nedeljivih enot)"/>
@@ -1619,9 +1619,9 @@
     <tableColumn id="31" xr3:uid="{6059D037-013F-3443-92BE-556256221BB9}" name="Intenzivnost turizma (število nočitev na dan / 100 prebivalcev)"/>
     <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)" totalsRowDxfId="24"/>
     <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" totalsRowDxfId="23"/>
-    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="64" totalsRowDxfId="22"/>
-    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="63" totalsRowDxfId="21"/>
-    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="62" totalsRowDxfId="20"/>
+    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="57" totalsRowDxfId="22"/>
+    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="56" totalsRowDxfId="21"/>
+    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="55" totalsRowDxfId="20"/>
     <tableColumn id="37" xr3:uid="{52A7F38A-5C90-964D-B065-B17C7BA263D5}" name="Delež delovno aktivnih v turizmu (OECD/WTO)" totalsRowDxfId="19"/>
     <tableColumn id="38" xr3:uid="{C0F240E5-648C-7342-B26C-C8B4E0C3F6B4}" name="Število vseh vrst podjetij na območju" totalsRowDxfId="18"/>
     <tableColumn id="39" xr3:uid="{36A2CDB3-CA3D-9043-ADE8-DD7F31F3FE73}" name="Prihodek (v 1000 EUR) vseh podjetij na območju" totalsRowDxfId="17"/>
@@ -2185,43 +2185,43 @@
         <v>379</v>
       </c>
       <c r="AF1" t="s">
+        <v>391</v>
+      </c>
+      <c r="AG1" t="s">
         <v>380</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>381</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>382</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>383</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>384</v>
       </c>
       <c r="AK1" t="s">
         <v>376</v>
       </c>
       <c r="AL1" t="s">
+        <v>384</v>
+      </c>
+      <c r="AM1" t="s">
         <v>385</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>386</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>387</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>388</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>389</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>390</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>391</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>355</v>

--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit_turisticne_regije_app_v4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F5DBDC-0618-EF47-9648-5404E3CEEFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DBE14D-E92F-2F4A-8FD6-D741CF5AE026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31220" yWindow="11140" windowWidth="54620" windowHeight="29900" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
+    <workbookView xWindow="22180" yWindow="14160" windowWidth="54620" windowHeight="29900" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Skupna Tabela" sheetId="1" r:id="rId1"/>
@@ -1400,69 +1400,6 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
@@ -1502,6 +1439,36 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
@@ -1529,7 +1496,40 @@
       <numFmt numFmtId="165" formatCode="0.0%"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1582,22 +1582,22 @@
     <tableColumn id="106" xr3:uid="{F7FF3683-D64C-B84C-B130-995DD9ED829C}" name="Prenočitve turistov SKUPAJ - 2019"/>
     <tableColumn id="107" xr3:uid="{DFFD75B6-E4A3-0C44-9D48-17B3516A305A}" name="Prenočitve turistov Domači - 2019"/>
     <tableColumn id="108" xr3:uid="{584DB04E-60D9-1744-B6A1-6952195DC361}" name="Prenočitve turistov Tuji - 2019"/>
-    <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ - 2024" dataDxfId="84" totalsRowDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači - 2024" dataDxfId="83" totalsRowDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov Tuji - 2024" dataDxfId="82" totalsRowDxfId="52"/>
-    <tableColumn id="122" xr3:uid="{552065FC-30CB-E140-83A3-C3991B55A8C6}" name="Prenočitve turistov SKUPAJ - 2025" dataDxfId="81" totalsRowDxfId="51"/>
-    <tableColumn id="123" xr3:uid="{AA739D98-B21D-8C4B-8209-6847B58DF8F4}" name="Prenočitve turistov Domači - 2025" dataDxfId="80" totalsRowDxfId="50"/>
-    <tableColumn id="124" xr3:uid="{0D52A3F1-C861-A84F-A614-D77C5FA49216}" name="Prenočitve turistov Tuji - 2025" dataDxfId="79" totalsRowDxfId="49"/>
-    <tableColumn id="105" xr3:uid="{3F73618F-8B9D-9C40-9ABE-1663CD0B4B36}" name="Prenočitve - povprečno število prenočitev na mesec" dataDxfId="78" totalsRowDxfId="48"/>
-    <tableColumn id="109" xr3:uid="{B1220855-9F1D-CF43-9E92-775EB008AA16}" name="Delež tujih prenočitev - 2019" dataDxfId="77" totalsRowDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ - 2024" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači - 2024" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov Tuji - 2024" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="122" xr3:uid="{552065FC-30CB-E140-83A3-C3991B55A8C6}" name="Prenočitve turistov SKUPAJ - 2025" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="123" xr3:uid="{AA739D98-B21D-8C4B-8209-6847B58DF8F4}" name="Prenočitve turistov Domači - 2025" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="124" xr3:uid="{0D52A3F1-C861-A84F-A614-D77C5FA49216}" name="Prenočitve turistov Tuji - 2025" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="105" xr3:uid="{3F73618F-8B9D-9C40-9ABE-1663CD0B4B36}" name="Prenočitve - povprečno število prenočitev na mesec" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="109" xr3:uid="{B1220855-9F1D-CF43-9E92-775EB008AA16}" name="Delež tujih prenočitev - 2019" dataDxfId="70" totalsRowDxfId="69"/>
     <tableColumn id="10" xr3:uid="{AE7EC853-0402-A44C-9F12-18D82AF38827}" name="Delež tujih prenočitev - 2024"/>
     <tableColumn id="125" xr3:uid="{8BC79AC6-F78F-4B4D-9748-B88B6AFF69EE}" name="Delež tujih prenočitev - 2025"/>
     <tableColumn id="110" xr3:uid="{A139B468-44D6-C04C-9966-6DB28C506A45}" name="Rast števila prenočitev 2024/2019 - SKUPAJ"/>
     <tableColumn id="111" xr3:uid="{9040517C-15E6-8C4D-8D7F-E856E27F299C}" name="Rast števila prenočitev 2024/2019 - Domači"/>
     <tableColumn id="112" xr3:uid="{9A1AC9F7-3946-384A-8284-60731B1A7003}" name="Rast števila prenočitev 2024/2019 - Tuji"/>
-    <tableColumn id="126" xr3:uid="{37DB623B-8FCA-2E46-BB4A-C8A36B9D3AEE}" name="Rast števila prenočitev 2025/2019 - SKUPAJ" dataDxfId="76" totalsRowDxfId="46"/>
-    <tableColumn id="127" xr3:uid="{FB1CE38A-E750-9246-972D-AB5C38B8E853}" name="Rast števila prenočitev 2025/2019 - Domači" dataDxfId="75" totalsRowDxfId="45"/>
-    <tableColumn id="128" xr3:uid="{C06A9023-037E-AE4C-AF11-D1DBF757480E}" name="Rast števila prenočitev 2025/2019 - Tuji" dataDxfId="74" totalsRowDxfId="44"/>
+    <tableColumn id="126" xr3:uid="{37DB623B-8FCA-2E46-BB4A-C8A36B9D3AEE}" name="Rast števila prenočitev 2025/2019 - SKUPAJ" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="127" xr3:uid="{FB1CE38A-E750-9246-972D-AB5C38B8E853}" name="Rast števila prenočitev 2025/2019 - Domači" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="128" xr3:uid="{C06A9023-037E-AE4C-AF11-D1DBF757480E}" name="Rast števila prenočitev 2025/2019 - Tuji" dataDxfId="64" totalsRowDxfId="63"/>
     <tableColumn id="100" xr3:uid="{646738F1-12E5-3D42-B08F-732CB4BD71FB}" name="Delež vseh prenočitev - Domači trg - 2024"/>
     <tableColumn id="101" xr3:uid="{E13F778E-7B5E-764D-A93E-CE2E6F497E0A}" name="Delež vseh prenočitev - DACH trgi - 2024"/>
     <tableColumn id="97" xr3:uid="{4353E62C-3E00-A742-97A0-09F93BE31459}" name="Delež vseh prenočitev - Italijanski trg - 2024"/>
@@ -1614,42 +1614,42 @@
     <tableColumn id="134" xr3:uid="{47D138F1-3468-0446-A0A8-1298EA2CC048}" name="Delež vseh prenočitev - Prekomorski trgi (ZDA, VB, CAN, AU, Azija) - 2025"/>
     <tableColumn id="135" xr3:uid="{99963EE1-0660-E74E-B6D4-6DADD5F900F4}" name="Delež vseh prenočitev - Trgi JV Evrope - 2025"/>
     <tableColumn id="136" xr3:uid="{C21D36A1-E635-E346-9F0E-242FFBC2D5F9}" name="Delež vseh prenočitev - Vsi drugi tuji trgi - 2025"/>
-    <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ - 2024" dataDxfId="73" totalsRowDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači - 2024" dataDxfId="72" totalsRowDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji - 2024" dataDxfId="71" totalsRowDxfId="41"/>
-    <tableColumn id="114" xr3:uid="{79DBE021-6724-BA4B-A6CC-BF8D5E62986D}" name="Prihodi turistov SKUPAJ - 2025" dataDxfId="70" totalsRowDxfId="40"/>
-    <tableColumn id="115" xr3:uid="{7330AE28-8ABF-1442-912F-D54E4863351F}" name="Prihodi turistov Domači - 2025" dataDxfId="69" totalsRowDxfId="39"/>
-    <tableColumn id="116" xr3:uid="{677B102C-DD5D-C542-98A6-030FC27E5DCE}" name="Prihodi turistov Tuji - 2025" dataDxfId="68" totalsRowDxfId="38"/>
-    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev - 2024" dataDxfId="67" totalsRowDxfId="37"/>
-    <tableColumn id="113" xr3:uid="{6F600461-C50A-4040-BD92-B01925DC3C2B}" name="Gibanje GINI Indeksa prenoč. 2024/2019" dataDxfId="66" totalsRowDxfId="36"/>
-    <tableColumn id="120" xr3:uid="{78864389-753D-0644-96EE-43E33DC457C5}" name="GINI Indeks - sezonskost prenočitev - 2025" dataDxfId="65" totalsRowDxfId="35"/>
-    <tableColumn id="121" xr3:uid="{EB237473-7927-E543-9439-92CA8EF4944C}" name="Gibanje GINI Indeksa prenoč. 2025/2019" dataDxfId="64" totalsRowDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ - 2024" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači - 2024" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji - 2024" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="114" xr3:uid="{79DBE021-6724-BA4B-A6CC-BF8D5E62986D}" name="Prihodi turistov SKUPAJ - 2025" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="115" xr3:uid="{7330AE28-8ABF-1442-912F-D54E4863351F}" name="Prihodi turistov Domači - 2025" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="116" xr3:uid="{677B102C-DD5D-C542-98A6-030FC27E5DCE}" name="Prihodi turistov Tuji - 2025" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev - 2024" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="113" xr3:uid="{6F600461-C50A-4040-BD92-B01925DC3C2B}" name="Gibanje GINI Indeksa prenoč. 2024/2019" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="120" xr3:uid="{78864389-753D-0644-96EE-43E33DC457C5}" name="GINI Indeks - sezonskost prenočitev - 2025" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="121" xr3:uid="{EB237473-7927-E543-9439-92CA8EF4944C}" name="Gibanje GINI Indeksa prenoč. 2025/2019" dataDxfId="44" totalsRowDxfId="43"/>
     <tableColumn id="14" xr3:uid="{494C63A2-19AC-0544-861F-B7FA12714240}" name="PDB turistov SKUPAJ - 2024"/>
     <tableColumn id="15" xr3:uid="{A743FB1C-E3E3-8340-BA42-61AD9082C50D}" name="PDB turistov Domači - 2024"/>
     <tableColumn id="16" xr3:uid="{D6397E34-AE62-1B40-8641-B68E90F526C0}" name="PDB turistov Tuji - 2024"/>
     <tableColumn id="117" xr3:uid="{6885EC95-5659-F04B-A251-AE53BDE48149}" name="PDB turistov SKUPAJ - 2025"/>
     <tableColumn id="118" xr3:uid="{4E7DDFB8-17E3-2C4C-AC60-14DA7C782C4D}" name="PDB turistov Domači - 2025"/>
     <tableColumn id="119" xr3:uid="{91E8E2BD-823C-4543-991A-D421CEB98935}" name="PDB turistov Tuji - 2025"/>
-    <tableColumn id="17" xr3:uid="{FF46E309-259F-F74C-B4E3-7DF480EC498E}" name="Nastanitvene kapacitete - Nedeljive enote" totalsRowDxfId="33"/>
-    <tableColumn id="18" xr3:uid="{DFA7A743-7B9B-AC4B-B555-AB008106AD20}" name="Nastanitvene kapacitete - vsa ležišča" totalsRowDxfId="32"/>
-    <tableColumn id="19" xr3:uid="{978F1FBB-9333-EE42-8F86-066AF03E32F3}" name="Nastanitvene kapacitete - stalna ležišča" totalsRowDxfId="31"/>
-    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="63" totalsRowDxfId="30"/>
-    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="62" totalsRowDxfId="29"/>
-    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="61" totalsRowDxfId="28"/>
-    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="60" totalsRowDxfId="27"/>
-    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="59" totalsRowDxfId="26"/>
-    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="58" totalsRowDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{FF46E309-259F-F74C-B4E3-7DF480EC498E}" name="Nastanitvene kapacitete - Nedeljive enote" totalsRowDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{DFA7A743-7B9B-AC4B-B555-AB008106AD20}" name="Nastanitvene kapacitete - vsa ležišča" totalsRowDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{978F1FBB-9333-EE42-8F86-066AF03E32F3}" name="Nastanitvene kapacitete - stalna ležišča" totalsRowDxfId="40"/>
+    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="29" totalsRowDxfId="28"/>
     <tableColumn id="26" xr3:uid="{6B98A6DD-4A64-EE45-AE54-458C05388214}" name="Delež stalnih ležišč v Hotelih ipd."/>
     <tableColumn id="27" xr3:uid="{CC3F87E6-B3CD-E841-BCED-E5C77DFA385B}" name="Povprečna letna zasedenost staln. ležišč"/>
     <tableColumn id="28" xr3:uid="{36E12EEC-F431-7640-B38F-3F28A52A27A2}" name="Ocenjena povp. Letna zased. sob (nedeljivih enot)"/>
     <tableColumn id="29" xr3:uid="{E32E1653-4218-8144-AE1B-7DA0234BDD6B}" name="Pritisk turizma na družbeni prostor (število stalnih ležišč / 100 prebivalcev)"/>
     <tableColumn id="30" xr3:uid="{6235832E-2F71-6247-9BC2-BB497EF940F1}" name="Gostota turizma"/>
     <tableColumn id="31" xr3:uid="{6059D037-013F-3443-92BE-556256221BB9}" name="Intenzivnost turizma (število nočitev na dan / 100 prebivalcev)"/>
-    <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)" totalsRowDxfId="24"/>
-    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" totalsRowDxfId="23"/>
-    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="57" totalsRowDxfId="22"/>
-    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="56" totalsRowDxfId="21"/>
-    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="55" totalsRowDxfId="20"/>
+    <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)" totalsRowDxfId="27"/>
+    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" totalsRowDxfId="26"/>
+    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="21" totalsRowDxfId="20"/>
     <tableColumn id="37" xr3:uid="{52A7F38A-5C90-964D-B065-B17C7BA263D5}" name="Delež delovno aktivnih v turizmu (OECD/WTO)" totalsRowDxfId="19"/>
     <tableColumn id="38" xr3:uid="{C0F240E5-648C-7342-B26C-C8B4E0C3F6B4}" name="Število vseh vrst podjetij na območju" totalsRowDxfId="18"/>
     <tableColumn id="39" xr3:uid="{36A2CDB3-CA3D-9043-ADE8-DD7F31F3FE73}" name="Prihodek (v 1000 EUR) vseh podjetij na območju" totalsRowDxfId="17"/>

--- a/Skupna tabela občine.xlsx
+++ b/Skupna tabela občine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peter/Desktop/Slovenija/Razširjeni kazalniki/streamlit_turisticne_regije_app_v4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DBE14D-E92F-2F4A-8FD6-D741CF5AE026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035E900F-19A7-504E-ACA0-F742238BB4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22180" yWindow="14160" windowWidth="54620" windowHeight="29900" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
+    <workbookView xWindow="11500" yWindow="13040" windowWidth="54620" windowHeight="29900" xr2:uid="{855CFD84-EAB2-0A43-A92D-394EE615CEA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Skupna Tabela" sheetId="1" r:id="rId1"/>
@@ -731,9 +731,6 @@
     <t>Gostota turizma</t>
   </si>
   <si>
-    <t>Delovno aktivni v  turizmu (OECD/WTO)</t>
-  </si>
-  <si>
     <t>Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p.</t>
   </si>
   <si>
@@ -1172,9 +1169,6 @@
     <t>Delež vseh prenočitev - Domači trg - 2024</t>
   </si>
   <si>
-    <t>Delež vseh prenočitev - DACH trgi - 2024</t>
-  </si>
-  <si>
     <t>Delež vseh prenočitev - Italijanski trg - 2024</t>
   </si>
   <si>
@@ -1188,9 +1182,6 @@
   </si>
   <si>
     <t>Delež vseh prenočitev - Vsi drugi tuji trgi - 2024</t>
-  </si>
-  <si>
-    <t>Delež vseh prenočitev - DACH trgi - 2025</t>
   </si>
   <si>
     <t>Delež vseh prenočitev - Italijanski trg - 2025</t>
@@ -1212,6 +1203,15 @@
   </si>
   <si>
     <t>Delež vseh prenočitev - Vzh.evropski trgi (PL,CZ,HU,SK,LIT,LTV,EST,RU,UKR) - 2024</t>
+  </si>
+  <si>
+    <t>Delež vseh prenočitev - DACH trgi (nemško govoreči trgi: D, A in CH) - 2024</t>
+  </si>
+  <si>
+    <t>Delež vseh prenočitev - DACH trgi (nemško govoreči trgi: D, A in CH) - 2025</t>
+  </si>
+  <si>
+    <t>Delovno aktivno prebivalstvo v turizmu (OECD/WTO)</t>
   </si>
 </sst>
 </file>
@@ -1400,6 +1400,69 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
@@ -1439,36 +1502,6 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
@@ -1496,40 +1529,7 @@
       <numFmt numFmtId="165" formatCode="0.0%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1582,24 +1582,24 @@
     <tableColumn id="106" xr3:uid="{F7FF3683-D64C-B84C-B130-995DD9ED829C}" name="Prenočitve turistov SKUPAJ - 2019"/>
     <tableColumn id="107" xr3:uid="{DFFD75B6-E4A3-0C44-9D48-17B3516A305A}" name="Prenočitve turistov Domači - 2019"/>
     <tableColumn id="108" xr3:uid="{584DB04E-60D9-1744-B6A1-6952195DC361}" name="Prenočitve turistov Tuji - 2019"/>
-    <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ - 2024" dataDxfId="84" totalsRowDxfId="83"/>
-    <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači - 2024" dataDxfId="82" totalsRowDxfId="81"/>
-    <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov Tuji - 2024" dataDxfId="80" totalsRowDxfId="79"/>
-    <tableColumn id="122" xr3:uid="{552065FC-30CB-E140-83A3-C3991B55A8C6}" name="Prenočitve turistov SKUPAJ - 2025" dataDxfId="78" totalsRowDxfId="77"/>
-    <tableColumn id="123" xr3:uid="{AA739D98-B21D-8C4B-8209-6847B58DF8F4}" name="Prenočitve turistov Domači - 2025" dataDxfId="76" totalsRowDxfId="75"/>
-    <tableColumn id="124" xr3:uid="{0D52A3F1-C861-A84F-A614-D77C5FA49216}" name="Prenočitve turistov Tuji - 2025" dataDxfId="74" totalsRowDxfId="73"/>
-    <tableColumn id="105" xr3:uid="{3F73618F-8B9D-9C40-9ABE-1663CD0B4B36}" name="Prenočitve - povprečno število prenočitev na mesec" dataDxfId="72" totalsRowDxfId="71"/>
-    <tableColumn id="109" xr3:uid="{B1220855-9F1D-CF43-9E92-775EB008AA16}" name="Delež tujih prenočitev - 2019" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="7" xr3:uid="{E209E213-8FD4-4C47-B297-1F887AE8D7A7}" name="Prenočitve turistov SKUPAJ - 2024" dataDxfId="84" totalsRowDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{2911BC09-A9DE-DC43-94D4-9C9E6E23A668}" name="Prenočitve turistov Domači - 2024" dataDxfId="83" totalsRowDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{F2E07E25-D318-EF4C-9D58-4F9D024FA8A8}" name="Prenočitve turistov Tuji - 2024" dataDxfId="82" totalsRowDxfId="52"/>
+    <tableColumn id="122" xr3:uid="{552065FC-30CB-E140-83A3-C3991B55A8C6}" name="Prenočitve turistov SKUPAJ - 2025" dataDxfId="81" totalsRowDxfId="51"/>
+    <tableColumn id="123" xr3:uid="{AA739D98-B21D-8C4B-8209-6847B58DF8F4}" name="Prenočitve turistov Domači - 2025" dataDxfId="80" totalsRowDxfId="50"/>
+    <tableColumn id="124" xr3:uid="{0D52A3F1-C861-A84F-A614-D77C5FA49216}" name="Prenočitve turistov Tuji - 2025" dataDxfId="79" totalsRowDxfId="49"/>
+    <tableColumn id="105" xr3:uid="{3F73618F-8B9D-9C40-9ABE-1663CD0B4B36}" name="Prenočitve - povprečno število prenočitev na mesec" dataDxfId="78" totalsRowDxfId="48"/>
+    <tableColumn id="109" xr3:uid="{B1220855-9F1D-CF43-9E92-775EB008AA16}" name="Delež tujih prenočitev - 2019" dataDxfId="77" totalsRowDxfId="47"/>
     <tableColumn id="10" xr3:uid="{AE7EC853-0402-A44C-9F12-18D82AF38827}" name="Delež tujih prenočitev - 2024"/>
     <tableColumn id="125" xr3:uid="{8BC79AC6-F78F-4B4D-9748-B88B6AFF69EE}" name="Delež tujih prenočitev - 2025"/>
     <tableColumn id="110" xr3:uid="{A139B468-44D6-C04C-9966-6DB28C506A45}" name="Rast števila prenočitev 2024/2019 - SKUPAJ"/>
     <tableColumn id="111" xr3:uid="{9040517C-15E6-8C4D-8D7F-E856E27F299C}" name="Rast števila prenočitev 2024/2019 - Domači"/>
     <tableColumn id="112" xr3:uid="{9A1AC9F7-3946-384A-8284-60731B1A7003}" name="Rast števila prenočitev 2024/2019 - Tuji"/>
-    <tableColumn id="126" xr3:uid="{37DB623B-8FCA-2E46-BB4A-C8A36B9D3AEE}" name="Rast števila prenočitev 2025/2019 - SKUPAJ" dataDxfId="68" totalsRowDxfId="67"/>
-    <tableColumn id="127" xr3:uid="{FB1CE38A-E750-9246-972D-AB5C38B8E853}" name="Rast števila prenočitev 2025/2019 - Domači" dataDxfId="66" totalsRowDxfId="65"/>
-    <tableColumn id="128" xr3:uid="{C06A9023-037E-AE4C-AF11-D1DBF757480E}" name="Rast števila prenočitev 2025/2019 - Tuji" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="126" xr3:uid="{37DB623B-8FCA-2E46-BB4A-C8A36B9D3AEE}" name="Rast števila prenočitev 2025/2019 - SKUPAJ" dataDxfId="76" totalsRowDxfId="46"/>
+    <tableColumn id="127" xr3:uid="{FB1CE38A-E750-9246-972D-AB5C38B8E853}" name="Rast števila prenočitev 2025/2019 - Domači" dataDxfId="75" totalsRowDxfId="45"/>
+    <tableColumn id="128" xr3:uid="{C06A9023-037E-AE4C-AF11-D1DBF757480E}" name="Rast števila prenočitev 2025/2019 - Tuji" dataDxfId="74" totalsRowDxfId="44"/>
     <tableColumn id="100" xr3:uid="{646738F1-12E5-3D42-B08F-732CB4BD71FB}" name="Delež vseh prenočitev - Domači trg - 2024"/>
-    <tableColumn id="101" xr3:uid="{E13F778E-7B5E-764D-A93E-CE2E6F497E0A}" name="Delež vseh prenočitev - DACH trgi - 2024"/>
+    <tableColumn id="101" xr3:uid="{E13F778E-7B5E-764D-A93E-CE2E6F497E0A}" name="Delež vseh prenočitev - DACH trgi (nemško govoreči trgi: D, A in CH) - 2024"/>
     <tableColumn id="97" xr3:uid="{4353E62C-3E00-A742-97A0-09F93BE31459}" name="Delež vseh prenočitev - Italijanski trg - 2024"/>
     <tableColumn id="98" xr3:uid="{610ECDE2-6D04-A047-91E5-67167D9D99DB}" name="Delež vseh prenočitev - Vzh.evropski trgi (PL,CZ,HU,SK,LIT,LTV,EST,RU,UKR) - 2024"/>
     <tableColumn id="99" xr3:uid="{CD8B1967-9DD5-D64C-8F1F-161A789F5F39}" name="Delež vseh prenočitev - Drugi zah.in sev. evropski trgi (ES,P, F,Benelux, Skandinavske države) - 2024"/>
@@ -1607,49 +1607,49 @@
     <tableColumn id="95" xr3:uid="{D5614879-03D8-BE4D-8BB9-B1493690172E}" name="Delež vseh prenočitev - Trgi JV Evrope - 2024"/>
     <tableColumn id="94" xr3:uid="{5E5059F9-5ABE-A940-B1FB-98129F4C2C53}" name="Delež vseh prenočitev - Vsi drugi tuji trgi - 2024"/>
     <tableColumn id="129" xr3:uid="{E27E0654-A1C7-554D-B611-6461B0A40D2C}" name="Delež vseh prenočitev - Domači trg - 2025"/>
-    <tableColumn id="130" xr3:uid="{4545FC34-2172-0A4A-BE8D-4B9E0765B913}" name="Delež vseh prenočitev - DACH trgi - 2025"/>
+    <tableColumn id="130" xr3:uid="{4545FC34-2172-0A4A-BE8D-4B9E0765B913}" name="Delež vseh prenočitev - DACH trgi (nemško govoreči trgi: D, A in CH) - 2025"/>
     <tableColumn id="131" xr3:uid="{4929DA25-B637-2E44-A07F-E42459929194}" name="Delež vseh prenočitev - Italijanski trg - 2025"/>
     <tableColumn id="132" xr3:uid="{4FC91462-2081-1248-824D-7F98A0EE4F46}" name="Delež vseh prenočitev - Vzh.evropski trgi (PL,CZ,HU,SK,LIT,LTV,EST,RU,UKR) - 2025"/>
     <tableColumn id="133" xr3:uid="{293709AE-30D5-4548-9C79-951416DE2864}" name="Delež vseh prenočitev - Drugi zah.in sev. evropski trgi (ES,P, F,Benelux, Skandinavske države) - 2025"/>
     <tableColumn id="134" xr3:uid="{47D138F1-3468-0446-A0A8-1298EA2CC048}" name="Delež vseh prenočitev - Prekomorski trgi (ZDA, VB, CAN, AU, Azija) - 2025"/>
     <tableColumn id="135" xr3:uid="{99963EE1-0660-E74E-B6D4-6DADD5F900F4}" name="Delež vseh prenočitev - Trgi JV Evrope - 2025"/>
     <tableColumn id="136" xr3:uid="{C21D36A1-E635-E346-9F0E-242FFBC2D5F9}" name="Delež vseh prenočitev - Vsi drugi tuji trgi - 2025"/>
-    <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ - 2024" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači - 2024" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji - 2024" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="114" xr3:uid="{79DBE021-6724-BA4B-A6CC-BF8D5E62986D}" name="Prihodi turistov SKUPAJ - 2025" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="115" xr3:uid="{7330AE28-8ABF-1442-912F-D54E4863351F}" name="Prihodi turistov Domači - 2025" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="116" xr3:uid="{677B102C-DD5D-C542-98A6-030FC27E5DCE}" name="Prihodi turistov Tuji - 2025" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev - 2024" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="113" xr3:uid="{6F600461-C50A-4040-BD92-B01925DC3C2B}" name="Gibanje GINI Indeksa prenoč. 2024/2019" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="120" xr3:uid="{78864389-753D-0644-96EE-43E33DC457C5}" name="GINI Indeks - sezonskost prenočitev - 2025" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="121" xr3:uid="{EB237473-7927-E543-9439-92CA8EF4944C}" name="Gibanje GINI Indeksa prenoč. 2025/2019" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{5CF30DCA-BA0F-D047-9308-6222A89F2E07}" name="Prihodi turistov SKUPAJ - 2024" dataDxfId="73" totalsRowDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{2608AA17-F184-2D44-B158-EC683F751D56}" name="Prihodi turistov Domači - 2024" dataDxfId="72" totalsRowDxfId="42"/>
+    <tableColumn id="13" xr3:uid="{D040950F-FE38-AF40-AC39-E818CABE1FE1}" name="Prihodi turistov Tuji - 2024" dataDxfId="71" totalsRowDxfId="41"/>
+    <tableColumn id="114" xr3:uid="{79DBE021-6724-BA4B-A6CC-BF8D5E62986D}" name="Prihodi turistov SKUPAJ - 2025" dataDxfId="70" totalsRowDxfId="40"/>
+    <tableColumn id="115" xr3:uid="{7330AE28-8ABF-1442-912F-D54E4863351F}" name="Prihodi turistov Domači - 2025" dataDxfId="69" totalsRowDxfId="39"/>
+    <tableColumn id="116" xr3:uid="{677B102C-DD5D-C542-98A6-030FC27E5DCE}" name="Prihodi turistov Tuji - 2025" dataDxfId="68" totalsRowDxfId="38"/>
+    <tableColumn id="92" xr3:uid="{260CB2C1-DC34-5F48-81C1-0035A515C7E8}" name="GINI Indeks - sezonskost prenočitev - 2024" dataDxfId="67" totalsRowDxfId="37"/>
+    <tableColumn id="113" xr3:uid="{6F600461-C50A-4040-BD92-B01925DC3C2B}" name="Gibanje GINI Indeksa prenoč. 2024/2019" dataDxfId="66" totalsRowDxfId="36"/>
+    <tableColumn id="120" xr3:uid="{78864389-753D-0644-96EE-43E33DC457C5}" name="GINI Indeks - sezonskost prenočitev - 2025" dataDxfId="65" totalsRowDxfId="35"/>
+    <tableColumn id="121" xr3:uid="{EB237473-7927-E543-9439-92CA8EF4944C}" name="Gibanje GINI Indeksa prenoč. 2025/2019" dataDxfId="64" totalsRowDxfId="34"/>
     <tableColumn id="14" xr3:uid="{494C63A2-19AC-0544-861F-B7FA12714240}" name="PDB turistov SKUPAJ - 2024"/>
     <tableColumn id="15" xr3:uid="{A743FB1C-E3E3-8340-BA42-61AD9082C50D}" name="PDB turistov Domači - 2024"/>
     <tableColumn id="16" xr3:uid="{D6397E34-AE62-1B40-8641-B68E90F526C0}" name="PDB turistov Tuji - 2024"/>
     <tableColumn id="117" xr3:uid="{6885EC95-5659-F04B-A251-AE53BDE48149}" name="PDB turistov SKUPAJ - 2025"/>
     <tableColumn id="118" xr3:uid="{4E7DDFB8-17E3-2C4C-AC60-14DA7C782C4D}" name="PDB turistov Domači - 2025"/>
     <tableColumn id="119" xr3:uid="{91E8E2BD-823C-4543-991A-D421CEB98935}" name="PDB turistov Tuji - 2025"/>
-    <tableColumn id="17" xr3:uid="{FF46E309-259F-F74C-B4E3-7DF480EC498E}" name="Nastanitvene kapacitete - Nedeljive enote" totalsRowDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{DFA7A743-7B9B-AC4B-B555-AB008106AD20}" name="Nastanitvene kapacitete - vsa ležišča" totalsRowDxfId="41"/>
-    <tableColumn id="19" xr3:uid="{978F1FBB-9333-EE42-8F86-066AF03E32F3}" name="Nastanitvene kapacitete - stalna ležišča" totalsRowDxfId="40"/>
-    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{FF46E309-259F-F74C-B4E3-7DF480EC498E}" name="Nastanitvene kapacitete - Nedeljive enote" totalsRowDxfId="33"/>
+    <tableColumn id="18" xr3:uid="{DFA7A743-7B9B-AC4B-B555-AB008106AD20}" name="Nastanitvene kapacitete - vsa ležišča" totalsRowDxfId="32"/>
+    <tableColumn id="19" xr3:uid="{978F1FBB-9333-EE42-8F86-066AF03E32F3}" name="Nastanitvene kapacitete - stalna ležišča" totalsRowDxfId="31"/>
+    <tableColumn id="20" xr3:uid="{36A5B684-693C-D046-A589-28E1F1CB9AD8}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Hoteli in podobni obrati" dataDxfId="63" totalsRowDxfId="30"/>
+    <tableColumn id="21" xr3:uid="{2B702555-9FD7-D940-90E2-CF22763449FC}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote)_x0009_- Kampi" dataDxfId="62" totalsRowDxfId="29"/>
+    <tableColumn id="22" xr3:uid="{B2C76693-F53B-BB47-B0BB-91CDFB3515C1}" name="Struktura nastanitvenih kapacitet - Sobe (nedeljive enote) - Druge vrste kapacitet" dataDxfId="61" totalsRowDxfId="28"/>
+    <tableColumn id="23" xr3:uid="{4DBA3760-7B2D-614B-8D1E-57BF8CACAD66}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Hoteli in podobni obrati" dataDxfId="60" totalsRowDxfId="27"/>
+    <tableColumn id="24" xr3:uid="{B83E8E03-6D6E-4749-935D-B72B0FDB49EF}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Kampi" dataDxfId="59" totalsRowDxfId="26"/>
+    <tableColumn id="25" xr3:uid="{14BC2615-1A3E-6548-803D-A6EE273713C4}" name="Struktura nastanitvenih kapacitet - Stalna ležišča - Druge vrste kapacitet" dataDxfId="58" totalsRowDxfId="25"/>
     <tableColumn id="26" xr3:uid="{6B98A6DD-4A64-EE45-AE54-458C05388214}" name="Delež stalnih ležišč v Hotelih ipd."/>
     <tableColumn id="27" xr3:uid="{CC3F87E6-B3CD-E841-BCED-E5C77DFA385B}" name="Povprečna letna zasedenost staln. ležišč"/>
     <tableColumn id="28" xr3:uid="{36E12EEC-F431-7640-B38F-3F28A52A27A2}" name="Ocenjena povp. Letna zased. sob (nedeljivih enot)"/>
     <tableColumn id="29" xr3:uid="{E32E1653-4218-8144-AE1B-7DA0234BDD6B}" name="Pritisk turizma na družbeni prostor (število stalnih ležišč / 100 prebivalcev)"/>
     <tableColumn id="30" xr3:uid="{6235832E-2F71-6247-9BC2-BB497EF940F1}" name="Gostota turizma"/>
     <tableColumn id="31" xr3:uid="{6059D037-013F-3443-92BE-556256221BB9}" name="Intenzivnost turizma (število nočitev na dan / 100 prebivalcev)"/>
-    <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivni v  turizmu (OECD/WTO)" totalsRowDxfId="27"/>
-    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" totalsRowDxfId="26"/>
-    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="32" xr3:uid="{0EC9E9BB-E7DF-8F40-8DAC-C329014153B6}" name="Delovno aktivno prebivalstvo v turizmu (OECD/WTO)" totalsRowDxfId="24"/>
+    <tableColumn id="33" xr3:uid="{70783B5E-3FC1-DD44-9C4B-F29ABE2F730A}" name="Število zaposl. in samozaposl. v aktivnih podjetjih v Gostinstvu (I)" totalsRowDxfId="23"/>
+    <tableColumn id="34" xr3:uid="{55BC080C-8A66-C04E-A1E9-A6D4133CCFE0}" name="Zaposleni v Gostinstvu (I) v registr.podjetjih in s.p." dataDxfId="57" totalsRowDxfId="22"/>
+    <tableColumn id="35" xr3:uid="{88DF1418-F448-F64B-AB10-E2E30ADD50CE}" name="Zaposleni v nastan.dejav. (I55) v registr.podjetjih in s.p." dataDxfId="56" totalsRowDxfId="21"/>
+    <tableColumn id="36" xr3:uid="{135A837A-5EB5-2546-AB5F-35C76A605B6C}" name="Vsi delovni aktivni na območju" dataDxfId="55" totalsRowDxfId="20"/>
     <tableColumn id="37" xr3:uid="{52A7F38A-5C90-964D-B065-B17C7BA263D5}" name="Delež delovno aktivnih v turizmu (OECD/WTO)" totalsRowDxfId="19"/>
     <tableColumn id="38" xr3:uid="{C0F240E5-648C-7342-B26C-C8B4E0C3F6B4}" name="Število vseh vrst podjetij na območju" totalsRowDxfId="18"/>
     <tableColumn id="39" xr3:uid="{36A2CDB3-CA3D-9043-ADE8-DD7F31F3FE73}" name="Prihodek (v 1000 EUR) vseh podjetij na območju" totalsRowDxfId="17"/>
@@ -2126,13 +2126,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F1" t="s">
         <v>214</v>
@@ -2141,7 +2141,7 @@
         <v>225</v>
       </c>
       <c r="H1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I1" t="s">
         <v>224</v>
@@ -2150,184 +2150,184 @@
         <v>226</v>
       </c>
       <c r="K1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L1" t="s">
+        <v>343</v>
+      </c>
+      <c r="M1" t="s">
+        <v>344</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="L1" t="s">
-        <v>344</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="P1" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="V1" t="s">
         <v>346</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" t="s">
         <v>371</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" t="s">
+        <v>348</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>350</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>349</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>376</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>389</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>377</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>388</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>378</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>380</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>381</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>375</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>390</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>382</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>383</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>385</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>386</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>387</v>
+      </c>
+      <c r="AT1" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="V1" t="s">
-        <v>347</v>
-      </c>
-      <c r="W1" t="s">
-        <v>372</v>
-      </c>
-      <c r="X1" t="s">
-        <v>349</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="AU1" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="BA1" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="Z1" t="s">
-        <v>350</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>377</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>378</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>379</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>391</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>380</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>381</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>382</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>383</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>376</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>384</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>385</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>386</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>387</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>388</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>389</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>390</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="AY1" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="AZ1" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="BA1" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BC1" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" t="s">
         <v>362</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>363</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>364</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>365</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>366</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>367</v>
       </c>
-      <c r="BI1" t="s">
-        <v>368</v>
-      </c>
       <c r="BJ1" t="s">
+        <v>280</v>
+      </c>
+      <c r="BK1" t="s">
         <v>281</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>282</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="BS1" t="s">
         <v>227</v>
@@ -2339,196 +2339,196 @@
         <v>229</v>
       </c>
       <c r="BV1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BW1" t="s">
         <v>230</v>
       </c>
       <c r="BX1" t="s">
+        <v>294</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>391</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>290</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="CB1" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="BY1" t="s">
-        <v>231</v>
-      </c>
-      <c r="BZ1" t="s">
+      <c r="CC1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>233</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>234</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>235</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>236</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>237</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>238</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>239</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>240</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>241</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>242</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>243</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>244</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>245</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>246</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>247</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>248</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>249</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>250</v>
+      </c>
+      <c r="CV1" t="s">
         <v>291</v>
       </c>
-      <c r="CA1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CW1" t="s">
+        <v>251</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>252</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>253</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>254</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>255</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>256</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>257</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>292</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>258</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>259</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>260</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>261</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>262</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>263</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>264</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>265</v>
+      </c>
+      <c r="DM1" t="s">
         <v>296</v>
       </c>
-      <c r="CC1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>234</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>235</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>236</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>237</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>238</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>239</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>240</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>241</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>242</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>243</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>244</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>245</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>246</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>247</v>
-      </c>
-      <c r="CR1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>249</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>251</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>292</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>252</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>253</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>254</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>255</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>256</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>257</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>258</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>293</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>259</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>260</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>261</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>262</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>263</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>264</v>
-      </c>
-      <c r="DK1" t="s">
-        <v>265</v>
-      </c>
-      <c r="DL1" t="s">
+      <c r="DN1" t="s">
+        <v>298</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>297</v>
+      </c>
+      <c r="DP1" t="s">
         <v>266</v>
       </c>
-      <c r="DM1" t="s">
-        <v>297</v>
-      </c>
-      <c r="DN1" t="s">
+      <c r="DQ1" t="s">
+        <v>267</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>268</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>269</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>270</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>271</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>272</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>273</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>274</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>275</v>
+      </c>
+      <c r="DZ1" t="s">
         <v>299</v>
       </c>
-      <c r="DO1" t="s">
-        <v>298</v>
-      </c>
-      <c r="DP1" t="s">
-        <v>267</v>
-      </c>
-      <c r="DQ1" t="s">
-        <v>268</v>
-      </c>
-      <c r="DR1" t="s">
-        <v>269</v>
-      </c>
-      <c r="DS1" t="s">
-        <v>270</v>
-      </c>
-      <c r="DT1" t="s">
-        <v>271</v>
-      </c>
-      <c r="DU1" t="s">
-        <v>272</v>
-      </c>
-      <c r="DV1" t="s">
-        <v>273</v>
-      </c>
-      <c r="DW1" t="s">
-        <v>274</v>
-      </c>
-      <c r="DX1" t="s">
-        <v>275</v>
-      </c>
-      <c r="DY1" t="s">
+      <c r="EA1" t="s">
         <v>276</v>
       </c>
-      <c r="DZ1" t="s">
+      <c r="EB1" t="s">
         <v>300</v>
       </c>
-      <c r="EA1" t="s">
+      <c r="EC1" t="s">
         <v>277</v>
       </c>
-      <c r="EB1" t="s">
+      <c r="ED1" t="s">
+        <v>278</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>279</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>302</v>
+      </c>
+      <c r="EG1" t="s">
         <v>301</v>
-      </c>
-      <c r="EC1" t="s">
-        <v>278</v>
-      </c>
-      <c r="ED1" t="s">
-        <v>279</v>
-      </c>
-      <c r="EE1" t="s">
-        <v>280</v>
-      </c>
-      <c r="EF1" t="s">
-        <v>303</v>
-      </c>
-      <c r="EG1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:137" x14ac:dyDescent="0.2">
@@ -2937,13 +2937,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D3" t="s">
         <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F3" t="s">
         <v>215</v>
@@ -3350,13 +3350,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D4" t="s">
         <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F4" t="s">
         <v>216</v>
@@ -3763,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D5" t="s">
         <v>218</v>
@@ -4170,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D6" t="s">
         <v>218</v>
@@ -4577,13 +4577,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D7" t="s">
         <v>218</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F7" t="s">
         <v>219</v>
@@ -4990,16 +4990,16 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D8" t="s">
         <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G8">
         <v>31</v>
@@ -5403,7 +5403,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D9" t="s">
         <v>218</v>
@@ -5412,7 +5412,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G9">
         <v>72</v>
@@ -5816,13 +5816,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D10" t="s">
         <v>218</v>
       </c>
       <c r="E10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F10" t="s">
         <v>215</v>
@@ -6223,7 +6223,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D11" t="s">
         <v>218</v>
@@ -6232,7 +6232,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G11">
         <v>334</v>
@@ -6636,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D12" t="s">
         <v>218</v>
@@ -7043,16 +7043,16 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D13" t="s">
         <v>218</v>
       </c>
       <c r="E13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G13">
         <v>367</v>
@@ -7456,10 +7456,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E14" t="s">
         <v>218</v>
@@ -7863,7 +7863,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D15" t="s">
         <v>218</v>
@@ -8276,7 +8276,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D16" t="s">
         <v>218</v>
@@ -8689,16 +8689,16 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D17" t="s">
         <v>218</v>
       </c>
       <c r="E17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G17">
         <v>268</v>
@@ -9102,7 +9102,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D18" t="s">
         <v>218</v>
@@ -9509,7 +9509,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D19" t="s">
         <v>218</v>
@@ -9922,16 +9922,16 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D20" t="s">
         <v>218</v>
       </c>
       <c r="E20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G20">
         <v>78</v>
@@ -10335,13 +10335,13 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D21" t="s">
         <v>218</v>
       </c>
       <c r="E21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F21" t="s">
         <v>215</v>
@@ -10748,7 +10748,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D22" t="s">
         <v>218</v>
@@ -10757,7 +10757,7 @@
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G22">
         <v>132</v>
@@ -11161,13 +11161,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D23" t="s">
         <v>218</v>
       </c>
       <c r="E23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F23" t="s">
         <v>219</v>
@@ -11568,10 +11568,10 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D24" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E24" t="s">
         <v>218</v>
@@ -11975,7 +11975,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D25" t="s">
         <v>218</v>
@@ -12382,13 +12382,13 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D26" t="s">
         <v>218</v>
       </c>
       <c r="E26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F26" t="s">
         <v>222</v>
@@ -12789,16 +12789,16 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D27" t="s">
         <v>218</v>
       </c>
       <c r="E27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G27">
         <v>340</v>
@@ -13202,7 +13202,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D28" t="s">
         <v>218</v>
@@ -13609,13 +13609,13 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D29" t="s">
         <v>218</v>
       </c>
       <c r="E29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F29" t="s">
         <v>215</v>
@@ -14022,10 +14022,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D30" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E30" t="s">
         <v>218</v>
@@ -14432,7 +14432,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D31" t="s">
         <v>218</v>
@@ -14845,7 +14845,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D32" t="s">
         <v>218</v>
@@ -15258,7 +15258,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D33" t="s">
         <v>218</v>
@@ -15665,7 +15665,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D34" t="s">
         <v>218</v>
@@ -16078,7 +16078,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D35" t="s">
         <v>218</v>
@@ -16491,16 +16491,16 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D36" t="s">
         <v>218</v>
       </c>
       <c r="E36" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F36" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G36">
         <v>110</v>
@@ -16904,7 +16904,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D37" t="s">
         <v>218</v>
@@ -17317,7 +17317,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D38" t="s">
         <v>218</v>
@@ -17724,13 +17724,13 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D39" t="s">
         <v>218</v>
       </c>
       <c r="E39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F39" t="s">
         <v>222</v>
@@ -18137,13 +18137,13 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D40" t="s">
         <v>218</v>
       </c>
       <c r="E40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F40" t="s">
         <v>219</v>
@@ -18550,7 +18550,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D41" t="s">
         <v>218</v>
@@ -18559,7 +18559,7 @@
         <v>176</v>
       </c>
       <c r="F41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G41">
         <v>153</v>
@@ -18963,7 +18963,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D42" t="s">
         <v>218</v>
@@ -19367,16 +19367,16 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D43" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E43" t="s">
         <v>218</v>
       </c>
       <c r="F43" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G43">
         <v>116</v>
@@ -19780,7 +19780,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D44" t="s">
         <v>218</v>
@@ -20193,13 +20193,13 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D45" t="s">
         <v>218</v>
       </c>
       <c r="E45" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F45" t="s">
         <v>222</v>
@@ -20606,7 +20606,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D46" t="s">
         <v>218</v>
@@ -21019,7 +21019,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D47" t="s">
         <v>218</v>
@@ -21426,7 +21426,7 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D48" t="s">
         <v>218</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D49" t="s">
         <v>218</v>
@@ -22252,13 +22252,13 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D50" t="s">
         <v>218</v>
       </c>
       <c r="E50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F50" t="s">
         <v>219</v>
@@ -22665,7 +22665,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D51" t="s">
         <v>218</v>
@@ -23072,7 +23072,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D52" t="s">
         <v>218</v>
@@ -23479,10 +23479,10 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D53" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E53" t="s">
         <v>218</v>
@@ -23886,13 +23886,13 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D54" t="s">
         <v>218</v>
       </c>
       <c r="E54" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F54" t="s">
         <v>215</v>
@@ -24299,7 +24299,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D55" t="s">
         <v>218</v>
@@ -24308,7 +24308,7 @@
         <v>54</v>
       </c>
       <c r="F55" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G55">
         <v>293</v>
@@ -24712,7 +24712,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D56" t="s">
         <v>218</v>
@@ -25125,13 +25125,13 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D57" t="s">
         <v>218</v>
       </c>
       <c r="E57" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F57" t="s">
         <v>215</v>
@@ -25538,7 +25538,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D58" t="s">
         <v>218</v>
@@ -25951,13 +25951,13 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D59" t="s">
         <v>218</v>
       </c>
       <c r="E59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F59" t="s">
         <v>216</v>
@@ -26364,16 +26364,16 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D60" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E60" t="s">
         <v>218</v>
       </c>
       <c r="F60" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G60">
         <v>76</v>
@@ -26777,16 +26777,16 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D61" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E61" t="s">
         <v>218</v>
       </c>
       <c r="F61" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G61">
         <v>69</v>
@@ -27190,7 +27190,7 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D62" t="s">
         <v>218</v>
@@ -27597,7 +27597,7 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D63" t="s">
         <v>218</v>
@@ -28010,16 +28010,16 @@
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D64" t="s">
         <v>218</v>
       </c>
       <c r="E64" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F64" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G64">
         <v>147</v>
@@ -28423,7 +28423,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D65" t="s">
         <v>218</v>
@@ -28830,16 +28830,16 @@
         <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D66" t="s">
         <v>218</v>
       </c>
       <c r="E66" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F66" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G66">
         <v>193</v>
@@ -29243,7 +29243,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D67" t="s">
         <v>218</v>
@@ -29650,16 +29650,16 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D68" t="s">
         <v>218</v>
       </c>
       <c r="E68" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F68" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G68">
         <v>556</v>
@@ -30063,13 +30063,13 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D69" t="s">
         <v>218</v>
       </c>
       <c r="E69" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F69" t="s">
         <v>215</v>
@@ -30476,7 +30476,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D70" t="s">
         <v>218</v>
@@ -30889,13 +30889,13 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D71" t="s">
         <v>218</v>
       </c>
       <c r="E71" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F71" t="s">
         <v>216</v>
@@ -31302,16 +31302,16 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D72" t="s">
         <v>218</v>
       </c>
       <c r="E72" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G72">
         <v>58</v>
@@ -31709,16 +31709,16 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D73" t="s">
         <v>218</v>
       </c>
       <c r="E73" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F73" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G73">
         <v>56</v>
@@ -32122,7 +32122,7 @@
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D74" t="s">
         <v>218</v>
@@ -32535,7 +32535,7 @@
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D75" t="s">
         <v>218</v>
@@ -32544,7 +32544,7 @@
         <v>74</v>
       </c>
       <c r="F75" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G75">
         <v>151</v>
@@ -32948,7 +32948,7 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D76" t="s">
         <v>218</v>
@@ -32957,7 +32957,7 @@
         <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G76">
         <v>256</v>
@@ -33361,7 +33361,7 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D77" t="s">
         <v>218</v>
@@ -33774,16 +33774,16 @@
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D78" t="s">
         <v>218</v>
       </c>
       <c r="E78" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F78" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G78">
         <v>287</v>
@@ -34187,13 +34187,13 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D79" t="s">
         <v>218</v>
       </c>
       <c r="E79" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F79" t="s">
         <v>219</v>
@@ -34600,7 +34600,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D80" t="s">
         <v>218</v>
@@ -35013,7 +35013,7 @@
         <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D81" t="s">
         <v>218</v>
@@ -35426,13 +35426,13 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D82" t="s">
         <v>218</v>
       </c>
       <c r="E82" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F82" t="s">
         <v>219</v>
@@ -35839,7 +35839,7 @@
         <v>1</v>
       </c>
       <c r="C83" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D83" t="s">
         <v>218</v>
@@ -36252,10 +36252,10 @@
         <v>1</v>
       </c>
       <c r="C84" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D84" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E84" t="s">
         <v>218</v>
@@ -36665,7 +36665,7 @@
         <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D85" t="s">
         <v>218</v>
@@ -37078,13 +37078,13 @@
         <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D86" t="s">
         <v>218</v>
       </c>
       <c r="E86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F86" t="s">
         <v>222</v>
@@ -37491,7 +37491,7 @@
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D87" t="s">
         <v>218</v>
@@ -37904,7 +37904,7 @@
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D88" t="s">
         <v>218</v>
@@ -38317,7 +38317,7 @@
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D89" t="s">
         <v>218</v>
@@ -38730,13 +38730,13 @@
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D90" t="s">
         <v>218</v>
       </c>
       <c r="E90" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F90" t="s">
         <v>215</v>
@@ -39143,16 +39143,16 @@
         <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D91" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E91" t="s">
         <v>218</v>
       </c>
       <c r="F91" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G91">
         <v>135</v>
@@ -39556,13 +39556,13 @@
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D92" t="s">
         <v>218</v>
       </c>
       <c r="E92" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F92" t="s">
         <v>219</v>
@@ -39963,13 +39963,13 @@
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D93" t="s">
         <v>218</v>
       </c>
       <c r="E93" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F93" t="s">
         <v>222</v>
@@ -40370,7 +40370,7 @@
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D94" t="s">
         <v>218</v>
@@ -40783,10 +40783,10 @@
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D95" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E95" t="s">
         <v>218</v>
@@ -41190,13 +41190,13 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D96" t="s">
         <v>218</v>
       </c>
       <c r="E96" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F96" t="s">
         <v>219</v>
@@ -41603,13 +41603,13 @@
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D97" t="s">
         <v>218</v>
       </c>
       <c r="E97" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F97" t="s">
         <v>219</v>
@@ -42016,7 +42016,7 @@
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D98" t="s">
         <v>218</v>
@@ -42423,7 +42423,7 @@
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D99" t="s">
         <v>218</v>
@@ -42836,7 +42836,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D100" t="s">
         <v>218</v>
@@ -43249,16 +43249,16 @@
         <v>1</v>
       </c>
       <c r="C101" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D101" t="s">
         <v>218</v>
       </c>
       <c r="E101" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F101" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G101">
         <v>109</v>
@@ -43662,13 +43662,13 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D102" t="s">
         <v>218</v>
       </c>
       <c r="E102" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F102" t="s">
         <v>222</v>
@@ -44075,13 +44075,13 @@
         <v>1</v>
       </c>
       <c r="C103" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D103" t="s">
         <v>218</v>
       </c>
       <c r="E103" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F103" t="s">
         <v>219</v>
@@ -44488,13 +44488,13 @@
         <v>1</v>
       </c>
       <c r="C104" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D104" t="s">
         <v>218</v>
       </c>
       <c r="E104" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F104" t="s">
         <v>215</v>
@@ -44895,16 +44895,16 @@
         <v>1</v>
       </c>
       <c r="C105" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D105" t="s">
         <v>218</v>
       </c>
       <c r="E105" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F105" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G105">
         <v>31</v>
@@ -45302,16 +45302,16 @@
         <v>1</v>
       </c>
       <c r="C106" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D106" t="s">
         <v>218</v>
       </c>
       <c r="E106" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F106" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G106">
         <v>48</v>
@@ -45709,13 +45709,13 @@
         <v>1</v>
       </c>
       <c r="C107" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D107" t="s">
         <v>218</v>
       </c>
       <c r="E107" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F107" t="s">
         <v>222</v>
@@ -46116,16 +46116,16 @@
         <v>1</v>
       </c>
       <c r="C108" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D108" t="s">
         <v>218</v>
       </c>
       <c r="E108" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F108" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G108">
         <v>73</v>
@@ -46523,7 +46523,7 @@
         <v>1</v>
       </c>
       <c r="C109" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D109" t="s">
         <v>218</v>
@@ -46930,7 +46930,7 @@
         <v>1</v>
       </c>
       <c r="C110" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D110" t="s">
         <v>218</v>
@@ -47343,13 +47343,13 @@
         <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D111" t="s">
         <v>218</v>
       </c>
       <c r="E111" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F111" t="s">
         <v>222</v>
@@ -47756,7 +47756,7 @@
         <v>1</v>
       </c>
       <c r="C112" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D112" t="s">
         <v>218</v>
@@ -48169,13 +48169,13 @@
         <v>1</v>
       </c>
       <c r="C113" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D113" t="s">
         <v>218</v>
       </c>
       <c r="E113" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F113" t="s">
         <v>222</v>
@@ -48582,7 +48582,7 @@
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D114" t="s">
         <v>218</v>
@@ -48591,7 +48591,7 @@
         <v>218</v>
       </c>
       <c r="F114" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G114">
         <v>28</v>
@@ -48989,13 +48989,13 @@
         <v>1</v>
       </c>
       <c r="C115" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D115" t="s">
         <v>218</v>
       </c>
       <c r="E115" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F115" t="s">
         <v>222</v>
@@ -49402,13 +49402,13 @@
         <v>1</v>
       </c>
       <c r="C116" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D116" t="s">
         <v>218</v>
       </c>
       <c r="E116" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F116" t="s">
         <v>215</v>
@@ -49815,16 +49815,16 @@
         <v>1</v>
       </c>
       <c r="C117" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D117" t="s">
         <v>218</v>
       </c>
       <c r="E117" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F117" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G117">
         <v>236</v>
@@ -50228,7 +50228,7 @@
         <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D118" t="s">
         <v>218</v>
@@ -50635,13 +50635,13 @@
         <v>1</v>
       </c>
       <c r="C119" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D119" t="s">
         <v>218</v>
       </c>
       <c r="E119" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F119" t="s">
         <v>219</v>
@@ -51048,10 +51048,10 @@
         <v>1</v>
       </c>
       <c r="C120" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D120" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E120" t="s">
         <v>218</v>
@@ -51461,16 +51461,16 @@
         <v>1</v>
       </c>
       <c r="C121" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D121" t="s">
         <v>218</v>
       </c>
       <c r="E121" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F121" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G121">
         <v>36</v>
@@ -51874,13 +51874,13 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D122" t="s">
         <v>218</v>
       </c>
       <c r="E122" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F122" t="s">
         <v>219</v>
@@ -52287,13 +52287,13 @@
         <v>1</v>
       </c>
       <c r="C123" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D123" t="s">
         <v>218</v>
       </c>
       <c r="E123" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F123" t="s">
         <v>216</v>
@@ -52700,13 +52700,13 @@
         <v>1</v>
       </c>
       <c r="C124" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D124" t="s">
         <v>218</v>
       </c>
       <c r="E124" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F124" t="s">
         <v>215</v>
@@ -53113,7 +53113,7 @@
         <v>1</v>
       </c>
       <c r="C125" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D125" t="s">
         <v>218</v>
@@ -53526,10 +53526,10 @@
         <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D126" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E126" t="s">
         <v>218</v>
@@ -53939,13 +53939,13 @@
         <v>1</v>
       </c>
       <c r="C127" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D127" t="s">
         <v>218</v>
       </c>
       <c r="E127" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F127" t="s">
         <v>222</v>
@@ -54346,13 +54346,13 @@
         <v>1</v>
       </c>
       <c r="C128" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D128" t="s">
         <v>218</v>
       </c>
       <c r="E128" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F128" t="s">
         <v>219</v>
@@ -54753,10 +54753,10 @@
         <v>1</v>
       </c>
       <c r="C129" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D129" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E129" t="s">
         <v>218</v>
@@ -55166,13 +55166,13 @@
         <v>1</v>
       </c>
       <c r="C130" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D130" t="s">
         <v>218</v>
       </c>
       <c r="E130" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F130" t="s">
         <v>215</v>
@@ -55579,10 +55579,10 @@
         <v>1</v>
       </c>
       <c r="C131" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D131" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E131" t="s">
         <v>218</v>
@@ -55992,16 +55992,16 @@
         <v>1</v>
       </c>
       <c r="C132" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D132" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E132" t="s">
         <v>218</v>
       </c>
       <c r="F132" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G132">
         <v>87</v>
@@ -56399,13 +56399,13 @@
         <v>1</v>
       </c>
       <c r="C133" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D133" t="s">
         <v>218</v>
       </c>
       <c r="E133" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F133" t="s">
         <v>222</v>
@@ -56806,7 +56806,7 @@
         <v>1</v>
       </c>
       <c r="C134" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D134" t="s">
         <v>218</v>
@@ -57219,7 +57219,7 @@
         <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D135" t="s">
         <v>218</v>
@@ -57632,13 +57632,13 @@
         <v>1</v>
       </c>
       <c r="C136" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D136" t="s">
         <v>218</v>
       </c>
       <c r="E136" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F136" t="s">
         <v>219</v>
@@ -58039,16 +58039,16 @@
         <v>1</v>
       </c>
       <c r="C137" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D137" t="s">
         <v>218</v>
       </c>
       <c r="E137" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F137" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G137">
         <v>52</v>
@@ -58446,7 +58446,7 @@
         <v>1</v>
       </c>
       <c r="C138" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D138" t="s">
         <v>218</v>
@@ -58859,13 +58859,13 @@
         <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D139" t="s">
         <v>218</v>
       </c>
       <c r="E139" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F139" t="s">
         <v>222</v>
@@ -59272,7 +59272,7 @@
         <v>1</v>
       </c>
       <c r="C140" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D140" t="s">
         <v>218</v>
@@ -59281,7 +59281,7 @@
         <v>139</v>
       </c>
       <c r="F140" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G140">
         <v>119</v>
@@ -59685,13 +59685,13 @@
         <v>1</v>
       </c>
       <c r="C141" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D141" t="s">
         <v>218</v>
       </c>
       <c r="E141" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F141" t="s">
         <v>222</v>
@@ -60098,7 +60098,7 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D142" t="s">
         <v>218</v>
@@ -60511,13 +60511,13 @@
         <v>1</v>
       </c>
       <c r="C143" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D143" t="s">
         <v>218</v>
       </c>
       <c r="E143" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F143" t="s">
         <v>222</v>
@@ -60924,13 +60924,13 @@
         <v>1</v>
       </c>
       <c r="C144" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D144" t="s">
         <v>218</v>
       </c>
       <c r="E144" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F144" t="s">
         <v>215</v>
@@ -61337,16 +61337,16 @@
         <v>1</v>
       </c>
       <c r="C145" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D145" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E145" t="s">
         <v>218</v>
       </c>
       <c r="F145" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G145">
         <v>154</v>
@@ -61750,13 +61750,13 @@
         <v>1</v>
       </c>
       <c r="C146" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D146" t="s">
         <v>218</v>
       </c>
       <c r="E146" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F146" t="s">
         <v>222</v>
@@ -62163,7 +62163,7 @@
         <v>1</v>
       </c>
       <c r="C147" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D147" t="s">
         <v>218</v>
@@ -62576,7 +62576,7 @@
         <v>1</v>
       </c>
       <c r="C148" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D148" t="s">
         <v>218</v>
@@ -62989,7 +62989,7 @@
         <v>1</v>
       </c>
       <c r="C149" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D149" t="s">
         <v>218</v>
@@ -63402,13 +63402,13 @@
         <v>1</v>
       </c>
       <c r="C150" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D150" t="s">
         <v>218</v>
       </c>
       <c r="E150" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F150" t="s">
         <v>219</v>
@@ -63815,13 +63815,13 @@
         <v>1</v>
       </c>
       <c r="C151" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D151" t="s">
         <v>218</v>
       </c>
       <c r="E151" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F151" t="s">
         <v>219</v>
@@ -64222,16 +64222,16 @@
         <v>1</v>
       </c>
       <c r="C152" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D152" t="s">
         <v>218</v>
       </c>
       <c r="E152" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F152" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G152">
         <v>147</v>
@@ -64635,16 +64635,16 @@
         <v>1</v>
       </c>
       <c r="C153" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D153" t="s">
         <v>218</v>
       </c>
       <c r="E153" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F153" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G153">
         <v>272</v>
@@ -65048,13 +65048,13 @@
         <v>1</v>
       </c>
       <c r="C154" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D154" t="s">
         <v>218</v>
       </c>
       <c r="E154" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F154" t="s">
         <v>215</v>
@@ -65461,13 +65461,13 @@
         <v>1</v>
       </c>
       <c r="C155" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D155" t="s">
         <v>218</v>
       </c>
       <c r="E155" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F155" t="s">
         <v>222</v>
@@ -65874,13 +65874,13 @@
         <v>1</v>
       </c>
       <c r="C156" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D156" t="s">
         <v>218</v>
       </c>
       <c r="E156" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F156" t="s">
         <v>219</v>
@@ -66287,13 +66287,13 @@
         <v>1</v>
       </c>
       <c r="C157" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D157" t="s">
         <v>218</v>
       </c>
       <c r="E157" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F157" t="s">
         <v>219</v>
@@ -66700,16 +66700,16 @@
         <v>1</v>
       </c>
       <c r="C158" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D158" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E158" t="s">
         <v>218</v>
       </c>
       <c r="F158" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G158">
         <v>49</v>
@@ -67107,13 +67107,13 @@
         <v>1</v>
       </c>
       <c r="C159" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D159" t="s">
         <v>218</v>
       </c>
       <c r="E159" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F159" t="s">
         <v>222</v>
@@ -67520,10 +67520,10 @@
         <v>1</v>
       </c>
       <c r="C160" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D160" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E160" t="s">
         <v>218</v>
@@ -67927,13 +67927,13 @@
         <v>1</v>
       </c>
       <c r="C161" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D161" t="s">
         <v>218</v>
       </c>
       <c r="E161" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F161" t="s">
         <v>219</v>
@@ -68340,16 +68340,16 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D162" t="s">
         <v>218</v>
       </c>
       <c r="E162" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F162" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G162">
         <v>29</v>
@@ -68753,13 +68753,13 @@
         <v>1</v>
       </c>
       <c r="C163" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D163" t="s">
         <v>218</v>
       </c>
       <c r="E163" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F163" t="s">
         <v>219</v>
@@ -69166,13 +69166,13 @@
         <v>1</v>
       </c>
       <c r="C164" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D164" t="s">
         <v>218</v>
       </c>
       <c r="E164" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F164" t="s">
         <v>219</v>
@@ -69573,7 +69573,7 @@
         <v>1</v>
       </c>
       <c r="C165" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D165" t="s">
         <v>218</v>
@@ -69980,7 +69980,7 @@
         <v>1</v>
       </c>
       <c r="C166" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D166" t="s">
         <v>218</v>
@@ -70387,13 +70387,13 @@
         <v>1</v>
       </c>
       <c r="C167" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D167" t="s">
         <v>218</v>
       </c>
       <c r="E167" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F167" t="s">
         <v>219</v>
@@ -70800,10 +70800,10 @@
         <v>1</v>
       </c>
       <c r="C168" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D168" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E168" t="s">
         <v>218</v>
@@ -71207,7 +71207,7 @@
         <v>1</v>
       </c>
       <c r="C169" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D169" t="s">
         <v>218</v>
@@ -71614,13 +71614,13 @@
         <v>1</v>
       </c>
       <c r="C170" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D170" t="s">
         <v>218</v>
       </c>
       <c r="E170" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F170" t="s">
         <v>215</v>
@@ -72027,7 +72027,7 @@
         <v>1</v>
       </c>
       <c r="C171" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D171" t="s">
         <v>218</v>
@@ -72036,7 +72036,7 @@
         <v>218</v>
       </c>
       <c r="F171" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G171">
         <v>40</v>
@@ -72440,13 +72440,13 @@
         <v>1</v>
       </c>
       <c r="C172" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D172" t="s">
         <v>218</v>
       </c>
       <c r="E172" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F172" t="s">
         <v>219</v>
@@ -72853,16 +72853,16 @@
         <v>1</v>
       </c>
       <c r="C173" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D173" t="s">
         <v>218</v>
       </c>
       <c r="E173" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F173" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G173">
         <v>96</v>
@@ -73260,10 +73260,10 @@
         <v>1</v>
       </c>
       <c r="C174" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D174" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E174" t="s">
         <v>218</v>
@@ -73673,16 +73673,16 @@
         <v>1</v>
       </c>
       <c r="C175" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D175" t="s">
         <v>218</v>
       </c>
       <c r="E175" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F175" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G175">
         <v>49</v>
@@ -74080,16 +74080,16 @@
         <v>1</v>
       </c>
       <c r="C176" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D176" t="s">
         <v>218</v>
       </c>
       <c r="E176" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F176" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G176">
         <v>61</v>
@@ -74487,7 +74487,7 @@
         <v>1</v>
       </c>
       <c r="C177" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D177" t="s">
         <v>218</v>
@@ -74496,7 +74496,7 @@
         <v>176</v>
       </c>
       <c r="F177" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G177">
         <v>146</v>
@@ -74900,7 +74900,7 @@
         <v>1</v>
       </c>
       <c r="C178" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D178" t="s">
         <v>218</v>
@@ -75313,10 +75313,10 @@
         <v>1</v>
       </c>
       <c r="C179" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D179" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E179" t="s">
         <v>218</v>
@@ -75726,16 +75726,16 @@
         <v>1</v>
       </c>
       <c r="C180" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D180" t="s">
         <v>218</v>
       </c>
       <c r="E180" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F180" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G180">
         <v>34</v>
@@ -76139,13 +76139,13 @@
         <v>1</v>
       </c>
       <c r="C181" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D181" t="s">
         <v>218</v>
       </c>
       <c r="E181" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F181" t="s">
         <v>222</v>
@@ -76552,7 +76552,7 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D182" t="s">
         <v>218</v>
@@ -76959,13 +76959,13 @@
         <v>1</v>
       </c>
       <c r="C183" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D183" t="s">
         <v>218</v>
       </c>
       <c r="E183" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F183" t="s">
         <v>222</v>
@@ -77372,10 +77372,10 @@
         <v>1</v>
       </c>
       <c r="C184" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D184" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E184" t="s">
         <v>218</v>
@@ -77779,10 +77779,10 @@
         <v>1</v>
       </c>
       <c r="C185" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D185" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E185" t="s">
         <v>218</v>
@@ -78186,7 +78186,7 @@
         <v>1</v>
       </c>
       <c r="C186" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D186" t="s">
         <v>218</v>
@@ -78593,16 +78593,16 @@
         <v>1</v>
       </c>
       <c r="C187" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D187" t="s">
         <v>218</v>
       </c>
       <c r="E187" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F187" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G187">
         <v>382</v>
@@ -79006,10 +79006,10 @@
         <v>1</v>
       </c>
       <c r="C188" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D188" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E188" t="s">
         <v>218</v>
@@ -79419,16 +79419,16 @@
         <v>1</v>
       </c>
       <c r="C189" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D189" t="s">
         <v>218</v>
       </c>
       <c r="E189" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F189" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G189">
         <v>163</v>
@@ -79832,7 +79832,7 @@
         <v>1</v>
       </c>
       <c r="C190" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D190" t="s">
         <v>218</v>
@@ -80239,7 +80239,7 @@
         <v>1</v>
       </c>
       <c r="C191" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D191" t="s">
         <v>218</v>
@@ -80652,16 +80652,16 @@
         <v>1</v>
       </c>
       <c r="C192" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D192" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E192" t="s">
         <v>218</v>
       </c>
       <c r="F192" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G192">
         <v>155</v>
@@ -81059,7 +81059,7 @@
         <v>1</v>
       </c>
       <c r="C193" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D193" t="s">
         <v>218</v>
@@ -81466,13 +81466,13 @@
         <v>1</v>
       </c>
       <c r="C194" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D194" t="s">
         <v>218</v>
       </c>
       <c r="E194" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F194" t="s">
         <v>222</v>
@@ -81879,7 +81879,7 @@
         <v>1</v>
       </c>
       <c r="C195" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D195" t="s">
         <v>218</v>
@@ -82286,7 +82286,7 @@
         <v>1</v>
       </c>
       <c r="C196" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D196" t="s">
         <v>218</v>
@@ -82699,7 +82699,7 @@
         <v>1</v>
       </c>
       <c r="C197" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D197" t="s">
         <v>218</v>
@@ -83112,10 +83112,10 @@
         <v>1</v>
       </c>
       <c r="C198" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D198" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E198" t="s">
         <v>218</v>
@@ -83525,13 +83525,13 @@
         <v>1</v>
       </c>
       <c r="C199" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D199" t="s">
         <v>218</v>
       </c>
       <c r="E199" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F199" t="s">
         <v>215</v>
@@ -83938,13 +83938,13 @@
         <v>1</v>
       </c>
       <c r="C200" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D200" t="s">
         <v>218</v>
       </c>
       <c r="E200" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F200" t="s">
         <v>219</v>
@@ -84345,7 +84345,7 @@
         <v>1</v>
       </c>
       <c r="C201" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D201" t="s">
         <v>218</v>
@@ -84752,10 +84752,10 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D202" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E202" t="s">
         <v>218</v>
@@ -85165,10 +85165,10 @@
         <v>1</v>
       </c>
       <c r="C203" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D203" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E203" t="s">
         <v>218</v>
@@ -85578,7 +85578,7 @@
         <v>1</v>
       </c>
       <c r="C204" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D204" t="s">
         <v>218</v>
@@ -85991,13 +85991,13 @@
         <v>1</v>
       </c>
       <c r="C205" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D205" t="s">
         <v>218</v>
       </c>
       <c r="E205" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F205" t="s">
         <v>222</v>
@@ -86398,10 +86398,10 @@
         <v>1</v>
       </c>
       <c r="C206" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D206" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E206" t="s">
         <v>218</v>
@@ -86811,10 +86811,10 @@
         <v>1</v>
       </c>
       <c r="C207" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D207" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E207" t="s">
         <v>218</v>
@@ -87224,13 +87224,13 @@
         <v>1</v>
       </c>
       <c r="C208" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D208" t="s">
         <v>218</v>
       </c>
       <c r="E208" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F208" t="s">
         <v>219</v>
@@ -87637,10 +87637,10 @@
         <v>1</v>
       </c>
       <c r="C209" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D209" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E209" t="s">
         <v>218</v>
@@ -88050,7 +88050,7 @@
         <v>1</v>
       </c>
       <c r="C210" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D210" t="s">
         <v>218</v>
@@ -88059,7 +88059,7 @@
         <v>176</v>
       </c>
       <c r="F210" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G210">
         <v>164</v>
@@ -88463,10 +88463,10 @@
         <v>1</v>
       </c>
       <c r="C211" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D211" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E211" t="s">
         <v>218</v>
@@ -88870,7 +88870,7 @@
         <v>1</v>
       </c>
       <c r="C212" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D212" t="s">
         <v>218</v>
@@ -88879,7 +88879,7 @@
         <v>176</v>
       </c>
       <c r="F212" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G212">
         <v>49</v>
@@ -89283,16 +89283,16 @@
         <v>1</v>
       </c>
       <c r="C213" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D213" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E213" t="s">
         <v>218</v>
       </c>
       <c r="F213" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G213">
         <v>43</v>
@@ -89690,16 +89690,16 @@
         <v>1</v>
       </c>
       <c r="C214" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D214" t="s">
         <v>218</v>
       </c>
       <c r="E214" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F214" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G214">
         <v>164</v>
